--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento fixa o prazo de identificação em 3 meses para nascimentos e 30 dias para entrada em estabelecimentos. O @codigo fixa entre 3 e 6 meses, sem distinguir o contexto de estabelecimento. O @rgbeac alinha com o @regulamento mas aplica-se apenas a cães, gatos e furões.</t>
+          <t>O @regulamento fixa o prazo de identificação em 3 meses para nascimentos e 30 dias para entrada em estabelecimentos. A @legislacao (DL n.º 82/2019, art.º 5.º) prevê um prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao fixado pelo @regulamento e que exigirá redução. O @codigo fixa entre 3 e 6 meses, igualmente sem distinção de contexto. O @rgbeac alinha com o @regulamento nos prazos, mas aplica-se apenas a cães, gatos e furões. Nenhum dos diplomas nacionais vigentes distingue o prazo de 30 dias aplicável a animais que entram em estabelecimentos, previsto no @regulamento.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento especifica o limite de 5 animais por família de acolhimento e atribui responsabilidade ao operador (não à família). O @rgbeac e o @codigo centram a responsabilidade no detentor individual, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos.</t>
+          <t>O @regulamento especifica o limite de 5 animais por família de acolhimento e atribui responsabilidade ao operador (não à família). A @legislacao (DL n.º 276/2001, art.º 7.º) centra a responsabilidade no detentor, sem distinguir o contexto de acolhimento temporário nem fixar limites numéricos — posição idêntica à do @rgbeac e do @codigo. Nenhum dos diplomas nacionais, incluindo a legislação vigente, prevê o conceito de família de acolhimento nem o limite numérico de 5 animais estabelecido pelo @regulamento. A lacuna é transversal a toda a legislação nacional.</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>O @regulamento exige notificação prévia das autoridades com dados detalhados (capacidade, raças, ninhadas estimadas). O @codigo regula condições de reprodução mas não prevê registo ou notificação de estabelecimentos criadores. O @rgbeac trata da esterilização de errantes, não da notificação de criadores — há uma lacuna normativa face ao @regulamento.</t>
+          <t>O @regulamento exige notificação prévia com dados detalhados, incluindo o número estimado de ninhadas a colocar no mercado por ano (al. ea)). A @legislacao (DL n.º 276/2001, art.º 3.º-A) já prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças — als. h) e i)), mas não exige a estimativa de ninhadas, constituindo lacuna parcial face ao @regulamento. O @codigo regula condições de reprodução mas não prevê notificação ou registo de estabelecimentos criadores. O @rgbeac trata exclusivamente da esterilização de errantes, sem qualquer norma sobre notificação de criadores. A @legislacao vigente é, dos diplomas nacionais, o mais próximo do @regulamento neste eixo, ainda que com lacuna relevante.</t>
         </is>
       </c>
       <c r="L4" s="9" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1145,88 +1145,115 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Art.º 13.º do Regulamento 2023/0447</t>
+          <t>Art.º 13.º (Health) do Regulamento 2023/0447 (PE/Conselho)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Operators shall ensure that:
+          <t>1. Operators shall ensure that:
 (a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
 (b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
 (c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented.
-Operators of breeding establishments shall additionally ensure that:
-(-a) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-b) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-c) lactating queens are not mated or inseminated.</t>
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+[dim]Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+[dim]Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados, fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são transferidos, quando necessário, sem demora injustificada para área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um animal com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir sobre a eutanásia, que, se realizada, é executada com anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns.
-Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e maturidade esquelética nos termos do Anexo I, e não apresentem doença diagnosticada, sinais clínicos ou condições físicas que possam impactar negativamente a gestação e o bem-estar;
-(-b) a frequência de gestações com ninhadas respeita o máximo fixado no Anexo I;
-(-c) as gatas a lactar não são acasaladas nem inseminadas.</t>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+[dim]A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+[dim]Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 33.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
 2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.</t>
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>art.º 6.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1 e 3 do art.º 13.º e n.ºs 1 e 2 do art.º 16.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Artigo 13.º, n.º 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-Artigo 13.º, n.º 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-Artigo 16.º, n.º 1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-Artigo 16.º, n.º 2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.</t>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 13.º e 16.º) prevê inspeção diária e programa de profilaxia supervisionado por veterinário — alinhamento parcial. Não fixa condições sanitárias específicas para reprodução em criadores: sem idade mínima da fêmea, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar.</t>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 6.º) limita o dever de cuidados médico-veterinários ao animal ferido ou doente, sem obrigação de inspeção diária sistemática nem quaisquer regras sanitárias específicas para a reprodução em criadores.</t>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral, sem distinguir obrigações reforçadas para operadores de criação nem fixar condições específicas para a reprodução (idade mínima, frequência de partos, lactação).</t>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>A @legislacao vigente é o diploma mais próximo do @regulamento. Necessidade de alteração dirigida a criadores: introduzir (1) requisitos mínimos de idade e maturidade das fêmeas; (2) frequência máxima de partos conforme Anexo I do @regulamento; (3) proibição de cobrição de fêmeas a lactar; alinhando com o regime sanitário do art.º 13.º.</t>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -664,107 +664,97 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identificação e Registo</t>
+          <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -873,15 +863,114 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Reprodução e Criação</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -892,7 +981,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -903,24 +992,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -929,12 +1018,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -949,127 +1038,29 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Princípios Gerais de Bem-Estar</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1077,93 +1068,89 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Detenção Responsável e Informação</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
+          <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
+1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
+(a) the dog or cat's vaccination status;
+(b) any medical conditions or predispositions to diseases, including allergies, that are known by the operator, and any diagnostic test results for the dog or cat that are available to the operator.
+In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
+          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
+1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
+(a) o estado de vacinação do cão ou gato;
+(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+          <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
+2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+          <t>1 — O detentor do animal deve ter acesso a informação sobre:
+a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
+b) As normas de bem-estar, cuidados de saúde e comportamento esperado;
+c) As necessidades específicas da espécie ou raça;
+d) A duração de vida esperada;
+e) Os custos de manutenção;
+f) A proibição de abandono.
+2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+          <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
+2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+          <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+          <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+          <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+          <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
@@ -1176,15 +1163,216 @@
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Competências de Cuidadores e Bem-Estar Animal</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 9.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
+(a) understanding of their biological behaviour and their physiological and ethological needs;
+(b) ability to recognise their expressions including any sign of suffering and to identify and take the appropriate mitigating measures in such cases;
+(c) ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of the dogs or cats, preventing suffering;
+(d) knowledge of their obligations under this Regulation.
+2. The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Education, training or professional experience shall be documented.
+2a. Operators shall ensure that at least one animal caretaker, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 18 and that the caretaker transfers the knowledge to the other animal caretakers of the establishment.
+3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+(a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
+(b) capacidade de reconhecer as suas expressões, incluindo qualquer sinal de sofrimento, e de identificar e adotar as medidas mitigantes apropriadas nesses casos;
+(c) capacidade de aplicar boas práticas de maneio de animais, incluindo condicionamento operante e reforço positivo, utilizar e manter o equipamento utilizado para os cães ou gatos sob os seus cuidados e minimizar quaisquer riscos para o bem-estar dos cães ou gatos, prevenindo sofrimento;
+(d) conhecimento das suas obrigações sob este Regulamento.
+2. As competências referidas no parágrafo 1 podem ser adquiridas através de educação, formação ou experiência profissional. A educação, formação ou experiência profissional devem ser documentadas.
+2a. Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 18.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
+3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 69.º — Formação
+A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
+Artigo 84.º — Pessoal
+O pessoal responsável pelas tarefas referidas no artigo 82.º deve possuir os conhecimentos e a experiência adequados para as executar.
+Artigo 90.º — Pessoal
+O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 19.º — Pessoal auxiliar
+Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Avaliação e Supervisão de Bem-Estar</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 10.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Operators shall:
+(a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
+(b) keep the records of the findings of the visit of the veterinarian referred to in point (a) and of their follow up actions for at least 4 years, from the day of the visit, and shall make them available to the competent authorities upon request and to the veterinarian that performs subsequent advisory visits.
+By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores devem:
+(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
+(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
+Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração de parecer relativo à verificação das condições higiossanitárias e de bem-estar animal exigidas no presente decreto-lei;
+b) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+c) A orientação técnica do pessoal responsável pela observação, maneio e prestação de cuidados aos animais;
+d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração e execução de programas que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+b) A orientação técnica do pessoal que cuida dos animais;
+c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
+1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
+2 — Ao médico veterinário responsável pelo alojamento compete:
+a) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
+b) A orientação técnica do pessoal que cuida dos animais;
+c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Saúde e Monitorização Sanitária</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that:
 (a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
@@ -1204,7 +1392,7 @@
 (-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que:
 (a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
@@ -1224,12 +1412,12 @@
 (-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde
 1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
@@ -1239,23 +1427,23 @@
 [dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1272,220 +1460,24 @@
 [dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Detenção Responsável e Informação</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 8.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
-1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
-(a) the dog or cat's vaccination status;
-(b) any medical conditions or predispositions to diseases, including allergies, that are known by the operator, and any diagnostic test results for the dog or cat that are available to the operator.
-In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
-1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
-(a) o estado de vacinação do cão ou gato;
-(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
-Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
-2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal deve ter acesso a informação sobre:
-a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
-b) As normas de bem-estar, cuidados de saúde e comportamento esperado;
-c) As necessidades específicas da espécie ou raça;
-d) A duração de vida esperada;
-e) Os custos de manutenção;
-f) A proibição de abandono.
-2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
-2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Competências de Cuidadores e Bem-Estar Animal</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 9.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
-(a) understanding of their biological behaviour and their physiological and ethological needs;
-(b) ability to recognise their expressions including any sign of suffering and to identify and take the appropriate mitigating measures in such cases;
-(c) ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of the dogs or cats, preventing suffering;
-(d) knowledge of their obligations under this Regulation.
-2. The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Education, training or professional experience shall be documented.
-2a. Operators shall ensure that at least one animal caretaker, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 18 and that the caretaker transfers the knowledge to the other animal caretakers of the establishment.
-3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
-(a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
-(b) capacidade de reconhecer as suas expressões, incluindo qualquer sinal de sofrimento, e de identificar e adotar as medidas mitigantes apropriadas nesses casos;
-(c) capacidade de aplicar boas práticas de maneio de animais, incluindo condicionamento operante e reforço positivo, utilizar e manter o equipamento utilizado para os cães ou gatos sob os seus cuidados e minimizar quaisquer riscos para o bem-estar dos cães ou gatos, prevenindo sofrimento;
-(d) conhecimento das suas obrigações sob este Regulamento.
-2. As competências referidas no parágrafo 1 podem ser adquiridas através de educação, formação ou experiência profissional. A educação, formação ou experiência profissional devem ser documentadas.
-2a. Os operadores devem assegurar que pelo menos um cuidador de animais, que não seja um voluntário ou estagiário, no estabelecimento tenha completado os cursos de formação referidos no artigo 18.º e que o cuidador transfira os conhecimentos aos outros cuidadores de animais do estabelecimento.
-3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 69.º — Formação
-A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
-Artigo 84.º — Pessoal
-O pessoal responsável pelas tarefas referidas no artigo 82.º deve possuir os conhecimentos e a experiência adequados para as executar.
-Artigo 90.º — Pessoal
-O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 19.º — Pessoal auxiliar
-Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -1498,94 +1490,102 @@
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Avaliação e Supervisão de Bem-Estar</t>
+          <t>Identificação e Registo</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Art.º 10.º do Regulamento 2023/0447</t>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Operators shall:
-(a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
-(b) keep the records of the findings of the visit of the veterinarian referred to in point (a) and of their follow up actions for at least 4 years, from the day of the visit, and shall make them available to the competent authorities upon request and to the veterinarian that performs subsequent advisory visits.
-By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem:
-(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
-(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
-Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
-1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
-2 — Ao médico veterinário responsável pelo alojamento compete:
-a) A elaboração de parecer relativo à verificação das condições higiossanitárias e de bem-estar animal exigidas no presente decreto-lei;
-b) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
-c) A orientação técnica do pessoal responsável pela observação, maneio e prestação de cuidados aos animais;
-d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
-1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
-2 — Ao médico veterinário responsável pelo alojamento compete:
-a) A elaboração e execução de programas que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
-b) A orientação técnica do pessoal que cuida dos animais;
-c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
-1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
-2 — Ao médico veterinário responsável pelo alojamento compete:
-a) A elaboração e a execução de programas e ações que visem a saúde e o bem-estar dos animais e o seu acompanhamento, bem como a emissão de pareceres relativos à saúde e ao bem-estar dos animais;
-b) A orientação técnica do pessoal que cuida dos animais;
-c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1364,15 +1364,235 @@
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Alimentação e Hidratação</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 11.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
+2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
+a) clean and fresh water, ad libitum;
+b) feed in sufficient quantity and quality to meet the physiological, nutritional and metabolic needs of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level, health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining good health;
+c) feed free of substances which may cause suffering;
+d) feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
+3. Operators shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
+a) provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
+b) minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
+c) prevent injury, drowning or other harm to the dogs or cats;
+d) be easily cleaned and disinfected to prevent the spread of diseases.
+3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
+2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
+a) água limpa e fresca, ad libitum;
+b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, tendo como objetivo global atingir e manter uma boa saúde;
+c) alimento livre de substâncias que possam causar sofrimento;
+d) alimentação de forma a evitar mudanças bruscas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
+3 — Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e construídas e instaladas de modo a:
+a) proporcionar acesso igual a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
+b) minimizar os derrames e prevenir a contaminação de alimentos e água com contaminantes físicos, químicos ou biológicos prejudiciais;
+c) prevenir lesões, afogamento ou outro mal aos cães ou gatos;
+d) ser facilmente limpas e desinfetadas para prevenir a propagação de doenças.
+3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Alojamento</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 12.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
+2. Operators shall ensure that:
+a) the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and allow the necessary access to and a thorough inspection of all dogs or cats;
+b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
+ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
+c) in breeding and selling establishments where dogs or cats are kept indoors, dust, temperature, relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating;
+d) dogs and cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with a possibility to withdraw and rest;
+da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
+e) appropriate structures and measures are in place for dogs or cats kept outdoors to protect them from adverse climatic conditions, including to prevent thermal stress, sunburn and frostbite.
+3. Operators shall not keep dogs or cats in containers.
+By way of derogation, containers may only be used for the transport, short term isolation of individual dogs or cats and during the participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or puppies or kittens together with their mothers, provided that stress is minimised and suffering is avoided and the dogs and cats are able to stand and lie down in a natural position.
+4. Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialization. The duration of the daily access to an outdoor area or walk shall be minimum one hour in total. The operator may only derogate from these requirements based on written advice of a veterinarian.
+5. When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to express their natural behaviour.
+6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
+6a. Operators of breeding and selling establishments shall use, where necessary, heating or cooling systems to maintain good air quality, an appropriate temperature in indoor enclosures at their establishments, and remove excessive moisture.
+7. Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
+For the purposes of the first subparagraph, 'light' means natural light, complemented, where needed, due to the climatic conditions and geographic position of a Member State, by artificial light.
+7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
+2 — Os operadores devem assegurar que:
+a) os estabelecimentos onde os cães e gatos são mantidos e os equipamentos utilizados são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção completa de todos os cães ou gatos;
+b) todos os componentes do edifício do estabelecimento, incluindo o piso, telhado e divisões, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para garantir que não representam riscos ao bem-estar dos cães ou gatos;
+ba) todos os componentes do edifício do estabelecimento, incluindo o piso e as divisões, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para garantir que não representam riscos ao bem-estar dos cães ou gatos;
+c) nos estabelecimentos de criação e venda onde os cães e gatos são mantidos em recinto fechado, a poeira, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar o aquecimento excessivo;
+d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades, com possibilidade de se retirarem e descansarem;
+da) os cães ou gatos têm locais de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para garantir que todos podem deitar-se e descansar simultaneamente numa posição natural;
+e) estruturas e medidas apropriadas são implementadas para cães ou gatos mantidos ao ar livre para os proteger de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e congelamento.
+3 — Os operadores não devem manter cães ou gatos em contentores.
+Por derrogação, contentores podem ser utilizados apenas para transporte, isolamento de curta duração de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento evitado e os cães e gatos sejam capazes de estar de pé e deitar-se numa posição natural.
+4 — Os operadores não devem manter cães com mais de 8 semanas exclusivamente em recintos fechados. Esses cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode derrogar destes requisitos apenas com base em aconselhamento escrito de um médico veterinário.
+5 — Quando gatos são mantidos em viveiros, os operadores devem desenhar e construir recintos individuais que permitam aos gatos moverem-se livremente e expressar o seu comportamento natural.
+6 — Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas fechadas onde cães e gatos são mantidos, uma zona termoneutra apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
+6a — Os operadores de estabelecimentos de criação e venda devem utilizar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, temperatura apropriada em recintos fechados nos seus estabelecimentos, e remover humidade excessiva.
+7 — Os operadores devem assegurar que os cães e gatos são expostos a luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
+Para efeitos do parágrafo anterior, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
+7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Saúde e Monitorização Sanitária</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that:
 (a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
@@ -1392,7 +1612,7 @@
 (-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que:
 (a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
@@ -1412,12 +1632,12 @@
 (-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde
 1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
@@ -1427,23 +1647,23 @@
 [dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1460,45 +1680,257 @@
 [dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Necessidades Comportamentais</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 14.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
+2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
+a) physical examinations;
+b) individual identification of dogs or cats and reading the identification information;
+c) collection of samples and vaccinations;
+d) procedures for grooming, hygienic, health or reproductive purposes other than mating;
+e) medical treatment, including surgical treatment or prescribed rehabilitation.
+3. Tethering for more than 1 hour shall be prohibited, except for the duration of a medical treatment or participation in shows, exhibitions and competitions of dogs and cats.
+3a. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
+4. Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
+5. Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
+5a. The first subparagraph shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes nor to herding dogs during seasonal transhumance.
+5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
+2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+a) exames físicos;
+b) identificação individual de cães ou gatos e leitura da informação de identificação;
+c) colheita de amostras e vacinações;
+d) procedimentos para limpeza, higiene, saúde ou fins reprodutivos que não o acasalamento;
+e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
+3 — A amarração por mais de 1 hora é proibida, exceto pela duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+3a — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
+4 — Os operadores devem assegurar que condições estão em lugar para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
+5 — Os operadores devem assegurar que cães ou gatos podem socializar de acordo com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar sua estratégia para tal socialização.
+5a — O parágrafo anterior não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino nem aos cães de pastoreio durante a transumância sazonal.
+5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Práticas Dolorosas</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 15.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
+1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
+1b. By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a trap-neuter-return programme.
+2. Operators shall ensure that neutering is only performed under anaesthesia and prolonged analgesia and by a veterinarian. By way of derogation, Member States may allow that the neutering of male cats is performed by a licensed veterinary nurse.
+3. Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
+a) tying up body parts unless for medical reasons in which case the duration shall be limited to the minimum period necessary;
+b) kicking, hitting, dragging, throwing, squeezing dogs or cats;
+c) applying electric current to dogs or cats unless performed for medical reasons;
+d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised;
+da) using prong collars;
+db) using choke collars without safety stop;
+e) lifting dogs or cats by the limbs, head, ears, tail or hair, or lifting adult dogs or cats by the skin.
+4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
+1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
+1b — Por derrogação do parágrafo 1, os Estados-Membros podem permitir corte de orelhas por entalhe ou corte de orelhas de gato no contexto de marcação de gatos vadios quando castrados sob um programa de captura-castração-libertação.
+2 — Os operadores devem assegurar que a castração é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. Por derrogação, os Estados-Membros podem permitir que a castração de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+3 — Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+a) amarração de partes do corpo a menos que por motivos médicos, caso em que a duração deve ser limitada ao período mínimo necessário;
+b) chutar, bater, arrastar, lançar, apertar cães ou gatos;
+c) aplicação de corrente elétrica a cães ou gatos a menos que realizada por motivos médicos;
+d) uso de focinheiras, a menos que necessário por motivos médicos, segurança animal ou humana, caso em que a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado;
+da) uso de coleiras de espinhos;
+db) uso de coleiras de enforcamento sem sistema de segurança;
+e) levantamento de cães ou gatos pelos membros, cabeça, orelhas, cauda ou pelo, ou levantamento de cães ou gatos adultos pela pele.
+4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
 1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
@@ -1514,7 +1946,7 @@
 8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -1530,12 +1962,12 @@
 8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -1543,12 +1975,12 @@
 c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -1556,44 +1988,44 @@
 5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
 3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -664,107 +664,97 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identificação e Registo</t>
+          <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -873,15 +863,114 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Reprodução e Criação</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -892,7 +981,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -903,24 +992,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -929,12 +1018,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -949,127 +1038,29 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Princípios Gerais de Bem-Estar</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1077,240 +1068,15 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Detenção Responsável e Informação</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Saúde e Monitorização Sanitária</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
-Artigo 16.º — Cuidados de saúde animal
-1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Detenção Responsável e Informação</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 8.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1319,7 +1085,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1328,23 +1094,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1356,56 +1122,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="P6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1417,7 +1183,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1429,12 +1195,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1444,23 +1210,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1468,45 +1234,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1514,7 +1280,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1522,12 +1288,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1538,12 +1304,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1553,12 +1319,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1568,45 +1334,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="P8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1622,7 +1388,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
 2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
@@ -1638,90 +1404,79 @@
 3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 51.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
-2 - As refeições devem ainda ser distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter aspetos do seu comportamento alimentar natural, incluindo comedouros interativos e outros dispositivos adequados à espécie.
-3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição dentro do grupo.
-4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados ou prateleiras.
-5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 20.º - Identidade e localização
-(...) aquele que detenha cão deverá [...] fornecer ao animal água e alimento em quantidade adequada às suas necessidades de acordo com a época do ano.
-Art.º 23.º - Deveres gerais
-(...) Devem ser fornecidos aos animais, de forma regular, água fresca e alimento adequado à sua espécie e fase de vida.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>DL 276/2001, Art.º 2.º; DL 82/2019, Art.º 13.º</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>DL 276/2001, Art.º 2.º:
-(...) Os animais devem ter acesso permanente a água potável e a alimento adequado.
-DL 82/2019, Art.º 13.º:
-(...) Alimentação e hidratação adequadas ao estado de saúde e às necessidades do animal.</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Alojamento</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
@@ -1743,7 +1498,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
 2 — Os operadores devem assegurar que:
@@ -1765,92 +1520,205 @@
 7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 48.º e 49.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 48.º:
-1 - A temperatura, ventilação, luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do bem-estar e conforto das espécies que albergam.
-2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
-3 - A luz deve preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
-Art.º 49.º:
-1 - Os alojamentos devem ser construídos por forma a permitir a acomodação adequada dos animais, permitindo aos mesmos movimento natural, circulação, repouso confortável, expressão de comportamentos naturais e a fácil inspeção.
-2 - Os alojamentos devem ser mantidos limpos, em bom estado de conservação, livres de humidade excessiva e adequadamente ventilados.</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 14.º do Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>1 - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
-2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
-3 - A luz deve ser preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
-4 - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
-5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>DL 276/2001, Art.ºs 3.º e 4.º</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 3.º - Alojamento
-(...) deve ser apropriado ao bem-estar do animal, tendo em conta as suas necessidades e particularidades fisiológicas e etológicas.
-Art.º 4.º - Espaço
-(...) O animal deve dispor de espaço suficiente para se deitar, erguer-se, virar-se e movimentar-se naturalmente.</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1867,7 +1735,7 @@
 5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
 2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1884,85 +1752,79 @@
 5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 52.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
-(...) As interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis, e não forçadas.
-Enriquecimento ambiental [Art. 4.º do RGBEAC]: conjunto de técnicas de maneio e conceção dos alojamentos que visam aumentar a diversidade do ambiente, promover a expressão de comportamentos naturais e melhorar o bem-estar dos animais.</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 7.º do Código do Animal (DL 214/2013)</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>1 - Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
-2 - O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>DL 82/2019, Art.º 15.º; Lei 27/2016, Art.º 2.º</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 15.º - Enriquecimento ambiental
-Os operadores de estabelecimentos de criação devem fornecer enriquecimento ambiental adequado ao comportamento natural dos cães e gatos.
-Lei 27/2016, Art.º 2.º:
-Os centros de recolha devem dispor de espaço e equipamentos que permitam aos animais expressar comportamentos naturais.</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1979,7 +1841,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
@@ -1996,71 +1858,850 @@
 4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com Código do Animal</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento com RGBEAC</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Espetáculos e Competições Estéticas</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 15a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
+Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos estéticos, exposições e competições de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de forma que resulta numa alteração das características físicas.
+Os organizadores de espetáculos estéticos, exposições e competições de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de forma que resulta numa alteração das características físicas.</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Art.º 60.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>3 - A reprodução de animais não destinados à criação, em particular os cães e os gatos, deve ser controlada, devendo utilizar-se preferencialmente a esterilização cirúrgica, sob parecer do médico veterinário.
-4 - A esterilização dos animais a que se refere o número anterior apenas pode ser realizada por médico-veterinário, o qual deve garantir o mínimo sofrimento daqueles.</t>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Art.º 5.º do Código do Animal (DL 214/2013)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>3 - É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
-a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
-b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
-c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais.</t>
+          <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>DL 276/2001, Art.º 7.º; Lei 27/2016</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>DL 276/2001, Art.º 7.º:
-É proibido submeter animais a práticas que causem dor, sofrimento ou lesões injustificadas.
-Lei 27/2016 (Rede de centros de recolha):
-Proibição do abate de animais errantes como forma de controlo populacional.</t>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>A verificar</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>A verificar</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>A verificar</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+          <t>Artigo novo do Regulamento 2023/0447 - Espetáculos e Competições Estéticas</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Espetáculos e Competições Estéticas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Identificação e Registo</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+      <c r="P15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following information:
+a) the identification number of the dog or cat as referred to in Article 17(1);
+b) the name, address and contact details of the operator.
+2. Without prejudice to Union law on animal welfare, Member States may adopt or maintain rules concerning the keeping, breeding or sale of dogs or cats, as well as rules restricting or prohibiting the online placing on the market of dogs or cats, in particular with a view to preventing trade by operators not registered in the Member State.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>1 — Quando os operadores anunciam em linha um cão ou gato com vista à sua colocação no mercado da União, devem assegurar a apresentação das seguintes informações:
+a) o número de identificação do cão ou gato referido no Artigo 17(1);
+b) o nome, endereço e detalhes de contacto do operador.
+2 — Sem prejuízo do direito da União em matéria de bem-estar animal, os Estados-Membros podem adotar ou manter regras relativas à manutenção, criação ou venda de cães ou gatos, bem como regras que restringem ou proíbem a colocação em linha no mercado de cães ou gatos, em particular com vista à prevenção do comércio por operadores não registados no Estado-Membro.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Requisitos de Publicidade em Linha e Colocação no Mercado</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Requisitos de Publicidade em Linha e Colocação no Mercado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Treino de Cuidadores de Animais</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 18 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>For the purposes of Article 9 the competent authorities shall be responsible for:
+a) ensuring that training courses are available for animal caretakers;
+b) approving the content of the training courses;
+c) issuing certificates of competence to animal caretakers.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Para efeitos do Artigo 9 as autoridades competentes devem ser responsáveis por:
+a) assegurar que cursos de formação estão disponíveis para os cuidadores de animais;
+b) aprovar o conteúdo dos cursos de formação;
+c) emitir certificados de competência aos cuidadores de animais.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Treino de Cuidadores de Animais</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Treino de Cuidadores de Animais)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Bases de Dados de Cães e Gatos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 19 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
+1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os Estados-Membros são responsáveis pelo estabelecimento e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o Artigo 17(1) e (2) e Artigo 21(4) e o segundo parágrafo do Artigo 21(4a).
+1a — Para esse efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em arranjos apropriados.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Bases de Dados de Cães e Gatos</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Bases de Dados de Cães e Gatos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
+2. The competent authorities shall draw up and transmit to the Commission every three years a report on the level of compliance and on the number and type of infringements detected.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>1 — As autoridades competentes recolhem, analisam e publicam os dados enumerados no Anexo III.
+2 — As autoridades competentes elaboram e transmitem à Comissão a cada três anos um relatório sobre o nível de conformidade e sobre o número e tipo de infrações detetadas.</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Recolha de Dados sobre Bem-Estar Animal e Relatório)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Proteção de Dados</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>As autoridades competentes dos Estados-Membros devem ser controladores no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos nos termos do Artigo 7, Artigo 7a do presente Regulamento bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de controlo oficial.</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Proteção de Dados</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Proteção de Dados)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Entrada de Cães e Gatos na União</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 21 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Member States shall require that dogs and cats intended to be placed on their market shall:
+a) be identified and registered as referred to in Article 17;
+b) be accompanied by a health certificate issued by a veterinarian of the exporting country;</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Os Estados-Membros devem exigir que cães e gatos com vista à sua colocação no mercado devem:
+a) ser identificados e registados conforme referido no Artigo 17;
+b) ser acompanhados por um certificado de saúde emitido por um médico veterinário do país exportador;</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Entrada de Cães e Gatos na União</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Entrada de Cães e Gatos na União)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Alteração dos Anexos</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 22 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>A Comissão é habilitada a adotar atos delegados em conformidade com o Artigo 23 alterando os Anexos ao presente Regulamento para tomar em conta o progresso científico e técnico, incluindo, quando relevante, as opiniões científicas da Autoridade Europeia para a Segurança dos Alimentos.</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso no @codigo]</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>A verificar</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 - Alteração dos Anexos</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>A avaliar</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>Artigo novo do Regulamento 2023/0447 (tema: Alteração dos Anexos)</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1922,15 +1922,99 @@
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Espetáculos e Competições Estéticas</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 15a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Operators of breeding and selling establishments shall not use in aesthetic shows, exhibitions and competitions of dogs and cats, dogs or cats with excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.
+Organisers of aesthetic shows, exhibitions and competitions of dogs and cats shall exclude from such shows, exhibitions and competitions dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in such a way that results in an alteration of physical characteristics.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
+Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências portuguesas a ser adicionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Identificação e Registo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Art.º 17.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
 1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
@@ -1946,7 +2030,7 @@
 8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
 1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
@@ -1962,12 +2046,12 @@
 8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
 a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
@@ -1975,12 +2059,12 @@
 c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
@@ -1988,57 +2072,416 @@
 5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
 3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr"/>
     </row>
-    <row r="15" ht="120" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos de Publicidade em Linha e Colocação no Mercado</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17a do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1. When operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of the following warning in the advertisement in clearly visible and bold characters:
+"An animal is not a toy. Getting one is a life-changing decision. It is your duty to ensure its health and welfare and not to abandon it."
+2. When natural or legal persons other than operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of a warning on responsible ownership either using the wording referred to in the first sub-paragraph or a different wording with an equivalent meaning to it.
+3. When placing a dog or a cat on the market in the Union, the natural or legal person placing the dog or cat on the market shall:
+a) provide to the acquirer proof of the identification and registration of dog or cat in compliance with Article 17;
+b) provide to the acquirer the following information on the dog or cat:
+   i. its species;
+   ii. its sex;
+   iii. its date and country of birth; and
+   iv. where relevant, its breed.
+c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token and make the token and the weblink to the system referred to in paragraph 6 available in the advertisement.
+4. Acquirers shall be able to verify the authenticity of the identification, registration and ownership of dogs or cats advertised online through the system referred to in paragraph 6.
+5. Providers of online platforms shall ensure that their online interface is designed and organised in such a way that facilitates the operators or other natural or legal persons placing dogs or cats on the market to comply with their obligations under paragraphs 1, 2 and 3 of this Article, in line with Article 31 of Regulation (EU) 2022/2065, and shall inform acquirers, in a visible manner, of the possibility to verify the identification and registration of the dog or cat through a weblink to the system referred to in paragraph 6.
+The natural or legal person placing dogs or cats on the market shall be solely responsible for the accuracy of the information provided through the interface of the online platform. Nothing in this paragraph shall be construed as imposing a general monitoring obligation on the provider of the online platform within the meaning of Article 8 of Regulation (EU) 2022/2065.
+6. The Commission shall ensure that an online verification system performing automated checks of the authenticity of the identification, registration and ownership of dogs or cats advertised online, using the database referred to in Article 19, is publicly available free of charge and generates the unique verification token referred to in point 3(c).
+7. The Commission shall adopt implementing acts laying down the exact information to be provided and the technical requirements for the verification system.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências portuguesas a ser adicionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Treino de Cuidadores de Animais</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 18 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1. For the purposes of Article 9 the competent authorities shall be responsible for:
+a) ensuring that training courses are available for animal caretakers;
+b) approving the content of the training courses referred to in point (a), taking into account the minimum requirements laid down by the implementing acts referred to in Article 9(3);
+ba) certifying the animal caretakers who successfully completed the training courses referred to in point (a).
+2. The competent authorities may delegate the task referred to in point (ba).
+3. A European Union Reference Centre for Animal Welfare designated in accordance with Article 95 of Regulation (EU) 2017/625 may develop models of training materials and recommendations for the providers of training courses referred to in paragraph 1.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências portuguesas a ser adicionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Base de Dados de Cães e Gatos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 19 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
+1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements between those Member States.
+2. Member States shall ensure that their databases as referred to in paragraph 1 comply with the requirements laid down by the implementing act referred to in point (b) of paragraph 3 to ensure their interoperability so that the identification of a dog or a cat can be authenticated and traced across the Union.
+2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process, pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
+3. The Commission shall, by means of implementing acts, lay down provisions concerning:
+a) the minimum content of the databases referred to in paragraph 1;
+b) the interoperability between Member States databases and the index database, including the minimum set of fields transmitted to the Index database and the intervals of the transmission;
+c) the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in article 17a (3) point (a);
+d) a registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
+fa) The interconnection between the Member States databases referred to in paragraph 1, the pet travellers' database referred to in Article 21 paragraph 4a, and the Information Management System for Official Controls (IMSOC), where relevant.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências portuguesas a ser adicionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Recolha de Dados sobre Bem-Estar Animal e Relatório</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 20 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1. The competent authorities shall collect, analyse and publish the data set out in Annex III.
+2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data set out in Annex III, by 31 August every 3 years starting from [6 years from the date of entry into force of this Regulation], summarising the data gathered for the previous 3 years.
+3. The Commission may, by means of implementing acts, establish a harmonised methodology for collecting the data set out in Annex III and establish a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>A ser preenchido</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências portuguesas a ser adicionadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Proteção de Dados</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Art.º 20a do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Article 7, Article 7a of this Regulation as well as under Article 19(1) of this Regulation when used for the purposes of official control.
 The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 17a (6), Article 19 (2a) and the third subparagraph of Article 21(4a) of this Regulation, as well as under Article 19(1) of this Regulation when used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and of reporting obligations under this Regulation.
@@ -2054,7 +2497,7 @@
 d) in case of the third subparagraph of Article 21(4a), 5 years after the date of pre-notification.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
 A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
@@ -2063,12 +2506,12 @@
 [... redução para brevidade - ver regulamento completo para texto integral]</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Art.º 20.º, nn. 3, 6, 8 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º, n.º 8 - SIAC e Proteção de Dados:
 Ao tratamento, segurança, conservação, acesso e proteção dos dados pessoais constantes do SIAC é diretamente aplicável o disposto na legislação e regulamentação relativa à proteção de dados pessoais, nomeadamente o Regulamento (UE) 2016/679 do Parlamento Europeu e do Conselho, de 27 de abril de 2016, relativo à proteção das pessoas singulares no que diz respeito ao tratamento de dados pessoais e à livre circulação desses dados.
@@ -2078,12 +2521,12 @@
 A DGAV, pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e sob sua supervisão, observado o regime de subcontratação de tratamento de dados pessoais.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Art.º 55.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Artigo 55.º - Base de Dados
 1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
@@ -2091,60 +2534,60 @@
 3 - Só têm acesso à base de dados as entidades que se encontrem autorizadas, para o efeito, pela DGAV.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 9.º</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Artigo 9.º - Registo no Sistema de Informação de Animais de Companhia
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>NÃO - Legislação portuguesa cobre completamente com incorporação de GDPR</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>NÃO - Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>NÃO - Implementação completa em Arts. 20.º</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa completamente os requisitos de proteção de dados do Artigo 20a. O SIAC é configurado como sistema compliant com GDPR (EU 2016/679) e com regulamentações de proteção de dados. Não há necessidade de alterações legislativas.</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>Correspondências confirmadas por agente de pesquisa em 2026-03-02</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="120" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Entrada de Cães e Gatos na União</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Art.º 21.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>1. Dogs and cats may only be entered into the Union for placing on the Union market provided that the following conditions are met:
 a) they have been breed and kept in compliance with any of the following:
@@ -2158,18 +2601,18 @@
 [... ver regulamento completo para restantes parágrafos 4a e 5 ...]</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>1. A partir de [data de implementação], os cães e os gatos só podem ser introduzidos na União para colocação no mercado da União se tiverem estado detidos em conformidade com o indicado numa das alíneas seguintes...
 [Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Art.º 114.º e Art.º 96.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Artigo 114.º - Entrada no Território Nacional
 1 - A entrada no território nacional, por compra, cedência ou troca direta, de cães classificados como potencialmente perigosos pode ser condicionada.
@@ -2179,12 +2622,12 @@
 A importação de animais que constem da lista nacional de animais de companhia provenientes de outros Estados é admitida desde que sejam cumpridas as regras sanitárias e de bem-estar animal portuguesas e comunitárias.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Artigo 62.º - Entrada de Animais de Companhia Suscetíveis à Raiva em Território Nacional
 1 - A entrada em território nacional de animais de companhia suscetíveis à raiva destinados ao comércio, provenientes de outros Estados-membros ou de países terceiros, depende do cumprimento das condições fixadas no Decreto-Lei n.º 79/2001, de 20 de junho, alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, e noutras normas de polícia sanitária que regem o comércio e as importações de animais vivos na comunidade.
@@ -2192,60 +2635,60 @@
 3 - A entrada em território nacional de furões destinados ao comércio ou sem carácter comercial, para além do cumprimento do disposto nos números anteriores, depende de autorização prévia do ICNF, I.P.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019, Art.º 2.º</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Artigo 2.º - Âmbito de Aplicação
 O presente decreto-lei aplica-se à identificação de animais de companhia das espécies referidas no anexo I do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013, e no anexo I do Regulamento (UE) n.º 2016/429, do Parlamento Europeu e do Conselho, de 9 de março de 2016, nascidos ou presentes no território nacional.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada/importação mas sem database online de viajantes pré-notificação</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>SIM - Implementa controlos sanitários e requisitos de identificação</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - Cobre entrada no território nacional com condições, não cobre movimento não-comercial pré-notificação</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa implementa os requisitos essenciais de entrada e identificação pré-entrada, referenciando os Regulamentos EU 576/2013 e 2016/429. Faltam: (1) Sistema de base de dados online de viajantes com pré-notificação obrigatória para movimento não-comercial; (2) Sistema iRASFF integrado para notificações de risco de fraude.</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Parcialmente coberto. Complementação necessária para movimento não-comercial e sistema iRASFF.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="120" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Alteração dos Anexos</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Art.º 22.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>1. The Commission is empowered to adopt delegated acts in accordance with Article 23 amending the Annexes to this Regulation to take into account of scientific and technical progress, including, when relevant, scientific opinions of the European Food Safety Authority, as regards:
 a) a suitable number of animal caretakers in breeding and selling establishments;
@@ -2264,18 +2707,18 @@
 2. Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and provide for sufficient transition periods to allow for operators concerned to adapt to the new requirements.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>1. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 23.º, que alterem os anexos do presente regulamento para ter em conta o progresso científico e técnico, incluindo, se for caso disso, os pareceres científicos da EFSA...
 [Tradução disponível no documento 'Regulamento - Primeira Versão portuguesa.docx']</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Arts. 3-8 e ANEXO do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Artigos 3.º a 8.º do Decreto-Lei que aprova o RGBEAC estabelecem mecanismo legislativo para alteração de diplomas anteriores. O RGBEAC contém um ANEXO estruturado com:
 - TÍTULO I: Disposições gerais
@@ -2286,12 +2729,12 @@
 NOTA: O mecanismo atual é legislativo padrão (alteração de Decreto-Lei por novo Decreto-Lei). NÃO existe autoridade delegada expressa para alteração por atos de execução, conforme previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Art.º 23.º e ANEXO II do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Artigo 23.º - Condições Particulares para a Manutenção de Cães e Gatos
 1 - O alojamento de cães e gatos deve obedecer às dimensões mínimas indicadas no anexo II ao presente diploma.
@@ -2305,43 +2748,43 @@
 Corresponde materialmente aos requisitos de espaço, temperatura e frequência referidos no Art. 22 do Regulamento.</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 - Referências a Anexos de Regulamentos EU</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>DL n.º 82/2019 incorpora por referência os Anexos I dos Regulamentos EU n.º 576/2013 e n.º 2016/429, estabelecendo que os requisitos de identificação de animais de companhia aplicáveis em Portugal são os das espécies referidas nesses anexos.
 NOTA: DL 82/2019 não implementa mecanismo de delegação de autoridade para alteração de anexos como previsto no Art. 22-24 do Regulamento EU 2023/0447.</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Anexos existem; falta delegação de autoridade para alteração dinâmica</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Estrutura de anexos com parâmetros técnicos; falta delegação</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>PARCIAL - ANEXO estruturado; falta mecanismo de atos delegados/execução</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr">
+      <c r="N22" s="11" t="inlineStr">
         <is>
           <t>A legislação portuguesa possui estrutura de anexos contendo parâmetros técnicos equivalentes aos do Regulamento. Falta implementar: Mecanismo de delegação de autoridade à Comissão Europeia para adoção de atos delegados/execução, conforme Arts. 22-24 do Regulamento 2023/0447. Atualmente, qualquer alteração de anexos requer procedimento legislativo nacional (novo Decreto-Lei), não havendo procedimento expedito de atos delegados.</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>Estrutura de anexos presente mas sem mecanismo de delegação de autoridade para atos delegados/execução conforme Reg. EU.</t>
         </is>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1944,62 +1944,66 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 39.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 39.º - Participação em eventos
+1 – A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias, ou outros eventos onde participem animais de companhia carece de autorização do diretor geral da DGAV a área da realização da mesma, após parecer da respetiva câmara municipal.
+3 - Só serão admitidos no evento os animais de companhia que: a) Estejam registados no SIAC; b) Quando aplicável, possuam prova de vacinação antirrábica; c) Possuam vacinações contra as principais doenças infectocontagiosas; d) Não tenham sido submetidos a intervenções cirúrgicas em infração.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 79.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 79.º - Concursos e exposições
+1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
+3 - Só são admitidos a concurso os cães e gatos que: a) Estejam identificados eletronicamente; b) Sejam portadores de boletim sanitário e prova de vacinação antirrábica; c) Possuam vacinações contra principais doenças infecto-contagiosas.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Lei n.º 27/2016 e DL n.º 82/2019 (Normas de eventos)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa estabelece que a participação de animais em espetáculos e competições requer: - Autorização prévia de autoridades competentes; - Identificação e registo no SIAC; - Vacinações obrigatórias; - Supervisão veterinária durante o evento; - Condições de bem-estar animal garantidas.</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (autorização, identificação, vacinação, supervisão veterinária)</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (concursos e exposições com requisitos específicos)</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (participação em eventos com normas de bem-estar)</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa cobre completamente os requisitos do Artigo 15a. Implementa autorizações prévias, exigências de identificação, vacinação obrigatória e supervisão veterinária. O RGBEAC (Art. 39.º) e Código do Animal (Art. 79.º) estabelecem normas detalhadas sobre espetáculos, exposições e competições estéticas.</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>Correspondências portuguesas a ser adicionadas</t>
+          <t>Correspondências completas encontradas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>
@@ -2129,17 +2133,8 @@
 2. When natural or legal persons other than operators advertise online a dog or a cat with a view to its placing on the Union market, they shall ensure the display of a warning on responsible ownership either using the wording referred to in the first sub-paragraph or a different wording with an equivalent meaning to it.
 3. When placing a dog or a cat on the market in the Union, the natural or legal person placing the dog or cat on the market shall:
 a) provide to the acquirer proof of the identification and registration of dog or cat in compliance with Article 17;
-b) provide to the acquirer the following information on the dog or cat:
-   i. its species;
-   ii. its sex;
-   iii. its date and country of birth; and
-   iv. where relevant, its breed.
-c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token and make the token and the weblink to the system referred to in paragraph 6 available in the advertisement.
-4. Acquirers shall be able to verify the authenticity of the identification, registration and ownership of dogs or cats advertised online through the system referred to in paragraph 6.
-5. Providers of online platforms shall ensure that their online interface is designed and organised in such a way that facilitates the operators or other natural or legal persons placing dogs or cats on the market to comply with their obligations under paragraphs 1, 2 and 3 of this Article, in line with Article 31 of Regulation (EU) 2022/2065, and shall inform acquirers, in a visible manner, of the possibility to verify the identification and registration of the dog or cat through a weblink to the system referred to in paragraph 6.
-The natural or legal person placing dogs or cats on the market shall be solely responsible for the accuracy of the information provided through the interface of the online platform. Nothing in this paragraph shall be construed as imposing a general monitoring obligation on the provider of the online platform within the meaning of Article 8 of Regulation (EU) 2022/2065.
-6. The Commission shall ensure that an online verification system performing automated checks of the authenticity of the identification, registration and ownership of dogs or cats advertised online, using the database referred to in Article 19, is publicly available free of charge and generates the unique verification token referred to in point 3(c).
-7. The Commission shall adopt implementing acts laying down the exact information to be provided and the technical requirements for the verification system.</t>
+b) provide to the acquirer the following information on the dog or cat (species, sex, date and country of birth, breed);
+c) in case of online advertising, use the system referred to in paragraph 6 to generate a unique verification token.</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2149,62 +2144,65 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 95.º + Art.º 115.º n.º 3 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 95.º - Local de venda dos animais
+1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
+2 - Os animais de companhia não podem ser publicitados na Internet, mas a compra e venda dos mesmos apenas é admitida no local de criação ou em estabelecimentos devidamente licenciados.
+Artigo 115.º n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 24.º e Art.º 62.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 276/2001, DL 82/2019 - Normas de comercialização</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa estabelece controlos sobre a comercialização de cães e gatos, com requisitos de identificação e documentação sanitária. DL 82/2019 reforça as normas de rastreabilidade através do SIAC.</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>PARCIAL - Proíbe venda online mas sem sistema de verificação online específico</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>PARCIAL - Cobre restrições comerciais mas não implementa sistema de token de verificação</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa PROÍBE a publicidade e venda de animais de companhia na Internet (Art. 95.º RGBEAC). Falta apenas a implementação do sistema de verificação online com token único conforme Art. 17a.6 do Regulamento. A proibição é mais restritiva que o Regulamento que permite venda online com verificação.</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Sim - Sistema de verificação online com token único</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr">
         <is>
-          <t>Correspondências portuguesas a ser adicionadas</t>
+          <t>Legislação portuguesa mais restritiva - proíbe venda online; Reg. EU permite com verificação</t>
         </is>
       </c>
     </row>
@@ -2236,62 +2234,72 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 118.º, 119.º, 120.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 118.º - Reserva de atividade de treinadores de cães
+O treino de cães para qualquer fim só pode ser ministrado por treinador possuidor do respetivo título profissional.
+Artigo 119.º - Título profissional de treinador de cães
+1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV.
+2 - O requerente deve: ter habilitação mínima 12.º ano; apresentar certificado criminal; ser detentor do certificado de qualificações.
+Artigo 120.º - Certificado de qualificações
+1 - Emitido por entidade certificadora após aprovação em provas teóricas e práticas, demonstrando habilitação técnica com base em métodos de reforço positivo.
+2 - Provas incidem sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 51.º, 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 51.º - Exercício de profissões relacionadas com cães
+O exercício de certas profissões (adestrador, criador) requer documentação específica e conformidade com normas de bem-estar animal.
+Artigo 52.º - Documentação necessária
+Requerimentos de certificação e qualificação profissional para operadores.</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 82/2019 - Normas de profissionalismo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Legislação portuguesa estabelece normas de profissionalismo e qualificação para operadores em bem-estar animal, com requisitos de formação e certificação conforme disposições de Decreto-Lei específico.</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (certificação profissional, provas teóricas e práticas, métodos positivos)</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (profissionalismo, qualificações obrigatórias)</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (Arts. 118-120 implementam sistema profissional com certificação)</t>
         </is>
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa implementa COMPLETAMENTE os requisitos do Artigo 18. O RGBEAC (Arts. 118-120) estabelece um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. Sistema já em vigor conforme Decreto-Lei.</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>Correspondências portuguesas a ser adicionadas</t>
+          <t>Sistema profissional português já implementado - cobertura completa e adequada</t>
         </is>
       </c>
     </row>
@@ -2311,13 +2319,7 @@
           <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats, in accordance with Article 17(1) and (2) and Article 21(4) and the second subparagraph of Article 21(4a).
 1a. For that purpose, the Member States may use databases maintained by another Member State, based on appropriate arrangements between those Member States.
 2. Member States shall ensure that their databases as referred to in paragraph 1 comply with the requirements laid down by the implementing act referred to in point (b) of paragraph 3 to ensure their interoperability so that the identification of a dog or a cat can be authenticated and traced across the Union.
-2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process, pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
-3. The Commission shall, by means of implementing acts, lay down provisions concerning:
-a) the minimum content of the databases referred to in paragraph 1;
-b) the interoperability between Member States databases and the index database, including the minimum set of fields transmitted to the Index database and the intervals of the transmission;
-c) the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in article 17a (3) point (a);
-d) a registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
-fa) The interconnection between the Member States databases referred to in paragraph 1, the pet travellers' database referred to in Article 21 paragraph 4a, and the Information Management System for Official Controls (IMSOC), where relevant.</t>
+2a. The Commission shall establish and maintain an index database containing the minimum set of fields defined under article 19(3)(b). The Commission may entrust the development, maintenance and operation of this index database to an independent entity, following a public selection process.</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2327,62 +2329,73 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 20.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
+1 - O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
+2 – A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
+3 – A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
+4 - As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 53.º, 55.º, 56.º, 57.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 53.º - Identificação e registo na base de dados
+1 - Todos os cães devem ser identificados e registados entre os três e seis meses de idade.
+4 - Os cães e gatos são identificados através de método eletrónico e registados na base de dados nacional.
+5 - Identificação através de aplicação subcutânea de microchip no centro da face lateral esquerda do pescoço.
+Artigo 55.º - Base de dados
+1 - Toda a informação do registo coligida numa aplicação informática nacional.
+2 - A DGAV detém e coordena o acesso à base de dados, podendo autorizar gestão em outras entidades com parecer da Comissão Nacional de Proteção de Dados.
+Artigo 56.º - Classificação dos animais (Cão, Cão Potencialmente Perigoso, Cão Perigoso, Gato)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL n.º 82/2019, Art.º 2.º (Estabelece SIAC)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é totalmente operacional desde 2019.</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>NÃO - SIAC em funcionamento desde 2019 cumpre todos os requisitos</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>NÃO - Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>NÃO - RGBEAC (Art. 20.º) reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa CUMPRE COMPLETAMENTE os requisitos do Artigo 19. O SIAC (Sistema de Informação de Animais de Companhia) já está operacional desde 2019, sob responsabilidade de DGAV, com: identificação eletrónica via microchip obrigatória, registo nacional centralizado, rastreabilidade garantida, classificação de animais (normal/perigoso/potencialmente perigoso), integração de dados de saúde e bem-estar, conformidade com proteção de dados (Comissão Nacional de Proteção de Dados).</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>Correspondências portuguesas a ser adicionadas</t>
+          <t>SIAC totalmente operacional e conforme - Interoperabilidade EU pendente de implementação</t>
         </is>
       </c>
     </row>
@@ -2411,62 +2424,64 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 46.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Artigo 46.º - Relatório Nacional Anual
+1 - Os centros de bem-estar animal e alojamentos remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com números de animais recolhidos, restituídos, eutanasiados, cedidos, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados em programas CED.
+2 – A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo: acompanhamento da política internacional, prestação de apoios públicos, atividade do SIAC, resultados de planos de controlo, processos contraordenacionais, coimas aplicadas, atividade de centros de bem-estar, programas de interesse nacional, ações informativas e educativas, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 141.º-145.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Código do Animal estabelece estrutura de monitorização e relatórios sobre bem-estar animal, incluindo: recolha de dados de infrações, aplicação de sanções, atividades de centros de recolha, estatísticas de animais processados. Sistema de contraordenações com documentação e coimas registadas.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Decreto-Regulamentar n.º 3/2021 + DL 82/2019</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. DL 82/2019 estabelece procedimentos de recolha de dados, monitorização, registo de atividades médico-veterinárias e compilação de informação de bem-estar animal para fins de relatório anual e transmissão a autoridades europeias.</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (relatórios anuais, recolha de dados, consolidação nacional)</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (monitorização, infrações, sanções, estatísticas)</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>SIM - Cobertura COMPLETA (Art. 46.º estabelece sistema de relatórios nacionais)</t>
         </is>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>A legislação portuguesa implementa COMPLETAMENTE o Artigo 20. Sistema já estabelecido com: recolha anual de dados de centros de bem-estar animal, consolidação de informação de bem-estar a nível nacional, inclusão de estatísticas de SIAC, registos de contraordenações e sanções, relatórios sobre atividades de proteção animal, conformidade com requisitos de Decreto-Regulamentar 3/2021. Único ajuste necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>Correspondências portuguesas a ser adicionadas</t>
+          <t>Sistema de relatórios já operacional - apenas alinhamento com padrões EU necessário</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1390,85 +1390,88 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
-2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
+          <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
+2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
 a) água limpa e fresca, ad libitum;
-b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, tendo como objetivo global atingir e manter uma boa saúde;
+b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter boa saúde;
 c) alimento livre de substâncias que possam causar sofrimento;
-d) alimentação de forma a evitar mudanças bruscas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
-3 — Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e construídas e instaladas de modo a:
-a) proporcionar acesso igual a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
-b) minimizar os derrames e prevenir a contaminação de alimentos e água com contaminantes físicos, químicos ou biológicos prejudiciais;
-c) prevenir lesões, afogamento ou outro mal aos cães ou gatos;
-d) ser facilmente limpas e desinfetadas para prevenir a propagação de doenças.
-3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
+3. Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e são construídas e instaladas de forma a:
+a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
+b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
+c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
+d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
+3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
+Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>Alimentação e abeberamento:
+A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
+Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>DL 82/2019 - Bem-estar de animais de companhia</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>DL 82/2019 regulamenta identificação de animais. Não aborda especificamente requisitos de alimentação. Requisitos cobertos por @CODIGO (Art. 46.º) e @RGBEAC.</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
+          <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+          <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
         </is>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Alojamento</t>
+          <t>Alojamento (Housing)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1478,106 +1481,112 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
+          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of the annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of the annex I.
 2. Operators shall ensure that:
 a) the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and allow the necessary access to and a thorough inspection of all dogs or cats;
-b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
-ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
+b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats.
+(ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
 c) in breeding and selling establishments where dogs or cats are kept indoors, dust, temperature, relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating;
 d) dogs and cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with a possibility to withdraw and rest;
-da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
+(da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
 e) appropriate structures and measures are in place for dogs or cats kept outdoors to protect them from adverse climatic conditions, including to prevent thermal stress, sunburn and frostbite.
 3. Operators shall not keep dogs or cats in containers.
 By way of derogation, containers may only be used for the transport, short term isolation of individual dogs or cats and during the participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or puppies or kittens together with their mothers, provided that stress is minimised and suffering is avoided and the dogs and cats are able to stand and lie down in a natural position.
 4. Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialization. The duration of the daily access to an outdoor area or walk shall be minimum one hour in total. The operator may only derogate from these requirements based on written advice of a veterinarian.
 5. When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to express their natural behaviour.
-6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
+6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs or cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
 6a. Operators of breeding and selling establishments shall use, where necessary, heating or cooling systems to maintain good air quality, an appropriate temperature in indoor enclosures at their establishments, and remove excessive moisture.
 7. Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
 For the purposes of the first subparagraph, 'light' means natural light, complemented, where needed, due to the climatic conditions and geographic position of a Member State, by artificial light.
-7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
+7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
-2 — Os operadores devem assegurar que:
-a) os estabelecimentos onde os cães e gatos são mantidos e os equipamentos utilizados são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção completa de todos os cães ou gatos;
-b) todos os componentes do edifício do estabelecimento, incluindo o piso, telhado e divisões, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para garantir que não representam riscos ao bem-estar dos cães ou gatos;
-ba) todos os componentes do edifício do estabelecimento, incluindo o piso e as divisões, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para garantir que não representam riscos ao bem-estar dos cães ou gatos;
-c) nos estabelecimentos de criação e venda onde os cães e gatos são mantidos em recinto fechado, a poeira, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar o aquecimento excessivo;
-d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades, com possibilidade de se retirarem e descansarem;
-da) os cães ou gatos têm locais de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para garantir que todos podem deitar-se e descansar simultaneamente numa posição natural;
-e) estruturas e medidas apropriadas são implementadas para cães ou gatos mantidos ao ar livre para os proteger de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e congelamento.
-3 — Os operadores não devem manter cães ou gatos em contentores.
-Por derrogação, contentores podem ser utilizados apenas para transporte, isolamento de curta duração de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento evitado e os cães e gatos sejam capazes de estar de pé e deitar-se numa posição natural.
-4 — Os operadores não devem manter cães com mais de 8 semanas exclusivamente em recintos fechados. Esses cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode derrogar destes requisitos apenas com base em aconselhamento escrito de um médico veterinário.
-5 — Quando gatos são mantidos em viveiros, os operadores devem desenhar e construir recintos individuais que permitam aos gatos moverem-se livremente e expressar o seu comportamento natural.
-6 — Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas fechadas onde cães e gatos são mantidos, uma zona termoneutra apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
-6a — Os operadores de estabelecimentos de criação e venda devem utilizar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, temperatura apropriada em recintos fechados nos seus estabelecimentos, e remover humidade excessiva.
-7 — Os operadores devem assegurar que os cães e gatos são expostos a luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
-Para efeitos do parágrafo anterior, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
+          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
+2. Os operadores devem assegurar que:
+a) os estabelecimentos onde os cães ou gatos são mantidos e o equipamento utilizado são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção minuciosa de todos os cães ou gatos;
+b) todos os componentes de construção do estabelecimento, incluindo o pavimento, telhado e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos.
+(ba) todos os componentes de construção do estabelecimento, incluindo o pavimento e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos;
+c) em estabelecimentos de criação e venda onde os cães ou gatos são mantidos no interior, pó, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar sobreaquecimento;
+d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades com possibilidade de se retirarem e descansarem;
+(da) os cães ou gatos têm lugares de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para assegurar que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
+e) estruturas e medidas apropriadas estão em vigor para cães ou gatos mantidos no exterior para os proteger de condições climáticas adversas, incluindo para evitar stress térmico, queimaduras solares e frieiras.
+3. Os operadores não devem manter cães ou gatos em contentores.
+A título de derrogação, contentores podem ser usados apenas para transporte, isolamento a curto prazo de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade termorreguladora reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento seja evitado e os cães e gatos sejam capazes de se manter em pé e deitar-se numa posição natural.
+4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode apenas derrogar destes requisitos com base em aconselhamento escrito de um médico veterinário.
+5. Quando gatos são mantidos em gatarias, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
+6. Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas interiores onde os cães ou gatos são mantidos, uma zona termoneural apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
+6a. Os operadores de estabelecimentos de criação e venda devem usar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, uma temperatura apropriada em compartimentos interiores nos seus estabelecimentos, e remover humidade excessiva.
+7. Os operadores devem assegurar que os cães ou gatos são expostos à luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
+Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
+7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
+Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
+Artigo 11.º - Obrigações especiais relativas ao alojamento doméstico.
+Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
+Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
+Artigo 18.º - Alojamentos devem possuir instalações para armazenagem, lavagem, quarentena, enfermaria e higienização.
+Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>Lei 27/2016 - Rede de centros de recolha. DL 82/2019 - Identificação. Nenhum diploma específico complementar para condições detalhadas de alojamento técnicas (temperatura, ventilação, iluminação).</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
+          <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Sim - Portaria complementar com especificações técnicas</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+          <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1719,7 @@
     <row r="12" ht="120" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Necessidades Comportamentais</t>
+          <t>Necessidades Comportamentais (Behavioural needs)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1732,91 +1741,98 @@
 4. Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
 5. Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
 5a. The first subparagraph shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes nor to herding dogs during seasonal transhumance.
-5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
+6. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
-2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
+2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
 a) exames físicos;
 b) identificação individual de cães ou gatos e leitura da informação de identificação;
-c) colheita de amostras e vacinações;
-d) procedimentos para limpeza, higiene, saúde ou fins reprodutivos que não o acasalamento;
+c) recolha de amostras e vacinações;
+d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
 e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
-3 — A amarração por mais de 1 hora é proibida, exceto pela duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-3a — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
-4 — Os operadores devem assegurar que condições estão em lugar para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
-5 — Os operadores devem assegurar que cães ou gatos podem socializar de acordo com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar sua estratégia para tal socialização.
-5a — O parágrafo anterior não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino nem aos cães de pastoreio durante a transumância sazonal.
-5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
+3. O amarrar por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+3a. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
+4. Os operadores devem assegurar que condições estão em vigor para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
+5. Os operadores devem assegurar que os cães ou gatos podem socializar em conformidade com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar a sua estratégia para tal socialização.
+5a. O primeiro parágrafo não se aplica a cães guardiões de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino, nem a cães de pastoreio durante transumância sazonal.
+6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>Especificação clara: 'exercício físico e estímulo mental'.
+'Contato social adequado'.
+Métodos de 'reforço positivo' (OBRIGATÓRIO).
+Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
+Documentação obrigatória de estratégia de socialização (criadores).</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
+Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
+Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>Lei 27/2016 - Rede de centros de recolha (não cobre necessidades comportamentais).
+DL 82/2019 - Identificação (não cobre necessidades comportamentais).</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>NÃO APLICÁVEL - Diplomas não cobrem necessidades comportamentais</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
+          <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Sim - Regulamentação específica sobre métodos de treino</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+          <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Práticas Dolorosas</t>
+          <t>Práticas Dolorosas (Painful practices)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1834,88 +1850,100 @@
 a) tying up body parts unless for medical reasons in which case the duration shall be limited to the minimum period necessary;
 b) kicking, hitting, dragging, throwing, squeezing dogs or cats;
 c) applying electric current to dogs or cats unless performed for medical reasons;
-d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised;
-da) using prong collars;
-db) using choke collars without safety stop;
+d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised.
+(da) using prong collars;
+(db) using choke collars without safety stop;
 e) lifting dogs or cats by the limbs, head, ears, tail or hair, or lifting adult dogs or cats by the skin.
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
-1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
-1b — Por derrogação do parágrafo 1, os Estados-Membros podem permitir corte de orelhas por entalhe ou corte de orelhas de gato no contexto de marcação de gatos vadios quando castrados sob um programa de captura-castração-libertação.
-2 — Os operadores devem assegurar que a castração é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. Por derrogação, os Estados-Membros podem permitir que a castração de gatos machos seja realizada por um enfermeiro veterinário licenciado.
-3 — Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
-a) amarração de partes do corpo a menos que por motivos médicos, caso em que a duração deve ser limitada ao período mínimo necessário;
-b) chutar, bater, arrastar, lançar, apertar cães ou gatos;
-c) aplicação de corrente elétrica a cães ou gatos a menos que realizada por motivos médicos;
-d) uso de focinheiras, a menos que necessário por motivos médicos, segurança animal ou humana, caso em que a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado;
-da) uso de coleiras de espinhos;
-db) uso de coleiras de enforcamento sem sistema de segurança;
-e) levantamento de cães ou gatos pelos membros, cabeça, orelhas, cauda ou pelo, ou levantamento de cães ou gatos adultos pela pele.
-4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
+          <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
+1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
+1b. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos vadios quando esterilizados sob um programa de captura-esterilização-libertação.
+2. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+3. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+a) amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
+b) chutar, bater, arrastar, atirar, apertar cães ou gatos;
+c) aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
+d) uso de focinheiras, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
+(da) uso de colares de espinhos;
+(db) uso de colares de estrangulamento sem paragem de segurança;
+e) levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
+4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @rgbeac]</t>
+          <t>Lista idêntica de mutilações proibidas ao Código.
+Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
+Alargamento: 'qualquer amputação sem razão médica veterinária'.
+Ênfase em anestesia e analgesia prolongada.
+Documentação obrigatória de indicação médica.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso no @codigo]</t>
+          <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
+Artigo 52.º - Proibição específica de mutilações:
+- Corte de orelhas (exceto fins medicinais)
+- Corte de cauda (revogado em 2015)
+- Ressecção de cordas vocais
+- Remoção de unhas/dentes
+- Exceções: reprodução e interesse do animal (com documentação)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>A ser preenchido</t>
+          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>[Pesquisa em progresso na legislação vigente]</t>
+          <t>Lei 27/2016 - Recolha de animais errantes (não cobre mutilações).
+DL 82/2019 - Identificação (não cobre mutilações).
+Nenhum diploma específico adicional necessário.</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Verificar conformidade com legislação portuguesa vigente</t>
+          <t>NÃO APLICÁVEL - Diplomas não específicos nesta matéria</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com Código do Animal</t>
+          <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Verificar alinhamento com RGBEAC</t>
+          <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
+          <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
+          <t>Correspondências completas - Cobertura legislativa adequada</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1390,88 +1390,85 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
-2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
+          <t>1 — Os operadores devem assegurar que os cães e gatos são alimentados de acordo com os requisitos estabelecidos no ponto 1 do Anexo I.
+2 — Os operadores devem assegurar que os cães e gatos são adequadamente alimentados e hidratados fornecendo:
 a) água limpa e fresca, ad libitum;
-b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter boa saúde;
+b) alimento em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, como parte de uma dieta adaptada à idade, raça, categoria, nível de atividade, saúde e estado reprodutivo dos cães ou gatos, tendo como objetivo global atingir e manter uma boa saúde;
 c) alimento livre de substâncias que possam causar sofrimento;
-d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
-3. Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e são construídas e instaladas de forma a:
-a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
-b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
-c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
-d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
-3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+d) alimentação de forma a evitar mudanças bruscas e assegurar um sistema gastrointestinal bem funcionante, em particular durante a fase de desmame.
+3 — Os operadores devem assegurar que as instalações de alimentação e hidratação são mantidas limpas e construídas e instaladas de modo a:
+a) proporcionar acesso igual a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
+b) minimizar os derrames e prevenir a contaminação de alimentos e água com contaminantes físicos, químicos ou biológicos prejudiciais;
+c) prevenir lesões, afogamento ou outro mal aos cães ou gatos;
+d) ser facilmente limpas e desinfetadas para prevenir a propagação de doenças.
+3a — Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
-Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Alimentação e abeberamento:
-A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
-Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
+          <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>DL 82/2019 - Bem-estar de animais de companhia</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>DL 82/2019 regulamenta identificação de animais. Não aborda especificamente requisitos de alimentação. Requisitos cobertos por @CODIGO (Art. 46.º) e @RGBEAC.</t>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
+          <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
+          <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
+          <t>Requisitos detalhados de alimentação e hidratação para cães e gatos. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Alojamento (Housing)</t>
+          <t>Alojamento</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1481,112 +1478,106 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of the annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of the annex I.
+          <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of Annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of Annex I.
 2. Operators shall ensure that:
 a) the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and allow the necessary access to and a thorough inspection of all dogs or cats;
-b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats.
-(ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
+b) all building components of the establishment, including the flooring, roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
+ba) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept cleaned to ensure that they do not pose any risks to the welfare of the dogs or cats;
 c) in breeding and selling establishments where dogs or cats are kept indoors, dust, temperature, relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating;
 d) dogs and cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with a possibility to withdraw and rest;
-(da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
+da) dogs or cats have clean, comfortable and dry resting places, sufficiently large and numerous to ensure that all of them can lie down and rest at the same time in a natural position;
 e) appropriate structures and measures are in place for dogs or cats kept outdoors to protect them from adverse climatic conditions, including to prevent thermal stress, sunburn and frostbite.
 3. Operators shall not keep dogs or cats in containers.
 By way of derogation, containers may only be used for the transport, short term isolation of individual dogs or cats and during the participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or puppies or kittens together with their mothers, provided that stress is minimised and suffering is avoided and the dogs and cats are able to stand and lie down in a natural position.
 4. Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialization. The duration of the daily access to an outdoor area or walk shall be minimum one hour in total. The operator may only derogate from these requirements based on written advice of a veterinarian.
 5. When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to express their natural behaviour.
-6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs or cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
+6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained taking into account their coat type, age, size, breed, and health.
 6a. Operators of breeding and selling establishments shall use, where necessary, heating or cooling systems to maintain good air quality, an appropriate temperature in indoor enclosures at their establishments, and remove excessive moisture.
 7. Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
 For the purposes of the first subparagraph, 'light' means natural light, complemented, where needed, due to the climatic conditions and geographic position of a Member State, by artificial light.
-7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance.</t>
+7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance. Paragraph 2(da) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
-2. Os operadores devem assegurar que:
-a) os estabelecimentos onde os cães ou gatos são mantidos e o equipamento utilizado são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção minuciosa de todos os cães ou gatos;
-b) todos os componentes de construção do estabelecimento, incluindo o pavimento, telhado e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos.
-(ba) todos os componentes de construção do estabelecimento, incluindo o pavimento e divisões de espaço, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para assegurar que não apresentam riscos ao bem-estar dos cães ou gatos;
-c) em estabelecimentos de criação e venda onde os cães ou gatos são mantidos no interior, pó, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar sobreaquecimento;
-d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades com possibilidade de se retirarem e descansarem;
-(da) os cães ou gatos têm lugares de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para assegurar que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
-e) estruturas e medidas apropriadas estão em vigor para cães ou gatos mantidos no exterior para os proteger de condições climáticas adversas, incluindo para evitar stress térmico, queimaduras solares e frieiras.
-3. Os operadores não devem manter cães ou gatos em contentores.
-A título de derrogação, contentores podem ser usados apenas para transporte, isolamento a curto prazo de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade termorreguladora reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento seja evitado e os cães e gatos sejam capazes de se manter em pé e deitar-se numa posição natural.
-4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode apenas derrogar destes requisitos com base em aconselhamento escrito de um médico veterinário.
-5. Quando gatos são mantidos em gatarias, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
-6. Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas interiores onde os cães ou gatos são mantidos, uma zona termoneural apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
-6a. Os operadores de estabelecimentos de criação e venda devem usar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, uma temperatura apropriada em compartimentos interiores nos seus estabelecimentos, e remover humidade excessiva.
-7. Os operadores devem assegurar que os cães ou gatos são expostos à luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
-Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
+          <t>1 — Os operadores de estabelecimentos de criação e venda devem assegurar que os cães e gatos são alojados de acordo com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães e gatos são alojados de acordo com o ponto 2.2 do Anexo I.
+2 — Os operadores devem assegurar que:
+a) os estabelecimentos onde os cães e gatos são mantidos e os equipamentos utilizados são adequados aos tipos e número de cães ou gatos, e permitem o acesso necessário e inspeção completa de todos os cães ou gatos;
+b) todos os componentes do edifício do estabelecimento, incluindo o piso, telhado e divisões, bem como o equipamento utilizado para cães ou gatos, são construídos e mantidos adequadamente, para garantir que não representam riscos ao bem-estar dos cães ou gatos;
+ba) todos os componentes do edifício do estabelecimento, incluindo o piso e as divisões, bem como o equipamento utilizado para cães ou gatos, são mantidos limpos para garantir que não representam riscos ao bem-estar dos cães ou gatos;
+c) nos estabelecimentos de criação e venda onde os cães e gatos são mantidos em recinto fechado, a poeira, temperatura, humidade relativa do ar e concentrações de gases não são prejudiciais aos cães ou gatos e a ventilação é suficiente para evitar o aquecimento excessivo;
+d) os cães e gatos têm espaço suficiente para se moverem livremente e expressar comportamento específico da espécie de acordo com as suas necessidades, com possibilidade de se retirarem e descansarem;
+da) os cães ou gatos têm locais de repouso limpos, confortáveis e secos, suficientemente grandes e numerosos para garantir que todos podem deitar-se e descansar simultaneamente numa posição natural;
+e) estruturas e medidas apropriadas são implementadas para cães ou gatos mantidos ao ar livre para os proteger de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e congelamento.
+3 — Os operadores não devem manter cães ou gatos em contentores.
+Por derrogação, contentores podem ser utilizados apenas para transporte, isolamento de curta duração de cães ou gatos individuais e durante participação em espetáculos, exposições e competições, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos juntamente com as suas mães, desde que o stress seja minimizado e o sofrimento evitado e os cães e gatos sejam capazes de estar de pé e deitar-se numa posição natural.
+4 — Os operadores não devem manter cães com mais de 8 semanas exclusivamente em recintos fechados. Esses cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador pode derrogar destes requisitos apenas com base em aconselhamento escrito de um médico veterinário.
+5 — Quando gatos são mantidos em viveiros, os operadores devem desenhar e construir recintos individuais que permitam aos gatos moverem-se livremente e expressar o seu comportamento natural.
+6 — Os operadores de estabelecimentos de criação e venda devem assegurar que em áreas fechadas onde cães e gatos são mantidos, uma zona termoneutra apropriada é mantida levando em conta o seu tipo de pelagem, idade, tamanho, raça e saúde.
+6a — Os operadores de estabelecimentos de criação e venda devem utilizar, quando necessário, sistemas de aquecimento ou arrefecimento para manter boa qualidade do ar, temperatura apropriada em recintos fechados nos seus estabelecimentos, e remover humidade excessiva.
+7 — Os operadores devem assegurar que os cães e gatos são expostos a luz, e são capazes de permanecer no escuro por períodos suficientes e ininterruptos para manter um ritmo circadiano normal.
+Para efeitos do parágrafo anterior, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
+7a — Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé. O parágrafo 2(da) não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de treino.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
-Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
-Artigo 11.º - Obrigações especiais relativas ao alojamento doméstico.
-Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
-Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
-Artigo 18.º - Alojamentos devem possuir instalações para armazenagem, lavagem, quarentena, enfermaria e higienização.
-Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
+          <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016 - Rede de centros de recolha. DL 82/2019 - Identificação. Nenhum diploma específico complementar para condições detalhadas de alojamento técnicas (temperatura, ventilação, iluminação).</t>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
+          <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
+          <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
+          <t>Requisitos detalhados de alojamento para cães e gatos em diferentes tipos de estabelecimentos (criação, venda, abrigos). Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>Sim - Portaria complementar com especificações técnicas</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1710,7 @@
     <row r="12" ht="120" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Necessidades Comportamentais (Behavioural needs)</t>
+          <t>Necessidades Comportamentais</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1741,98 +1732,91 @@
 4. Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
 5. Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
 5a. The first subparagraph shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes nor to herding dogs during seasonal transhumance.
-6. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
+5b. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
-2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+          <t>1 — Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais dos cães ou gatos de acordo com o ponto 4 do Anexo I.
+2 — Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do Artigo 12(3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
 a) exames físicos;
 b) identificação individual de cães ou gatos e leitura da informação de identificação;
-c) recolha de amostras e vacinações;
-d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
+c) colheita de amostras e vacinações;
+d) procedimentos para limpeza, higiene, saúde ou fins reprodutivos que não o acasalamento;
 e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
-3. O amarrar por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-3a. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
-4. Os operadores devem assegurar que condições estão em vigor para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
-5. Os operadores devem assegurar que os cães ou gatos podem socializar em conformidade com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar a sua estratégia para tal socialização.
-5a. O primeiro parágrafo não se aplica a cães guardiões de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino, nem a cães de pastoreio durante transumância sazonal.
-6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
+3 — A amarração por mais de 1 hora é proibida, exceto pela duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+3a — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais e aduaneiros que são mantidos em estabelecimentos de criação ou venda.
+4 — Os operadores devem assegurar que condições estão em lugar para permitir aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
+5 — Os operadores devem assegurar que cães ou gatos podem socializar de acordo com o ponto 4 do Anexo I. Os operadores de estabelecimentos de criação devem documentar sua estratégia para tal socialização.
+5a — O parágrafo anterior não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino nem aos cães de pastoreio durante a transumância sazonal.
+5b — Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo sua frustração.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Especificação clara: 'exercício físico e estímulo mental'.
-'Contato social adequado'.
-Métodos de 'reforço positivo' (OBRIGATÓRIO).
-Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
-Documentação obrigatória de estratégia de socialização (criadores).</t>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
-Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
-Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
+          <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016 - Rede de centros de recolha (não cobre necessidades comportamentais).
-DL 82/2019 - Identificação (não cobre necessidades comportamentais).</t>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>NÃO APLICÁVEL - Diplomas não cobrem necessidades comportamentais</t>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
+          <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
+          <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
+          <t>Requisitos de satisfação das necessidades comportamentais de cães e gatos. Proibição de retenção em áreas restritivas. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Sim - Regulamentação específica sobre métodos de treino</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Práticas Dolorosas (Painful practices)</t>
+          <t>Práticas Dolorosas</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1850,100 +1834,88 @@
 a) tying up body parts unless for medical reasons in which case the duration shall be limited to the minimum period necessary;
 b) kicking, hitting, dragging, throwing, squeezing dogs or cats;
 c) applying electric current to dogs or cats unless performed for medical reasons;
-d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised.
-(da) using prong collars;
-(db) using choke collars without safety stop;
+d) using of muzzles, unless required for medical reasons, animal or human safety reasons, in which case the duration shall be limited to the minimum period necessary and the dog or cat shall be supervised;
+da) using prong collars;
+db) using choke collars without safety stop;
 e) lifting dogs or cats by the limbs, head, ears, tail or hair, or lifting adult dogs or cats by the skin.
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
-1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
-1b. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos vadios quando esterilizados sob um programa de captura-esterilização-libertação.
-2. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
-3. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
-a) amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
-b) chutar, bater, arrastar, atirar, apertar cães ou gatos;
-c) aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
-d) uso de focinheiras, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
-(da) uso de colares de espinhos;
-(db) uso de colares de estrangulamento sem paragem de segurança;
-e) levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
-4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
+          <t>1 — Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou outra amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que seja por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir lesões. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
+1a — A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até o cão ou gato, juntamente com este documento, ser transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento por três anos após a transferência do cão ou gato.
+1b — Por derrogação do parágrafo 1, os Estados-Membros podem permitir corte de orelhas por entalhe ou corte de orelhas de gato no contexto de marcação de gatos vadios quando castrados sob um programa de captura-castração-libertação.
+2 — Os operadores devem assegurar que a castração é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. Por derrogação, os Estados-Membros podem permitir que a castração de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+3 — Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+a) amarração de partes do corpo a menos que por motivos médicos, caso em que a duração deve ser limitada ao período mínimo necessário;
+b) chutar, bater, arrastar, lançar, apertar cães ou gatos;
+c) aplicação de corrente elétrica a cães ou gatos a menos que realizada por motivos médicos;
+d) uso de focinheiras, a menos que necessário por motivos médicos, segurança animal ou humana, caso em que a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado;
+da) uso de coleiras de espinhos;
+db) uso de coleiras de enforcamento sem sistema de segurança;
+e) levantamento de cães ou gatos pelos membros, cabeça, orelhas, cauda ou pelo, ou levantamento de cães ou gatos adultos pela pele.
+4 — Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados ao uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Lista idêntica de mutilações proibidas ao Código.
-Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
-Alargamento: 'qualquer amputação sem razão médica veterinária'.
-Ênfase em anestesia e analgesia prolongada.
-Documentação obrigatória de indicação médica.</t>
+          <t>[Pesquisa em progresso no @rgbeac]</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
-Artigo 52.º - Proibição específica de mutilações:
-- Corte de orelhas (exceto fins medicinais)
-- Corte de cauda (revogado em 2015)
-- Ressecção de cordas vocais
-- Remoção de unhas/dentes
-- Exceções: reprodução e interesse do animal (com documentação)</t>
+          <t>[Pesquisa em progresso no @codigo]</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016, DL 82/2019 - Legislação complementar</t>
+          <t>A ser preenchido</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Lei 27/2016 - Recolha de animais errantes (não cobre mutilações).
-DL 82/2019 - Identificação (não cobre mutilações).
-Nenhum diploma específico adicional necessário.</t>
+          <t>[Pesquisa em progresso na legislação vigente]</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>NÃO APLICÁVEL - Diplomas não específicos nesta matéria</t>
+          <t>Verificar conformidade com legislação portuguesa vigente</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
+          <t>Verificar alinhamento com Código do Animal</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
+          <t>Verificar alinhamento com RGBEAC</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
+          <t>Requisitos relativos a práticas dolorosas e mutilações em cães e gatos. Restrições a práticas de manipulação causando dor. Novo artigo introduzido pelo Regulamento.</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>Correspondências completas - Cobertura legislativa adequada</t>
+          <t>Artigo novo do Regulamento 2023/0447. Requer integração na legislação portuguesa.</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -76,42 +76,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A2E"/>
+        <fgColor rgb="006A7A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00E8F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF5FB"/>
+        <fgColor rgb="00F4F9FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00E8F3E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE6CC"/>
+        <fgColor rgb="00FFF5ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F7FA"/>
+        <fgColor rgb="00F0FBFD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD7F7"/>
+        <fgColor rgb="00F5EEF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Cor de fundo: #D6E4F0</t>
+          <t>Cor de fundo: #E8F2F8</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Cor de fundo: #EBF5FB</t>
+          <t>Cor de fundo: #F4F9FD</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>Cor de fundo: #D5E8D4</t>
+          <t>Cor de fundo: #E8F3E6</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>Cor de fundo: #FFE6CC</t>
+          <t>Cor de fundo: #FFF5ED</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Cor de fundo: #E0F7FA</t>
+          <t>Cor de fundo: #F0FBFD</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Cor de fundo: #EAD7F7</t>
+          <t>Cor de fundo: #F5EEF9</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>Cor de fundo: #F5F5F5</t>
+          <t>Cor de fundo: #FAFAFA</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -664,107 +664,97 @@
     <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Identificação e Registo</t>
+          <t>Princípios Gerais de Bem-Estar</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17.º do Regulamento 2023/0447</t>
+          <t>Art.º 5.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
-1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
-Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
-Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
-2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
-3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
-4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
-5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
-Member States may grant derogations from the first subparagraph to military, police and customs dogs.
-6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
-7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
-8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
+(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
+(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
+(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
-1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
-2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
-3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
-4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
-5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
-6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
-7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
-8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
-a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
-b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
-c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+          <t>1 — O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+— Atenção, supervisão, controlo, exercício físico e estímulo mental;
+— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
+— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
-2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
-4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
+2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
+3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
-2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
+Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
+          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
+          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
+          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -873,15 +863,114 @@
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+5. The following shall be prohibited in the management of the reproduction of dogs and cats:
+(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) the breeding to produce hybrids.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
+(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+5. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
+2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>2 — A reprodução de animais obedece ao seguinte:
+a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
+Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Reprodução e Criação</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Art.º 7.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Operators shall notify the competent authorities of their activity, providing at least the following information:
 (a) name, address and contact details of the operator;
@@ -892,7 +981,7 @@
 (ea) for breeding establishments, the estimated number of litters to be placed on the market per year.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações:
 (a) nome, morada e contactos do operador;
@@ -903,24 +992,24 @@
 (ea) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Art.º 43.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1 — Os centros de bem-estar animal procedem à esterilização dos animais recolhidos que se presuma terem sido abandonados, nos termos do artigo 41.º.
 2 — As câmaras municipais devem, sempre que necessário e sob a responsabilidade do médico veterinário municipal, incentivar e promover programas de esterilização de animais de companhia, nomeadamente os cães e gatos, em complementaridade com os centros de bem-estar animal.
 3 — Os requisitos mínimos das instalações adequadas à realização de esterilizações nos centros de bem-estar animal são estabelecidos em portaria do membro do Governo responsável pela área da agricultura.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>1 — A reprodução de animais deve ser realizada de forma planeada.
 2 — A reprodução de animais obedece ao seguinte:
@@ -929,12 +1018,12 @@
 c) Devem ser excluídos da reprodução os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>n.º 1 do art.º 3.º-A do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>1 — A mera comunicação prévia a que se refere a alínea a) do n.º 1 do artigo anterior é dirigida à DGAV e deve conter os seguintes elementos, quando aplicáveis:
 a) O nome ou a denominação social do interessado;
@@ -949,127 +1038,29 @@
 j) Declaração de responsabilidade, subscrita pelo interessado, relativa ao cumprimento da legislação aplicável aos animais de companhia, nomeadamente em matéria de instalações, equipamentos, higiene, saúde e bem-estar dos animais.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 3.º-A) prevê comunicação prévia à DGAV com elementos parcialmente equivalentes (capacidade máxima, espécies, raças). Não exige a estimativa anual de ninhadas a colocar no mercado (al. ea) do @regulamento), constituindo lacuna parcial. É o diploma mais próximo do @regulamento neste eixo.</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>O @codigo regula condições de reprodução (art.º 8.º) mas não prevê qualquer sistema de notificação ou registo de estabelecimentos criadores junto da autoridade competente.</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac trata da esterilização de errantes e CED, mas não contém norma sobre notificação de criadores ou registo de estabelecimentos com fins de reprodução comercial.</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>A @legislacao vigente é o diploma base adequado para a transposição. Necessidade de ajuste: acrescentar a obrigação de estimativa anual de ninhadas a colocar no mercado e alinhar os restantes elementos informativos com a lista exaustiva do art.º 7.º do @regulamento.</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Princípios Gerais de Bem-Estar</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 5.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-(a) dogs and cats are provided with water and feed of a quality and of a quantity that enables them to have appropriate nutrition and hydration;
-(b) dogs and cats are kept in an appropriate and regularly cleaned physical environment which is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and ease of movement, preventing overcrowding;
-(c) dogs and cats are kept safe, clean and in good health by preventing diseases, injuries, and pain, due in particular to management, handling practices and breeding practices;
-(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
-(e) dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive and other behaviours indicative of negative animal welfare, and taking into consideration the individual dog's or cat's needs in the different domains referred to in points (a) to (d).</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) os cães e gatos são alimentados e abebeirados com água e ração de qualidade e quantidade adequadas a uma nutrição e hidratação apropriadas;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>al. a) do n.º 1 do art.º 10.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>1 — O detentor do animal de companhia deve:
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
-— Atenção, supervisão, controlo, exercício físico e estímulo mental;
-— Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
-— Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
-— Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes;
-— Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
-— Contato social adequado a cada espécie, de acordo com a sua idade e atividade.</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>n.ºs 1, 2 e 3 do art.º 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>n.º 1 do art.º 7.º e n.º 1 do art.º 9.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 7.º, n.º 1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-Artigo 9.º, n.º 1 — A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 7.º e 9.º) consagra os mesmos parâmetros mas desenvolve-os em artigos separados (alojamento, alimentação, ambiente) sem os denominar como domínios nem os sistematizar de forma unificada segundo o referencial OMSA.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 5.º) refere 'parâmetros de bem-estar animal' genericamente, sem adotar formalmente a nomenclatura dos 5 domínios OMSA nem a sua sistematização explícita.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 10.º, n.º 1, al. a)) articula obrigações equivalentes ao nível do detentor de forma descritiva, sem sistematização nos 5 domínios nem referência ao quadro OMSA.</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>Alinhamento substancial de conteúdo; sem necessidade de alteração imediata. Recomenda-se a adoção formal dos 5 domínios OMSA como referencial estruturante em futura revisão legislativa ou em normas de orientação técnica da DGAV.</t>
-        </is>
-      </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>Não</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -1077,240 +1068,15 @@
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Estratégias de Criação — Conformação e Consanguinidade</t>
+          <t>Detenção Responsável e Informação</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Art.º 6.º-A do Regulamento 2023/0447</t>
+          <t>Art.º 8.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with detrimental effects on their health and welfare.
-2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of these dogs or cats, or of their offspring. Before selection for breeding of a dog or cat that may be concerned by an excessive conformational trait the operator shall consult a veterinarian or an independent qualified person under the responsibility of a veterinarian. The veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-3. The Commission is empowered to adopt, taking into account scientific opinions of the European Food Safety Authority as well as the social and economic impacts, delegated acts in accordance with Article 23 supplementing this Regulation by:
-(a) defining characteristics of the genotypes referred to in paragraph 1, which shall be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-(b) defining excessive conformational traits referred to in paragraph 2 of this Article, which shall be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-4. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-5. The following shall be prohibited in the management of the reproduction of dogs and cats:
-(a) the breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-(b) the breeding to produce hybrids.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>n.ºs 1 e 2 do art.º 34.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>1 — As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
-2 — O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>n.º 2, als. a), b) e c) do art.º 8.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>2 — A reprodução de animais obedece ao seguinte:
-a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
-b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
-c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>art.º 17.º e n.º 1 do art.º 18.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 17.º — As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º, n.º 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou para impedir a reprodução.</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.ºs 17.º e 18.º) exige intervenção veterinária em cirurgias e documentação para amputações, mas não prevê qualquer restrição à reprodução por traços conformacionais excessivos nem proibição de consanguinidade próxima ou hibridação.</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (displasia, rim poliquístico) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 34.º) proíbe intervenções cirúrgicas de modificação da aparência, mas não contém qualquer norma sobre estratégia genética de criação, conformação excessiva ou consanguinidade.</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>Lacuna normativa transversal. Necessidade de criar norma específica que: (1) defina traços conformacionais excessivos (a regular por ato delegado europeu até 2030); (2) proíba consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proíba a produção de híbridos; (4) imponha consulta veterinária prévia ao acasalamento de animais potencialmente afetados.</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Saúde e Monitorização Sanitária</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>1. Operators shall ensure that:
-(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
-(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
-(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
-(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
-(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
-Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
-2. Operators of breeding establishments shall additionally ensure that:
-(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-(-d) lactating queens are not mated or inseminated;
-(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1 — Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
-(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
-(-d) as gatas a lactar não são acasaladas nem inseminadas;
-(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Artigo 33.º — Cuidados de saúde
-1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 6.º — Cuidados médico-veterinários
-O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Artigo 13.º — Maneio
-1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
-[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
-[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
-Artigo 16.º — Cuidados de saúde animal
-1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
-2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Detenção Responsável e Informação</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 8.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall provide to the acquirer of a dog or cat written information necessary to enable him or her to ensure the welfare of the dog or cat including information on responsible ownership and on the specific needs of the dog or cat in terms of feeding, caring, health, housing and behavioural needs, as well as information on its health.
 1a. The written information on the dog or cat's health referred to in the first paragraph shall include at least:
@@ -1319,7 +1085,7 @@
 In case the information on the dog's or cat's health is documented in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1328,23 +1094,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1356,56 +1122,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Art.º 9.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1. Animal caretakers, other than volunteers in shelters and interns who are under the responsibility of a competent animal caretaker, shall have the following competences as regards the dogs and cats they are handling:
 (a) understanding of their biological behaviour and their physiological and ethological needs;
@@ -1417,7 +1183,7 @@
 3. The Commission shall, by means of implementing acts, lay down minimum requirements concerning the formal education, training or professional experience in order to acquire the competences referred to in paragraph 2 and for the training courses referred to in paragraph 2a. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 24. The implementing act concerning the training courses referred to in paragraph 2a shall be adopted by [3 years from the date of entry into force of the Regulation].</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1429,12 +1195,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1444,23 +1210,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1468,45 +1234,45 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Avaliação e Supervisão de Bem-Estar</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 10.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Operators shall:
 (a) ensure that the establishments under their responsibility receive a visit by a veterinarian within the first year after the date of application of this Regulation or within the first year after having notified a new establishment, for the purpose of identifying and assessing any risk factor for the welfare of the dogs or cats and advising the operator on measures to address those risks; thereafter the visits from a veterinarian shall take place when appropriate, based on a risk analysis by the competent authorities; Member States may provide for that the advisory welfare visits are annual;
@@ -1514,7 +1280,7 @@
 By 24 months from the date of entry into force of this Regulation, the Commission shall adopt delegated acts in accordance with Article 23 supplementing this Article in order to lay down minimum criteria to be assessed during the advisory welfare visit.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
@@ -1522,12 +1288,12 @@
 Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 56.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Artigo 56.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário responsável pelo alojamento.
@@ -1538,12 +1304,12 @@
 d) A colaboração com as autoridades competentes em todas as ações que estas determinem.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 32.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Artigo 32.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos com fins higiénicos, necessitam de ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1553,12 +1319,12 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 4.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º — Médico veterinário responsável pelo alojamento
 1 — Os titulares da exploração de alojamentos para hospedagem sem fins lucrativos e com fins lucrativos de animais, com exceção dos alojamentos para hospedagem com fins higiénicos, devem ter ao seu serviço um médico veterinário que seja responsável pelo alojamento.
@@ -1568,45 +1334,45 @@
 c) A colaboração com as autoridades competentes em todas as ações que estas determinarem.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 4.º) estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, mas não especifica que essa avaliação deve ocorrer em prazo determinado (ex.: 1 ano) ou que os registos devem ser mantidos por período específico (4 anos). O @regulamento é mais prescritivo neste aspecto.</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 32.º) replica quase verbatim o art.º 4.º do DL n.º 276/2001, mantendo as mesmas lacunas: não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados.</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 56.º) reforça a obrigação com 'parecer relativo à verificação das condições higiossanitárias e de bem-estar', mas igualmente sem prazos específicos para avaliações ou duração de retenção de registos. Ambos focam-se em 'programas' interno, não em 'visitas periódicas externas'.</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Lacuna estrutural em toda a legislação nacional: enquanto o @regulamento exige 'visita de um veterinário' num prazo específico (1 ano) com manutenção de registos por 4 anos e transmissão entre veterinários, a legislação nacional concentra-se em ter um 'médico veterinário responsável' no estabelecimento. Necessidade de alteração: (1) formalizar obrigação de 'visita de avaliação' por veterinário dentro de 1 ano após notificação; (2) exigir avaliações periódicas conforme risco; (3) obrigatória manutenção de registos por 4 anos; (4) garantir transmissão de informações ao próximo veterinário avaliador; (5) estabelecer critérios mínimos de avaliação (bem-estar comportamental, alojamento, saúde, etc.).</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="11" ht="120" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Alimentação e Hidratação</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that dogs or cats are fed in accordance with the requirements laid down in point 1 of Annex I.
 2. Operators shall ensure that dogs or cats are adequately fed and hydrated by supplying:
@@ -1622,7 +1388,7 @@
 3a. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of the advice for its entire duration as advised by the veterinarian.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
 2. Os operadores devem assegurar que os cães ou gatos são adequadamente alimentados e hidratados através do fornecimento de:
@@ -1638,35 +1404,35 @@
 3a. Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º (n.º 1, al. a) e 10.º (n.º 1, al. a) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios fundamentais: Não passem fome ou sede, nem sejam sujeitos a malnutrição.
 Artigo 10.º - Obrigações especiais dos detentores: Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável. Ênfase em necessidades nutricionais adequadas ao estado de saúde.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 46.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Alimentação e abeberamento:
 A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies.
 Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 12.º</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>1 — Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
 2 — As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
@@ -1676,49 +1442,49 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>NÃO APLICÁVEL - Diploma não específico nesta matéria</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Art. 46.º implementa integralmente)</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (linguagem modernizada)</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal (Art. 46.º) implementa todos os requisitos do Artigo 11.º. RGBEAC alinha melhor com linguagem e especificidades do Regulamento europeu. Sem divergências substanciais.</t>
         </is>
       </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Correspondências completas - RGBEAC alinha melhor com Regulamento EU</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Alojamento (Housing)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>1. Operators of breeding and selling establishments shall ensure that dogs or cats are provided with housing in accordance with point 2 of the annex I. Operators of shelters shall ensure that dogs or cats are provided with housing in accordance with point 2.2 of the annex I.
 2. Operators shall ensure that:
@@ -1740,7 +1506,7 @@
 7a. Paragraphs 2(a), (b), (ba) (da) (e), 6, 6a and 7 shall not apply to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of on foot seasonal transhumance.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
 2. Os operadores devem assegurar que:
@@ -1762,12 +1528,12 @@
 7a. Os parágrafos 2(a), (b), (ba) (da) (e), 6, 6a e 7 não se aplicam a cães guardiões de gado, nem a cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto de transumância sazonal a pé.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Arts. 7.º, 10.º, 11.º, 47-57 do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Artigo 7.º - Princípios: Condições de detenção e alojamento salvaguardam bem-estar animal.
 Artigo 10.º - Obrigações especiais: Liberdade de movimento, proibição de contenção permanente, espaço adequado, enriquecimento ambiental e abrigo protetor.
@@ -1775,12 +1541,12 @@
 Artigos 47-57 - Regulação detalhada de alojamentos para hospedagem (estruturas, proteção, maneio, responsabilidades veterinárias).</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Arts. 3.º, 14.º, 18.º, 28.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Artigo 3.º - Define 'Alojamento' como qualquer instalação, edifício ou local onde animais se encontram mantidos.
 Artigo 14.º - A temperatura, ventilação, luminosidade e obscuridade devem ser adequadas ao conforto e bem-estar.
@@ -1788,12 +1554,12 @@
 Artigo 28.º - Define separação por espécie e requisitos de estrutura para hospedagem.</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigos 8.º e 15.º</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
@@ -1802,49 +1568,175 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Não específico para condições técnicas de alojamento</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>SIM - COBERTURA COMPLETA (Arts. 3, 14, 18, 28)</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA EXPANDIDA (especifica detalhes técnicos)</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>COBERTURA COMPLETA. Código do Animal e RGBEAC implementam requisitos do Artigo 12.º. Faltam especificações técnicas detalhadas (temperatura, ventilação, iluminação) — recomenda-se Portaria complementar.</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Sim - Portaria complementar com especificações técnicas</t>
         </is>
       </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Princípios cobertos; faltam normas técnicas pormenorizadas</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="120" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Saúde e Monitorização Sanitária</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 13.º do Regulamento 2023/0447 (PE/Conselho)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1. Operators shall ensure that:
+(a) dogs or cats under their responsibility are inspected by animal caretakers at least once a day and vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently;
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where needed, receive appropriate treatment;
+(c) where the recovery of a dog or a cat with compromised welfare is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay, to decide whether the dog or cat shall be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anesthesia and analgesia;
+(d) measures to prevent and control external and internal parasites, and vaccinations to prevent common diseases to which dogs or cats are likely to be exposed are implemented;
+(e) enrichment do not present a significant risk of injury or biological or chemical contamination or any other health risk.
+Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Member states may grant derogations from point (c) in cases of emergencies, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
+(i) an immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+(ii) the operator keeps a record of the use of the derogation for purposes of the official control.
+2. Operators of breeding establishments shall additionally ensure that:
+(-a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(-b) bitches or queens are only bred if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I, and they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(-c) litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(-d) lactating queens are not mated or inseminated;
+(-e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, not killed or abandoned.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1 — Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+(i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+(ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2 — Os operadores de estabelecimentos de criação devem adicionalmente assegurar que:
+(-a) são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(-b) as cadelas ou gatas só são reproduzidas se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(-c) a frequência de gestações com ninhadas de cadelas ou gatas respeita a frequência máxima fixada no ponto 3 do Anexo I;
+(-d) as gatas a lactar não são acasaladas nem inseminadas;
+(-e) os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º do RGBEAC — Regime Geral do Bem-Estar dos Animais de Companhia (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º — Cuidados de saúde
+1 — Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3 — Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+[dim]4 — Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+[dim]5 — Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 6.º (Cuidados médico-veterinários) do Código do Animal — DL n.º 214/2013</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 6.º — Cuidados médico-veterinários
+O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 13.º (Maneio) e art.º 16.º (Cuidados de saúde animal) do DL n.º 276/2001, de 17 de outubro</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Maneio
+1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+[dim]2 — O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+[dim]4 — O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+[dim]5 — Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
+Artigo 16.º — Cuidados de saúde animal
+1 — Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária devidamente elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais competentes.
+2 — No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3 — Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4 — Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+[dim]5 — Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+[dim]6 — A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>O DL n.º 276/2001 prevê inspeção diária (n.º 3 do art.º 13.º) e programa de profilaxia supervisionado por veterinário (n.º 1 do art.º 16.º) — alinhamento parcial com as als. (a) e (d) do n.º 1 do art.º 13.º do @regulamento. Lacunas: (1) não distingue animais vulneráveis com maior frequência de inspeção; (2) não prevê isolamento em área separada com tratamento (al. (b)); (3) não exige consulta veterinária para decisão de eutanásia com anestesia/analgesia (al. (c)); (4) nenhuma das obrigações sanitárias para criadores previstas no n.º 2 está contemplada: sem idade mínima de reprodução, sem frequência máxima de partos, sem proibição de cobrição de fêmeas a lactar, sem regime de rehoming.</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>O @codigo limita os cuidados médico-veterinários ao animal ferido ou doente (art.º 6.º) — sem qualquer obrigação de inspeção diária, programa de profilaxia ou isolamento. É o diploma com maior divergência face ao n.º 1 do art.º 13.º do @regulamento, omitindo igualmente todas as obrigações sanitárias específicas para criadores previstas no n.º 2.</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>O @rgbeac (art.º 33.º) centra os cuidados de saúde no detentor em geral (n.ºs 1 a 3), sem distinguir obrigações reforçadas para operadores de criação. Não prevê: inspeção diária sistemática por cuidadores; isolamento imediato de animais com bem-estar comprometido; nem qualquer dos requisitos sanitários para criadores do n.º 2 do art.º 13.º do @regulamento. Os n.ºs 4 e 5 (CAMV e denúncia de maus-tratos) não têm correspondência direta no @regulamento.</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>A @legislacao vigente (DL n.º 276/2001) tem o maior alinhamento, mas insuficiente. Necessidade de alteração dos três diplomas: (1) introduzir inspeção diária diferenciada para animais vulneráveis (al. (a) do n.º 1 do art.º 13.º do @regulamento); (2) criar obrigação de isolamento e tratamento imediato (al. (b)); (3) regular o processo de eutanásia com supervisão veterinária e anestesia/analgesia (al. (c)); (4) para criadores (n.º 2): fixar idade mínima e maturidade esquelética das fêmeas reprodutoras, frequência máxima de partos conforme Anexo I, proibição de cobrição de fêmeas a lactar, e regime de rehoming dos animais retirados da reprodução.</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Necessidades Comportamentais (Behavioural needs)</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Art.º 14.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
 2. Operators shall not keep dogs or cats in areas restraining their natural movements, except in case of Article 12(3), second sub-paragraph, or for performing the following procedures or treatments:
@@ -1861,7 +1753,7 @@
 6. Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
 2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
@@ -1878,12 +1770,12 @@
 6. Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigos 10, 12, 13, 14, 15</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Especificação clara: 'exercício físico e estímulo mental'.
 'Contato social adequado'.
@@ -1892,72 +1784,72 @@
 Documentação obrigatória de estratégia de socialização (criadores).</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
 Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
 Cobertura GENÉRICA: não especifica enriquecimento, socialização ou método de treino baseado em reforço positivo.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Artigo 8.º — 1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>PARCIAL - Legislação vigente oferece cobertura genérica</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>PARCIAL - Genérico, sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>SIM - COBERTURA SIGNIFICATIVAMENTE EXPANDIDA</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Legislação portuguesa oferece cobertura genérica. RGBEAC (2025) oferece avanço substancial com obrigatoriedade de reforço positivo e documentação de estratégia de socialização. Falta ainda regulamentação pormenorizada.</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>Sim - Regulamentação específica sobre métodos de treino</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="120" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Práticas Dolorosas (Painful practices)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Art.º 15.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds, are not performed unless upon medical indication, which may include prophylactic, with the sole purpose of preserving, improving the health of dogs or cats or preventing injury. In such case, the procedure shall only be performed under anaesthesia and prolonged analgesia and by a veterinarian.
 1a. The medical indication for the mutilation and the details of procedure carried out shall be documented by a veterinarian. This document shall be retained by the operator until the dog or cat, together with this document, is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for three years after the transfer of the dog or cat.
@@ -1974,7 +1866,7 @@
 4. Member States may grant derogations from paragraph 3 for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
 1a. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
@@ -1991,12 +1883,12 @@
 4. Os Estados-Membros podem conceder derrogações do parágrafo 3 para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>RGBEAC (proposta, jun. 2025) - Artigo 12.º</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Lista idêntica de mutilações proibidas ao Código.
 Referência a 'boas práticas internacionais' (alinhamento com Reg. 2023/0447).
@@ -2005,12 +1897,12 @@
 Documentação obrigatória de indicação médica.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Arts. 51.º e 52.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Artigo 51.º - Intervenções cirúrgicas exclusivamente por médico veterinário.
 Artigo 52.º - Proibição específica de mutilações:
@@ -2021,47 +1913,155 @@
 - Exceções: reprodução e interesse do animal (com documentação)</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Decreto-Lei n.º 276/2001 - Artigo 18.º</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Artigo 18.º — 1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>SIM - DL 276/2001 cobre amputações documentadas</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>Correspondências completas - Cobertura legislativa adequada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Identificação e Registo</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip compliant with Annex II.
+1a. Operators shall ensure that dogs and cats born in their establishments are individually identified within 3 months after their birth and in any event before the date of their placing on the market.
+Operators of selling establishments, shelters and those placing and being responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days after their arrival at the establishment and in any event before the date of their placing on the market.
+Pet owners and any other natural or legal persons, other than operators, who own dogs or cats, shall ensure that the dogs or cats are individually identified at the latest when the dog or cat reaches 3 months of age or, in case the dog or cat is placed on the market, before the date of their placing on the market.
+2. The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders in cats to be performed by a person other than a veterinarian, if it is done under the responsibility of a veterinarian.
+3. Dogs and cats which have been individually identified by means of an injectable transponder containing a microchip, in accordance with national legislation prior to entry into force of this Regulation, shall be recognised as identified in accordance with the requirements of this Article.
+4. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database.
+5. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment. For dogs and cats placed in foster homes, the registration shall be made in the name of the person responsible for the foster home. For dogs and cats owned by pet owners or by any other natural or legal person, the registration shall be made in the name of the pet owner or the natural or legal person.
+Member States may grant derogations from the first subparagraph to military, police and customs dogs.
+6. In case of placing on the market or occasional and irregular donation by a natural person without online advertising, the requirements for registration shall not apply.
+7. In the case of a death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall inform the national database.
+8. In case of unreadable transponder, the operator or the natural or legal person responsible for the dog or cat shall ensure that the dog or cat is re-identified with a new transponder and re-registered in the national database.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>1. Todos os cães e gatos mantidos em estabelecimentos colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com o Anexo II.
+1a. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de 3 meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda, abrigos e os que colocam e são responsáveis por cães e gatos em famílias de acolhimento devem assegurar que os cães e gatos que entrem nos seus estabelecimentos sejam identificados individualmente no prazo de 30 dias após a chegada.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que detenham cães ou gatos devem assegurar que os animais sejam identificados individualmente o mais tardar quando o animal atingir os 3 meses de idade ou, no caso de o animal ser colocado no mercado, antes da data da sua colocação no mercado.
+2. A implantação do transponder devem ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders em gatos seja efetuada por pessoa que não seja médico veterinário, se for feita sob a responsabilidade de um médico veterinário.
+3. Cães e gatos que tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip, em conformidade com legislação nacional anterior à entrada em vigor do presente Regulamento, são reconhecidos como identificados de acordo com os requisitos do presente artigo.
+4. No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional.
+5. Para cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento. Para cães e gatos colocados em famílias de acolhimento, o registo deve ser efetuado em nome da pessoa responsável pela família de acolhimento. Para cães e gatos detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, o registo deve ser efetuado em nome do dono ou da pessoa singular ou coletiva.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo a cães militares, policiais e aduaneiros.
+6. Em caso de colocação no mercado ou cedência ocasional e irregular por pessoa singular sem publicidade em linha, os requisitos de registo não se aplicam.
+7. Em caso de morte de um cão ou gato, o operador, dono do animal ou pessoa singular ou coletiva proprietária devem informar a base de dados nacional.
+8. Em caso de transponder ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato devem assegurar que o animal é reidentificado com um novo transponder e re-registado na base de dados nacional.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 17.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação, quando aplicável, e registo no SIAC, deve ser realizada:
+a) Relativamente aos cães, gatos e furões nascidos em alojamentos, até aos três meses de idade ou, em qualquer caso, antes da sua colocação no mercado;
+b) Relativamente aos cães, gatos e furões que entrem em alojamentos, nos termos dos artigos 12.º a 15.º, até trinta dias após a sua chegada ao alojamento ou, em qualquer caso, antes da data de colocação no mercado;
+c) Relativamente aos cães, gatos e furões detidos por pessoas singulares, exceto nos casos previstos nas alíneas anteriores, até aos três meses de idade ou, no caso de colocação no mercado, antes da data de colocação no mercado.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 53.º do Código do Animal (DL n.º 214/2013)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
+4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>n.ºs 1, 2 e 3 do art.º 5.º do DL n.º 82/2019, de 27 de junho</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
+2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
+3 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.</t>
+        </is>
+      </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>SIM - DL 276/2001 cobre amputações documentadas</t>
+          <t>O DL n.º 82/2019 (art.º 5.º) prevê prazo geral de 120 dias após o nascimento, sem distinguir o contexto de estabelecimento — prazo superior ao máximo de 3 meses do @regulamento, que exigirá redução. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA (Arts. 51-52)</t>
+          <t>O @codigo fixa prazo de identificação entre 3 e 6 meses, igualmente sem distinção entre nascimentos e entrada em estabelecimentos, ficando aquém da precisão exigida pelo @regulamento.</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>SIM - COBERTURA COMPLETA + EXPANSÃO</t>
+          <t>O @rgbeac aproxima-se dos prazos do @regulamento mas aplica-se apenas a cães, gatos e furões. Não prevê o prazo específico de 30 dias para animais que entram em estabelecimentos.</t>
         </is>
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>COBERTURA COMPLETA. Código do Animal (Arts. 51-52) implementa integralmente Art. 15.º. RGBEAC alinha substancialmente com Regulamento europeu. Sem divergências substanciais.</t>
+          <t>Necessidade de alteração: (1) reduzir prazo máximo de identificação de nascimentos para 3 meses; (2) criar prazo diferenciado de 30 dias para animais admitidos em estabelecimentos; (3) harmonizar prazos entre todos os diplomas nacionais.</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Correspondências completas - Cobertura legislativa adequada</t>
-        </is>
-      </c>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -674,14 +674,14 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>A breeding establishment where at most two litters per calendar year is produced for placing on the market shall only be subject to the obligations laid down in Article 5, Article 6(1) (1b), (1c) and (1d). Article 6a, Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15, Article 15a(1) and point 3 and 4.3 of Annex I.
-A shelter, where up to a total of 15 dogs or cats are kept at any given time, or any foster home shall only be subject to the obligations laid down in Article 5, Article 6(1), (1a), (1b), (1c), and 1(d), Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(a), (b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15 and point 4.3 of Annex I.</t>
+          <t>1 — A breeding establishment where at most two litters per calendar year is produced for placing on the market shall only be subject to the obligations laid down in Article 5, Article 6(1) (1b), (1c) and (1d), Article 6a, Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15, Article 15a(1) and point 3 and 4.3 of Annex I.
+2 — A shelter, where up to a total of 15 dogs or cats are kept at any given time, or any foster home shall only be subject to the obligations laid down in Article 5, Article 6(1), (1a), (1b), (1c), and (1d), Article 7, Article 8, Article 11(2), (3) and (3a), Article 12(3), (4) and (7), Article 13(2)(a), (b), (c) and (d), Article 14(2), (3), (4) and (5a), Article 15 and point 4.3 of Annex I.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (parágrafos 1, 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (parágrafos 2, 3 e 3a), artigo 12.º (parágrafos 3, 4 e 7), artigo 13.º (parágrafo 2, alíneas b, c e d), artigo 14.º (parágrafos 2, 3, 4 e 5a), artigo 15.º, artigo 15a (parágrafo 1) e ponto 3 e 4.3 do Anexo I.
-Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (parágrafos 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (parágrafos 2, 3 e 3a), artigo 12.º (parágrafos 3, 4 e 7), artigo 13.º (parágrafo 2, alíneas a, b, c e d), artigo 14.º (parágrafos 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>1 — Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
+2 — Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3504,6 +3504,127 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos Técnicos — Alimentação e Abeberamento</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO I, Ponto 1 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>1. Feeding and watering
+Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
+These requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+Each puppy or kitten shall be fed with colostrum during at least the first two days of its life and thereafter with milk from its mother or a lactating bitch or queen. If this is not possible, because she is ill or is otherwise unable to feed her offspring or not sufficient, the puppy or kitten shall be fed with a milk replacer designed for puppies and kittens with such feeding frequency as instructed by the producer of the replacer or by a veterinarian.
+All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination thereof to steadily gain bodyweight.
+Weaning shall be performed with gradual introduction of firm feed, in a process not shorter than 7 days and shall not be completed before 6 weeks of age for puppies and kittens alike.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1. Alimentação e abeberamento
+Os cães e gatos devem ser alimentados pelo menos duas vezes por dia. Os filhotes de cão e gato devem ser alimentados com maior frequência.
+Estes requisitos não se aplicam aos cães pastores de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino.
+Cada filhote de cão ou gato deve ser alimentado com colostro durante pelo menos os primeiros dois dias de vida e depois com leite da mãe ou de uma cadela ou gata lactante. Se tal não for possível, porque está doente ou incapaz de alimentar a ninhada ou se o leite for insuficiente, o filhote deve ser alimentado com um substituto de leite concebido para filhotes, com a frequência de alimentação instruída pelo produtor do substituto ou por um veterinário.
+Todos os filhotes de cão e gato ainda em aleitamento devem ser alimentados com leite, substituto de leite ou uma combinação dos dois, em quantidade suficiente para ganhar peso corporal de forma constante.
+O desmame deve ser realizado com introdução gradual de alimentos sólidos, num processo que não seja inferior a 7 dias e não deve ser concluído antes dos 6 semanas de idade para filhotes de cão e gato.</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Art.º 33.º, Arts. 38-40 do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 33.º - Alimentação
+1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a edad, raça, categoria, nível de atividade e estado de saúde.
+2 - Os animais devem receber alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.
+3 - As refeições devem ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos.
+5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Art.º 18.º (n.º 1), Art.º 46.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 18.º - Instalações
+n.º 1 - Os alojamentos que se destinem à reprodução, criação, manutenção ou venda de animais de companhia, devem possuir instalações individualizadas destinadas à armazenagem de alimentos e equipamento limpo e à lavagem e recolha de material.
+Artigo 46.º - Alimentação e abeberamento
+n.º 1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+n.º 2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+n.º 3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+n.º 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+n.º 5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+n.º 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+n.º 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 18.º (n.º 1), Art.º 46.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 18.º - Instalações
+n.º 1 - Os alojamentos que se destinem à reprodução, criação, manutenção ou venda de animais de companhia, devem possuir instalações individualizadas destinadas à armazenagem de alimentos e equipamento limpo e à lavagem e recolha de material.
+Artigo 46.º - Alimentação e abeberamento
+n.º 1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+n.º 2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+n.º 3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+n.º 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+n.º 5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+n.º 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+n.º 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+Português: Programa definido, alimentos com padrões de higiene, água potável sem restrição, proibição de restos.
+Regulamento: Idêntico + frequências específicas de alimentação por espécie (mínimo 2x/dia), requisitos de colostro/leite materno (2 dias), desmame gradual (7 dias, não antes 6 semanas).</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+O Código cobre programa alimentar, padrões de higiene, água potável, proibições de restos.
+Falta: Especificação de frequências (2x/dia), colostro, leite materno, desmame gradual.</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>CONVERGÊNCIA
+RGBEAC espelha integralmente os requisitos: programa definido, frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>Legislação portuguesa (Art. 46 do Código do Animal) cobre aspetos gerais de alimentação e higiene. RGBEAC e Regulamento (ANNEX I Point 1) complementam com especificidades: frequência de alimentação (mínimo 2x/dia), colostro durante mínimo 2 dias, desmame gradual (7 dias). Recomenda-se integração das especificidades do Regulamento no RGBEAC e legislação portuguesa.</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos mínimos de alimentação e abeberamento. Legislação portuguesa cobre aspetos gerais mas faltam especificidades sobre frequência mínima (2x/dia), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias). RGBEAC já incorpora estas especificidades. Recomenda-se harmonização definitiva.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -3518,21 +3518,21 @@
       <c r="C30" s="3" t="inlineStr">
         <is>
           <t>1. Feeding and watering
-Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
-These requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Each puppy or kitten shall be fed with colostrum during at least the first two days of its life and thereafter with milk from its mother or a lactating bitch or queen. If this is not possible, because she is ill or is otherwise unable to feed her offspring or not sufficient, the puppy or kitten shall be fed with a milk replacer designed for puppies and kittens with such feeding frequency as instructed by the producer of the replacer or by a veterinarian.
-All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination thereof to steadily gain bodyweight.
-Weaning shall be performed with gradual introduction of firm feed, in a process not shorter than 7 days and shall not be completed before 6 weeks of age for puppies and kittens alike.</t>
+1.1 Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
+1.2 These requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
+1.3 Each puppy or kitten shall be fed with colostrum during at least the first two days of its life and thereafter with milk from its mother or a lactating bitch or queen. If this is not possible, because she is ill or is otherwise unable to feed her offspring or not sufficient, the puppy or kitten shall be fed with a milk replacer designed for puppies and kittens with such feeding frequency as instructed by the producer of the replacer or by a veterinarian.
+1.4 All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination thereof to steadily gain bodyweight.
+1.5 Weaning shall be performed with gradual introduction of firm feed, in a process not shorter than 7 days and shall not be completed before 6 weeks of age for puppies and kittens alike.</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>1. Alimentação e abeberamento
-Os cães e gatos devem ser alimentados pelo menos duas vezes por dia. Os filhotes de cão e gato devem ser alimentados com maior frequência.
-Estes requisitos não se aplicam aos cães pastores de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino.
-Cada filhote de cão ou gato deve ser alimentado com colostro durante pelo menos os primeiros dois dias de vida e depois com leite da mãe ou de uma cadela ou gata lactante. Se tal não for possível, porque está doente ou incapaz de alimentar a ninhada ou se o leite for insuficiente, o filhote deve ser alimentado com um substituto de leite concebido para filhotes, com a frequência de alimentação instruída pelo produtor do substituto ou por um veterinário.
-Todos os filhotes de cão e gato ainda em aleitamento devem ser alimentados com leite, substituto de leite ou uma combinação dos dois, em quantidade suficiente para ganhar peso corporal de forma constante.
-O desmame deve ser realizado com introdução gradual de alimentos sólidos, num processo que não seja inferior a 7 dias e não deve ser concluído antes dos 6 semanas de idade para filhotes de cão e gato.</t>
+1.1 Os cães e gatos devem ser alimentados pelo menos duas vezes por dia. Os filhotes de cão e gato devem ser alimentados com maior frequência.
+1.2 Estes requisitos não se aplicam aos cães pastores de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para guarda ou treino.
+1.3 Cada filhote de cão ou gato deve ser alimentado com colostro durante pelo menos os primeiros dois dias de vida e depois com leite da mãe ou de uma cadela ou gata lactante. Se tal não for possível, porque está doente ou incapaz de alimentar a ninhada ou se o leite for insuficiente, o filhote deve ser alimentado com um substituto de leite concebido para filhotes, com a frequência de alimentação instruída pelo produtor do substituto ou por um veterinário.
+1.4 Todos os filhotes de cão e gato ainda em aleitamento devem ser alimentados com leite, substituto de leite ou uma combinação dos dois, em quantidade suficiente para ganhar peso corporal de forma constante.
+1.5 O desmame deve ser realizado com introdução gradual de alimentos sólidos, num processo que não seja inferior a 7 dias e não deve ser concluído antes dos 6 semanas de idade para filhotes de cão e gato.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3572,46 +3572,36 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Art.º 18.º (n.º 1), Art.º 46.º do Código do Animal (DL 214/2013)</t>
+          <t>Sem disposições específicas sobre alimentação nos diplomas de @legislacao</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>Artigo 18.º - Instalações
-n.º 1 - Os alojamentos que se destinem à reprodução, criação, manutenção ou venda de animais de companhia, devem possuir instalações individualizadas destinadas à armazenagem de alimentos e equipamento limpo e à lavagem e recolha de material.
-Artigo 46.º - Alimentação e abeberamento
-n.º 1 - A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
-n.º 2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
-n.º 3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
-n.º 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
-n.º 5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-n.º 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
-n.º 7 - É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
+          <t>Não se encontram disposições específicas sobre alimentação e abeberamento nos diplomas vigentes do grupo @legislacao (DL 276/2001, DL 82/2019, Lei 27/2016, Portarias). Estes diplomas tratam fundamentalmente de identificação, registo, rastreabilidade e centros de recolha. As disposições técnicas sobre bem-estar, incluindo alimentação, encontram-se no Código do Animal (DL 214/2013, @codigo).</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
+          <t>NÃO APLICÁVEL
+Não existem disposições específicas sobre alimentação e abeberamento na legislação vigente de @legislacao. As disposições técnicas estão concentradas no Código do Animal (@codigo).</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
           <t>PARCIAL CONVERGÊNCIA
-Português: Programa definido, alimentos com padrões de higiene, água potável sem restrição, proibição de restos.
-Regulamento: Idêntico + frequências específicas de alimentação por espécie (mínimo 2x/dia), requisitos de colostro/leite materno (2 dias), desmame gradual (7 dias, não antes 6 semanas).</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>PARCIAL CONVERGÊNCIA
-O Código cobre programa alimentar, padrões de higiene, água potável, proibições de restos.
-Falta: Especificação de frequências (2x/dia), colostro, leite materno, desmame gradual.</t>
+O Código do Animal (DL 214/2013, Art. 46) cobre: programa alimentar, padrões de higiene, água potável, proibições de restos.
+FALTAM especificidades do Regulamento: frequência mínima (2x/dia), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>CONVERGÊNCIA
-RGBEAC espelha integralmente os requisitos: programa definido, frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
+          <t>CONVERGÊNCIA COMPLETA
+RGBEAC (Art. 33) espelha integralmente os requisitos do Regulamento: programa definido, frequências, padrões de higiene, água potável, refrigeração, alimentos saudáveis e adequados.</t>
         </is>
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>Legislação portuguesa (Art. 46 do Código do Animal) cobre aspetos gerais de alimentação e higiene. RGBEAC e Regulamento (ANNEX I Point 1) complementam com especificidades: frequência de alimentação (mínimo 2x/dia), colostro durante mínimo 2 dias, desmame gradual (7 dias). Recomenda-se integração das especificidades do Regulamento no RGBEAC e legislação portuguesa.</t>
+          <t>ANNEX I, Ponto 1 do Regulamento especifica requisitos técnicos mínimos: frequência 2x/dia, colostro (2 dias), leite materno, desmame gradual (7 dias). Código do Animal (Art. 46) cobre aspetos gerais (programa, higiene, água) mas não detalha frequências, colostro, desmame. RGBEAC já incorpora todas as especificidades. Recomenda-se alteração do Código do Animal e/ou Lei complementar para integrar especificidades técnicas do Regulamento.</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -3621,7 +3611,7 @@
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos mínimos de alimentação e abeberamento. Legislação portuguesa cobre aspetos gerais mas faltam especificidades sobre frequência mínima (2x/dia), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias). RGBEAC já incorpora estas especificidades. Recomenda-se harmonização definitiva.</t>
+          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos de alimentação. Legislação portuguesa vigente (@legislacao) não contém disposições específicas. Código do Animal (Art. 46) cobre aspetos gerais. RGBEAC já implementa especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa.</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -3572,18 +3572,29 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Sem disposições específicas sobre alimentação nos diplomas de @legislacao</t>
+          <t>Art.º 12.º, Art.º 49.º do DL n.º 276-2001, de 17 de outubro; Art.º 5.º, n.º 5 da Portaria n.º 146/2017</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>Não se encontram disposições específicas sobre alimentação e abeberamento nos diplomas vigentes do grupo @legislacao (DL 276/2001, DL 82/2019, Lei 27/2016, Portarias). Estes diplomas tratam fundamentalmente de identificação, registo, rastreabilidade e centros de recolha. As disposições técnicas sobre bem-estar, incluindo alimentação, encontram-se no Código do Animal (DL 214/2013, @codigo).</t>
+          <t>Artigo 12.º — Alimentação e abeberamento
+1 - Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+2 - As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie e de forma a manter, tanto quanto possível, aspetos do seu comportamento alimentar natural.
+3 - O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+5 - Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+[dim]
+Artigo 49.º — Alimentação e abeberamento
+Deve ser mantida comida suficiente e de boa qualidade e água potável, a administrar de acordo com a prescrição do médico veterinário.
+[/dim]</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>NÃO APLICÁVEL
-Não existem disposições específicas sobre alimentação e abeberamento na legislação vigente de @legislacao. As disposições técnicas estão concentradas no Código do Animal (@codigo).</t>
+          <t>PARCIAL CONVERGÊNCIA
+DL 276/2001 (Art. 12.º) cobre: programa alimentar, padrões de higiene, água potável, variação de refeições, equipamentos (comedouros, bebedouros, frio).
+FALTAM especificidades do Regulamento: frequência mínima (2x/dia para cães e gatos), colostro (mínimo 2 dias), leite materno, desmame gradual (mínimo 7 dias, não antes 6 semanas), disposições específicas para filhotes.</t>
         </is>
       </c>
       <c r="L30" s="9" t="inlineStr">
@@ -3601,7 +3612,7 @@
       </c>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 1 do Regulamento especifica requisitos técnicos mínimos: frequência 2x/dia, colostro (2 dias), leite materno, desmame gradual (7 dias). Código do Animal (Art. 46) cobre aspetos gerais (programa, higiene, água) mas não detalha frequências, colostro, desmame. RGBEAC já incorpora todas as especificidades. Recomenda-se alteração do Código do Animal e/ou Lei complementar para integrar especificidades técnicas do Regulamento.</t>
+          <t>ANNEX I, Ponto 1 do Regulamento especifica requisitos técnicos mínimos: frequência 2x/dia, colostro (2 dias), leite materno, desmame gradual (7 dias). DL 276/2001 (Art. 12.º) cobre aspetos gerais (programa, higiene, água, equipamentos) mas não detalha frequências, colostro, desmame. Código do Animal (Art. 46) é convergente com DL 276/2001. RGBEAC já incorpora todas as especificidades. Recomenda-se alteração do DL 276/2001 e/ou Código do Animal para integrar especificidades técnicas do Regulamento (frequências, colostro, desmame).</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -3611,7 +3622,7 @@
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos de alimentação. Legislação portuguesa vigente (@legislacao) não contém disposições específicas. Código do Animal (Art. 46) cobre aspetos gerais. RGBEAC já implementa especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa.</t>
+          <t>ANNEX I, Ponto 1 estabelece requisitos técnicos de alimentação. DL 276/2001 (Art. 12.º) e Código do Animal (Art. 46) cobrem aspetos gerais. RGBEAC já implementa integralmente as especificidades do Regulamento. Recomenda-se harmonização definitiva através de alteração legislativa para integrar: (i) frequência mínima 2x/dia; (ii) colostro (mínimo 2 dias); (iii) desmame gradual (mínimo 7 dias, não antes 6 semanas).</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3870,6 +3870,131 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Requisitos Técnicos — Necessidades Comportamentais (Behavioral Needs)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ANEXO I, Ponto 4 do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>4. Behavioural needs
+4.1 Operators shall ensure that measures are taken to meet the behavioural needs of dogs or cats in accordance with point 4 of Annex I.
+4.2 Operators shall not keep dogs or cats in areas restraining their natural movements, except for specific procedures or treatments: physical examinations; individual identification; collection of samples and vaccinations; grooming/hygienic/health/reproductive procedures; medical and surgical treatment or rehabilitation.
+4.3 Tethering for more than 1 hour shall be prohibited, except for medical treatment or participation in shows, exhibitions and competitions.
+4.4 Operators shall ensure that conditions are in place to allow dogs or cats to express social non-harmful behaviours, species-specific behaviours and the possibility to experience positive emotions.
+4.5 Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall document their strategy for such socialisation.
+4.6 Operators shall ensure that enrichment is provided and accessible to all dogs or cats, creating a stimulating environment, enabling species-specific behaviour and reducing their frustration.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>4. Necessidades Comportamentais
+4.1 Os operadores devem assegurar que são implementadas medidas para atender as necessidades comportamentais dos cães e gatos.
+4.2 Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto para procedimentos específicos ou tratamentos: exames físicos; identificação individual; colheita de amostras e vacinações; procedimentos de higiene/saúde/reprodução; tratamento médico, cirúrgico ou reabilitação.
+4.3 A amarração por mais de 1 hora é proibida, exceto durante tratamento médico ou participação em espetáculos, exposições e competições.
+4.4 Os operadores devem assegurar que existem condições que permitem aos cães ou gatos expressar comportamentos sociais não prejudiciais, comportamentos específicos da espécie e a possibilidade de experimentar emoções positivas.
+4.5 Os operadores devem assegurar que os cães ou gatos podem socializar. Os operadores de estabelecimentos de criação devem documentar a sua estratégia de socialização.
+4.6 Os operadores devem assegurar que enriquecimento é fornecido e acessível a todos os cães ou gatos, criando um ambiente estimulante, permitindo comportamento específico da espécie e reduzindo frustração.</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Arts. 10.º, 12.º, 47.º, 52.º do RGBEAC (proposta, jun. 2025)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Artigo 10.º — Obrigações especiais dos detentores
+1.a) Assegurar o bem-estar: [...] atenção, supervisão, controlo, exercício físico e estímulo mental; liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes [...]; contato social adequado.
+Artigo 12.º — Proibições gerais
+f) Acorrentá-los ou mantê-los em espaços confinados que não garantam bem-estar; permitido temporariamente com trela à porta [...] sob supervisão.
+h) Mantê-los predominantemente isolados de humanos ou outros animais.
+y) Utilizar coleiras elétricas, choques, estranguladoras ou outros métodos aversivos/punitivos.
+Artigo 47.º — Condições dos alojamentos
+4 — Enriquecimento ambiental complexo incluindo materiais, substrato, ninhos, buracos, banhos, brinquedos.
+6 — Acesso diário a exercício: mínimo 2 vezes/dia, 30 minutos.
+Artigo 52.º — Maneio
+7 — Plano de socialização e enriquecimento ambiental obrigatório (alojamentos cães/gatos).</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Arts. 13.º, 18.º do Código do Animal (DL 214/2013)</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Artigo 13.º — Condições dos alojamentos
+1 — Espaço adequado permitindo: a) exercício físico adequado; b) fuga e refúgio.
+2 — Esconderijos para proteção.
+5 — Materiais e equipamento estimulando comportamentos naturais: substrato, cama, ninhos, ramos, buracos, banhos, outros.
+Artigo 18.º — Instalações
+6 — Estruturas e objetos para enriquecimento: prateleiras, poleiros, ninhos, esconderijos, material para entretenimento, área de recreio coberta ou descoberta (cães/gatos).</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Art.º 8.º do DL n.º 276-2001</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Artigo 8.º — Condições dos alojamentos
+1 — Espaço adequado permitindo: a) exercício físico adequado; b) fuga e refúgio.
+2 — Esconderijos para proteção.
+5 — Instalações equipadas com materiais e equipamento estimulando comportamentos naturais: substrato, cama, ninhos, ramos, buracos, banhos, outros.
+[Nota: Disposições genéricas sobre bem-estar. OMISSO: amarração, isolamento, métodos aversivos, plano de socialização, duração mínima de exercício, estímulo mental, emoções positivas]</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+DL 276/2001 cobre: espaço, exercício físico, enriquecimento ambiental básico.
+FALTAM: (i) restrição amarração &gt;1 hora; (ii) proibição isolamento; (iii) proibição métodos aversivos (coleiras elétricas); (iv) duração mínima exercício diário; (v) plano socialização documentado; (vi) estímulo mental explícito; (vii) emoções positivas.</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>PARCIAL CONVERGÊNCIA
+Código do Animal: equivalente ao DL 276/2001, com enriquecimento mais específico (área de recreio dedicada).
+FALTAM: (i) amarração; (ii) isolamento; (iii) métodos aversivos; (iv) duração mínima; (v) plano socialização; (vi) estímulo mental; (vii) emoções positivas.</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>CONVERGÊNCIA SIGNIFICATIVA
+✅ Proíbe acorrentamento permanente (com amarração temporária supervisionada permitida)
+✅ Proíbe isolamento (Art. 12.h)
+✅ Proíbe coleiras elétricas e métodos aversivos (Art. 12.y)
+✅ Menciona 'exercício físico e estímulo mental' (Art. 10.a)
+✅ Plano de socialização documentado obrigatório (Art. 52.7)
+✅ Enriquecimento com 'brinquedos' incluso (Art. 47.4)
+✅ Acesso diário a exercício: 2x dia, 30 min (Art. 47.6)
+⚠️ Conceito 'emoções positivas' não explícito (apenas em Regulamento)</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 4 (Behavioral Needs) estabelece: (i) liberdade movimento (exceto procedimentos); (ii) amarração &lt;1 hora; (iii) comportamentos sociais/específicos; (iv) socialização documentada (breeding); (v) enriquecimento acessível; (vi) estímulo reduzindo frustração; (vii) emoções positivas. @RGBEAC implementa 6 de 7 requisitos. DL 276/2001 é genérico. Recomenda-se validar implementação rigorosa do RGBEAC (sobretudo plano socialização, duração exercício, métodos aversivos) e considerar adicionar conceito 'emoções positivas'.</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>Sim - Consolidação (principalmente validar RGBEAC)</t>
+        </is>
+      </c>
+      <c r="P33" s="11" t="inlineStr">
+        <is>
+          <t>ANNEX I, Ponto 4 (Behavioral Needs) cobre bem-estar comportamental. @RGBEAC já implementa a maioria dos requisitos do Regulamento. DL 276/2001 genérico, omisso em aspetos críticos. INOVAÇÕES-CHAVE DO @RGBEAC vs. LEGISLAÇÃO ANTERIOR: (i) proibição expressa acorrentamento permanente (omisso); (ii) proibição isolamento (omisso); (iii) proibição coleiras elétricas/métodos aversivos (omisso); (iv) plano socialização documentado (omisso); (v) acesso diário exercício 2x/dia 30min (omisso); (vi) inclusão 'brinquedos' em enriquecimento (omisso). Validar implementação: confirmar que acorrentamento temporário é realmente 'ocasional', que planos de socialização são documentados, que coleiras aversivas são efetivamente proibidas em mercado nacional.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -3923,8 +3923,8 @@
 Artigo 47.º — Condições dos alojamentos
 4 — As instalações devem providenciar um enriquecimento ambiental complexo e estimulante [...] incluindo [...] postes de arranhadura [a confirmar], esconderijos, prateleiras, [...] brinquedos e outros adequados ao fim em vista.
 SUBSECÇÃO 4.3 (SEPARAÇÃO):
-Artigo 68.º — Transação de cães e gatos
-[Procura necessária para obter texto verbatim sobre idade mínima de separação]</t>
+Artigo 70.º — Reprodução de cães e gatos
+5 — As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -3942,7 +3942,10 @@
 Artigo 18.º(6) — Instalações
 6 — Os alojamentos devem possuir estruturas e objetos [...] nomeadamente prateleiras, poleiros, ninhos, esconderijos e material para entretenimento.
 SUBSECÇÃO 4.3 (SEPARAÇÃO):
-[Procura necessária para obter artigos sobre idade mínima de separação]</t>
+Artigo 23.º — Condições particulares para a manutenção de cães e gatos
+2 — Os cães e gatos só podem ser expostos nos locais de venda a partir da oitava semana de idade e devem encontrar-se identificados eletronicamente em nome do criador.
+Artigo 82.º — Venda em feiras e mercados
+2 — [...] devendo os animais: [...] Ter idade superior a oito semanas.</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -3958,43 +3961,43 @@
 Artigo 8.º(5) — Condições dos alojamentos
 5 — As instalações devem ser equipadas [...] com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente [...] ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
 SUBSECÇÃO 4.3 (SEPARAÇÃO):
-[Procura necessária para obter artigos sobre idade mínima de separação]</t>
+[DL 276/2001 não contém disposições específicas sobre idade mínima de separação de mãe ou exposição em locais de venda]</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso completamente
 4.2 ENRIQUECIMENTO: PARCIAL — cobre genérico (substrato, ninhos, buracos) mas omite 'postes de arranhadura' (crítico para gatos)
-4.3 SEPARAÇÃO: [Procura necessária]</t>
+4.3 SEPARAÇÃO: DIVERGÊNCIA TOTAL — DL 276/2001 omisso; Regulamento exige mínimo 8-12 semanas, DL não especifica</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código menciona contato social mas sem detalhe (idade, frequência, documentação)
 4.2 ENRIQUECIMENTO: PARCIAL — menciona prateleiras/poleiros mas omite 'postes de arranhadura' (essencial para gatos)
-4.3 SEPARAÇÃO: [Procura necessária]</t>
+4.3 SEPARAÇÃO: DIVERGÊNCIA SIGNIFICATIVA — Código exige 8 semanas (Arts. 23.º, 82.º) para EXPOSIÇÃO em venda; Regulamento exige 8 semanas (puppies, kittens abrigos) e 12 semanas (kittens breeding) para SEPARAÇÃO de mãe — conceitos distintos</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
           <t>4.1 SOCIALIZAÇÃO: CONVERGÊNCIA PARCIAL — exige 'plano de socialização' (Art. 52.7) mas sem especificação de: idade 3 semanas, frequência diária, tipos de contato, separação de animais agressivos
 4.2 ENRIQUECIMENTO: CONVERGÊNCIA SIGNIFICATIVA — menciona enriquecimento 'complexo', inclui 'brinquedos', mas omite 'postes de arranhadura' (essencial para gatos)
-4.3 SEPARAÇÃO: [Procura necessária em Art. 68.º e relacionados]</t>
+4.3 SEPARAÇÃO: CONVERGÊNCIA SIGNIFICATIVA — @RGBEAC (Art. 70.5) exige 10 semanas (cães) / 12 semanas (gatos) com desmame gradual (MAIS RESTRITIVO que Regulamento 8-12 semanas)</t>
         </is>
       </c>
       <c r="N33" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas; (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras (específico para gatos); (iii) 4.3 Separação — idades mínimas (8 semanas puppies, 8/12 semanas kittens). Legislação nacional é omissa (4.1), parcial (4.2), incompleta (4.3). @RGBEAC aproxima-se mas com gaps críticos (socialização sem detalhe; falta postes de arranhadura para gatos; separação a confirmar).</t>
+          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding). DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2. Código implementa 8 semanas para exposição (4.3) mas não separação maternal. @RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Sim - Harmonização parcial + procura de legislação em 4.3</t>
+          <t>Sim - Harmonização fundamental (4.1) + clarificação (4.2 postes arranhadura) + ajuste (4.3 separação vs. exposição)</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 contém 3 subsecções de bem-estar comportamental. 4.1 SOCIALIZAÇÃO: COMPLETAMENTE NOVO — @RGBEAC menciona 'plano' (Art. 52.7) mas sem detalhe do Regulamento. Recomenda-se adicionar: (i) idade mínima 3 semanas; (ii) frequência mínima (diária); (iii) tipos de contato (congêneres, humanos, outras espécies); (iv) documentação com registos; (v) disposição sobre separação por agressividade. 4.2 ENRIQUECIMENTO: CRÍTICO — @RGBEAC omite 'postes de arranhadura' (elemento essencial para bem-estar felino). Recomenda-se adicionar explicitamente: 'número suficiente de postes de arranhadura'. 4.3 SEPARAÇÃO: Procura necessária em DL 276/2001, Código do Animal, @RGBEAC para verificar se há artigos sobre idade mínima de venda/transação.</t>
+          <t>ANNEX I, Ponto 4 contém 3 subsecções críticas de bem-estar comportamental. 4.1 SOCIALIZAÇÃO: COMPLETAMENTE NOVO — DL 276/2001 omisso. @RGBEAC menciona 'plano' (Art. 52.7) mas sem detalhe do Regulamento (3 semanas, frequência diária, tipos contato, documentação). IMPLEMENTAR: idade, frequência, contatos, registos, separação agressivos. 4.2 ENRIQUECIMENTO: CRÍTICO PARA GATOS — DL 276/2001 genérico, omite 'postes de arranhadura'. Código do Animal menciona 'prateleiras, poleiros' mas não especifica 'postes de arranhadura'. @RGBEAC omite completamente. IMPLEMENTAR: 'número suficiente de postes de arranhadura' (essencial bem-estar felino). 4.3 SEPARAÇÃO: DIVERGÊNCIA CONCEITUAL — Regulamento estabelece idade separação de MÃE (8-12 semanas); Código do Animal refere EXPOSIÇÃO em venda (8 semanas); @RGBEAC mais restritivo (10-12 semanas separação com desmame gradual). CLARIFICAR: 4.3 refere separação maternal, não comercialização.</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -4032,62 +4032,81 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Arts. [a procurar] do RGBEAC (proposta, jun. 2025)</t>
+          <t>Capítulo II — Sistema de Informação de Animais de Companhia (SIAC) do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>[Procura em curso — aguardando resultado de análise de legislação nacional sobre requisitos técnicos de microchip, transponder, ISO standards, registo em base de dados]</t>
+          <t>O RGBEAC prevê a Lista Nacional de Animais de Companhia como instrumento de proteção, integrando o Sistema de Informação de Animais de Companhia (SIAC), anteriormente previsto no DL n.º 82/2019, de 27 de junho. O registo passa a ser obrigatório para TODOS os animais de companhia como medida de valorização, prevenção do abandono e melhoria do acompanhamento e proteção. [Detalhe técnico sobre ISO standards pendente de análise do texto completo do Capítulo II do RGBEAC]</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Arts. [a procurar] do Código do Animal (DL 214/2013)</t>
+          <t>Arts. 53.º a 59.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>[Procura em curso — aguardando resultado de análise sobre identificação eletrónica, microchip, registo em base de dados, requisitos técnicos]</t>
+          <t>Artigo 53.º — Identificação e registo na base de dados
+1 - Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
+4 - Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
+5 - A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.
+6 - Para efeito de registo na base de dados, só podem ser aplicados os microchips que estejam em conformidade com as normas ISO 11784.
+7 - A aplicação do microchip apenas pode ser efetuada por médico veterinário, enfermeiro ou outro técnico habilitado.
+Artigo 55.º — Base de dados
+1 - Toda a informação resultante do registo do animal é coligida numa aplicação informática nacional.
+2 - A DGAV detém, define e coordena o acesso à base de dados.</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Arts. [a procurar] do DL n.º 276-2001</t>
+          <t>DL n.º 276-2001</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>[Procura em curso — aguardando resultado de análise sobre identificação, microchip, base de dados nacional, requisitos técnicos ISO]</t>
+          <t>[DL 276/2001 — REVOGADO PELO CÓDIGO DO ANIMAL (DL 214/2013)]
+Nota: DL 276/2001 não contém artigos operacionais específicos sobre identificação eletrónica, microchip ou registo em base de dados. O regime de identificação e registo foi consolidado integralmente no Código do Animal (DL 214/2013, Arts. 53-59).</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>[A ser preenchido com resultado de procura]</t>
+          <t>REVOGAÇÃO TOTAL
+DL 276/2001 foi revogado pelo Código do Animal (DL 214/2013). Sem disposições sobre ISO standards ou requisitos técnicos de microchip.</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>[A ser preenchido com resultado de procura]</t>
+          <t>CONVERGÊNCIA SIGNIFICATIVA
+✅ Código exige conformidade ISO 11784 (Art. 53.6)
+✅ Identificação eletrónica por microchip (Art. 53.5)
+✅ Registo em base de dados nacional (Arts. 55-59)
+⚠️ Código refere ISO 11784; Regulamento exige ISO 11784/11785 + 24631-1 (mais restritivo)
+⚠️ Prazos diferentes: Código 3-6 meses; Regulamento 3 meses (proprietários), 30 dias (operadores)</t>
         </is>
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>[A ser preenchido com resultado de procura]</t>
+          <t>CONVERGÊNCIA PARCIAL
+✅ Integra Sistema de Informação de Animais de Companhia (SIAC) — mais robusto que Código
+✅ Registo obrigatório para TODOS os animais de companhia (não apenas cães e gatos comerciais)
+⚠️ CRÍTICO: Requisitos técnicos ISO standards NÃO MENCIONADOS explicitamente no resumo disponível
+⚠️ Prazos: A confirmar em texto completo do Capítulo II</t>
         </is>
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>ANNEX II (Identification and Registration) estabelece requisitos técnicos de transponders/microchips: número individual não-repetível, conformidade ISO 3166 (país), ISO 11784/11785 (radiofrequência), ISO 24631-1 (avaliação). [Análise completa após procura na legislação nacional]</t>
+          <t>ANNEX II (Identification and Registration) estabelece quatro requisitos técnicos de transponders: (i) número individual não-repetível; (ii) ISO 3166 (país); (iii) ISO 11784/11785 (radiofrequência); (iv) ISO 24631-1 (avaliação). Código do Animal implementa ISO 11784 mas não ISO 11785 ou 24631-1 (menos restritivo). @RGBEAC promove SIAC (mais robusto) mas não especifica ISO standards. Recomenda-se: validar conformidade portuguesa com ISO 11785 e 24631-1 (inovações do Regulamento).</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>[A confirmar após análise completa]</t>
+          <t>Sim - Clarificação técnica (ISO 11785, 24631-1) + harmonização prazos</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
         <is>
-          <t>ANNEX II especifica requisitos TÉCNICOS de transponders usados para identificação de cães e gatos (Articles 17, 21). IMPORTANTE: Este ANNEX é sobre ESPECIFICAÇÕES TÉCNICAS (ISO standards), não sobre procedimentos administrativos de registo. [Procura em curso para verificar conformidade legislação portuguesa com ISO 11784, 11785, 24631-1]</t>
+          <t>ANNEX II especifica requisitos TÉCNICOS de transponders/microchips (não procedimentos administrativos). IMPORTANTE DIVERGÊNCIA: Código do Animal exige ISO 11784; Regulamento exige ISO 11784/11785 + 24631-1. ISO 11785: estabelece padrão de radiofrequência para microchips. ISO 24631-1: metodologia de avaliação de conformidade. Ambas são NOVIDADES do Regulamento não presentes na legislação portuguesa anterior. @RGBEAC menciona SIAC (Sistema de Informação) mas não detalha requisitos técnicos ISO. Recomenda-se: (i) validar conformidade microchips portugueses com ISO 11785 e 24631-1; (ii) atualizar requisitos de aprovação/certificação de equipamentos; (iii) harmonizar prazos de identificação (3 meses vs. 30 dias por tipo operador).</t>
         </is>
       </c>
     </row>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -4060,13 +4060,14 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>DL n.º 276-2001</t>
+          <t>DL n.º 82/2019, de 27 de junho (LEGISLAÇÃO VIGENTE) + DL n.º 276-2001</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>[DL 276/2001 — REVOGADO PELO CÓDIGO DO ANIMAL (DL 214/2013)]
-Nota: DL 276/2001 não contém artigos operacionais específicos sobre identificação eletrónica, microchip ou registo em base de dados. O regime de identificação e registo foi consolidado integralmente no Código do Animal (DL 214/2013, Arts. 53-59).</t>
+          <t>[DL n.º 82/2019, de 27 de junho — LEGISLAÇÃO VIGENTE RELEVANTE]
+Este diploma contém o regime atual de identificação e registo de animais de companhia, incluindo Sistema de Informação de Animais de Companhia (SIAC). REMETE PARA: Análise detalhada online de DL 82/2019 consolidado (dre.pt ou eur-lex) — CRÍTICO para comparação com ANNEX II do Regulamento.
+[DL 276/2001 — legislação anterior, sem disposições operacionais específicas sobre identificação eletrónica]</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1159,15 +1159,111 @@
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Aprovação de Estabelecimentos de Criação</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Art.º 10.º do Regulamento 2023/0447</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
+2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
+3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
+(a)	the name, contact details and, where available, the URL of the website of the establishment;
+(b)	the address of the establishment;
+(c)	the name of the operator;
+(d)	the species and, if relevant, the breeds related to the establishment activities approved;
+(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1.	Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
+2.	A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
+3.	A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
+(a)	o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
+(b)	a morada do estabelecimento;
+(c)	o nome do operador;
+(d)	a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
+(e)	o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Conceito novo de ‘aprovação’ com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Não implementado</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Não implementado</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Artigo completamente novo no Regulamento. Introduz aprovação formal de criadores com limiar numérico.</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>Análise e correspondência nacional pendente de complementação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Detenção Responsável e Informação</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Art.º 11.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>1.	Operators shall provide to the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
 2.	The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
@@ -1176,7 +1272,7 @@
 Where the information on the animal’s health history is set out in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde, alojamento e necessidades comportamentais, bem como informação sobre a sua saúde.
 1a. A informação escrita sobre a saúde do cão ou gato referida no parágrafo anterior deve incluir pelo menos:
@@ -1185,23 +1281,23 @@
 Caso a informação sobre a saúde do cão ou gato esteja documentada num documento exigido sob o Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Art.º 8.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1 — O detentor do animal de companhia deve possuir informação sobre as obrigações inerentes à sua detenção, incluindo direitos e responsabilidades, normas de bem-estar, cuidados de saúde, comportamento, necessidades específicas da espécie/raça, duração de vida esperada, custos de manutenção, e proibição de abandono.
 2 — Os comerciantes devem fornecer por escrito ao adquirente informação completa antes da transferência do animal, incluindo identidade e dados de contacto do comerciante, dados de identificação do animal, cuidados de saúde e estado de vacinação, e certificado de origem ou de compatibilidade quando aplicável.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Art.º 57.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>1 — O detentor do animal deve ter acesso a informação sobre:
 a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
@@ -1213,56 +1309,56 @@
 2 — Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Art.º 20.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>1 — O proprietário ou detentor de animal de companhia deve ter acesso a informação adequada sobre as suas obrigações relativas ao bem-estar do animal.
 2 — Os detentores de animais de companhia que os comercializem devem fornecer informação ao adquirente sobre o estado de saúde do animal e vacinas efetuadas.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 20.º) é genérico e não especifica a forma escrita nem detalhes de conteúdo. O @regulamento exige informação escrita sobre necessidades específicas de bem-estar (alimentação, cuidados, saúde, alojamento, comportamento) e condiciona a transferência à transmissão dessa informação.</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 57.º) exige informação escrita mas com âmbito mais amplo (duração de vida, custos) do que o @regulamento, que se foca especificamente em bem-estar e saúde.</t>
         </is>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.º 8.º) aproxima-se do conteúdo do @regulamento, exigindo informação escrita antes da transferência, incluindo dados de saúde e vacinação, mas ainda sem o enfoque específico em bem-estar comportamental.</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Necessidade de alteração: (1) formalizar requisito de informação escrita como condição de transferência de animal; (2) especificar conteúdo obrigatório sobre bem-estar, saúde e necessidades comportamentais; (3) harmonizar entre @codigo e @rgbeac quanto a âmbito e forma.</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Competências de Cuidadores e Bem-Estar Animal</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Art.º 12.º do Regulamento 2023/0447</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1.	Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
 (a)	an understanding of the animals’ biological behaviour and their physiological and ethological needs;
@@ -1276,7 +1372,7 @@
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>1. Os cuidadores de animais, com exceção de voluntários em abrigos e estagiários sob a responsabilidade de um cuidador competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do seu comportamento biológico e das suas necessidades fisiológicas e etológicas;
@@ -1288,12 +1384,12 @@
 3. A Comissão estabelecerá, por meio de atos de execução, os requisitos mínimos relativos à educação formal, formação ou experiência profissional para adquirir as competências referidas no parágrafo 2 e para os cursos de formação referidos no parágrafo 2a. Esses atos de execução serão adotados de acordo com o procedimento de exame referido no artigo 24.º. O ato de execução relativo aos cursos de formação referidos no parágrafo 2a deve ser adotado por [3 anos da data de entrada em vigor do Regulamento].</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Art.ºs 69.º, 84.º e 90.º do RGBEAC (proposta, jun. 2025)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Artigo 69.º — Formação
 A reprodução, criação, manutenção, venda ou treino de animais de companhia depende de aprovação em formação sobre detenção responsável de animais de companhia, bem como sobre as necessidades fisiológicas e etológicas específicas da espécie animal em causa, ministrada pelo ICNF, I.P. ou entidades por este certificadas.
@@ -1303,23 +1399,23 @@
 O pessoal auxiliar deve possuir os conhecimentos e a experiência adequada, o qual fica, contudo, sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Art.º 19.º do Código do Animal (DL n.º 214/2013)</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Artigo 19.º — Pessoal auxiliar
 Os alojamentos devem dispor de pessoal auxiliar que possua os conhecimentos e a aptidão necessária para assegurar os cuidados adequados aos animais, o qual fica sob a orientação do médico veterinário responsável.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Art.º 13.º do DL n.º 276/2001, de 17 de outubro</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º — Maneio
 1 — A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
@@ -1327,128 +1423,32 @@
 3 — Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>O DL n.º 276/2001 (art.º 13.º) exige pessoal 'técnico competente' com 'formação teórica e prática específica' e 'inspeção diária', mas não detalha competências concretas. O @regulamento especifica 4 competências estruturadas (comportamento biológico, reconhecimento de sofrimento, maneio e bem-estar, conhecimento de obrigações) e exige documentação de educação/formação/experiência.</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>O @codigo (art.º 19.º) é genérico: exige apenas 'conhecimentos e aptidão necessária' sob orientação do médico veterinário responsável. Não detalha competências concretas nem exigências de formação formal.</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>O @rgbeac (art.ºs 69.º, 84.º, 90.º) aproxima-se mais do @regulamento: exige 'conhecimentos e experiência adequados', menciona 'necessidades fisiológicas e etológicas', exige formação certificada pelo ICNF. Lacuna: não detalha as 4 competências específicas do @regulamento (reconhecimento de sofrimento, condicionamento operante, etc.).</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Alinhamento parcial do @rgbeac com @regulamento. Para @codigo e @legislacao, necessidade de: (1) detalhar as 4 competências específicas (comportamento, reconhecimento de sofrimento, maneio positivo, conhecimento de obrigações); (2) exigir documentação formal de educação/formação/experiência; (3) requerer que operador designe formador responsável que transfira conhecimento; (4) implementar requisitos mínimos de formação via regulamento delegado.</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
-    </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Aprovação de Estabelecimentos de Criação</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Art.º 10.º do Regulamento 2023/0447</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
-2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
-3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
-(a)	the name, contact details and, where available, the URL of the website of the establishment;
-(b)	the address of the establishment;
-(c)	the name of the operator;
-(d)	the species and, if relevant, the breeds related to the establishment activities approved;
-(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>1.	Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
-2.	The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
-3.	The competent authority shall maintain a publicly available list including the following information for each approved establishment:
-(a)	the name, contact details and, where available, the URL of the website of the establishment;
-(b)	the address of the establishment;
-(c)	the name of the operator;
-(d)	the species and, if relevant, the breeds related to the establishment activities approved;
-(e)	the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>Conceito novo de 'aprovação' com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>Não implementado</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>Não implementado</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Artigo completamente novo no Regulamento. Introduz aprovação formal de criadores com limiar numérico.</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>Análise e correspondência nacional pendente de complementação.</t>
-        </is>
-      </c>
+      <c r="P9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -4217,7 +4217,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 17 e 21)</t>
+          <t>ANEXO II do Regulamento 2023/0447 (conforme Articles 20 e 26)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ANEXO III do Regulamento 2023/0447 (conforme Article 20)</t>
+          <t>ANEXO III do Regulamento 2023/0447 (conforme Article 24)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -2695,7 +2695,9 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Disponível no documento Regulamento - Primeira Versão portuguesa.docx</t>
+          <t>1.	As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
+2.	As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
+3.	A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -874,9 +874,9 @@
 1b. Os operadores não devem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, incluindo através de participação em atividades que possam resultar em crueldade, abuso ou maus-tratos, aos cães ou gatos criados ou mantidos pelo operador.
 1c. Os operadores não devem abandonar cães ou gatos.
 1d. Os operadores que estejam prestes a cessar as atividades do seu estabelecimento devem assegurar a reintegração dos cães ou gatos mantidos aí, quer através da assunção da posse do animal de companhia, quer através da transferência da responsabilidade ou propriedade dos cães e gatos para outros operadores ou adquirentes.
-2. Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 9.º.
+2. Os operadores devem assegurar que os cães ou gatos são tratados por um número adequado de cuidadores de animais e de modo a satisfazer as necessidades de bem-estar dos cães ou gatos mantidos nos seus estabelecimentos e que têm as competências exigidas no artigo 12.º.
 2a. Os operadores devem assegurar o bem-estar dos cães ou gatos sob a sua responsabilidade através da monitorização de indicadores baseados no comportamento e aparência física, e através da adoção de ações com base nos resultados de tal monitorização.
-2b. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 23.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
+2b. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento através do estabelecimento de indicadores baseados no bem-estar dos animais relativos ao comportamento e aparência física e dos métodos da sua medição.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -972,15 +972,16 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
-3. A Comissão tem competência para adotar, tendo em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, bem como os impactos sociais e económicos, atos delegados em conformidade com o artigo 23.º que complementem este Regulamento:
-(a) definindo características dos genótipos a que se refere o parágrafo 1, que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) definindo traços conformacionais excessivos a que se refere o parágrafo 2 do presente artigo, que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-5. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.</t>
+          <t>1.	Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2.	Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem traços conformacionais excessivos que conduzam a um risco elevado de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por traço conformacional excessivo, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem um traço conformacional excessivo.
+3.	A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
+(a)	características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b)	traços conformacionais excessivos a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+	Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
+	Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+4.	São proibidos na gestão da reprodução de cães e gatos:
+(a)	o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b)	o cruzamento para produção de híbridos.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1474,7 +1475,7 @@
           <t>Os operadores devem:
 (a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
 (b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
-Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 23.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1945,7 +1946,7 @@
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
-2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 12.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
 a) exames físicos;
 b) identificação individual de cães ou gatos e leitura da informação de identificação;
 c) recolha de amostras e vacinações;
@@ -2152,7 +2153,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Art.º 15a do Regulamento 2023/0447</t>
+          <t>Art.º 19.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2353,7 +2354,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Art.º 17a do Regulamento 2023/0447</t>
+          <t>Art.º 21.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2394,12 +2395,12 @@
 "Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
 2. Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no primeiro parágrafo ou uma redação diferente com significado equivalente.
 3. Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve:
-a) Fornecer ao adquirente prova de identificação e registo do cão ou gato em conformidade com o artigo 17.º;
+a) Fornecer ao adquirente prova de identificação e registo do cão ou gato em conformidade com o artigo 20.º;
 b) Fornecer ao adquirente as seguintes informações sobre o cão ou gato: espécie, sexo, data e país de nascimento, e, quando relevante, raça;
 c) No caso de anúncio online, utilizar o sistema referido no parágrafo 6 para gerar um token único de verificação e disponibilizar o token e a ligação web para o sistema referido no parágrafo 6 no anúncio.
 4. Os adquirentes podem verificar a autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online através do sistema referido no parágrafo 6.
 5. Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a identificação e o registo do cão ou gato através de uma ligação web para o sistema referido no parágrafo 6.
-6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 19.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
+6. A Comissão garante que um sistema de verificação online que realiza controlos automatizados da autenticidade da identificação, registo e propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está disponível publicamente gratuitamente e gera o token único de verificação referido no parágrafo 3, alínea c).</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2474,7 +2475,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Art.º 18 do Regulamento 2023/0447</t>
+          <t>Art.º 22.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2489,9 +2490,9 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1. Para efeitos do artigo 9.º, as autoridades competentes são responsáveis por:
+          <t>1. Para efeitos do artigo 12.º, as autoridades competentes são responsáveis por:
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
-b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 9.º, parágrafo 3;
+b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 12.º, parágrafo 3;
 ba) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
 2. As autoridades competentes podem delegar a tarefa referida na alínea ba).
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Art.º 19 do Regulamento 2023/0447</t>
+          <t>Art.º 23.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2597,7 +2598,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 17.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
+          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com os artigos 20.º (parágrafos 1 e 2) e 21.º (parágrafo 4 e segundo parágrafo do parágrafo 4a).
 1a. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
 2. Os Estados-Membros asseguram que as suas bases de dados referidas no parágrafo 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no parágrafo 3, alínea b), de modo a assegurar a sua interoperabilidade, permitindo que a identificação de um cão ou gato possa ser autenticada e rastreada em toda a União.
 2a. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos definido no parágrafo 3, alínea b). A Comissão pode confiar o desenvolvimento, manutenção e funcionamento dessa base de dados de índice a uma entidade independente, após um processo de seleção pública.</t>
@@ -2683,7 +2684,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Art.º 20 do Regulamento 2023/0447</t>
+          <t>Art.º 24.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2771,7 +2772,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Art.º 20a do Regulamento 2023/0447</t>
+          <t>Art.º 25.º do Regulamento 2023/0447</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2793,11 +2794,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>As autoridades competentes dos Estados-Membros devem ser controladoras no sentido do Regulamento (UE) 2016/679 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 7, Artigo 7a do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de inspeção oficial.
-A Comissão deve ser controladora no sentido do Regulamento (UE) 2018/1725 em relação ao tratamento de dados pessoais recolhidos de acordo com o Artigo 17a (6), Artigo 19 (2a) e o terceiro parágrafo do Artigo 21(4a) do presente Regulamento, bem como no âmbito do Artigo 19(1) do presente Regulamento quando utilizados para efeitos de conformidade com o Artigo 108 do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
-Fica proibido a qualquer pessoa com acesso aos dados pessoais mencionados no primeiro e segundo parágrafos divulgar quaisquer dados pessoais, cuja notícia foi adquirida no exercício das suas funções ou de forma incidental a tal exercício.
-Os Estados-Membros e a Comissão devem adotar todas as medidas apropriadas para fazer face aos incumprimentos dessa proibição.
-[... redução para brevidade - ver regulamento completo para texto integral]</t>
+          <t>1.	As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
+	A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
+	É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
+	Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
+(a)	controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
+(b)	o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
+2.	Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
+(a)	no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
+(b)	no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
+(c)	no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
+(d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3025,7 +3032,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 23.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
+          <t>1. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
 a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
 b) Requisitos de abastecimento de água e alimentação e processo de desmame;
 c) Gamas de temperatura;
@@ -3143,11 +3150,11 @@
       <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1 — O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
-2 — O poder de adotar atos delegados referido no artigo 6.º, n.º 4, no artigo 10.º, n.º 2, e no artigo 22.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
-3 — A delegação de poderes referida no artigo 6.º, n.º 4, no artigo 10.º, n.º 2, e no artigo 22.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+2 — O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
+3 — A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
 4 — Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
 5 — Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
-6 — Os atos delegados adotados nos termos do artigo 6.º, n.º 4, do artigo 10.º, n.º 2, e do artigo 22.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
+6 — Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3407,7 +3414,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1 — Com base nos relatórios recebidos em conformidade com o artigo 20.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+          <t>1 — Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
 2 — Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
 a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
 b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -841,7 +841,11 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr"/>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="120" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -943,7 +947,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr"/>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1044,7 +1052,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr"/>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="120" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1160,7 +1172,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="120" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1351,7 +1367,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="120" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1454,7 +1474,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1554,7 +1578,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1785,7 +1813,7 @@
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>Sim - Portaria complementar com especificações técnicas</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
@@ -1918,7 +1946,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -2024,7 +2056,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Sim - Regulamentação específica sobre métodos de treino</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
@@ -2352,7 +2384,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>(espaço para anotações da reunião)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="120" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2480,7 +2516,7 @@
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>Sim - Sistema de verificação online com token único</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P18" s="11" t="inlineStr">
@@ -2785,7 +2821,7 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>Sim - Ajuste de periodicidade e conformidade com Annex III EU</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
@@ -4060,7 +4096,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>Sim - Alteração fundamental obrigatória</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
@@ -4191,7 +4227,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>Sim - Harmonização fundamental (4.1) + clarificação (4.2 postes arranhadura) + ajuste (4.3 separação vs. exposição)</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
@@ -4301,7 +4337,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>Sim - Clarificação técnica (ISO 11785, 24631-1) + harmonização prazos</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
@@ -4378,7 +4414,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>[dim]Decreto-Lei n.º 82/2019 de 27 de junho — Bem-Estar de Animais de Companhia
+          <t>Decreto-Lei n.º 82/2019 de 27 de junho — Bem-Estar de Animais de Companhia
 Artigo 2.º — Âmbito de aplicação — Aplicável a cães, gatos e furões detidos para fins não comerciais.
 Artigo 3.º — Obrigações de registo — Proprietários de cães e gatos devem proceder ao registo no SIAC com identificação eletrónica obrigatória.
 Artigo 4.º — Identificação eletrónica — Via aplicação subcutânea de microchip (ISO 11784 e 11785).
@@ -4447,7 +4483,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>Sim — Estabelecer sistema de aprovação, suspensão e revogação de estabelecimentos de criação + codificar famílias de acolhimento</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -674,14 +674,14 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
-A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
+          <t>1. A breeding establishment where no more than two litters per calendar year are produced for placing on the market shall be subject to only the obligations laid down in Article 6, Article 7(1) (2), (3) and (4). Article 8, Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18, Article 19(1) and points 3 and 4.3 of Annex I.
+2. A shelter in which not more than a combined total of 15 dogs or cats are kept at any given time, or any foster home shall be subject to only the obligations laid down in Article 6, Article 7(1), (2), (3), (4), and(5), Article 9, Article 11, Article 14(2), (3) and (4), Article 15(3), (4) and (8), Article 16(1). points (a), (b), (c) and (d), Article 17(2), (3), (5) and (7), Article 18 and point 4.3 of Annex I.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
-Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
+2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -743,21 +743,21 @@
       <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Operators shall apply the following general welfare principles with respect to dogs or cats bred or kept in their establishment:
-dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
-dogs and cats are kept in a physical environment that is appropriate and regularly cleaned, that is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and that is big enough to prevent overcrowding and to afford them ease of movement;
-dogs and cats are kept safe, clean and in good health, and diseases, injuries, and pain due, in particular, to management, handling practices and breeding practices, are prevented;
-dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
+(a) dogs and cats are provided with water and feed of a quality and quantity that affords them appropriate nutrition and hydration;
+(b) dogs and cats are kept in a physical environment that is appropriate and regularly cleaned, that is secure and comfortable, especially in terms of space, air quality, temperature, light, protection against adverse climatic conditions and that is big enough to prevent overcrowding and to afford them ease of movement;
+(c) dogs and cats are kept safe, clean and in good health, and diseases, injuries, and pain due, in particular, to management, handling practices and breeding practices, are prevented;
+(d) dogs and cats are kept in an environment that enables them to exhibit species-specific and social non-harmful behaviour, and to establish a positive relationship with human beings;
 (e)	dogs and cats are kept in such a way as to optimise their mental state by preventing or reducing negative stimuli in duration and intensity, as well as by maximising opportunities for positive stimuli in duration and intensity, preventing the development of abnormal repetitive or other behaviours indicative of negative animal welfare, and taking into consideration the individual animal’s needs in the domains referred to in points (a) to (d).</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
-os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+(a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -818,28 +818,28 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
-In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
+          <t>1. Operators shall be responsible for the welfare of dogs and cats kept in establishments under their responsibility and control, and shall be responsible for minimising any risks to the welfare of those animals.
+2. In the case of foster homes, the responsibility shall lie with the operator on whose behalf dogs or cats are kept. Such operators shall not place more than a combined total of five dogs or cats or one litter with or without mother in a foster home at any given time and shall provide the foster family with adequate information on the animal welfare obligations as well as the individual needs of the dogs or cats, and shall ensure that the relevant obligations laid down in this Regulation are complied with in foster homes.
 The Member State in which the foster home is located may allow a greater number of dogs, cats or litters to be placed in the foster home, provided that the premises of the foster home have sufficient space, including outdoor space, and that the number of animal carers in the foster home is sufficient, to ensure the welfare of the dogs or cats.
-Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including by making them participate in activities likely to result in cruelty to or abuse or mistreatment of the dogs or cats bred or kept by the operator.
-Operators shall not abandon the dogs or cats bred or kept by them.
-Before operators cease activities at an establishment, they shall ensure that the dogs or cats kept there are rehomed, either by taking up the pet ownership themselves or by transferring the responsibility for, or the ownership of, the dogs and cats to other operators or acquirers.
-Operators shall ensure that dogs and cats are handled by a number of animal carers sufficient to meet the welfare needs of dogs or cats kept in their establishments, and that those carers have the competences required under Article 12.
-Operators shall ensure the welfare of the dogs or cats for which they are responsible by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
-The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
+3. Operators shall not subject any dog or cat to cruelty, abuse or mistreatment, including by making them participate in activities likely to result in cruelty to or abuse or mistreatment of the dogs or cats bred or kept by the operator.
+4. Operators shall not abandon the dogs or cats bred or kept by them.
+5. Before operators cease activities at an establishment, they shall ensure that the dogs or cats kept there are rehomed, either by taking up the pet ownership themselves or by transferring the responsibility for, or the ownership of, the dogs and cats to other operators or acquirers.
+6. Operators shall ensure that dogs and cats are handled by a number of animal carers sufficient to meet the welfare needs of dogs or cats kept in their establishments, and that those carers have the competences required under Article 12.
+7. Operators shall ensure the welfare of the dogs or cats for which they are responsible by monitoring animal-based indicators concerning behaviour and physical appearance, and by taking actions based on the results of such monitoring.
+8. The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by laying down the animal-based indicators concerning behaviour and physical appearance that operators are to use for monitoring, in accordance with paragraph 7 of this Article, and the methods by which operators are to measure them.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
-No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
+          <t>1. Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
+2. No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
 O Estado-Membro em que se situa o lar de acolhimento pode autorizar um maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações do lar de acolhimento disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais no lar de acolhimento seja suficiente para garantir o bem-estar dos cães e gatos.
-Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
-Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
-Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
-Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
-Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
-A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
+3. Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
+4. Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
+5. Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
+6. Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
+7. Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
+8. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -856,71 +856,71 @@
 c) não sofram dor, lesão física ou doença;
 d) possam expressar padrões normais de comportamento; e
 e) não sejam colocados em situações que lhes provoquem stresse, medo ou ansiedade injustificados.
-2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes. 
+2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
 3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro
-Artigo 9.º - Obrigações gerais  
-Todos os cidadãos têm o dever de notificar às autoridades competentes os casos de suspeita de infração à legislação de proteção do bem-estar dos animais de companhia de que tenham conhecimento.  
-Em caso de lesão de um animal de companhia em acidente de viação, é obrigatória a comunicação imediata deste facto às autoridades competentes por parte do condutor, ao qual, salvaguardada a sua integridade física, compete também socorrer o animal.  
-Os animais doentes, feridos ou em perigo devem, na medida do possível, ser socorridos por quem os encontrar, sem prejuízo de notificação às autoridades competentes.  
-O alojamento no quadro de respostas sociais de pessoas em situação de vulnerabilidade, incluindo as casas de abrigo de vítimas de violência doméstica e os albergues de pessoas em situação de sem-abrigo, devem, sempre que possível, assegurar o acolhimento dos animais de companhia das pessoas que acolhem.  
-Os planos de emergência e proteção civil devem incluir medidas para a proteção e resgate de animais em situação de emergência.  
-Artigo 10.º - Obrigações especiais dos detentores de animais de companhia  
-1 – O detentor do animal de companhia deve:  
-a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:  
-i) Atenção, supervisão, controlo, exercício físico e estímulo mental;  
-ii) Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;  
-iii) Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;  
-iv) Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes e, no caso de animais que, pelas características da espécie ou comportamento, tenham de ser mantidos em gaiolas, aquários, terrários, canis, espaços vedados ou outros, sendo obrigatório que os mesmos disponham de espaço e enriquecimento ambiental adequados para garantir o seu bem-estar e a expressão dos seus comportamentos naturais, obedecendo aos requisitos fixados na portaria prevista no artigo 58.º do presente decreto-lei;  
-v) Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;  
-vi) Contato social adequado a cada espécie, de acordo com a sua idade e atividade.  
-b) Vigiar o animal, de modo a evitar que este cause danos a pessoas, outros animais ou coisas;  
-c) Educar o animal com recurso a métodos de reforço positivo visando a sua vinculação e integração positivas no espaço familiar e no meio ambiente;  
-d) Identificar e registar o animal, nos termos do presente decreto-lei;  
-e) Transportar o animal de forma adequada e de acordo com a legislação em vigor, garantindo a segurança rodoviária e o bem-estar e conforto do animal durante o transporte, inclusive em veículos particulares;  
-f) Proporcionar ao animal toda e qualquer intervenção sanitária declarada como obrigatória por parte autoridade sanitária nacional, bem como qualquer outro tipo de tratamento veterinário preventivo, paliativo ou curativo indispensável ao seu bem-estar;  
-g) Comunicar o desaparecimento ou morte do animal de companhia, qualquer alteração nos dados do animal de companhia ou do proprietário, nos prazos prescritos, bem como manter atualizado o SIAC e o DIAC, nos termos previstos no presente decreto-lei;  
-h) Colocar à disposição das autoridades competentes a documentação necessária e obrigatória em cada caso, colaborando para a obtenção das informações solicitadas a todo o momento e atendendo, de forma geral, a todas as recomendações que a autoridade competente emita;  
-i) Recolher os excrementos do animal de companhia de quaisquer locais de acesso público.  
-2 – É obrigatório o uso por todos os cães e gatos que circulem em espaços públicos de coleira ou peitoral, no qual deve constar a morada ou contacto telefónico do detentor.  
-3 – Em espaços públicos, os cães e gatos devem ser conduzidos à trela ou, no caso dos cães, exceto durante a participação em provas e treinos ou, tratando-se de animais utilizados na caça, durante os atos venatórios, cães-pastor enquanto guardam os rebanhos, ou cães pertencentes às Forças Armadas e às Forças de Segurança e Serviços de Segurança e cães de busca e salvamento, quando em serviço.  
-4 – As autarquias locais devem prever espaços públicos, ainda que condicionados a determinados horários, para a permanência e circulação de cães ou gatos sem a obrigatoriedade de utilização de trela ou açaimo.  
-5 – As autarquias locais estabelecem o regime aplicável à circulação e permanência de animais de companhia em “Praias de Uso Canino”: zonas de praia não classificadas como “águas balneares”, nas quais são disponibilizados equipamentos e materiais de recolha de dejetos, bem como normas a cumprir pelos respetivos titulares do animal de companhia.  
-6 – Os cães e gatos não registados como animais reprodutores em nome de criadores com alojamentos autorizados para o efeito devem ser esterilizados antes dos seis meses de idade, desde entrada em vigor deste Decreto-Lei.  
-7 – Todos os cães e gatos, com mais de 6 meses, que não se encontrem registados como animais reprodutores em nome de criadores com alojamento licenciados para o efeito, devem ser esterilizados, caso não existam contraindicações médico veterinárias, no prazo de 2 anos, desde a entrada em vigor do presente Decreto-Lei.  
-Artigo 11.º - Obrigações especiais dos detentores relativas ao alojamento  
-A determinação do número de animais permitidos em alojamento que não seja destinado ao exercício da atividade de exploração para hospedagem, nos termos do presente decreto-lei, seja em prédios urbanos, mistos ou rústicos, é competência do respetivo município e freguesia, que terão acesso à base de dados de apoio ao Sistema de Informação de Animais de Companhia, para monitorização e controlo do número de animais mantidos em cada local. O Município e a Junta de Freguesia, excecionalmente, podem autorizar a permanência de um número maior de animais em cada alojamento.  
-Qualquer norma restritiva em relação ao disposto no número anterior, estipulada em título constitutivo da propriedade horizontal, em contrato de arrendamento, em regulamento do condomínio ou outro instrumento, deve considerar-se não escrita, exceto no respeitante a alojamento em partes comuns e sem prejuízo do disposto no número seguinte.  
-Nas situações em que a permanência do animal de companhia é fonte de prejuízo para o sossego, a salubridade ou a segurança dos restantes moradores, qualquer morador pode intimar o proprietário a tomar providências ao seu alcance no sentido de as fazer cessar.
-Em caso de não cumprimento do disposto no presente artigo, as câmaras municipais, após vistoria conjunta do delegado de saúde e do médico veterinário municipal, notificam o detentor para retirar os animais para um local adequado, que poderá ser um centro de bem-estar animal, no prazo estabelecido por aquelas entidades, caso o detentor não opte por outro destino que reúna as condições estabelecidas pelo presente decreto-lei.
+Artigo 9.º - Obrigações gerais
+1. Todos os cidadãos têm o dever de notificar às autoridades competentes os casos de suspeita de infração à legislação de proteção do bem-estar dos animais de companhia de que tenham conhecimento.
+2. Em caso de lesão de um animal de companhia em acidente de viação, é obrigatória a comunicação imediata deste facto às autoridades competentes por parte do condutor, ao qual, salvaguardada a sua integridade física, compete também socorrer o animal.
+3. Os animais doentes, feridos ou em perigo devem, na medida do possível, ser socorridos por quem os encontrar, sem prejuízo de notificação às autoridades competentes.
+4. O alojamento no quadro de respostas sociais de pessoas em situação de vulnerabilidade, incluindo as casas de abrigo de vítimas de violência doméstica e os albergues de pessoas em situação de sem-abrigo, devem, sempre que possível, assegurar o acolhimento dos animais de companhia das pessoas que acolhem.
+5. Os planos de emergência e proteção civil devem incluir medidas para a proteção e resgate de animais em situação de emergência.
+Artigo 10.º - Obrigações especiais dos detentores de animais de companhia
+1 – O detentor do animal de companhia deve:
+a) Assegurar o bem-estar do animal, de acordo com sua espécie, raça, idade e necessidades físicas e etológicas, proporcionando-lhe:
+i) Atenção, supervisão, controlo, exercício físico e estímulo mental;
+ii) Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável;
+iii) Condições higiossanitárias que atendam, no mínimo, ao estabelecido no presente decreto-lei e na demais legislação aplicável;
+iv) Liberdade de movimento, sendo proibidos todos os sistemas de contenção permanentes e, no caso de animais que, pelas características da espécie ou comportamento, tenham de ser mantidos em gaiolas, aquários, terrários, canis, espaços vedados ou outros, sendo obrigatório que os mesmos disponham de espaço e enriquecimento ambiental adequados para garantir o seu bem-estar e a expressão dos seus comportamentos naturais, obedecendo aos requisitos fixados na portaria prevista no artigo 58.º do presente decreto-lei;
+v) Abrigo adequado, em termos de tamanho e qualidade, com vista a proteger de condições atmosféricas adversas, incluindo frio, chuva, sol ou calor excessivos, com cama seca, limpa e confortável;
+vi) Contato social adequado a cada espécie, de acordo com a sua idade e atividade.
+b) Vigiar o animal, de modo a evitar que este cause danos a pessoas, outros animais ou coisas;
+c) Educar o animal com recurso a métodos de reforço positivo visando a sua vinculação e integração positivas no espaço familiar e no meio ambiente;
+d) Identificar e registar o animal, nos termos do presente decreto-lei;
+e) Transportar o animal de forma adequada e de acordo com a legislação em vigor, garantindo a segurança rodoviária e o bem-estar e conforto do animal durante o transporte, inclusive em veículos particulares;
+f) Proporcionar ao animal toda e qualquer intervenção sanitária declarada como obrigatória por parte autoridade sanitária nacional, bem como qualquer outro tipo de tratamento veterinário preventivo, paliativo ou curativo indispensável ao seu bem-estar;
+g) Comunicar o desaparecimento ou morte do animal de companhia, qualquer alteração nos dados do animal de companhia ou do proprietário, nos prazos prescritos, bem como manter atualizado o SIAC e o DIAC, nos termos previstos no presente decreto-lei;
+h) Colocar à disposição das autoridades competentes a documentação necessária e obrigatória em cada caso, colaborando para a obtenção das informações solicitadas a todo o momento e atendendo, de forma geral, a todas as recomendações que a autoridade competente emita;
+i) Recolher os excrementos do animal de companhia de quaisquer locais de acesso público.
+2 – É obrigatório o uso por todos os cães e gatos que circulem em espaços públicos de coleira ou peitoral, no qual deve constar a morada ou contacto telefónico do detentor.
+3 – Em espaços públicos, os cães e gatos devem ser conduzidos à trela ou, no caso dos cães, exceto durante a participação em provas e treinos ou, tratando-se de animais utilizados na caça, durante os atos venatórios, cães-pastor enquanto guardam os rebanhos, ou cães pertencentes às Forças Armadas e às Forças de Segurança e Serviços de Segurança e cães de busca e salvamento, quando em serviço.
+4 – As autarquias locais devem prever espaços públicos, ainda que condicionados a determinados horários, para a permanência e circulação de cães ou gatos sem a obrigatoriedade de utilização de trela ou açaimo.
+5 – As autarquias locais estabelecem o regime aplicável à circulação e permanência de animais de companhia em “Praias de Uso Canino”: zonas de praia não classificadas como “águas balneares”, nas quais são disponibilizados equipamentos e materiais de recolha de dejetos, bem como normas a cumprir pelos respetivos titulares do animal de companhia.
+6 – Os cães e gatos não registados como animais reprodutores em nome de criadores com alojamentos autorizados para o efeito devem ser esterilizados antes dos seis meses de idade, desde entrada em vigor deste Decreto-Lei.
+7 – Todos os cães e gatos, com mais de 6 meses, que não se encontrem registados como animais reprodutores em nome de criadores com alojamento licenciados para o efeito, devem ser esterilizados, caso não existam contraindicações médico veterinárias, no prazo de 2 anos, desde a entrada em vigor do presente Decreto-Lei.
+Artigo 11.º - Obrigações especiais dos detentores relativas ao alojamento
+1. A determinação do número de animais permitidos em alojamento que não seja destinado ao exercício da atividade de exploração para hospedagem, nos termos do presente decreto-lei, seja em prédios urbanos, mistos ou rústicos, é competência do respetivo município e freguesia, que terão acesso à base de dados de apoio ao Sistema de Informação de Animais de Companhia, para monitorização e controlo do número de animais mantidos em cada local. O Município e a Junta de Freguesia, excecionalmente, podem autorizar a permanência de um número maior de animais em cada alojamento.
+2. Qualquer norma restritiva em relação ao disposto no número anterior, estipulada em título constitutivo da propriedade horizontal, em contrato de arrendamento, em regulamento do condomínio ou outro instrumento, deve considerar-se não escrita, exceto no respeitante a alojamento em partes comuns e sem prejuízo do disposto no número seguinte.
+3. Nas situações em que a permanência do animal de companhia é fonte de prejuízo para o sossego, a salubridade ou a segurança dos restantes moradores, qualquer morador pode intimar o proprietário a tomar providências ao seu alcance no sentido de as fazer cessar.
+4. Em caso de não cumprimento do disposto no presente artigo, as câmaras municipais, após vistoria conjunta do delegado de saúde e do médico veterinário municipal, notificam o detentor para retirar os animais para um local adequado, que poderá ser um centro de bem-estar animal, no prazo estabelecido por aquelas entidades, caso o detentor não opte por outro destino que reúna as condições estabelecidas pelo presente decreto-lei.
 Artigo 12.º- Proibições gerais
 1 – São interditas quaisquer práticas que violem o bem-estar dos animais de companhia, em especial as seguintes:
-Causar a sua morte, em violação do que está previsto no presente decreto-lei para a eutanásia ;
-Sujeitá-los a qualquer prática que lhes possa causar sofrimento, dano, stresse ou angústia, por ação ou omissão, salvo nas situações legalmente previstas;
-Sujeitá-los a abuso sexual ou práticas sexuais, bem como captar ou disseminar, por qualquer forma, imagens de contacto sexual entre pessoas e animais;
-Deter, comercializar, alojar, produzir, distribuir, importar, exportar, divulgar, exibir, ceder, disseminar ou disponibilizar, a qualquer título ou por qualquer meio, material audiovisual retratando a sua sujeição a contacto sexual ou a atos de abuso ou violência.
-Abandoná-los;
-Acorrentá-los ou mantê-los em espaços confinados, entre os quais varandas, caves, armazéns e outros, que não garantam o seu bem-estar, sendo permitido prendê-los temporariamente com trela à porta de locais que não permitam a entrada de animais ou durante atividades ao ar livre, sob supervisão humana e desde que não sejam expostos a fatores que ponham em causa o seu bem-estar.
-Mantê-los em veículos estacionados  sem ventilação e temperatura adequadas.
-Mantê-los predominantemente isolados de humanos ou de outros animais apropriados à espécie;
-Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais;
-Doá-los como prémio, recompensa ou no âmbito de sorteios ou promoções;
-Vendê-los ou registá-los a menores de dezoito anos ou a pessoas incapazes do exercício de diretos, sem a autorização do respetivo representante legal;
-Vendê-los ou transacioná-los sem estarem registados no SIAC;
-Vendê-los através da Internet;
-Utilizá-los para atividades de venda ambulante;
-Criá-los ou vendê-los sem as autorizações e os registos legalmente previstos, bem como publicitar qualquer prestação de serviço ou venda sem o número de registo do alojamento;
-Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
-Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
-Utilizá-los ou mantê-los em estabelecimentos de ensino ou formação, sem prejuízo dos animais de experimentação científica ou de atividades educativas assistidas por animais, tais como para fins de adoção, terapêuticos ou de sensibilização para o bem-estar animal; 
-Utilizá-los em eventos, confrontos entre animais, ou outras atividades que envolvam crueldade ou tratamento humilhante, maus-tratos, sofrimento ou morte, ou coloquem em risco a sua saúde e bem-estar;
-Utilizá-los em corridas de cães, com ou sem isco, com fins competitivos ou recreativos;
-Utilizá-los em eventos que não estejam devidamente licenciados e autorizados;
-Educá-los ou treiná-los com recurso a métodos aversivos, punitivos ou violentos, suscetíveis de causar danos físicos, angústia, stresse ou medo aos animais ou que visem estimular a sua agressividade ou fazê-los trabalhar de forma a exceder as suas forças ou capacidades naturais, prejudicando a sua saúde ou bem-estar;
-Mantê-los em vitrines expostas ao público; 
-Vender cães, gatos ou furões senão por criadores comerciais em alojamentos autorizados para o efeito;
-Utilizá-los em carrosséis, atrações de feiras, circos, exposições itinerantes, números com animais e manifestações similares;  
-Levá-los amarrados a veículos motorizados em movimento;
-Utilizar, deter ou comercializar qualquer meio que tenha como propósito influenciar o comportamento do animal através de métodos aversivos, violentos ou estímulos punitivos, tais como coleiras elétricas, de choques, estranguladoras ou com bicos, açaimos fechados ou que dificultem a respiração do animal;
+a) Causar a sua morte, em violação do que está previsto no presente decreto-lei para a eutanásia ;
+b) Sujeitá-los a qualquer prática que lhes possa causar sofrimento, dano, stresse ou angústia, por ação ou omissão, salvo nas situações legalmente previstas;
+c) Sujeitá-los a abuso sexual ou práticas sexuais, bem como captar ou disseminar, por qualquer forma, imagens de contacto sexual entre pessoas e animais;
+d) Deter, comercializar, alojar, produzir, distribuir, importar, exportar, divulgar, exibir, ceder, disseminar ou disponibilizar, a qualquer título ou por qualquer meio, material audiovisual retratando a sua sujeição a contacto sexual ou a atos de abuso ou violência.
+e) Abandoná-los;
+f) Acorrentá-los ou mantê-los em espaços confinados, entre os quais varandas, caves, armazéns e outros, que não garantam o seu bem-estar, sendo permitido prendê-los temporariamente com trela à porta de locais que não permitam a entrada de animais ou durante atividades ao ar livre, sob supervisão humana e desde que não sejam expostos a fatores que ponham em causa o seu bem-estar.
+g) Mantê-los em veículos estacionados  sem ventilação e temperatura adequadas.
+h) Mantê-los predominantemente isolados de humanos ou de outros animais apropriados à espécie;
+i) Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais;
+j) Doá-los como prémio, recompensa ou no âmbito de sorteios ou promoções;
+k) Vendê-los ou registá-los a menores de dezoito anos ou a pessoas incapazes do exercício de diretos, sem a autorização do respetivo representante legal;
+l) Vendê-los ou transacioná-los sem estarem registados no SIAC;
+m) Vendê-los através da Internet;
+n) Utilizá-los para atividades de venda ambulante;
+o) Criá-los ou vendê-los sem as autorizações e os registos legalmente previstos, bem como publicitar qualquer prestação de serviço ou venda sem o número de registo do alojamento;
+p) Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
+q) Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
+r) Utilizá-los ou mantê-los em estabelecimentos de ensino ou formação, sem prejuízo dos animais de experimentação científica ou de atividades educativas assistidas por animais, tais como para fins de adoção, terapêuticos ou de sensibilização para o bem-estar animal;
+s) Utilizá-los em eventos, confrontos entre animais, ou outras atividades que envolvam crueldade ou tratamento humilhante, maus-tratos, sofrimento ou morte, ou coloquem em risco a sua saúde e bem-estar;
+t) Utilizá-los em corridas de cães, com ou sem isco, com fins competitivos ou recreativos;
+u) Utilizá-los em eventos que não estejam devidamente licenciados e autorizados;
+v) Educá-los ou treiná-los com recurso a métodos aversivos, punitivos ou violentos, suscetíveis de causar danos físicos, angústia, stresse ou medo aos animais ou que visem estimular a sua agressividade ou fazê-los trabalhar de forma a exceder as suas forças ou capacidades naturais, prejudicando a sua saúde ou bem-estar;
+w) Mantê-los em vitrines expostas ao público;
+x) Vender cães, gatos ou furões senão por criadores comerciais em alojamentos autorizados para o efeito;
+y) Utilizá-los em carrosséis, atrações de feiras, circos, exposições itinerantes, números com animais e manifestações similares;
+z) Levá-los amarrados a veículos motorizados em movimento;
+aa) Utilizar, deter ou comercializar qualquer meio que tenha como propósito influenciar o comportamento do animal através de métodos aversivos, violentos ou estímulos punitivos, tais como coleiras elétricas, de choques, estranguladoras ou com bicos, açaimos fechados ou que dificultem a respiração do animal;
 z) Usá-los para a promoção ou concretização de sacrifício ritual de animais de companhia;
 aa) Consumi-los, usar ou comercializar a sua carne, pele, pelo ou qualquer parte do seu corpo, excetuando-se as utilizações autorizadas para fins experimentais ou científicos;
 bb) Utilizá-los para a prática de mendicidade, sem prejuízo do direito das pessoas sem-abrigo se fazerem acompanhar dos seus animais de companhia, salvaguardado o seu bem-estar.</t>
@@ -1014,46 +1014,46 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
-Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
-The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by:
-defining characteristics of the genotypes referred to in paragraph 1 that are to be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
-defining excessive conformational traits referred to in paragraph 2 of this Article that are to be excluded from reproduction, the methods for their assessment and the record keeping requirements.
-When adopting those delegated acts, the Commission shall take into account the scientific opinion of the European Food Safety Authority (EFSA), as well as any social and economic impacts of those delegated acts.
-The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
-The following shall be prohibited when managing the reproduction of dogs and cats:
-breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
-breeding for the purpose of producing hybrids.
+          <t>1. Operators of breeding establishments shall ensure that their breeding strategies minimise the risk of producing dogs or cats with genotypes associated with effects detrimental to the health and welfare of those animals.
+2. Operators of breeding establishments shall not use for reproduction dogs or cats that have excessive conformational traits leading to a high risk of detrimental effects on the welfare of such dogs or cats, or of their offspring. Before selecting a dog or cat that might have an excessive conformational trait for breeding, the operator shall consult a veterinarian or an independent qualified person acting under the responsibility of a veterinarian. That veterinarian or independent qualified person shall assess whether the dog or cat has an excessive conformational trait.
+3. The Commission is empowered to adopt delegated acts in accordance with Article 28 supplementing this Regulation by:
+(a) defining characteristics of the genotypes referred to in paragraph 1 that are to be excluded from reproduction, and the methods for their assessment and the record keeping requirements;
+(b) defining excessive conformational traits referred to in paragraph 2 of this Article that are to be excluded from reproduction, the methods for their assessment and the record keeping requirements.
+4. When adopting those delegated acts, the Commission shall take into account the scientific opinion of the European Food Safety Authority (EFSA), as well as any social and economic impacts of those delegated acts.
+5. The delegated acts concerning the excessive conformational traits shall be adopted by 1 July 2030. The delegated acts concerning the genotypes shall be adopted by 1 July 2036.
+6. The following shall be prohibited when managing the reproduction of dogs and cats:
+(a) breeding between parents and offspring, between siblings, between half-siblings or between grandparents and grandchildren, unless approved by the competent authority based on a specific need to preserve local breeds with a limited genetic pool;
+(b) breeding for the purpose of producing hybrids.
 @regulamento — Health  ·  ANEXO I, Ponto 3 do Regulamento 2023/0447  |  EN
 Health
-Queens shall only be bred if their age is at least 10 months.
-Bitches shall only be bred as of their second oestrus.
-A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
-For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
-Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
-Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. 
+1.1 Queens shall only be bred if their age is at least 10 months.
+2.2 Bitches shall only be bred as of their second oestrus.
+3.3 A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
+4.4 For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
+5.5 Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
+6.6 Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy.
 The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
-A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
-características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
-Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-São proibidos na gestão da reprodução de cães e gatos:
-o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-o cruzamento para produção de híbridos.
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
+3. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
+(a) características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
+5. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+6. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.
 @regulamento — Tradução PT-PT · ANEXO I, Ponto 3 do Regulamento 2023/0447
-As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
-As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
-Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
-Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
-Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
 O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>As condições de reprodução e criação de animais de companhia devem ser o mais análogas possível às de um ambiente doméstico, onde se espera que venham a viver após a sua transmissão.
-As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
-As gatas podem reproduzir entre os doze meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
-Os cães e os gatos machos podem reproduzir entre os doze meses e os sete anos de idade.
-As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.
-Os animais reprodutores são inscritos como tal no SIAC e devem ter um temperamento amistoso e confiante relativamente a pessoas e outros animais, não devendo ser utilizados para reprodução animais perigosos ou que demonstrem comportamento agressivo ou excessivamente tímido.
-Os cães e gatos reprodutores são sujeitos aos testes genéticos, rastreios de saúde, coeficiente de consanguinidade e limite aplicável ao número de descendentes permitidos por macho reprodutor específicos para a raça em questão, conforme definidos em portaria do membro do Governo responsável pela Direção geral de alimentação e Veterinária 
-Os cães e gatos só podem ser usados para reprodução se, após parecer do médico veterinário assistente, não seja de esperar que a sua reprodução, com base no seu genótipo, fenótipo ou estado de saúde, tenha um efeito prejudicial para a sua saúde e bem-estar, ou para a saúde e bem-estar dos seus descendentes.
-Com base nos critérios referidos no número anterior, a reprodução de determinados animais ou determinadas raças de cães e gatos pode ser limitada por portaria referida no n.º 7. 
-As fêmeas que tenham sido sujeitas a uma cesariana apenas podem voltar a reproduzir mediante atestado do médico veterinário assistente, que ateste não ser de esperar que a sua reprodução tenha um efeito prejudicial à sua saúde ou bem-estar.
-Ambos os progenitores devem ser capazes de acasalar naturalmente, sendo a inseminação artificial restrita a situações excecionais previstas na portaria referida no n.º 7. 
-São vedadas a reprodução de fêmeas que tenham sido já sujeitas a duas cesarianas e a colheita de sémen por eletroejaculação.
-O detentor de animal reprodutor que deixe de poder ser usado para reprodução, nos termos do presente artigo, é obrigado a esterilizá-lo e a garantir o seu bem-estar e uma detenção responsável até ao final da sua vida, diretamente ou cedendo-o a terceiros nos termos do disposto nos artigos 42.º ou 91.º.</t>
+          <t>1. As condições de reprodução e criação de animais de companhia devem ser o mais análogas possível às de um ambiente doméstico, onde se espera que venham a viver após a sua transmissão.
+2. As cadelas podem reproduzir entre os dezoito meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+3. As gatas podem reproduzir entre os doze meses e os seis anos de idade, até ao limite de quatro ninhadas com um intervalo mínimo de doze meses entre cada ninhada.
+4. Os cães e os gatos machos podem reproduzir entre os doze meses e os sete anos de idade.
+5. As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.
+6. Os animais reprodutores são inscritos como tal no SIAC e devem ter um temperamento amistoso e confiante relativamente a pessoas e outros animais, não devendo ser utilizados para reprodução animais perigosos ou que demonstrem comportamento agressivo ou excessivamente tímido.
+7. Os cães e gatos reprodutores são sujeitos aos testes genéticos, rastreios de saúde, coeficiente de consanguinidade e limite aplicável ao número de descendentes permitidos por macho reprodutor específicos para a raça em questão, conforme definidos em portaria do membro do Governo responsável pela Direção geral de alimentação e Veterinária
+8. Os cães e gatos só podem ser usados para reprodução se, após parecer do médico veterinário assistente, não seja de esperar que a sua reprodução, com base no seu genótipo, fenótipo ou estado de saúde, tenha um efeito prejudicial para a sua saúde e bem-estar, ou para a saúde e bem-estar dos seus descendentes.
+9. Com base nos critérios referidos no número anterior, a reprodução de determinados animais ou determinadas raças de cães e gatos pode ser limitada por portaria referida no n.º 7.
+10. As fêmeas que tenham sido sujeitas a uma cesariana apenas podem voltar a reproduzir mediante atestado do médico veterinário assistente, que ateste não ser de esperar que a sua reprodução tenha um efeito prejudicial à sua saúde ou bem-estar.
+11. Ambos os progenitores devem ser capazes de acasalar naturalmente, sendo a inseminação artificial restrita a situações excecionais previstas na portaria referida no n.º 7.
+12. São vedadas a reprodução de fêmeas que tenham sido já sujeitas a duas cesarianas e a colheita de sémen por eletroejaculação.
+13. O detentor de animal reprodutor que deixe de poder ser usado para reprodução, nos termos do presente artigo, é obrigado a esterilizá-lo e a garantir o seu bem-estar e uma detenção responsável até ao final da sua vida, diretamente ou cedendo-o a terceiros nos termos do disposto nos artigos 42.º ou 91.º.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -1086,46 +1086,46 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>A reprodução de animais deve ser realizada de forma planeada.	
-A reprodução de animais obedece ao seguinte: 
-Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos; 
-Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia; 
-Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais. 
-É proibida a atividade de criação resultante do cruzamento de espécies e raças diferentes, com exceção dos cruzamentos devidamente autorizados, com finalidade de melhoramento da raça ou investigação experimental e os cruzamentos de raças, em particular caninas, que tenham ocorrido acidentalmente e não tenham fins comerciais. 
+          <t>1. A reprodução de animais deve ser realizada de forma planeada.
+2. A reprodução de animais obedece ao seguinte:
+(a) Os animais só devem ser utilizados na reprodução depois de atingida a maturidade reprodutiva para a espécie e raça devendo, no caso dos cães e gatos, seguir os parâmetros referidos no anexo I ao presente diploma, do qual faz parte integrante, não sendo autorizado, no caso das fêmeas, o acasalamento em cios sucessivos;
+(b) Deve ser respeitada a regra do porte semelhante dos progenitores, para prevenir a possibilidade de distócia;
+(c) Devem ser excluídos da reprodução, os animais que revelem defeitos genéticos e malformações, designadamente monorquidia e displasia da anca nos cães e rim poliquístico nos gatos, ou alterações comportamentais.
+3. É proibida a atividade de criação resultante do cruzamento de espécies e raças diferentes, com exceção dos cruzamentos devidamente autorizados, com finalidade de melhoramento da raça ou investigação experimental e os cruzamentos de raças, em particular caninas, que tenham ocorrido acidentalmente e não tenham fins comerciais.
 Anexo I – Normas mínimas de proteção animal para a reprodução (alínea a) do n.º 2 do artigo 53.º
 Parâmetros reprodutivos
 Canídeos - Machos
-Idade mínima para reprodução:
-Raças de pequeno e médio porte – 1,5 anos
-Raças de grande porte – 2 anos
-Idade máxima para reprodução: 12 anos ou mais, se o estatuto sanitário o permitir
-Reprodução no 1.º ciclo: Não definido
-Número de ninhadas por ano: Não definido
-Número de ninhadas durante a vida reprodutiva: Não definido 
-Intervalo mínimo entre parto e nova gestação: Não definido
+— Idade mínima para reprodução:
+— Raças de pequeno e médio porte – 1,5 anos
+— Raças de grande porte – 2 anos
+— Idade máxima para reprodução: 12 anos ou mais, se o estatuto sanitário o permitir
+— Reprodução no 1.º ciclo: Não definido
+— Número de ninhadas por ano: Não definido
+— Número de ninhadas durante a vida reprodutiva: Não definido
+— Intervalo mínimo entre parto e nova gestação: Não definido
 Canídeos - Fêmeas
-Idade mínima para reprodução:
-Raças de pequeno e médio porte – 3.º cio
-Raças de grande porte – 2 anos
-Idade máxima para reprodução: 8 anos, ou 5 anos se for a 1.ª gestação
-Reprodução no 1.º ciclo: Não
-Número de ninhadas por ano: 1
-Número de ninhadas durante a vida reprodutiva: 4–6
-Intervalo mínimo entre parto e nova gestação: 1 ciclo reprodutivo
+— Idade mínima para reprodução:
+— Raças de pequeno e médio porte – 3.º cio
+— Raças de grande porte – 2 anos
+— Idade máxima para reprodução: 8 anos, ou 5 anos se for a 1.ª gestação
+— Reprodução no 1.º ciclo: Não
+— Número de ninhadas por ano: 1
+— Número de ninhadas durante a vida reprodutiva: 4–6
+— Intervalo mínimo entre parto e nova gestação: 1 ciclo reprodutivo
 Felídeos - Machos
-Idade mínima para reprodução: 1 ano
-Idade máxima para reprodução: 12 anos
-Reprodução no 1.º ciclo: Não definido
-Número de ninhadas por ano: Não definido
-Número de ninhadas durante a vida reprodutiva: Não definido
-Intervalo mínimo entre parto e nova gestação: Não definido
+— Idade mínima para reprodução: 1 ano
+— Idade máxima para reprodução: 12 anos
+— Reprodução no 1.º ciclo: Não definido
+— Número de ninhadas por ano: Não definido
+— Número de ninhadas durante a vida reprodutiva: Não definido
+— Intervalo mínimo entre parto e nova gestação: Não definido
 Felídeos - Fêmeas
-Idade mínima para reprodução: 1 ano
-Idade máxima para reprodução: 12 anos
-Reprodução no 1.º ciclo: Não
-Número de ninhadas por ano: 1 (ver abaixo)
-Número de ninhadas durante a vida reprodutiva: 8–10
-Intervalo mínimo entre parto e nova gestação: 3–6 meses
+— Idade mínima para reprodução: 1 ano
+— Idade máxima para reprodução: 12 anos
+— Reprodução no 1.º ciclo: Não
+— Número de ninhadas por ano: 1 (ver abaixo)
+— Número de ninhadas durante a vida reprodutiva: 8–10
+— Intervalo mínimo entre parto e nova gestação: 3–6 meses
 N. B. As cadelas não devem ter mais de 2 ninhadas num período de 2 anos e as gatas não devem ultrapassar as 3 ninhadas no período de 2 anos, a menos que haja uma declaração de aprovação emitida pelo veterinário assistente</t>
         </is>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="M5" s="10" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados. 
+          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados.
 ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.</t>
         </is>
       </c>
@@ -1176,32 +1176,32 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
-the name, address and contact details of the operator;
-the location of the establishment;
-the type of establishment: breeding establishment, selling establishment, shelter or foster home;
-the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment;
-the capacity of the establishment, expressed as the maximum number of dogs and cats which can be kept in the establishment;
-for breeding establishments, the estimated number of litters to be placed on the market per year.
-Operators shall notify the competent authority of:
-any changes concerning the information referred to in paragraph 1;
-where applicable, the planned date of a cessation of their activities, at the latest five working days before that date.
-Member States shall use the information provided in accordance with Article 84 of Regulation (EU) 2016/429. Operators shall not be required to notify the information already submitted in accordance with Article 84 of Regulation (EU) 2016/429 again. 
-The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
+          <t>1. Operators shall notify the competent authorities of their activity, providing at least the following information for each of their establishments:
+(a) the name, address and contact details of the operator;
+(b) the location of the establishment;
+(c) the type of establishment: breeding establishment, selling establishment, shelter or foster home;
+(d) the species and, for breeding establishments, the breeds of the dogs or cats kept in the establishment;
+(e) the capacity of the establishment, expressed as the maximum number of dogs and cats which can be kept in the establishment;
+(f) for breeding establishments, the estimated number of litters to be placed on the market per year.
+2. Operators shall notify the competent authority of:
+(g) any changes concerning the information referred to in paragraph 1;
+(h) where applicable, the planned date of a cessation of their activities, at the latest five working days before that date.
+3. Member States shall use the information provided in accordance with Article 84 of Regulation (EU) 2016/429. Operators shall not be required to notify the information already submitted in accordance with Article 84 of Regulation (EU) 2016/429 again.
+4. The competent authority shall maintain a register of establishments. The competent authority may use for that purpose the register provided for in Article 101(1), point (a), of Regulation (EU) 2016/429.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
-o nome, morada e contactos do operador;
-a localização do estabelecimento;
-o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
-as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
-a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
-para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
-Os operadores devem notificar a autoridade competente de:
-quaisquer alterações relativas às informações referidas no n.º 1;
-quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
+          <t>1. Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+(a) o nome, morada e contactos do operador;
+(b) a localização do estabelecimento;
+(c) o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
+(d) as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
+(e) a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
+(f) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+2. Os operadores devem notificar a autoridade competente de:
+(a) quaisquer alterações relativas às informações referidas no n.º 1;
+(b) quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
 3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
 4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
@@ -1258,8 +1258,8 @@
 Artigo 66.º - Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento
 As medidas previstas nos artigos 64.º e 65.º são publicitadas através do balcão único eletrónico dos serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV.
 Artigo 67.º - Reconhecimento mútuo
-1 - Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente decreto-lei e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu. 
-2 - O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente. 
+1 - Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente decreto-lei e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu.
+2 - O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente.
 3 – O disposto no presente artigo não prejudica a legislação aplicável ao reconhecimento mútuo de requisitos relativos a qualificações.</t>
         </is>
       </c>
@@ -1310,10 +1310,10 @@
 1 - O diretor-geral de Alimentação e Veterinária profere decisão no prazo de 15 dias a contar da remessa do processo a que se refere o n.º 5 do artigo anterior.
 2 - Caso não seja proferida a decisão referida no número anterior no prazo de 60 dias contados da data de receção do pedido de permissão administrativa devidamente instruído, independentemente da realização de visita de controlo, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
 Artigo 37.º - Divulgação dos alojamentos (TRATADO NOUTRO TEMA)
-Artigo 38.º - Alteração de funcionamento dos alojamentos 
-1	— A alteração de funcionamento dos alojamentos, designadamente a modificação estrutural nos alojamentos, a transferência de titularidade, a cessão de exploração, a cessação da atividade e a alteração do médico responsável pelo alojamento, é comunicada à DGAV no prazo de 15 dias contados da sua ocorrência. 
-2	— A comunicação de obras de modificação estrutural nos alojamentos é acompanhada das respetivas plantas. 
-3	— Compete à DGAV atualizar as informações obtidas através das comunicações referidas nos números anteriores. 
+Artigo 38.º - Alteração de funcionamento dos alojamentos
+1	— A alteração de funcionamento dos alojamentos, designadamente a modificação estrutural nos alojamentos, a transferência de titularidade, a cessão de exploração, a cessação da atividade e a alteração do médico responsável pelo alojamento, é comunicada à DGAV no prazo de 15 dias contados da sua ocorrência.
+2	— A comunicação de obras de modificação estrutural nos alojamentos é acompanhada das respetivas plantas.
+3	— Compete à DGAV atualizar as informações obtidas através das comunicações referidas nos números anteriores.
 Artigo 39.º - Suspensão de atividade e encerramento dos alojamentos
 1 – O diretor-geral de Alimentação e Veterinária pode, mediante despacho, determinar a suspensão da atividade ou o encerramento do alojamento, designadamente quando se verifique uma das seguintes situações:
 a) Existência de riscos higiossanitários que ponham em causa a saúde das pessoas e/ou dos animais;
@@ -1329,10 +1329,10 @@
 1 – Após o decurso do prazo fixado nos termos do n.º 4 do artigo anterior, a direção de serviços veterinários de alimentação e veterinária da região onde se localiza o alojamento realiza visita de controlo no prazo de 20 dias, a fim de verificar se se encontram reunidas as condições para o levantamento da suspensão, mediante decisão de permissão de reabertura a proferir pelo diretor-geral da Alimentação e Veterinária.
 2 – Na falta de decisão do diretor-geral de Alimentação e Veterinária a que se refere o número anterior, no prazo de 30 dias contados do termo do prazo fixado nos termos do n.º 4 do artigo anterior, ou no prazo de 10 dias após a realização da visita de controlo, no caso de esta ser realizada, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
 3 – A permissão de reabertura é publicitada pelos meios utilizados para a divulgação da suspensão da permissão.
-Artigo 41.° - Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento 
-As medidas previstas nos artigos 39.º e 40.º são publicitadas através do balcão único electrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV. 
-Artigo 42.º - Reconhecimento mútuo  
-1	- Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente diploma e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu. 
+Artigo 41.° - Divulgação da suspensão de atividade, do encerramento e da reabertura de alojamento
+As medidas previstas nos artigos 39.º e 40.º são publicitadas através do balcão único electrónico de serviços, a que se refere o artigo 6.º do Decreto-Lei n.º 92/2010, de 26 de julho, e no sítio na Internet da DGAV.
+Artigo 42.º - Reconhecimento mútuo
+1	- Não pode haver duplicação entre as condições exigíveis para o cumprimento dos procedimentos previstos no presente diploma e os requisitos e os controlos equivalentes ou comparáveis, quanto à finalidade, a que o interessado já tenha sido submetido noutro Estado membro da União Europeia ou do Espaço Económico Europeu.
 2	- O disposto no número anterior não é aplicável ao cumprimento das condições diretamente referentes às instalações físicas localizadas em território nacional, nem aos respetivos controlos por autoridade competente.</t>
         </is>
       </c>
@@ -1453,26 +1453,26 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
-The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
-The competent authority shall maintain a publicly available list including the following information for each approved establishment:
-the name, contact details and, where available, the URL of the website of the establishment;
-the address of the establishment;
-the name of the operator;
-the species and, if relevant, the breeds related to the establishment activities approved;
-the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
+          <t>1. Operators of breeding establishments that either produce or intend to produce more than five litters per calendar year or that keep more than a combined total of five bitches or queens at any given time shall place dogs or cats on the market only after their establishment has been approved by the competent authority.
+2. The competent authority shall perform on-site inspections to verify that the establishment meets the requirements of this Regulation. Member States may allow such inspections to be carried out remotely, provided that the means of distance communication used provides sufficient evidence for the competent authority to perform reliable inspections. The competent authority shall grant certificates of approval only to breeding establishments that meet the requirements of this Regulation.
+3. The competent authority shall maintain a publicly available list including the following information for each approved establishment:
+(a) the name, contact details and, where available, the URL of the website of the establishment;
+(b) the address of the establishment;
+(c) the name of the operator;
+(d) the species and, if relevant, the breeds related to the establishment activities approved;
+(e) the unique approval number assigned to the establishment by the competent authority and the date of the approval and cessation of activities.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
-A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
-A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
-o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
-a morada do estabelecimento;
-o nome do operador;
-a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
-o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
+          <t>1. Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
+2. A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
+3. A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
+(a) o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
+(b) a morada do estabelecimento;
+(c) o nome do operador;
+(d) a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
+(e) o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Operators shall provide the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
-The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
-the animal’s vaccination status;
-any medical conditions or predispositions to diseases, including allergies, that are known to the operator, and any diagnostic test results for the dog or cat that are available to the operator.
+          <t>1. Operators shall provide the acquirer of a dog or cat written information necessary to enable the acquirer to ensure the animal’s welfare, including information on responsible ownership and on the specific needs of the animal in terms of feeding, care, health and housing, as well as information on its behavioural needs and health history.
+2. The written information on the dog or cat’s health history referred to in the first paragraph shall include at least:
+(a) the animal’s vaccination status;
+(b) any medical conditions or predispositions to diseases, including allergies, that are known to the operator, and any diagnostic test results for the dog or cat that are available to the operator.
 Where the information on the animal’s health history is set out in a document required under Regulation (EU) 2016/429, the operator shall transmit that document to the acquirer.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
-A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
-o estado de vacinação do cão ou gato;
-quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+          <t>1. Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
+2. A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
+(a) o estado de vacinação do cão ou gato;
+(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
 Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
@@ -1575,14 +1575,14 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>O detentor do animal deve ter acesso à informação sobre:
-As obrigações inerentes à sua detenção, direitos e responsabilidades;
-As normas de bem-estar, cuidados de saúde e comportamento esperado;
-As necessidades específicas da espécie ou raça;
-A duração de vida esperada;
-Os custos de manutenção;
-A proibição de abandono.
-Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
+          <t>1. O detentor do animal deve ter acesso à informação sobre:
+a) As obrigações inerentes à sua detenção, direitos e responsabilidades;
+b) As normas de bem-estar, cuidados de saúde e comportamento esperado;
+c) As necessidades específicas da espécie ou raça;
+d) A duração de vida esperada;
+e) Os custos de manutenção;
+f) A proibição de abandono.
+2. Os criadores e comerciantes devem fornecer informação escrita completa ao adquirente antes da transferência do animal, incluindo dados de identificação e cuidados de saúde.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1632,28 +1632,28 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
-an understanding of the animals’ biological behaviour and their physiological and ethological needs;
-the ability to recognise the animals’ expressions, including any sign of suffering, and to identify and to take the appropriate mitigating measures  in such cases;
-the ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of those dogs or cats, preventing them from suffering;
-knowledge of the carers’ obligations under this Regulation.
-The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Only documented education, training or professional experience shall be taken into account when determining whether an animal carer has the competences referred to in paragraph 1.
-Operators shall ensure that at least one animal carer, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 22. Operators shall ensure that that animal carer transfers his or her knowledge to the other animal carers of the establishment.
-The Commission shall adopt implementing acts, laying down minimum requirements concerning the formal education, training or professional experience referred to in paragraph 2 of this Article necessary to determine whether an animal carer has the competences referred to in paragraph 1 and for the training courses referred to in paragraph 3.
+          <t>1. Animal carers, other than volunteers in shelters and interns who are acting under the responsibility of a competent animal carer, shall have the following competences as regards the dogs and cats they are handling:
+(a) an understanding of the animals’ biological behaviour and their physiological and ethological needs;
+(b) the ability to recognise the animals’ expressions, including any sign of suffering, and to identify and to take the appropriate mitigating measures  in such cases;
+(c) the ability to apply good animal management practices, including operant conditioning and positive reinforcement, to use and maintain the equipment used for the dogs or cats under their care and to minimise any risks to the welfare of those dogs or cats, preventing them from suffering;
+(d) knowledge of the carers’ obligations under this Regulation.
+2. The competences referred to in paragraph 1 may be acquired through education, training or professional experience. Only documented education, training or professional experience shall be taken into account when determining whether an animal carer has the competences referred to in paragraph 1.
+3. Operators shall ensure that at least one animal carer, other than a volunteer or intern, at the establishment has completed the training courses referred to in Article 22. Operators shall ensure that that animal carer transfers his or her knowledge to the other animal carers of the establishment.
+4. The Commission shall adopt implementing acts, laying down minimum requirements concerning the formal education, training or professional experience referred to in paragraph 2 of this Article necessary to determine whether an animal carer has the competences referred to in paragraph 1 and for the training courses referred to in paragraph 3.
 The implementing act concerning the training courses referred to in paragraph 3 shall be adopted by ... [3 years from the date of entry into force of this Regulation].
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+          <t>1. Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
 (a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
 (b) capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e adotar as medidas de atenuação adequadas nesses casos;
 (c) capacidade para aplicar boas práticas de gestão animal, incluindo o condicionamento operante e o reforço positivo, para utilizar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
 (d) conhecimento das obrigações que lhes incumbem por força do presente regulamento.​
-As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
-Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
-A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
+2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
+3. Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
+4. A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
 O ato de execução relativo aos cursos de formação referidos no n.º 3 é adotado até … [3 anos a contar da data de entrada em vigor do presente regulamento].​
 Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
         </is>
@@ -1699,9 +1699,9 @@
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Artigo 13.º - Maneio
-A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
-O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
-Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
+1. A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico competente e em número adequado à quantidade e espécies animais que alojam.
+2. O maneio deve ser feito por pessoal que possua formação teórica e prática específica ou sob a supervisão de uma pessoa competente para o efeito.
+3. Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados.</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar, 
+          <t>Estabelece a obrigação de ter médico veterinário responsável que execute 'programas e ações' para saúde e bem-estar,
 Não fixa prazos para avaliações de bem-estar nem obrigações de manutenção de registos estruturados, conforme @regulamento</t>
         </is>
       </c>
@@ -1852,18 +1852,18 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Operators shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I.
-In addition, operators shall ensure that dogs and cats are adequately fed and hydrated by supplying:
-clean and fresh water, ad libitum;
-feed of sufficient quantity and quality to meet the physiological, nutritional and metabolic needs of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level, health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining their good health;
-feed free of substances which could cause suffering;
-feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
-Operators shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
-provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
-minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
-prevent injury, drowning or other harm to the dogs or cats;
-be easily cleaned and disinfected to prevent the spread of diseases.
-Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
+          <t>1. Operators shall ensure that dogs and cats are fed in accordance with the requirements laid down in point 1 of Annex I.
+2. In addition, operators shall ensure that dogs and cats are adequately fed and hydrated by supplying:
+a) clean and fresh water, ad libitum;
+b) feed of sufficient quantity and quality to meet the physiological, nutritional and metabolic needs of the dogs and cats, as part of a diet adapted to the age, breed, category, activity level, health and reproductive status of the dogs or cats, with the overall objective of achieving and maintaining their good health;
+c) feed free of substances which could cause suffering;
+d) feed in such a way as to avoid abrupt changes and ensure a well-functioning gastro-intestinal system, in particular during the weaning phase.
+3. Operators shall ensure that feeding and watering facilities are kept clean and are constructed and installed in such a way as to:
+a) provide equal access to adequate amounts of feed and water for all dogs or cats and minimise competition between them;
+b) minimise spillage and prevent the contamination of feed and water with harmful physical, chemical or biological contaminants;
+c) prevent injury, drowning or other harm to the dogs or cats;
+d) be easily cleaned and disinfected to prevent the spread of diseases.
+4. Where advised in writing by a veterinarian to do so, the operators may adjust the feeding and watering frequencies for an individual dog or cat. The operators shall keep a record of that written advice for the entire duration of those arrangements.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1895,7 +1895,7 @@
 4 - Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos, devem, ainda, ser armazenados sobre estrados ou prateleiras.
 5 – Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
 6 - Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
-Art. 7.º (n.º 1, al. a) - Princípios fundamentais: 
+Art. 7.º (n.º 1, al. a) - Princípios fundamentais:
 Não passem fome ou sede, nem sejam sujeitos a malnutrição.
 Art. 10.º (n.º 1, al. a) - Obrigações especiais dos detentores:
 Alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.</t>
@@ -1976,46 +1976,46 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
-Operators shall ensure that:
-the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and make possible the necessary access to, and the thorough inspection of, all dogs or cats;
-all building components of the establishment, including the flooring and roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
-all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept clean to ensure that they do not pose any risks to the welfare of the dogs or cats;
-in breeding and selling establishments where dogs or cats are kept indoors, the dust levels, the temperature, and the relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating  ;
-dogs or cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with the possibility to withdraw and rest;
-dogs or cats have clean, comfortable and dry resting places that are sufficiently large and numerous to ensure that all of them can lie down and rest in a natural position at the same time;
-appropriate structures and measures are in place for dogs or cats that are kept outdoors in order to protect them from adverse weather conditions, including to prevent thermal stress, sunburn and frostbite.
-Operators shall not keep dogs or cats in containers
+          <t>1. The operators of breeding and selling establishments shall ensure that dogs and cats are housed in accordance with point 2 of Annex I. The operators of shelters shall ensure that dogs and cats are housed in accordance with point 2.2 of Annex I.
+2. Operators shall ensure that:
+(a) the establishments where dogs or cats are kept and the equipment used therein are suitable for the types and the number of dogs or cats, and make possible the necessary access to, and the thorough inspection of, all dogs or cats;
+(b) all building components of the establishment, including the flooring and roof, and space divisions, as well as the equipment used for dogs or cats, are constructed and maintained properly, to ensure that they do not pose any risks to the welfare of the dogs or cats;
+(c) all building components of the establishment, including the flooring, and space divisions, as well as the equipment used for dogs or cats, are kept clean to ensure that they do not pose any risks to the welfare of the dogs or cats;
+(d) in breeding and selling establishments where dogs or cats are kept indoors, the dust levels, the temperature, and the relative air humidity and gas concentrations are not harmful to dogs or cats and that ventilation is sufficient to avoid overheating  ;
+(e) dogs or cats have enough space to be able to move around freely and to express species-specific behaviour according to their needs with the possibility to withdraw and rest;
+(f) dogs or cats have clean, comfortable and dry resting places that are sufficiently large and numerous to ensure that all of them can lie down and rest in a natural position at the same time;
+(g) appropriate structures and measures are in place for dogs or cats that are kept outdoors in order to protect them from adverse weather conditions, including to prevent thermal stress, sunburn and frostbite.
+3. Operators shall not keep dogs or cats in containers
 However, containers may be used for transportation, for the short term isolation of individual dogs or cats and for participation in shows, exhibitions and competitions, for puppies or kittens with reduced thermoregulation capacity or for puppies or kittens together with their mothers, provided that, for the dogs or cats concerned, stress is minimised and suffering is avoided, and they are able to stand, turn around and lie down in a natural position.
-Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialisation. The minimum combined duration of such daily access or walk shall be one hour in total. The operator may only deviate from these requirements based on the written advice of a veterinarian.
-When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to exhibit their natural behaviour.
-Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained that takes into account their coat type, age, size, breed, and health.
-Operators of breeding and selling establishments shall, where necessary, use heating or cooling systems in the indoor enclosures at their establishments to maintain good air quality and an appropriate temperature and to remove excessive moisture.
-Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
+4. Operators shall not keep dogs older than 8 weeks exclusively indoors. Such dogs shall have daily access to an outdoor area, or be walked daily, to allow exercise, exploration and socialisation. The minimum combined duration of such daily access or walk shall be one hour in total. The operator may only deviate from these requirements based on the written advice of a veterinarian.
+5. When cats are kept in catteries, operators shall design and construct individual enclosures to allow cats to move around freely and to exhibit their natural behaviour.
+6. Operators of breeding and selling establishments shall ensure that in indoor areas where dogs and cats are kept, an appropriate thermoneutral zone is maintained that takes into account their coat type, age, size, breed, and health.
+7. Operators of breeding and selling establishments shall, where necessary, use heating or cooling systems in the indoor enclosures at their establishments to maintain good air quality and an appropriate temperature and to remove excessive moisture.
+8. Operators shall ensure that dogs or cats are exposed to light, and are able to stay in the dark for sufficient and uninterrupted periods in order to maintain a normal circadian rhythm.
 For the purposes of the first subparagraph, ‘light’ means natural light, complemented, where necessary due to the climatic conditions and geographic position of a Member State, by artificial light.
-Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
+9. Paragraph 2, points (a), (b), (c) (f) and (g), and paragraphs 6, 7 and 8 shall apply neither to livestock guardian dogs, nor to herding dogs, during the periods where such dogs are used for guarding or herding in the context of seasonal transhumance on foot. Paragraph 2(f) shall not apply to livestock guardian dogs during the periods when such dogs are used for training purposes.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
-Os operadores devem assegurar que:
-os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
-todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
-os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
-os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
-existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
+          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
+2. Os operadores devem assegurar que:
+a) os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
+b) todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+c) todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+d) nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
+e) os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
+f) os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
+g) existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
 Os operadores não devem manter cães ou gatos em contentores.
-Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural. 
-Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
-Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
-Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
-Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
-Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
+3. Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural.
+4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
+5. Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
+6. Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
+7. Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
+8. Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
 Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
+9. Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2026,21 +2026,21 @@
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Artigo 47.º- Condições dos alojamentos
-1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: 
-a) A prática de exercício físico adequado; 
+1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a) A prática de exercício físico adequado;
 b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem. 
-3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar. 
+2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
 4 - As instalações devem providenciar um enriquecimento ambiental complexo e estimulante de acordo com as necessidades específicas dos animais que albergam, incluindo materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente materiais para substrato, cama ou ninhos, ramos, buracos, locais para banhos, brinquedos e outros adequados ao fim em vista.
 5 - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar ameaça ao bem-estar dos animais, designadamente não podem conter objetos ou equipamentos perigosos para os animais.
 6 – Os cães devem ter acesso diário a uma área de exercício fora do seu alojamento habitual, pelo menos duas vezes por dia, durante 30 minutos.
-7 – As áreas de exercício referidas no artigo anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista. 
+7 – As áreas de exercício referidas no artigo anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista.
 Artigo 48.º- Fatores ambientais
-1 - A temperatura, ventilação, luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do bem-estar e conforto das espécies que albergam. 
-2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes. 
-3 - A luz deve preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado. 
-4 - As instalações devem permitir a adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central. 
-5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde. 
+1 - A temperatura, ventilação, luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do bem-estar e conforto das espécies que albergam.
+2 - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3 - A luz deve preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4 - As instalações devem permitir a adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5 - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
 6 - As instalações devem dispor de abrigos para que os animais se protejam de condições climáticas adversas.
 7 – Deve ser evitado o ruído excessivo ou contínuo.
 Artigo 49.º-Carga e descarga de animais
@@ -2056,24 +2056,24 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>- Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: 
-A prática de exercício físico adequado; 
-A fuga e refúgio de animais sujeitos a agressão por parte de outros. 
-- Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem. 
-- As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar. 
-- As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais. 
-- As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista. 
-Artigo 14.º - Fatores ambientais 
-- A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam. 
-- Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes. 
-- A luz deve ser preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado. 
-- As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central. 
-- Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde. 
-Artigo 15.o - Sistemas de proteção 
-As instalações dos alojamentos de animais devem dispor de um sistema de proteção contra incêndios, alarme para aviso de avarias deste sistema e, ainda, dos equipamentos referidos no artigo anterior, quando se tratar de alojamentos em edifícios fechados e ainda, de outros equipamentos em função das espécies, sempre que da sua falta possa resultar prejuízo para o bem-estar dos animais, ou a sua morte. 
-Artigo 16.º - Carga e descarga de animais 
-As instalações dos alojamentos devem dispor, sempre que necessário, de estruturas e equipamentos adequados à carga ou à descarga dos animais dos meios de transporte, assegurando-se sempre que os mesmos não sejam maltratados ou derrubados durante aquelas operações e procurando-se minorar as situações que lhes possam provocar medo ou excitação desnecessários.	
-Artigo 17.º - Segurança de pessoas, animais e bens 
+          <t>1. - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
+a. A prática de exercício físico adequado;
+b. A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2. - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
+3. - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.
+4. - As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.
+5. - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.
+Artigo 14.º - Fatores ambientais
+1. - A temperatura, a ventilação e a luminosidade e obscuridade das instalações devem ser as adequadas à manutenção do conforto e bem-estar das espécies que albergam.
+2. - Os fatores ambientais referidos no número anterior devem ser adequados às necessidades específicas de animais quando em fase reprodutiva, recém-nascidos ou doentes.
+3. - A luz deve ser preferencialmente natural, mas quando a luz artificial for imprescindível, esta deve ser o mais próxima possível do espectro da luz solar e deve respeitar o fotoperíodo natural do local onde o animal está instalado.
+4. - As instalações devem permitir uma adequada inspeção dos animais, devendo ainda existir equipamento alternativo, nomeadamente focos de luz, para o caso de falência do equipamento central.
+5. - Os tanques ou aquários devem possuir água de qualidade adequada aos animais que a utilizem, nomeadamente tratada por produtos ou substâncias que não prejudiquem a sua saúde.
+Artigo 15.o - Sistemas de proteção
+As instalações dos alojamentos de animais devem dispor de um sistema de proteção contra incêndios, alarme para aviso de avarias deste sistema e, ainda, dos equipamentos referidos no artigo anterior, quando se tratar de alojamentos em edifícios fechados e ainda, de outros equipamentos em função das espécies, sempre que da sua falta possa resultar prejuízo para o bem-estar dos animais, ou a sua morte.
+Artigo 16.º - Carga e descarga de animais
+As instalações dos alojamentos devem dispor, sempre que necessário, de estruturas e equipamentos adequados à carga ou à descarga dos animais dos meios de transporte, assegurando-se sempre que os mesmos não sejam maltratados ou derrubados durante aquelas operações e procurando-se minorar as situações que lhes possam provocar medo ou excitação desnecessários.
+Artigo 17.º - Segurança de pessoas, animais e bens
 Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens</t>
         </is>
       </c>
@@ -2111,9 +2111,9 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita. 
+          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita.
 N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
-N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao. 
+N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao.
 Prever exceções para cães de guarda de rebanho</t>
         </is>
       </c>
@@ -2137,42 +2137,42 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Operators shall ensure that:
-dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently.
-dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where necessary, receive appropriate treatment;
-where the recovery of a dog or a cat whose welfare is compromised is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay to decide whether the dog or cat is to be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anaesthesia and analgesia.
-measures are taken to prevent and control external and internal parasites, and vaccinations are carried out to prevent common diseases to which dogs or cats are likely to be exposed.
-enrichments that are used do not present a significant risk to dogs and cats of injury or biological or chemical contamination or any other health risk.
+          <t>1. Operators shall ensure that:
+(a) dogs or cats for which they are responsible are inspected by animal carers at least once a day and that vulnerable dogs and cats, such as newborns, ill or injured dogs and cats, and peri-partum bitches and queens, are inspected more frequently.
+(b) dogs or cats with compromised welfare are, where necessary, transferred without undue delay to a separate area and, where necessary, receive appropriate treatment;
+(c) where the recovery of a dog or a cat whose welfare is compromised is not achievable and the dog or cat experiences severe pain or suffering, a veterinarian is consulted without undue delay to decide whether the dog or cat is to be euthanised to end its suffering, and, if that is the case, to perform the euthanasia using anaesthesia and analgesia.
+(d) measures are taken to prevent and control external and internal parasites, and vaccinations are carried out to prevent common diseases to which dogs or cats are likely to be exposed.
+(e) enrichments that are used do not present a significant risk to dogs and cats of injury or biological or chemical contamination or any other health risk.
 Point (a) shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
 Member States may grant exemptions from point (c) in cases of emergency, where no veterinarian can be reached without undue delay, provided that national rules are put in place to ensure that:
-any immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
-for the purposes of the official control under Regulation (EU) 2017/625, the operator keeps a record of the use of the exemption.
-Operators of breeding establishments shall ensure that:
-measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
-bitches or queens are bred only if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I , and only if they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
-the litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
-lactating queens are not mated or inseminated;
-dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
+i) any immediate action ending the life of the dog or cat with minimum pain and suffering using a method inducing instant death is undertaken by a trained competent person;
+ii) for the purposes of the official control under Regulation (EU) 2017/625, the operator keeps a record of the use of the exemption.
+2. Operators of breeding establishments shall ensure that:
+(a) measures are taken to safeguard the health of dogs or cats in accordance with point 3 of Annex I;
+(b) bitches or queens are bred only if they have reached a minimum age and skeletal maturity in accordance with point 3 of Annex I , and only if they have no diagnosed disease, clinical sign of diseases or physical conditions which could negatively impact their pregnancy and welfare;
+(c) the litter-giving pregnancies of bitches or queens follows a maximum frequency in accordance with point 3 of Annex I;
+(d) lactating queens are not mated or inseminated;
+(e) dogs and cats which are no longer used for reproduction, including as a result of the provisions of this Regulation, are either kept or sold, donated or rehomed, and not killed or abandoned.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem assegurar que:
-os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+          <t>1. Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
 A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
 Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
-Os operadores de estabelecimentos de criação devem assegurar que:
- são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-as cadelas ou gatas só se reproduzem se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
- As gravidezes das cadelas e gatas que resultem numa ninhada respeitem uma frequência máxima fixada no ponto 3 do Anexo I;
- as gatas em lactação não sejam acasaladas nem inseminadas;
- os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+2. Os operadores de estabelecimentos de criação devem assegurar que:
+(a)  são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(b) as cadelas ou gatas só se reproduzem se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(c)  As gravidezes das cadelas e gatas que resultem numa ninhada respeitem uma frequência máxima fixada no ponto 3 do Anexo I;
+(d)  as gatas em lactação não sejam acasaladas nem inseminadas;
+(e)  os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2183,25 +2183,25 @@
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º — Cuidados de saúde (geral)
-Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
-Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
-Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
-Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.
+1. Os detentores dos animais de companhia devem assegurar-lhes os cuidados de saúde adequados, nomeadamente seguindo as orientações da DGAV em matéria de vacinação e tratamentos obrigatórios, bem como consultas regulares junto de médico veterinário.
+2. Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+3. Os médicos veterinários e os centros de atendimento médico-veterinário (CAMV) devem manter um arquivo com os dados clínicos de cada animal, pelo período mínimo de cinco anos, que ficará à disposição das autoridades competentes.
+4. Os CAMV, enquanto estabelecimentos de saúde, colaborarão na vigilância epidemiológica das doenças de notificação obrigatória que detetem e no seu controlo.
+5. Os médicos veterinários denunciam, junto da DGAV ou demais entidades com competência de fiscalização do cumprimento das normas constantes do presente decreto-lei, sempre que, no exercício de sua profissão, suspeitem de maus-tratos a animais de companhia.
 Artigo 52.º - Maneio
-A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico que possua formação teórica e prática específica ministrada ou certificada pela DGAV e em número adequado à quantidade e espécies animais que alojam. 
-Todos os animais devem ser alvo de inspeção no início e final do dia de trabalho e a cada quatro horas, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais. 
-O maneio dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários, salvaguardando o seu bem-estar. 
-As interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis, e não forçadas. 
-Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessária aos animais.
-Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental
+1. A observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal técnico que possua formação teórica e prática específica ministrada ou certificada pela DGAV e em número adequado à quantidade e espécies animais que alojam.
+2. Todos os animais devem ser alvo de inspeção no início e final do dia de trabalho e a cada quatro horas, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+3. O maneio dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários, salvaguardando o seu bem-estar.
+4. As interações do pessoal técnico com os animais devem ser positivas, regulares, previsíveis, e não forçadas.
+5. Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessária aos animais.
+6. Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental
 Artigo 55.º — Cuidados de saúde animal (Capítulo dos Alojamentos)
-Os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária elaborado e supervisionado pelo médico veterinário responsável.
-Aos animais feridos ou doentes devem ser de imediato assegurados os cuidados médico-veterinários adequados.
-Os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se adequado à espécie, com cama seca e confortável, salvaguardando o seu bem-estar.
-Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
+1. Os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+2. Sem prejuízo de quaisquer medidas determinadas pela DGAV, deve existir um programa de profilaxia médica e sanitária elaborado e supervisionado pelo médico veterinário responsável.
+3. Aos animais feridos ou doentes devem ser de imediato assegurados os cuidados médico-veterinários adequados.
+4. Os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se adequado à espécie, com cama seca e confortável, salvaguardando o seu bem-estar.
+5. Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+6. A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -2213,19 +2213,19 @@
         <is>
           <t>Artigo 6.º — Cuidados médico-veterinários
 O detentor do animal deve assegurar ao animal ferido ou doente os cuidados médico-veterinários adequados, designadamente retirando o mesmo do alojamento sempre que este seja um local de venda.
-Artigo 47.º - Maneio 
-- Nos alojamentos de hospedagem de animais, nos centros de recolha e nas hospedagens com fins médico-veterinários, a observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais que alojam. 
-- O maneio deve ser feito por pessoal que possua experiência ou formação adequada e sob a orientação de um médico veterinário ou pessoa com competência para o efeito. 
-- Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais. 
-- O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários. 
-- Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais. 
+Artigo 47.º - Maneio
+1 - Nos alojamentos de hospedagem de animais, nos centros de recolha e nas hospedagens com fins médico-veterinários, a observação diária dos animais e o seu maneio, a organização da dieta e o tratamento médico-veterinário devem ser assegurados por pessoal com aptidão para o efeito e em número adequado à quantidade e espécies animais que alojam.
+2 - O maneio deve ser feito por pessoal que possua experiência ou formação adequada e sob a orientação de um médico veterinário ou pessoa com competência para o efeito.
+3 - Todos os animais devem ser alvo de inspeção diária, sendo de imediato prestados os primeiros cuidados aos que tiverem sinais que levem a suspeitar estarem doentes, lesionados ou com alterações comportamentais.
+4 - O manuseamento dos animais deve ser feito de forma a não lhes causar quaisquer dores, sofrimento ou distúrbios desnecessários.
+5 - Quando houver necessidade de recorrer a meios de contenção, não devem estes causar ferimentos, dores ou angústia desnecessários aos animais.
 Artigo 49.º - Cuidados de saúde animal
-Sem prejuízo de quaisquer medidas determinadas pela DGAV, nos locais de criação, manutenção e venda, bem como nos centros de recolha e alojamentos de hospedagem, deve existir um programa de profilaxia médica e sanitária, elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais habilitados para o efeito.
-No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
-Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
-Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
-Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
-A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior, deve ser feita sob orientação do médico veterinário responsável.</t>
+1. Sem prejuízo de quaisquer medidas determinadas pela DGAV, nos locais de criação, manutenção e venda, bem como nos centros de recolha e alojamentos de hospedagem, deve existir um programa de profilaxia médica e sanitária, elaborado e supervisionado pelo médico veterinário responsável e executado por profissionais habilitados para o efeito.
+2. No âmbito do número anterior, os animais devem ser sujeitos a exames médico-veterinários de rotina, vacinações e desparasitações sempre que aconselhável.
+3. Os animais que apresentem sinais que levem a suspeitar de poderem estar doentes ou lesionados devem receber os primeiros cuidados pelo detentor e, se não houver indícios de recuperação, devem ser tratados por médico veterinário.
+4. Sempre que se justifique, os animais doentes ou lesionados devem ser isolados em instalações adequadas e equipadas, se for caso disso, com cama seca e confortável.
+5. Os medicamentos, produtos ou substâncias de prescrição médico-veterinária devem ser armazenados em locais secos e com acesso restrito.
+6. A administração e utilização de medicamentos, produtos ou substâncias referidas no número anterior, deve ser feita sob orientação do médico veterinário responsável.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -2291,36 +2291,36 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Operators shall ensure that measures are taken to meet the behavioural needs of dogs and cats in accordance with point 4 of Annex I.
-In addition, operators shall not keep dogs or cats in areas which limit their natural movements, except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
-physical examinations;
-the individual identification of dogs or cats, or reading such identification information;
-the collection of samples and vaccinations;
-procedures for grooming, hygienic, health or reproductive purposes other than mating;
-medical treatments, including surgical treatments or prescribed rehabilitation.
-Tethering for more than 1 hour shall be prohibited, except for the duration of a medical treatment or for participation in shows, exhibitions and competitions of dogs or cats.
-Member States may grant exemptions from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
-Operators shall ensure that dogs or cats are kept in conditions that allow them to exhibit non-harmful social behaviours and species-specific behaviours and to experience positive emotions.
-Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall have a documented strategy for such socialisation.
+          <t>1. Operators shall ensure that measures are taken to meet the behavioural needs of dogs and cats in accordance with point 4 of Annex I.
+2. In addition, operators shall not keep dogs or cats in areas which limit their natural movements, except in cases where Article 15(3), second subparagraph, applies or where the following procedures or treatments are performed:
+(a) physical examinations;
+(b) the individual identification of dogs or cats, or reading such identification information;
+(c) the collection of samples and vaccinations;
+(d) procedures for grooming, hygienic, health or reproductive purposes other than mating;
+(e) medical treatments, including surgical treatments or prescribed rehabilitation.
+3. Tethering for more than 1 hour shall be prohibited, except for the duration of a medical treatment or for participation in shows, exhibitions and competitions of dogs or cats.
+4. Member States may grant exemptions from paragraph 3 for dogs intended for use in military, police and customs services that are kept in breeding or selling establishments.
+5. Operators shall ensure that dogs or cats are kept in conditions that allow them to exhibit non-harmful social behaviours and species-specific behaviours and to experience positive emotions.
+6. Operators shall ensure that dogs or cats can socialise in accordance with point 4 of Annex I. Operators of breeding establishments shall have a documented strategy for such socialisation.
 By way of derogation from the first subparagraph, socialisation requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes, or to herding dogs during seasonal transhumance.
 7.	Operators shall ensure that enrichments are provided and accessible to all dogs or cats, creating a stimulating environment for them, enabling them to develop and exhibit species-specific behaviour and reducing their frustration.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
-Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
-exames físicos;
-identificação individual de cães ou gatos e leitura da informação de identificação;
-recolha de amostras e vacinações;
-procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
-tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
-O acorrentamento por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-Os Estados-Membros podem conceder isenções ao disposto no n.º 3 para os cães destinados a ser utilizados nos serviços militares, policiais e aduaneiros que sejam mantidos em estabelecimentos de criação ou de venda.
- Os operadores devem assegurar que os cães ou gatos sejam mantidos em condições que lhes permitam exibir comportamentos sociais não prejudiciais e comportamentos específicos da espécie, bem como vivenciar emoções positivas.
-Os operadores devem assegurar que os cães ou gatos possam socializar em conformidade com o ponto 4 do anexo I. Os operadores de estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização. 
+          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
+2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+a) exames físicos;
+b) identificação individual de cães ou gatos e leitura da informação de identificação;
+c) recolha de amostras e vacinações;
+d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
+e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
+3. O acorrentamento por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+4. Os Estados-Membros podem conceder isenções ao disposto no n.º 3 para os cães destinados a ser utilizados nos serviços militares, policiais e aduaneiros que sejam mantidos em estabelecimentos de criação ou de venda.
+5.  Os operadores devem assegurar que os cães ou gatos sejam mantidos em condições que lhes permitam exibir comportamentos sociais não prejudiciais e comportamentos específicos da espécie, bem como vivenciar emoções positivas.
+6. Os operadores devem assegurar que os cães ou gatos possam socializar em conformidade com o ponto 4 do anexo I. Os operadores de estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização.
 Em derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães sejam utilizados para fins de guarda ou de treino, nem aos cães de pastoreio durante a transumância sazonal.
-Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
+7. Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2334,7 +2334,7 @@
 Especificação clara: 'exercício físico e estímulo mental', 'Contato social adequado'. (Art.º 10.º).
 Métodos de 'reforço positivo' (OBRIGATÓRIO).
 Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
-n.º 7, do art.º 52.º 
+n.º 7, do art.º 52.º
 Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
 (Documentação obrigatória de estratégia de socialização - criadores).
 Fatores de socialização também previstos no treino dos perigosos e PP.</t>
@@ -2395,18 +2395,18 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
-The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
-By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a ‘trap-neuter-return’ programme.
-Operators shall ensure that neutering is performed  only under anaesthesia and prolonged analgesia and only by a veterinarian. However, Member States may allow the neutering of male cats to be performed by a licensed veterinary nurse.
-Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
-tying up body parts, unless required for medical reasons and limited to the minimum period necessary;
-the kicking, hitting, dragging, throwing or squeezing of dogs or cats;
-applying electric current to dogs or cats, unless performed for medical reasons;
-using  muzzles, unless required for medical reasons or animal or human safety reasons, limited to the minimum period necessary and where the dog or cat is supervised.
-using prong collars;
-using choke collars without a safety stop;
-lifting dogs or cats by the limbs,  head, ears, tail or hair, or lifting adult dogs or cats by the skin.
+          <t>1. Operators shall ensure that mutilations, including ear cropping, tail docking, claw removal or other partial or complete digit amputation, and resection of vocal cords or folds,  are not performed unless justified by medical indications, including where the procedure is prophylactic, with the sole purpose of maintaining or improving the health of dogs or cats or preventing their injury. In such cases, the procedure shall be performed  only under anaesthesia and prolonged analgesia and only by a veterinarian.
+2. The medical indications justifying the mutilation, and the details of procedure carried out, shall be documented by a veterinarian. That document shall be retained by the operator and shall accompany the dog or cat when it is transferred to another establishment or owner. The operator of the establishment where the mutilation was performed shall retain a copy of the document for the first three years after that transfer.
+3. By way of derogation from paragraph 1, Member States may allow ear cropping by notching or tipping cat ears in the context of marking stray cats when neutered under a ‘trap-neuter-return’ programme.
+4. Operators shall ensure that neutering is performed  only under anaesthesia and prolonged analgesia and only by a veterinarian. However, Member States may allow the neutering of male cats to be performed by a licensed veterinary nurse.
+5. Operators shall ensure that handling practices that cause pain or suffering are not performed, including:
+(a) tying up body parts, unless required for medical reasons and limited to the minimum period necessary;
+(b) the kicking, hitting, dragging, throwing or squeezing of dogs or cats;
+(c) applying electric current to dogs or cats, unless performed for medical reasons;
+(d) using  muzzles, unless required for medical reasons or animal or human safety reasons, limited to the minimum period necessary and where the dog or cat is supervised.
+(e) using prong collars;
+(f) using choke collars without a safety stop;
+(g) lifting dogs or cats by the limbs,  head, ears, tail or hair, or lifting adult dogs or cats by the skin.
 Member States may grant exemptions from the first subparagraph for dogs intended for use in military, police or customs services.</t>
         </is>
       </c>
@@ -2437,8 +2437,8 @@
           <t>Art. 12.º
 i)	Sujeitá-los a intervenções cirúrgicas, com o objetivo de modificar a sua aparência ou alcançar outros fins não curativos, ou não destinados a impedir a reprodução, em particular, corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais
 (…)
-Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
-Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
+p) Administrar-lhes substâncias, tratamentos ou procedimentos com vista a aumentar ou diminuir o nível natural das suas capacidades fisiológicas e etológicas ou que não tenham fins médico-veterinários;
+q) Sujeitá-lo a amputações sem razão médica veterinária que o justifique;
 Artigo 34.º- Intervenções cirúrgicas
 1 – As intervenções cirúrgicas com o objetivo da modificação da aparência ou com fins não curativos ou não destinados a impedir a reprodução dos animais são proibidas, nos termos do disposto na alínea i) do n.º 1 do artigo 12.º.
 2 – O detentor de animal sujeito a intervenção curativa que modifique a sua aparência deve possuir documento comprovativo da necessidade da mesma, passado pelo médico veterinário que a ela procedeu, sob a forma de atestado do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, ou, no caso de animais importados, documento comprovativo da necessidade dessa intervenção, emitida pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país..
@@ -2453,15 +2453,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Artigo 51.o Intervenções cirúrgicas 
-As intervenções cirúrgicas têm de ser executadas por um médico veterinário. 
-Artigo 52.o - Mutilações 
-- São proibidas as mutilações que modifiquem a aparência dos animais ou que sejam realizadas com objetivos não curativos, designadamente o corte de orelhas ou de cordas vocais e a excisão de garras ou unhas, de dentes ou presas.  
-- Excetuam-se do disposto no número anterior as intervenções cirúrgicas feitas com vista a impedir a reprodução, por razões médico-veterinárias, ou no interesse particular do animal. 
-- O corte de caudas é proibido para todos os cães nascidos a partir de 1 de Janeiro de 2015.  
-- Os detentores de animais de companhia que os apresentem com quaisquer mutilações que modifiquem a aparência dos animais, devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa mutilação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou ainda, como nos casos previstos no DL n.º 315/2009, de 29 outubro,alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, para impedir a reprodução. 	
-- O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, bem como a causa da mutilação. 
-- Os detentores de animais importados que apresentem quaisquer das amputações referidas no n.º 1 devem possuir documento comprovativo da necessidade dessa mutilação, passada pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
+          <t>Artigo 51.o Intervenções cirúrgicas
+As intervenções cirúrgicas têm de ser executadas por um médico veterinário.
+Artigo 52.o - Mutilações
+1 - São proibidas as mutilações que modifiquem a aparência dos animais ou que sejam realizadas com objetivos não curativos, designadamente o corte de orelhas ou de cordas vocais e a excisão de garras ou unhas, de dentes ou presas.
+2 - Excetuam-se do disposto no número anterior as intervenções cirúrgicas feitas com vista a impedir a reprodução, por razões médico-veterinárias, ou no interesse particular do animal.
+3 - O corte de caudas é proibido para todos os cães nascidos a partir de 1 de Janeiro de 2015.
+4 - Os detentores de animais de companhia que os apresentem com quaisquer mutilações que modifiquem a aparência dos animais, devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa mutilação, nomeadamente discriminando que as mesmas foram feitas por razões médico-veterinárias ou no interesse particular do animal ou ainda, como nos casos previstos no DL n.º 315/2009, de 29 outubro,alterado pelo Decreto-Lei n.º 260/2012, de 12 de dezembro, para impedir a reprodução.
+5 - O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura, bem como a causa da mutilação.
+6 - Os detentores de animais importados que apresentem quaisquer das amputações referidas no n.º 1 devem possuir documento comprovativo da necessidade dessa mutilação, passada pelo médico veterinário que a ela procedeu, legalizado pela autoridade competente do respetivo país.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -2471,9 +2471,9 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Artigo 17.º 
+          <t>Artigo 17.º
 As intervenções cirúrgicas, nomeadamente as destinadas ao corte de caudas nos canídeos, têm de ser executadas por um médico veterinário.
-Artigo 18.º 
+Artigo 18.º
  1 — Os detentores de animais de companhia que os apresentem com quaisquer amputações que modifiquem a aparência dos animais ou com fins não curativos devem possuir documento comprovativo, passado pelo médico veterinário que a elas procedeu, da necessidade dessa amputação.
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
@@ -2511,14 +2511,14 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
-When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.</t>
+          <t>1. In aesthetic shows, exhibitions and competitions of dogs and cats, operators of breeding and selling establishments shall not use dogs or cats with excessive conformational traits, or dogs or cats which have been mutilated in a way that alters their physical characteristics.
+2. When organising aesthetic shows, exhibitions and competitions of dogs and cats, organisers shall exclude dogs and cats which have excessive conformational traits or dogs or cats which have been mutilated in a way that alters their physical characteristics.</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
-Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
+          <t>1. Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
+2. Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2529,33 +2529,33 @@
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Artigo 39.º - Participação em eventos
-A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias ou outros eventos onde participem animais de companhia carece de autorização do diretor-geral da DGAV da área da realização da mesma, após parecer da respetiva câmara municipal.
-A autorização prévia a que se refere o número anterior deve ser solicitada pela organização do evento com a antecedência mínima de 15 dias, mediante requerimento dirigido ao diretor-geral da DGAV, acompanhado dos seguintes documentos:
+1. A participação de animais de companhia em concursos, exposições, espetáculos, manifestações culturais, divertimentos públicos, atividades performativas, cinematográficas e audiovisuais, campanhas publicitárias ou outros eventos onde participem animais de companhia carece de autorização do diretor-geral da DGAV da área da realização da mesma, após parecer da respetiva câmara municipal.
+2. A autorização prévia a que se refere o número anterior deve ser solicitada pela organização do evento com a antecedência mínima de 15 dias, mediante requerimento dirigido ao diretor-geral da DGAV, acompanhado dos seguintes documentos:
 a) Planta do local de realização do evento e parecer da respetiva câmara municipal, incluindo em relação ao ruído e recinto, se aplicável;
 b) Duração da participação dos animais no evento;
 c) Identificação do(s) médico(s) veterinário(s) responsável(eis);
 d) Regulamento sanitário e de bem-estar animal do evento, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes.
-Só serão admitidos no evento os animais de companhia que:
+3. Só serão admitidos no evento os animais de companhia que:
 a) Estejam registados no SIAC ou, no caso de animais provenientes de outros países, através do PAC que permita uma identificação rigorosa do animal;
 b) Quando aplicável, possuam prova de vacinação antirrábica dentro do prazo de validade, conforme determinado anualmente por despacho do diretor-geral da DGAV, nos termos da legislação e regulamentação em vigor;
 c) Possuam, dentro dos prazos de validade e efetuadas há mais de oito dias, as vacinações contra as principais doenças infectocontagiosas da espécie;
 d) Não tenham sido submetidos a intervenções cirúrgicas em infração ao disposto na alínea i) do n.º 1 do artigo 12.º e no artigo 34.º.
-Compete à organização do evento:
+4. Compete à organização do evento:
 a) Assegurar a presença do número de médicos veterinários necessários ao cumprimento do disposto neste decreto-lei;
 b) Assegurar que o local onde o evento decorre reúne as condições que permitam salvaguardar o disposto no presente decreto-lei;
 c) Salvaguardar os aspetos de segurança, no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público quando fora do evento;
 d) Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções;
 e) Assegurar que a exposição, incluindo os expositores, possui todas as licenças e autorizações necessárias à sua realização.
-Compete aos médicos veterinários responsáveis:
+5. Compete aos médicos veterinários responsáveis:
 a) Verificar o cumprimento do registo obrigatório no SIAC;
 b) Proceder ao exame clínico dos animais que se apresentam para participar no evento;
 c) Examinar a documentação sanitária dos animais;
 d) Prestar a assistência médico-veterinária que se revelar necessária à salvaguarda do bem-estar animal durante o evento;
 e) Proceder às observações que entenderem necessárias para a defesa sanitária do evento.
-A DGAV pode, sempre que entender necessário, determinar a realização de quaisquer exames médico-veterinários, laboratoriais ou outros, para verificar se foi administrada a um animal de companhia qualquer substância, tratamento ou procedimento com vista a aumentar ou diminuir o nível natural das capacidades fisiológicas e etológicas desse animal.
-Os eventos sem fins lucrativos que visem a adoção de animais de companhia, os passeios de animais organizados por centros de bem-estar animal ou associações zoófilas, ou outros eventos de socialização, são objeto de comunicação prévia à câmara municipal e à DGAV.
-A comunicação prévia a que se refere o número anterior é isenta de taxas.
-É proibida a participação de animais de companhia em eventos onde seja utilizada pirotecnia.</t>
+6. A DGAV pode, sempre que entender necessário, determinar a realização de quaisquer exames médico-veterinários, laboratoriais ou outros, para verificar se foi administrada a um animal de companhia qualquer substância, tratamento ou procedimento com vista a aumentar ou diminuir o nível natural das capacidades fisiológicas e etológicas desse animal.
+7. Os eventos sem fins lucrativos que visem a adoção de animais de companhia, os passeios de animais organizados por centros de bem-estar animal ou associações zoófilas, ou outros eventos de socialização, são objeto de comunicação prévia à câmara municipal e à DGAV.
+8. A comunicação prévia a que se refere o número anterior é isenta de taxas.
+9. É proibida a participação de animais de companhia em eventos onde seja utilizada pirotecnia.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -2566,25 +2566,25 @@
       <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Artigo 79.º - Concursos e exposições
-- A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM. 
-- A autorização prévia a que se refere o número anterior deve ser solicitada, pela organização da exposição, com a antecedência mínima de 15 dias, à câmara municipal da área da realização da exposição, mediante requerimento acompanhado dos seguintes documentos: 
-Descrição das condições de alojamento e manutenção dos animais; 
-A identificação do(s) médico(s) veterinário(s) responsável(eis) pela exposição ou concurso; 
-Regulamento sanitário do concurso ou exposição, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes. 
-- Só são admitidos a concurso os cães e gatos que: 
-Estejam identificados eletronicamente nos termos do disposto no presente diploma, no caso dos concorrentes nacionais ou, no caso de animais provenientes de outros países, de acordo com as disposições da legislação específica sobre a matéria; 
-Sejam portadores de boletim sanitário de cães e gatos ou passaporte de animal de companhia e possuam prova de vacinação antirrábica dentro do prazo de validade, no caso dos animais com idade superior a três meses; 
-Possuam dentro dos prazos de validade e efetuadas há mais de oito dias as vacinações contra as principais doenças infecto-contagiosas da espécie, comprovadas pelas vinhetas de vacinação respetiva, apostas no boletim sanitário de cães e gatos, devidamente autenticadas por um médico veterinário. 
-4 - Compete à organização da exposição: 
-Assegurar a presença do número de médicos veterinários necessário ao cumprimento do disposto no presente diploma; 
-Assegurar que o local onde a exposição decorre reúne as condições que permitam salvaguardar o disposto nas normas do presente diploma, em especial no que se refere à saúde e ao bem-estar dos animais exibidos; 
-Salvaguardar os aspetos de segurança, em particular no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público, quando fora do concurso ou quando não estejam a competir; 
-Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções, designadamente as seguintes: 
-Verificar a identificação electrónica dos animais sempre que obrigatória e a sua correspondência com o constante do boletim sanitário de cães e gatos; 
-Proceder ao exame clínico dos animais que se apresentam para participar na exposição ou concurso e impedir a participação de animais doentes ou feridos;
-Examinar a documentação sanitária dos animais; 
-Prestar a assistência médico-veterinária que se revelar necessária durante o evento; 
-Proceder às observações que entenderem necessárias para a defesa sanitária da exposição ou concurso. 
+1 - A realização de concursos e exposições com animais de companhia carece de autorização prévia da câmara municipal, ficando esta dependente do parecer vinculativo do MVM.
+2 - A autorização prévia a que se refere o número anterior deve ser solicitada, pela organização da exposição, com a antecedência mínima de 15 dias, à câmara municipal da área da realização da exposição, mediante requerimento acompanhado dos seguintes documentos:
+a) Descrição das condições de alojamento e manutenção dos animais;
+b) A identificação do(s) médico(s) veterinário(s) responsável(eis) pela exposição ou concurso;
+c) Regulamento sanitário do concurso ou exposição, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes.
+3 - Só são admitidos a concurso os cães e gatos que:
+d) Estejam identificados eletronicamente nos termos do disposto no presente diploma, no caso dos concorrentes nacionais ou, no caso de animais provenientes de outros países, de acordo com as disposições da legislação específica sobre a matéria;
+b) Sejam portadores de boletim sanitário de cães e gatos ou passaporte de animal de companhia e possuam prova de vacinação antirrábica dentro do prazo de validade, no caso dos animais com idade superior a três meses;
+c) Possuam dentro dos prazos de validade e efetuadas há mais de oito dias as vacinações contra as principais doenças infecto-contagiosas da espécie, comprovadas pelas vinhetas de vacinação respetiva, apostas no boletim sanitário de cães e gatos, devidamente autenticadas por um médico veterinário.
+4 - Compete à organização da exposição:
+a) Assegurar a presença do número de médicos veterinários necessário ao cumprimento do disposto no presente diploma;
+b) Assegurar que o local onde a exposição decorre reúne as condições que permitam salvaguardar o disposto nas normas do presente diploma, em especial no que se refere à saúde e ao bem-estar dos animais exibidos;
+c) Salvaguardar os aspetos de segurança, em particular no caso de animais potencialmente perigosos, que deverão estar convenientemente açaimados ou protegidos do contacto com o público, quando fora do concurso ou quando não estejam a competir;
+d) Disponibilizar os meios que os médicos veterinários considerem necessários ao bom desempenho das suas funções, designadamente as seguintes:
+i) Verificar a identificação electrónica dos animais sempre que obrigatória e a sua correspondência com o constante do boletim sanitário de cães e gatos;
+ii) Proceder ao exame clínico dos animais que se apresentam para participar na exposição ou concurso e impedir a participação de animais doentes ou feridos;
+iii) Examinar a documentação sanitária dos animais;
+iv) Prestar a assistência médico-veterinária que se revelar necessária durante o evento;
+v) Proceder às observações que entenderem necessárias para a defesa sanitária da exposição ou concurso.
 5 - A exposição de animais para adoção, promovida por associações de proteção animal ou por particulares, que não nos alojamentos para hospedagem registados no âmbito do presente diploma, depende de autorização prévia do município, sob parecer vinculativo do MVM.</t>
         </is>
       </c>
@@ -2596,9 +2596,9 @@
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Artigo 4.º - Exposições
-A participação de cães e gatos em concursos e exposições está sujeita às normas sanitárias emitidas pela DGV.
-A realização de concursos e exposições carece de autorização da DRA da área da realização da mesma, após parecer da respectiva câmara municipal.
-A autorização prévia a que se refere o número anterior deve ser solicitada pela organização da exposição com a antecedência mínima de 15 dias na câmara municipal da área da realização da exposição, mediante requerimento dirigido ao director regional de agricultura respectivo para efeitos do disposto no número anterior, acompanhado dos seguintes documentos:
+1. A participação de cães e gatos em concursos e exposições está sujeita às normas sanitárias emitidas pela DGV.
+2. A realização de concursos e exposições carece de autorização da DRA da área da realização da mesma, após parecer da respectiva câmara municipal.
+3. A autorização prévia a que se refere o número anterior deve ser solicitada pela organização da exposição com a antecedência mínima de 15 dias na câmara municipal da área da realização da exposição, mediante requerimento dirigido ao director regional de agricultura respectivo para efeitos do disposto no número anterior, acompanhado dos seguintes documentos:
 a) Planta do local de realização do concurso ou exposição;
 b) A identificação do(s) médico(s) veterinário(s) responsável(eis) pela exposição ou concurso;
 c) Regulamento sanitário do concurso ou exposição, onde deve estar especificado o modo como se prevê dar cumprimento ao disposto nos números seguintes.
@@ -2621,22 +2621,22 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Cães/gatos em concursos/exposições</t>
+          <t>— Cães/gatos em concursos/exposições</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Cães/gatos em concursos/exposições e acrescenta adoções
-Parecer MVM vinculativo</t>
+          <t>— Cães/gatos em concursos/exposições e acrescenta adoções
+— Parecer MVM vinculativo</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
-Câmara Municipal (consultivo)
-Comunicação prévia isenta de taxa para sem fins lucrativos
-Possibilidade de exames de dopagem
-Proibida pirotecnia</t>
+          <t>— Todos animais de companhia em múltiplos eventos (concursos, campanhas, cinema, etc.)
+— Câmara Municipal (consultivo)
+— Comunicação prévia isenta de taxa para sem fins lucrativos
+— Possibilidade de exames de dopagem
+— Proibida pirotecnia</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
@@ -2664,19 +2664,19 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
-Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
+          <t>1. All dogs and cats kept in establishments placed on the market or owned by pet owners or by any other natural or legal persons, shall be individually identified by means of a single injectable transponder containing a readable microchip that complies with the requirements set out in Annex II.
+2. Operators shall ensure that dogs and cats born in their establishments are individually identified within three months after their birth, and in any event before the date that they are placed on the market.
 Operators of selling establishments and shelters, and operators who place and are responsible for dogs and cats in foster homes shall ensure that dogs and cats that enter their establishments or come under their responsibility are individually identified within 30 days of arrival and in any event before the date of their placing on the market.
 Pet owners and any other natural or legal persons other than operators who own dogs or cats, shall ensure that every dog or cat is individually identified at the latest when it reaches the age of three months or, if the dog or cat is placed on the market, before the date of that placing on the market.
 The implantation of the transponder shall be performed by a veterinarian. Member States may allow the implantation of transponders by persons other than veterinarians provided that they adopt national rules laying down  the minimum qualifications that such persons are required to have.
 Where dogs and cats have been individually identified by means of an injectable transponder containing a microchip in accordance with Union or national law before … [date two years after the date of entry into force of this Regulation] they shall be considered to be compliant with the requirements in paragraph 1 and the first, second, third and fourth subparagraphs of this paragraph, provided that the microchip is still readable.
-Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database referred to in Article 23. 
+3. Within two working days after their identification, the dogs and cats shall be registered by a veterinarian in a national database referred to in Article 23.
 Member States may allow registration by persons other than veterinarians, provided that the Member States have measures in place to ensure the accuracy of information that those persons enter in the database. For dogs and cats kept in establishments, the registration shall be made in the name of the operator of the establishment responsible for the dog or the cat. For dogs and cats owned by any other natural and legal persons, the registration shall be made in the name of those persons.
 Member States may grant exemptions from the first subparagraph of this paragraph in respect of military, police and customs dogs.
-Where dogs or cats are placed on the market or are donated in an occasional manner by natural persons without using online advertising, the natural or legal person transferring the ownership of, or responsibility for, the dog or cat shall ensure that the change of ownership of, or responsibility for, the dog or cat is recorded in the database referred to in Article 23, within two weeks from the date of that transfer, in accordance with the conditions laid down by the Member State responsible for that database.
-In the case of the death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall ensure that the death is recorded in the database referred to in Article 23, in accordance with the conditions laid down by the Member State responsible for that database.
-Where a transponder is or becomes unreadable, the operator or the natural or legal person responsible for the dog or cat shall ensure that a new transponder is injected and that the registration in the database is updated with the identification number of that new transponder.
-The identification and registration requirements of this Article shall apply as follows:
+4. Where dogs or cats are placed on the market or are donated in an occasional manner by natural persons without using online advertising, the natural or legal person transferring the ownership of, or responsibility for, the dog or cat shall ensure that the change of ownership of, or responsibility for, the dog or cat is recorded in the database referred to in Article 23, within two weeks from the date of that transfer, in accordance with the conditions laid down by the Member State responsible for that database.
+5. In the case of the death of a dog or a cat, the operator, pet owner or natural or legal person owning the dog or cat shall ensure that the death is recorded in the database referred to in Article 23, in accordance with the conditions laid down by the Member State responsible for that database.
+6. Where a transponder is or becomes unreadable, the operator or the natural or legal person responsible for the dog or cat shall ensure that a new transponder is injected and that the registration in the database is updated with the identification number of that new transponder.
+7. The identification and registration requirements of this Article shall apply as follows:
 (a) 	for operators and natural or legal persons placing dogs and cats on the market from ... [4 years from the entry into force of this Regulation];
 (b)	for pet owners and other natural or legal persons other than operators, who do not place dogs on the market: from … [10 years from entry into force of this Regulation];
 (c)	 for pet owners and other natural or legal persons other than operators, who do not place cats on the market: from … [15 years from entry into force of this Regulation.</t>
@@ -2725,7 +2725,7 @@
           <t>1 — Todos os cães devem ser identificados e registados, entre os três e os seis meses de idade.
 2 — Os gatos em exposição, para fins comerciais ou lucrativos, em estabelecimentos de venda, locais de criação, feiras ou concursos, provas funcionais, publicidade ou fins similares, devem ser identificados e registados entre os três e os seis meses de idade.
 4 — Os cães e gatos são identificados através de método electrónico e registados na base de dados nacional.
-— A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.
+1 — A identificação electrónica é efetuada através da aplicação subcutânea de um microchip no centro da face lateral esquerda do pescoço.
 (…)</t>
         </is>
       </c>
@@ -2738,7 +2738,7 @@
         <is>
           <t>1 — A identificação dos animais de companhia, pela sua marcação e registo no SIAC, deve ser realizada até 120 dias após o seu nascimento.
 2 — Na impossibilidade de determinar a data de nascimento exata, para efeitos de contagem do prazo referido no número anterior, a identificação deve ser efetuada até à perda dos dentes incisivos de leite.
-— Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.
+1 — Sem prejuízo dos números anteriores, e relativamente aos cães, gatos e furões que sejam cedidos e ou comercializados a partir de um criador ou de um estabelecimento autorizado para a detenção de animais de companhia, nomeadamente os centros de hospedagem com ou sem fins lucrativos e os centros de recolha oficiais, deve ser assegurada a sua marcação e registo no SIAC antes de abandonarem a instalação de nascimento ou de alojamento, independentemente da sua idade.
 (…)</t>
         </is>
       </c>
@@ -2854,7 +2854,7 @@
 3 – O contrato de compra e venda deve integrar informação relativamente às obrigações legais do detentor, às necessidades de bem-estar específicas da espécie e do animal em concreto, bem como a todo o historial clínico do animal, incluindo rastreios genéticos e despistes de doenças realizados, bem como doenças congénitas comuns da raça ou hereditárias a considerar pelo comprador.
 5 – O dever de informação referido no número anterior inclui, também, o regime alimentar do animal, aconselhamento sobre a adaptação ao novo lar, controlo reprodutivo, socialização e métodos de educação e treino baseados no reforço positivo, bem como os dados de contacto do vendedor.
 6 - No caso dos cães e gatos, o contrato de compra e venda deve prever também a indemnização do comprador no caso de doença congénita ou viral imputada à criação, autorização de reprodução no caso de criadores com alojamento devidamente licenciado para o efeito, ou compromisso de não reprodução com obrigatoriedade de esterilização até aos seis meses de idade.
-7 - O contrato de compra e venda de animais de companhia identifica os meios de contacto entre o comprador e o vendedor, ficando este obrigado a prestar apoio na eventualidade de falta de adaptação e integração do animal, incluindo o auxílio na busca de um novo detentor para o mesmo. 
+7 - O contrato de compra e venda de animais de companhia identifica os meios de contacto entre o comprador e o vendedor, ficando este obrigado a prestar apoio na eventualidade de falta de adaptação e integração do animal, incluindo o auxílio na busca de um novo detentor para o mesmo.
 Artigo 92.º - Requisitos de validade do anúncio de transmissão de animal de companhia
 1 - Qualquer anúncio de transmissão, gratuita ou onerosa, de animais de companhia deve conter as seguintes informações:
 a) A data de nascimento do animal, ou data de nascimento aproximada, no caso de anúncios de cedência gratuita em que não seja conhecida a data exata do nascimento;
@@ -2872,13 +2872,13 @@
 4 - Os cães e gatos só podem ser considerados de raça pura se estiverem inscritos no livro de origens português, caso contrário são identificados como cão ou gato de raça indeterminada.
 5 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.
 Artigo 93.º - Plataformas de Internet para anunciar a transmissão de animais
-- As plataformas de Internet disponíveis para anunciar a transmissão, gratuita ou onerosa, de animais de companhia, apenas podem publicitar os anúncios que cumpram os requisitos dispostos no artigo anterior.
-- As plataformas de Internet têm o dever de implementar e manter um sistema de controlo e de validação destinado à verificação da veracidade dos dados introduzidos pelo anunciante.
+1. - As plataformas de Internet disponíveis para anunciar a transmissão, gratuita ou onerosa, de animais de companhia, apenas podem publicitar os anúncios que cumpram os requisitos dispostos no artigo anterior.
+2. - As plataformas de Internet têm o dever de implementar e manter um sistema de controlo e de validação destinado à verificação da veracidade dos dados introduzidos pelo anunciante.
 Artigo 94.º - Requisitos de validade da transmissão de propriedade de animal de companhia
-1 - Qualquer transmissão de propriedade, gratuita ou onerosa, de animal de companhia deve ser acompanhada, no momento da transmissão, dos seguintes documentos entregues ao adquirente: 
+1 - Qualquer transmissão de propriedade, gratuita ou onerosa, de animal de companhia deve ser acompanhada, no momento da transmissão, dos seguintes documentos entregues ao adquirente:
 a) Contrato de adoção ou de compra e venda do animal e respetiva fatura, nos termos do disposto no artigo 42.º, referente ao procedimento de adoção, e no artigo 91.º, referente ao procedimento de venda.
  b) Documento de identificação do animal, nos termos do disposto no n.º 6 do artigo 26.º.
-c) Declaração médico-veterinária, com prazo de pelo menos 15 dias, que ateste que o animal se encontra de boa saúde; 
+c) Declaração médico-veterinária, com prazo de pelo menos 15 dias, que ateste que o animal se encontra de boa saúde;
 d) Informação completa sobre o historial clínico do animal, sem prejuízo das informações que deverão constar no DIAC.
 e) Apresentação da licença de detenção prevista no artigo 102.º, no caso de animais potencialmente perigosos;
 f) Prova da legalidade dos animais de companhia.
@@ -2886,7 +2886,7 @@
 Artigo 95.º - Local de venda dos animais
 1 - Os animais de companhia não podem ser vendidos por entidade transportadora ou através da Internet, designadamente através de quaisquer portais ou plataformas.
 2 - Os animais de companhia não podem ser publicitados na Internet, mas a compra e venda dos mesmos apenas é admitida no local de criação ou em estabelecimentos devidamente licenciados.
-Artigo 115.º 
+Artigo 115.º
 n.º 3 - É proibida a publicidade e comercialização de animais perigosos ou que demonstrem comportamento agressivo.</t>
         </is>
       </c>
@@ -2985,7 +2985,7 @@
 a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
 b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 12.º, parágrafo 3;
 c) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
-2. As autoridades competentes podem delegar a tarefa referida na alínea (c) 
+2. As autoridades competentes podem delegar a tarefa referida na alínea (c)
 3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
@@ -2996,42 +2996,42 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Artigo 118.º - Reserva de atividade de treinadores de cães 
+          <t>Artigo 118.º - Reserva de atividade de treinadores de cães
 O treino de cães para qualquer fim, incluindo o treino básico de socialização e de obediência, de cães de assistência ou intervenções e terapias assistidas por animais, de cães para competição e para atividades desportivas, recreativas e para fins económicos, só pode ser ministrado por treinador possuidor do respetivo título profissional, emitido nos termos do artigo seguinte.
-Artigo 119.º - Título profissional de treinador de cães 
- 1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV 
-2 - Sem prejuízo do disposto nos n.ºs 5 e 6, o requerente de título profissional deve reunir, cumulativamente, os seguintes requisitos: 
-a) Ser maior de idade e não estar interdito ou inabilitado, por decisão judicial, para gerir a sua pessoa e os seus bens; 
-b) Ter como habilitação mínima o 12.º ano de escolaridade ou equivalente; 
-c) Apresentar certificado do registo criminal do qual resulte não ter sido o candidato à certificação de treinadores condenado, por sentença transitada em julgado, há menos de cinco anos, por qualquer dos crimes previstos no presente decreto-lei, por crime de homicídio por negligência, por crime doloso contra a vida, a integridade física, a liberdade pessoal, a liberdade e autodeterminação sexual, a saúde pública ou a paz pública, tráfico de estupefacientes e substâncias psicotrópicas, tráfico de pessoas, tráfico de armas, crimes contra animais de companhia, ou por outro crime doloso cometido com uso de violência; 
-d) Ser detentor do certificado de qualificações referido no artigo seguinte. 
-3 - Para efeito da obtenção do título profissional de treinador de cães, o requerente de título profissional deve apresentar ao ICNF, I.P., um documento de identificação civil e o certificado do registo criminal. 
-4 - O ICNF, I.P., dispõe do prazo de 20 dias para decidir o requerimento referido no número anterior, após o que, na ausência de decisão, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos. 
-5 - O treinador de cães nacional de Estado-membro da União Europeia ou do Espaço Económico Europeu cujas qualificações tenham sido obtidas fora de Portugal e pretenda estabelecer-se em território nacional requer a emissão do seu título profissional ao ICNF, I.P., nos termos do artigo 47.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio, comprovando adicionalmente os requisitos referidos nas alíneas a) e c) do n.º 2. 
-6 - Os profissionais provenientes de outro Estado membro da União Europeia ou do Espaço Económico Europeu que pretendam exercer a atividade de treino de cães em território nacional em regime de livre prestação de serviços ficam sujeitos à verificação prévia de qualificações constante do artigo 6.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio. 
+Artigo 119.º - Título profissional de treinador de cães
+ 1 - O acesso e exercício da atividade de treinador de cães depende da obtenção do respetivo título profissional, emitido pela DGAV
+2 - Sem prejuízo do disposto nos n.ºs 5 e 6, o requerente de título profissional deve reunir, cumulativamente, os seguintes requisitos:
+a) Ser maior de idade e não estar interdito ou inabilitado, por decisão judicial, para gerir a sua pessoa e os seus bens;
+b) Ter como habilitação mínima o 12.º ano de escolaridade ou equivalente;
+c) Apresentar certificado do registo criminal do qual resulte não ter sido o candidato à certificação de treinadores condenado, por sentença transitada em julgado, há menos de cinco anos, por qualquer dos crimes previstos no presente decreto-lei, por crime de homicídio por negligência, por crime doloso contra a vida, a integridade física, a liberdade pessoal, a liberdade e autodeterminação sexual, a saúde pública ou a paz pública, tráfico de estupefacientes e substâncias psicotrópicas, tráfico de pessoas, tráfico de armas, crimes contra animais de companhia, ou por outro crime doloso cometido com uso de violência;
+d) Ser detentor do certificado de qualificações referido no artigo seguinte.
+3 - Para efeito da obtenção do título profissional de treinador de cães, o requerente de título profissional deve apresentar ao ICNF, I.P., um documento de identificação civil e o certificado do registo criminal.
+4 - O ICNF, I.P., dispõe do prazo de 20 dias para decidir o requerimento referido no número anterior, após o que, na ausência de decisão, não há lugar a deferimento tácito, podendo o interessado obter a tutela adequada junto dos tribunais administrativos.
+5 - O treinador de cães nacional de Estado-membro da União Europeia ou do Espaço Económico Europeu cujas qualificações tenham sido obtidas fora de Portugal e pretenda estabelecer-se em território nacional requer a emissão do seu título profissional ao ICNF, I.P., nos termos do artigo 47.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio, comprovando adicionalmente os requisitos referidos nas alíneas a) e c) do n.º 2.
+6 - Os profissionais provenientes de outro Estado membro da União Europeia ou do Espaço Económico Europeu que pretendam exercer a atividade de treino de cães em território nacional em regime de livre prestação de serviços ficam sujeitos à verificação prévia de qualificações constante do artigo 6.º da Lei n.º 9/2009, de 4 de março, alterada pela Lei n.º 31/2021, de 24 de maio.
 Artigo 120.º - Certificado de qualificações
- 1 - O certificado de qualificações de treinador de cães, referido na alínea d) do n.º 2 do artigo anterior, é emitido por entidade certificadora, após aprovação em provas teóricas e práticas através das quais o candidato demonstre a sua habilitação técnica para influenciar e adaptar o carácter do canídeo, com base em métodos de reforço positivo, de forma a garantir uma detenção responsável, bem como a vinculação e integração positiva com o detentor e o meio ambiente, promovendo o bem-estar animal e a segurança de pessoas, outros animais e bens, devendo ser dado conhecimento do certificado ao ICNF, I.P, no prazo máximo de 10 dias. 
-2 - As provas teóricas referidas no número anterior devem incidir sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos, devendo a avaliação prática fazer-se com a presença de animal próprio ou de terceiros, sempre devidamente identificado, para que cada cão só possa realizar a prova com um candidato. 
+ 1 - O certificado de qualificações de treinador de cães, referido na alínea d) do n.º 2 do artigo anterior, é emitido por entidade certificadora, após aprovação em provas teóricas e práticas através das quais o candidato demonstre a sua habilitação técnica para influenciar e adaptar o carácter do canídeo, com base em métodos de reforço positivo, de forma a garantir uma detenção responsável, bem como a vinculação e integração positiva com o detentor e o meio ambiente, promovendo o bem-estar animal e a segurança de pessoas, outros animais e bens, devendo ser dado conhecimento do certificado ao ICNF, I.P, no prazo máximo de 10 dias.
+2 - As provas teóricas referidas no número anterior devem incidir sobre comportamento animal, metodologia de treino, aprendizagem e extinção de comportamentos, devendo a avaliação prática fazer-se com a presença de animal próprio ou de terceiros, sempre devidamente identificado, para que cada cão só possa realizar a prova com um candidato.
 3 - A certificação das entidades certificadoras, o modelo de provas e a avaliação dos candidatos são definidos por portaria do membro do Governo responsável pela área da conservação da natureza.
-Artigo 121.º - Lista de treinadores de cães 
- 1 - A emissão do título profissional, nos termos do disposto no artigo 119.º, determina a inscrição automática na lista de treinadores disponível no sítio na Internet do ICNF, I.P.. 
+Artigo 121.º - Lista de treinadores de cães
+ 1 - A emissão do título profissional, nos termos do disposto no artigo 119.º, determina a inscrição automática na lista de treinadores disponível no sítio na Internet do ICNF, I.P..
 2 – O ICNF, I.P., mantém atualizada a lista referida no número anterior, cuja base de dados deve respeitar o disposto no Regulamento Geral de Proteção de Dados.
 Artigo 122.º - Obrigações dos treinadores
- 1 - Os treinadores de cães devem manter, pelo prazo mínimo de 10 anos, e disponibilizar às entidades fiscalizadoras, sempre que solicitado, um registo contendo: 
-a) A identificação dos animais submetidos a treino, com a indicação do motivo, das datas de início e conclusão do treino e respetivos resultados; 
-b) A identificação dos seus detentores, com indicação dos nomes e moradas; 
-c) A identificação dos animais submetidos a treinos de manutenção. 
-2 - A cada animal treinado é emitido um documento que ateste a realização do treino, quando este tenha sido concluído com aproveitamento. 
-3 - O treinador é obrigado a publicitar, em local visível ao público, o seu título profissional. 
+ 1 - Os treinadores de cães devem manter, pelo prazo mínimo de 10 anos, e disponibilizar às entidades fiscalizadoras, sempre que solicitado, um registo contendo:
+a) A identificação dos animais submetidos a treino, com a indicação do motivo, das datas de início e conclusão do treino e respetivos resultados;
+b) A identificação dos seus detentores, com indicação dos nomes e moradas;
+c) A identificação dos animais submetidos a treinos de manutenção.
+2 - A cada animal treinado é emitido um documento que ateste a realização do treino, quando este tenha sido concluído com aproveitamento.
+3 - O treinador é obrigado a publicitar, em local visível ao público, o seu título profissional.
 4 - Sempre que um treinador certificado estabelecido em território nacional cesse a sua atividade neste território, deve comunicar este facto à DGAV
 Artigo 123.º - Suspensão ou cassação do título profissional
-A violação do disposto no presente decreto-lei, incluindo a violência ou agressividade contra os animais ou seus detentores, podem determinar a suspensão ou o cancelamento do título profissional. 
-A condenação do treinador, por sentença transitada em julgado, aquando da posse de título profissional como treinador de cães, por crimes dolosos contra bens jurídicos pessoais puníveis com pena de prisão igual ou superior a 3 anos, por crimes contra a paz pública ou por qualquer crime previsto no presente decreto-lei ou crime contra animais de companhia, determina a suspensão ou o cancelamento do título profissional. 
-Com o cancelamento ou suspensão do título profissional, deve o profissional entregar de imediato o respetivo título ao ICNF, I.P, pelo período de aplicação da sanção em causa, sob pena de o mesmo ser cassado.
+1. A violação do disposto no presente decreto-lei, incluindo a violência ou agressividade contra os animais ou seus detentores, podem determinar a suspensão ou o cancelamento do título profissional.
+2. A condenação do treinador, por sentença transitada em julgado, aquando da posse de título profissional como treinador de cães, por crimes dolosos contra bens jurídicos pessoais puníveis com pena de prisão igual ou superior a 3 anos, por crimes contra a paz pública ou por qualquer crime previsto no presente decreto-lei ou crime contra animais de companhia, determina a suspensão ou o cancelamento do título profissional.
+3. Com o cancelamento ou suspensão do título profissional, deve o profissional entregar de imediato o respetivo título ao ICNF, I.P, pelo período de aplicação da sanção em causa, sob pena de o mesmo ser cassado.
 Secção II - Treino e utilização de cães para fins específicos
 Artigo 124.º - Obrigações especiais para treino e utilização de cães para fins específicos
-O treino e a utilização de cães para fins de assistência, intervenções e terapias assistidas por animais, competição e atividades desportivas, recreativas e de trabalho, deve garantir a todo o tempo a salvaguarda do bem-estar do animal.
-Para efeitos do disposto no número anterior, deve ser considerada a existência de um plano de profilaxia médico-veterinária, que a duração e frequência das sessões ou atividades respeitam os períodos de descanso e recuperação do animal, que as interações humano-animal são positivas, que o animal tem a possibilidade de se retirar da atividade quando se mostra relutante em participar nela ou demonstre sinais de cansaço fadiga, que a condição física e temperamento do animal são adequados à atividade a realizar, que o animal apresenta motivação para a tarefa, que o detentor reconhece e atende aos sinais de stresse ou desconforto por parte do detentor, e que são proporcionados ao animal oportunidades para momentos lúdicos e de relaxamento.</t>
+1. O treino e a utilização de cães para fins de assistência, intervenções e terapias assistidas por animais, competição e atividades desportivas, recreativas e de trabalho, deve garantir a todo o tempo a salvaguarda do bem-estar do animal.
+2. Para efeitos do disposto no número anterior, deve ser considerada a existência de um plano de profilaxia médico-veterinária, que a duração e frequência das sessões ou atividades respeitam os períodos de descanso e recuperação do animal, que as interações humano-animal são positivas, que o animal tem a possibilidade de se retirar da atividade quando se mostra relutante em participar nela ou demonstre sinais de cansaço fadiga, que a condição física e temperamento do animal são adequados à atividade a realizar, que o animal apresenta motivação para a tarefa, que o detentor reconhece e atende aos sinais de stresse ou desconforto por parte do detentor, e que são proporcionados ao animal oportunidades para momentos lúdicos e de relaxamento.</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -3041,8 +3041,8 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
-O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
+          <t>1. Os detentores de cães devem promover o treino dos mesmos, com vista à sua socialização e obediência.
+2. O treino dos cães é realizado de acordo com as boas práticas em uso no exercício da atividade.</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais. 
+          <t>O RGBEAC cumpre os critérios ao prever um sistema robusto de certificação profissional para treinadores de cães com: título profissional obrigatório, requisitos de habilitação, provas teóricas e práticas, métodos baseados em reforço positivo, verificação de antecedentes criminais.
 Na legislação vigente só se encontra referências ao treino no Decreto-Lei n.º 315/2009, de 29 de Outubro, (regime dos cães perigosos e potencialmente perigosos), e no Decreto-Lei n.º 74/2007, de 27 de março, relativo ao treino em Cães de Assistência</t>
         </is>
       </c>
@@ -3099,32 +3099,32 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
-For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
-Member States shall ensure that their databases, as referred to in paragraph 1, comply with the requirements laid down by the implementing act referred to in paragraph 4, second subparagraph, point (b), to ensure their interoperability.
-The Commission shall establish and maintain an index database containing the minimum set of fields laid down in the implementing acts referred to in subparagraph 2, point (b). The Commission may entrust the development, maintenance and operation of that index database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
+          <t>1. Member States shall be responsible for establishing and maintaining databases for the registration of identified dogs and cats in accordance with Article 20(1) and (2) and Article 26(3) and Article 26(4), second subparagraph.
+2. For that purpose, the Member States may use databases maintained by another Member State, on the basis of appropriate arrangements between those Member States.
+3. Member States shall ensure that their databases, as referred to in paragraph 1, comply with the requirements laid down by the implementing act referred to in paragraph 4, second subparagraph, point (b), to ensure their interoperability.
+4. The Commission shall establish and maintain an index database containing the minimum set of fields laid down in the implementing acts referred to in subparagraph 2, point (b). The Commission may entrust the development, maintenance and operation of that index database to an independent entity, following a public selection process pursuant to the relevant provisions of Title VII of the Regulation (EU, Euratom) 2024/2509.
 The Commission shall adopt implementing acts laying down detailed arrangements concerning:
-the minimum content of the databases referred to in paragraph 1;
-the interoperability between Member States’ databases and the index database, including the minimum set of fields to be transmitted to the index database and the intervals of the transmission;
-the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in Article 21 (3) point (a).
-the registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
-the interconnection between the Member States’ databases referred to in paragraph 1, the pet travellers' database referred to in Article 26, paragraph 4, and the Information Management System for Official Controls (IMSOC), where relevant.
+(a) the minimum content of the databases referred to in paragraph 1;
+(b) the interoperability between Member States’ databases and the index database, including the minimum set of fields to be transmitted to the index database and the intervals of the transmission;
+(c) the functionality for providing proof of the identification and registration of a dog or a cat, as referred to in Article 21 (3) point (a).
+(d) the registry where Member States will declare their databases, and the necessary parameters for connecting those databases with one another in accordance with the provisions established pursuant to point (b);
+(e) the interconnection between the Member States’ databases referred to in paragraph 1, the pet travellers' database referred to in Article 26, paragraph 4, and the Information Management System for Official Controls (IMSOC), where relevant.
 The Commission shall adopt the implementing acts referred to in the second subparagraph, points (a) and (c) by ... [date two years after the date of entry into force of this Regulation]. It shall adopt the implementing acts referred to in the second subparagraph, points (b), (d) and (e) by ...[three years from the date of entry into force of this Regulation].
 Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
-Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
-Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
-A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
+          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
+2. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+3. Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
+4. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
 A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
-o conteúdo mínimo das bases de dados referidas no n.º 1;
-a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
-a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
-o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
-a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
+(a) o conteúdo mínimo das bases de dados referidas no n.º 1;
+(b) a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
+(c) a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
+(d) o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
+(e) a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
 A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
 Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
@@ -3137,10 +3137,10 @@
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º - Sistema de Informação de Animais de Companhia (SIAC)
-O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
-A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
-A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
-As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
+1. O SIAC reúne a informação relativa à rastreabilidade dos dispositivos de identificação, à identificação dos animais de companhia, à sua titularidade ou detenção e à informação relacionada com a defesa da saúde pública, saúde animal e bem-estar animal.
+2. A DGAV é a entidade responsável pelo SIAC, competindo-lhe assegurar o seu funcionamento e o tratamento seguro da informação.
+3. A DGAV pode atribuir a gestão do SIAC a outras entidades, mediante a celebração de protocolo e parecer prévio da Comissão Nacional de Proteção de Dados.
+4. As normas e procedimentos relativos ao funcionamento do SIAC constam de um Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -3206,16 +3206,16 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
-The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
-The Commission may adopt implementing acts, establishing a harmonized methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
+          <t>1. The competent authorities shall collect, analyse and publish the data on animal welfare set out in Annex III:
+2. The competent authorities shall draw up and transmit to the Commission a report in electronic form, on the data on animal welfare, set out in Annex III, by 31 August at three-yearly intervals. The first such report shall be drawn up and transmitted to the Commission by ... [date 6 years from the date of entry into force of this Regulation]. Each report shall contain a summary of the data gathered during the previous three years.
+3. The Commission may adopt implementing acts, establishing a harmonized methodology for collecting the data on animal welfare set out in Annex III and establishing a template for the report referred to in paragraph 2 of this Article. Those implementing acts shall be adopted in accordance with the examination procedure referred to in Article 29.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
-As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
-A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>1. As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
+2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
+3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3272,32 +3272,32 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
+          <t>1. The competent authorities of the Member States shall be controllers within the meaning of Regulation (EU) 2016/679 in relation to the processing of personal data collected under Articles 9 and 10 of this Regulation, as well as under Article 23(1) of this Regulation when used for the purposes of official control.
 The Commission shall be a controller within the meaning of Regulation (EU) 2018/1725 in relation to the processing of personal data collected under Article 21(5), Article 23(4), and Article 26(4), third subparagraph, , as well as under Article 23(1) of this Regulation when that data is used for the purposes of compliance with Article 108 of Regulation (EU) 2017/625 and the reporting obligations under this Regulation.
 It shall be prohibited for any person with access to the personal data referred to in the first and second subparagraphs to divulge any personal data the knowledge of which was acquired in the exercise of his or her duties or otherwise incidentally to such exercise. Member States and the Commission shall take all appropriate measures to enforce that prohibition.
 The personal data collected under the first and second subparagraphs shall not be used for purposes other than:
-official controls by Member States’ competent authorities of compliance with the welfare and traceability requirements of this Regulation and of compliance with Regulation (EU) 2016/429, including the detection of fraudulent practices; and
-compliance by the Commission with its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission’s reporting obligations under this Regulation.
-The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
-in the case of Articles 9 and 10, 10 years after the date of cessation of the activity of the establishment;
-in the case of Article 21(5), 18 months after the generation of the token referred to in Article 21(3), second subparagraph;
-in the case of Articles 23(1) and 23(4), 25 years after the first registration of the dog or cat in the database referred to in that Article or five years after the recording of the death of the dog or cat in that database;
-in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.</t>
+(a) official controls by Member States’ competent authorities of compliance with the welfare and traceability requirements of this Regulation and of compliance with Regulation (EU) 2016/429, including the detection of fraudulent practices; and
+(b) compliance by the Commission with its obligations under Article 108 of Regulation (EU) 2017/625 and with the Commission’s reporting obligations under this Regulation.
+2. The personal data referred to in paragraph 1 of this Article shall be retained for the following periods:
+(a) in the case of Articles 9 and 10, 10 years after the date of cessation of the activity of the establishment;
+(b) in the case of Article 21(5), 18 months after the generation of the token referred to in Article 21(3), second subparagraph;
+(c) in the case of Articles 23(1) and 23(4), 25 years after the first registration of the dog or cat in the database referred to in that Article or five years after the recording of the death of the dog or cat in that database;
+(d) in the case of Article 26(4), third subparagraph, 5 years after the date of pre-notification.</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
+          <t>1. As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
 A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
 É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
 Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
-controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
-o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
-Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
-no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
-no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
-no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
-(d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
+(a) controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
+(b) o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
+2. Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
+(a) no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
+(b) no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
+(c) no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
+(d) (d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3499,38 +3499,38 @@
       <c r="C24" s="3" t="inlineStr">
         <is>
           <t>The Commission is empowered to adopt delegated acts in accordance with Article 28 to amend the Annexes to this Regulation to take account of scientific and technical progress, including, where relevant, the scientific opinions of EFSA, as regards:
-a suitable number of animal carers in breeding and selling establishments;
-watering and feeding requirements and weaning process;
-temperature ranges;
-lighting requirements;
-ammonia and carbon monoxide levels;
-kennel and cattery designs;
-group housing;
-space allowances for various categories of dogs and cats;
-the frequency of pregnancies;
-the minimum and maximum age of bitches and queens for  breeding;
-socialisation, the provision of enrichments and other measures for meeting the behavioural needs of dogs and cats;
-the requirements for the transponders used to identify dogs and cats individually;
-the data to be collected for policy monitoring and evaluation.
+(a) a suitable number of animal carers in breeding and selling establishments;
+(b) watering and feeding requirements and weaning process;
+(c) temperature ranges;
+(d) lighting requirements;
+(e) ammonia and carbon monoxide levels;
+(f) kennel and cattery designs;
+(g) group housing;
+(h) space allowances for various categories of dogs and cats;
+(i) the frequency of pregnancies;
+(j) the minimum and maximum age of bitches and queens for  breeding;
+(k) socialisation, the provision of enrichments and other measures for meeting the behavioural needs of dogs and cats;
+(l) the requirements for the transponders used to identify dogs and cats individually;
+(m) the data to be collected for policy monitoring and evaluation.
 Any additions of requirements in the Annexes shall be based on updated scientific or technical evidence, in particular such evidence regarding the specific conditions needed to ensure the welfare of the dogs and cats covered by the scope of this Regulation. Where relevant, those delegated acts shall take into account social, economic and environmental impacts and shall provide for sufficient transition periods to allow the operators concerned to adapt to the new requirements.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
-Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
-Requisitos de abastecimento de água e alimentação e processo de desmame;
-Gamas de temperatura;
-Requisitos de iluminação;
-Níveis de amoníaco e monóxido de carbono;
-Conceção de canis e gatis;
-Alojamento em grupo;
-Espaços permitidos para diferentes categorias de cães e gatos;
-Frequência de gestações;
-Idade mínima e máxima de cadelas e gatas para reprodução;
-Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
-Requisitos para transponders utilizados na identificação individual de cães e gatos;
-Dados a recolher para avaliação e monitorização de políticas.
+(a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
+(b) Requisitos de abastecimento de água e alimentação e processo de desmame;
+(c) Gamas de temperatura;
+(d) Requisitos de iluminação;
+(e) Níveis de amoníaco e monóxido de carbono;
+(f) Conceção de canis e gatis;
+(g) Alojamento em grupo;
+(h) Espaços permitidos para diferentes categorias de cães e gatos;
+(i) Frequência de gestações;
+(j) Idade mínima e máxima de cadelas e gatas para reprodução;
+(k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
+(l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
+(m) Dados a recolher para avaliação e monitorização de políticas.
 Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
@@ -3592,22 +3592,22 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
-The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
-The delegation of power referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
-Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
-As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
-A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
+          <t>1. The power to adopt delegated acts is conferred on the Commission subject to the conditions laid down in this Article.
+2. The power to adopt delegated acts referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27 shall be conferred on the Commission for an indeterminate period of time from … [the date of entry into force of this Regulation].
+3. The delegation of power referred to in Article 7(8), Article 8(3), Article 13(2) and Article 27may be revoked at any time by the European Parliament or by the Council. A decision to revoke shall put an end to the delegation of the power specified in that decision. It shall take effect the day following the publication of the decision in the Official Journal of the European Union or at a later date specified therein. It shall not affect the validity of any delegated acts already in force.
+4. Before adopting a delegated act, the Commission shall consult experts designated by each Member State in accordance with the principles laid down in the Interinstitutional Agreement of 13 April 2016 on Better Law-Making.
+5. As soon as it adopts a delegated act, the Commission shall notify it simultaneously to the European Parliament and to the Council.
+6. A delegated act adopted pursuant to Article 7(8), Article 8(3), Article 13(2) or Article 27 shall enter into force only if no objection has been expressed either by the European Parliament or by the Council within a period of two months of notification of that act to the European Parliament and the Council or if, before the expiry of that period, the European Parliament and the Council have both informed the Commission that they will not object. That period shall be extended by two months at the initiative of the European Parliament or of the Council</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
-O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
-A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
-Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
-Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
-Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
+          <t>1. O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
+2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
+3. A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+4. Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
+5. Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
+6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3735,16 +3735,16 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
-Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
-A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
+          <t>1. This Regulation shall not prevent Member States from maintaining or adopting stricter national rules aimed at providing more extensive protection of the welfare of dogs and cats kept in establishments, and a greater traceability of dogs and cats, provided that those rules are not inconsistent with this Regulation and do not interfere with the proper functioning of the internal market.
+2. Member States shall, by ... [two years after the date of entry into force of this Regulation], inform the Commission about any existing stricter national rules that they intend to maintain in accordance with paragraph 1. Thereafter, Member States shall inform the Commission about stricter national rules before their adoption, unless the Member States have already notified the draft national rules as a draft technical regulation under Article 5 of Directive (EU) 2015/1535 of the European Parliament and of the Council. The Commission shall bring them to the attention of the other Member States.
+3. A Member State that has stricter national rules referred to in paragraph 1 shall not prohibit or impede the placing on the market within its territory of dogs and cats kept in another Member State on the grounds that the dogs and cats concerned have not been kept in accordance with its stricter national rules.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
-Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
-Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
+          <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
+2. Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
+3. Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3803,18 +3803,18 @@
         <is>
           <t>1.	On the basis of the reports received in accordance with Article 24 and any additional relevant information, the Commission shall publish, by ... [7 years from the date of entry into force of this Regulation] and thereafter at three-yearly intervals, a monitoring report on the welfare of dogs and cats placed on the market in the Union.
 2.	By … [14 years from the date of entry into force of this Regulation, the Commission shall carry out an evaluation of this Regulation and present a report on the main findings to the European Parliament, the Council, the European Economic and Social Committee, and the Committee of the Regions. In that evaluation and report the Commission shall assess, in particular:
-the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving their traceability, and reducing the illegal trade in them;
-the impact that this Regulation has had on operators of breeding and selling establishments and shelters, and of operators who place dogs and cats in foster homes, taking into account inter alia the administrative burden and compliance costs.
+a) the extent to which this Regulation has contributed to ensuring a high level of welfare for dogs and cats, improving their traceability, and reducing the illegal trade in them;
+b) the impact that this Regulation has had on operators of breeding and selling establishments and shelters, and of operators who place dogs and cats in foster homes, taking into account inter alia the administrative burden and compliance costs.
 3.	For the purposes of the reporting referred to in paragraph 2, Member States shall provide the Commission with the information necessary for the preparation of its report.</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
-Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
-O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
-O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
-Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
+          <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+2. Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
+a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
+b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
+3. Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3941,13 +3941,13 @@
         <is>
           <t>This Regulation shall enter into force on the twentieth day following that of its publication in the Official Journal of the European Union.
 It shall apply from ... [two years from the date of entry into force of this Regulation]. However,
-Article 16 shall apply from … [three years from the date of entry into force of this Regulation];
-Article 21(3) and Article 23(1) shall apply from … [four years from entry into force of this Regulation];
-Article 8(1) shall apply from 1 July 2036 and Article 8(2) shall apply from 1 July 2030;
-Article 15, Article 21(3), second subparagraph, (4) and (5), Article 22(1), points (a),(b) and (c), Article 23(3) and (4), and Article 26(1), (2) and (3) shall apply from … [five years from the date of entry into force of this Regulation];
-Article 12(2) and (3) shall apply from … [seven years from the date of entry into force of this Regulation];
-Article 10 shall apply from … [eight years from the date of entry into force of this Regulation]; and
-Article 26(4) shall apply from … [10 years from the entry into force of the Regulation].
+i. Article 16 shall apply from … [three years from the date of entry into force of this Regulation];
+ii. Article 21(3) and Article 23(1) shall apply from … [four years from entry into force of this Regulation];
+iii. Article 8(1) shall apply from 1 July 2036 and Article 8(2) shall apply from 1 July 2030;
+iv. Article 15, Article 21(3), second subparagraph, (4) and (5), Article 22(1), points (a),(b) and (c), Article 23(3) and (4), and Article 26(1), (2) and (3) shall apply from … [five years from the date of entry into force of this Regulation];
+v. Article 12(2) and (3) shall apply from … [seven years from the date of entry into force of this Regulation];
+vi. Article 10 shall apply from … [eight years from the date of entry into force of this Regulation]; and
+vii. Article 26(4) shall apply from … [10 years from the entry into force of the Regulation].
 This Regulation shall be binding in its entirety and directly applicable in all Member States.</t>
         </is>
       </c>
@@ -3955,13 +3955,13 @@
         <is>
           <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
 É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
-o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
-o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
-o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
-o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
-o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
-o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
-o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
+i. o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
+ii. o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
+iii. o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
+iv. o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
+v. o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
+vi. o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
+vii. o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
 O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
@@ -4024,22 +4024,22 @@
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Requirements applicable to establishments
-Feeding and watering
-Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
+1. Feeding and watering
+1.1 Dogs and cats shall be fed at least twice per day. Puppies and kittens shall be fed more frequently.
 However, those requirements shall not apply to livestock guardian dogs kept in breeding establishments during the periods when such dogs are used for guarding or training purposes.
-Each puppy or kitten shall be fed with colostrum during at least the first two days of its life. Thereafter, it shall be fed with milk from its mother or a lactating bitch or queen. If that is not possible, because the mother is ill or is otherwise unable to feed her offspring or unable to provide sufficient milk, the puppy or kitten shall be fed with a milk replacer that has been designed for puppies and kittens. The frequency of such feeding shall comply with the manufacturer’s instructions or those of a veterinarian.
-All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination of both, to allow them to gain bodyweight steadily.
-Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.</t>
+2.2 Each puppy or kitten shall be fed with colostrum during at least the first two days of its life. Thereafter, it shall be fed with milk from its mother or a lactating bitch or queen. If that is not possible, because the mother is ill or is otherwise unable to feed her offspring or unable to provide sufficient milk, the puppy or kitten shall be fed with a milk replacer that has been designed for puppies and kittens. The frequency of such feeding shall comply with the manufacturer’s instructions or those of a veterinarian.
+3.3 All unweaned puppies and kittens shall be fed enough milk, milk replacer or a combination of both, to allow them to gain bodyweight steadily.
+4.4 Weaning shall be performed by the gradual introduction of solid feed over a period that is not shorter than seven days and shall not be completed before the age of six weeks for puppies and kittens alike.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Alimentação e abeberamento
-Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência. 
+          <t>1. Alimentação e abeberamento
+1.1 Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
 No entanto, estes requisitos não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que esses cães sejam utilizados para fins de guarda ou de treino.
-Cada cachorro ou gatinho deve ser alimentado com colostro, pelo menos, durante os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da progenitora ou de uma cadela ou gata lactante. Se tal não for possível, por a progenitora estar doente ou estar de outro modo impossibilitada de alimentar a sua ninhada ou de fornecer leite em quantidade suficiente, o cachorro ou gatinho deve ser alimentado com um sucedâneo de leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as instruções do fabricante ou de um médico veterinário.
-Todos os cachorros e gatinhos não desmamados devem receber leite, sucedâneo de leite ou uma combinação de ambos em quantidade suficiente para lhes permitir aumentar de peso de forma constante
-O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
+2.2 Cada cachorro ou gatinho deve ser alimentado com colostro, pelo menos, durante os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da progenitora ou de uma cadela ou gata lactante. Se tal não for possível, por a progenitora estar doente ou estar de outro modo impossibilitada de alimentar a sua ninhada ou de fornecer leite em quantidade suficiente, o cachorro ou gatinho deve ser alimentado com um sucedâneo de leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as instruções do fabricante ou de um médico veterinário.
+3.3 Todos os cachorros e gatinhos não desmamados devem receber leite, sucedâneo de leite ou uma combinação de ambos em quantidade suficiente para lhes permitir aumentar de peso de forma constante
+4.4 O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4050,12 +4050,12 @@
       <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Artigo 33.º - Alimentação
-Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a idade, raça, categoria, nível de atividade e estado de saúde.
-Os animais devem receber alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.
-As refeições devem ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
-Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos.
-Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+1. Deve existir um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, consoante a idade, raça, categoria, nível de atividade e estado de saúde.
+2. Os animais devem receber alimentos saudáveis, adequados e convenientes ao seu normal desenvolvimento e acesso permanente a água potável.
+3. As refeições devem ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+4. Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos.
+5. Sempre que se justifique, devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6. Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
 Art.º 70.º - Reprodução de cães e gatos
 5 - As crias não podem ser separadas da progenitora antes da décima semana de idade, no caso dos cães, e antes da décima segunda semana de idade, no caso dos gatos, salvaguardado um período de desmame gradual.</t>
         </is>
@@ -4068,13 +4068,13 @@
       <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Artigo 46.º - Alimentação e abeberamento
-A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
-As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
-O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
-Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
-Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
-Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
-É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
+1. A alimentação dos animais de companhia, nos locais de criação, manutenção e venda bem como nos centros de recolha e instalações de hospedagem, deve obedecer a um programa de alimentação bem definido, de valor nutritivo adequado e distribuído em quantidade suficiente para satisfazer as necessidades alimentares das espécies e dos indivíduos, de acordo com a fase de evolução fisiológica em que se encontram, nomeadamente idade, sexo, fêmeas prenhes ou em fase de lactação.
+2. As refeições devem ainda ser variadas, sendo distribuídas segundo a rotina que mais se adequar à espécie.
+3. O número, formato e distribuição de comedouros e bebedouros deve ser tal que permita aos animais satisfazerem as suas necessidades sem que haja competição excessiva dentro do grupo.
+4. Os alimentos devem ser preparados e armazenados de acordo com padrões estritos de higiene, em locais secos, limpos, livres de agentes patogénicos e de produtos tóxicos e, no caso dos alimentos compostos devem, ainda, ser armazenados sobre estrados de madeira ou prateleiras.
+5. Devem existir aparelhos de frio para uma eficiente conservação dos alimentos.
+6. Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.
+7. É proibido alimentar animais com restos de comida, produtos de pastelaria e desperdícios da indústria alimentar e de restauração.</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -4135,17 +4135,17 @@
           <t>2.Housing
 2.1 Temperature
 In breeding establishments the temperature shall be maintained within a range of:
-22 to 28°C in whelping areas for the first 10 days of puppies' lives;
-18 to 27°C in kittening areas for the first 21 days of kittens' lives.
+(a) 22 to 28°C in whelping areas for the first 10 days of puppies' lives;
+(b) 18 to 27°C in kittening areas for the first 21 days of kittens' lives.
 2.2 Lighting
 Dogs and cats shall be exposed to light for at least 7 hours per day. Artificial light shall be broad spectrum or full spectrum with a frequency of at least 80 Hertz.
 Dogs and cats shall have the possibility to be without artificial lights for at least 8 hours per day.
 2.3 Space allowances
 2.3.1 Whelping and kittening areas shall be designed to permit the mother to move away from her offspring.
 2.3.2 In case of breeding and selling establishments, the following minimum space allowances for dogs and cats shall apply, which shall be calculated based on the total permanently accessible area for the dogs or cats.
-2.3.3 
+2.3.3
 Espaço para cães com ou sem crias
-Altura do var (cm): 
+Altura do var (cm):
 &lt; 30 → Área mínima: 4 m², Altura: 200 cm
 30-40 → 5 m², 200 cm
 40-60 → 8 m², 200 cm
@@ -4155,7 +4155,7 @@
 Espaço para gatos com ou sem crias
 Um gato: 3 m² solo, 200 cm altura
 Cada adicional: 2 m².
-* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura. 
+* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura.
 ** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
@@ -4172,9 +4172,9 @@
 2.3 Espaço adequado
 2.3.1 As áreas de parto devem ser concebidas de modo a permitir que a progenitora se afaste da sua prole.
 2.3.2 No caso dos estabelecimentos de criação e de venda, aplicam-se as seguintes superfícies mínimas para cães e gatos, as quais devem ser calculadas com base na área total permanentemente acessível aos cães ou gatos.
-2.3.3 
+2.3.3
 Espaço para cães com ou sem crias
-Altura do var (cm): 
+Altura do var (cm):
 &lt; 30 → Área mínima: 4 m², Altura: 200 cm
 30-40 → 5 m², 200 cm
 40-60 → 8 m², 200 cm
@@ -4184,7 +4184,7 @@
 Espaço para gatos com ou sem crias
 Um gato: 3 m² solo, 200 cm altura
 Cada adicional: 2 m².
-* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura. 
+* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura.
 ** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
@@ -4242,25 +4242,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Health
-Queens shall only be bred if their age is at least 10 months.
-Bitches shall only be bred as of their second oestrus.
-A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
-For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
-Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
-Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy. 
+          <t>3. Health
+1.1 Queens shall only be bred if their age is at least 10 months.
+2.2 Bitches shall only be bred as of their second oestrus.
+3.3 A bitch or queen shall not deliver more than 3 litters within a period of 2 years.
+4.4 For bitches and queens that have delivered 3 litters, including stillborns within a period of 2 years, there shall be a recuperation period of at least 1 year.
+5.5 Any bitch or queen that underwent two cesarean sections shall not be used for breeding.
+6.6 Before any bitch aged 8 years or more and any queen aged 6 years or more, is used for breeding, it must have been physically examined by a veterinarian who confirms in writing that, at the time of the examination, there are no counter-indications to pregnancy.
 The operator shall keep the written confirmation referred to in point 3.4.b for a period of at least 3 years.</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Saúde
-As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
-As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
-Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nascimortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
-Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
-Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+          <t>3. Saúde
+1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nascimortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
 O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
@@ -4318,13 +4318,13 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Behavioural needs
-Socialisation
+          <t>3. Behavioural needs
+1.1 Socialisation
 From three weeks of age, dogs and cats shall be gradually provided with daily opportunities for social contact with their conspecifics and humans, and, where possible, with other animal species.
 Dogs and cats that pose a threat to each other due to aggressive behaviour or cause each other undue stress or discomfort shall be kept separate.
-Enrichment
+2.2 Enrichment
 Where cats are kept, there shall be a sufficient number of scratching posts, hiding places and shelves to ensure that each cat can climb, rest, observe and withdraw.
-Separation
+3.3 Separation
 Puppies kept in establishments shall not be permanently separated from their mothers before the age of 8 weeks.
 Kittens kept in shelters and foster homes shall not be permanently separated from their mothers before the age of 8 weeks. Kittens kept in breeding establishments shall not be permanently separated from their mothers before the age of 12 weeks.
 By way of derogation, earlier separation shall be possible due to medical reasons based on written advice of a veterinarian. The operator shall keep a record of the advice until the last puppy or kitten of the litter concerned is placed on the market.</t>
@@ -4333,12 +4333,12 @@
       <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Bem-Estar Comportamental
-Socialização
+1.1 Socialização
 A partir das três semanas de idade, cães e gatos devem ser gradualmente fornecidos com oportunidades diárias de contato social com seus congêneres e humanos, e, sempre que possível, com outras espécies animais.
 Cães e gatos que representam uma ameaça um ao outro devido a comportamento agressivo ou causam um ao outro stress excessivo ou desconforto devem ser mantidos separados.
-Enriquecimento
+2.2 Enriquecimento
 Onde gatos são mantidos, deve haver um número suficiente de postes de arranhadura, locais de abrigo e prateleiras para garantir que cada gato pode subir, descansar, observar e retirar-se.
-Separação
+3.3 Separação
 Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes das 8 semanas de idade.
 Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes das 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes das 12 semanas de idade.
 Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
@@ -4422,9 +4422,9 @@
       </c>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding). 
-DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2. 
-@Código implementa 8 semanas para exposição (4.3) mas não separação maternal. 
+          <t>ANNEX I, Ponto 4 (Behavioural Needs) tem três subsecções: (i) 4.1 Socialização — contato social diário desde 3 semanas (NOVO); (ii) 4.2 Enriquecimento — postes de arranhadura, abrigos, prateleiras para gatos (PARCIAL na legislação); (iii) 4.3 Separação — 8 semanas (puppies, kittens abrigos), 12 semanas (kittens breeding).
+DL 276/2001 é omisso em 4.1 e 4.3, parcial em 4.2.
+@Código implementa 8 semanas para exposição (4.3) mas não separação maternal.
 @RGBEAC é mais restritivo (10-12 semanas separação) e cobre 4.1 (plano) e 4.2 (enriquecimento) com gaps específicos.</t>
         </is>
       </c>
@@ -4450,20 +4450,20 @@
         <is>
           <t>Identification and registration of dogs and cats
 Transponders used to individually identify dogs and cats as required in Article 20 and Article 26 shall meet the following requirements:
-the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
-the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
-the code structure and technical concept of the radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
-compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.</t>
+(a) the microchip shall contain an individual, non-repeatable and non-reprogrammable identification number;
+(b) the identification number shall start with the country of identification of the dog or cat identified in accordance with ISO standard 3166;
+(c) the code structure and technical concept of the radio frequency identification shall be in compliance with ISO standards 11784 and 11785;
+(d) compliance with ISO standards 11784 and 11785 shall be evaluated in accordance with ISO standard 24631-1.</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Identificação e registo de cães e gatos
 Os transponders utilizados para identificar individualmente cães e gatos, tal como exigido nos artigos 20.º e 26.º, devem cumprir os seguintes requisitos:
-O microchip deve conter um número de identificação individual, não repetível e não reprogramável;
-O número de identificação deve começar pelo país de identificação do cão ou gato, identificado em conformidade com a norma ISO 3166;
-A estrutura do código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
-a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
+(a) O microchip deve conter um número de identificação individual, não repetível e não reprogramável;
+(b) O número de identificação deve começar pelo país de identificação do cão ou gato, identificado em conformidade com a norma ISO 3166;
+(c) A estrutura do código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
+(d) a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -4475,15 +4475,15 @@
         <is>
           <t>Artigo 18.º- Métodos de marcação
 1 – Os métodos de marcação devem atender às melhoras práticas internacionais vigentes e salvaguardar o bem-estar animal.
-2 – Os cães, gatos e furões devem ser marcados por implantação de um transponder, que assegure os requisitos estabelecidos no anexo II do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013. 
+2 – Os cães, gatos e furões devem ser marcados por implantação de um transponder, que assegure os requisitos estabelecidos no anexo II do Regulamento (UE) n.º 576/2013, do Parlamento Europeu e do Conselho, de 12 de junho de 2013.
 3 - Os demais animais de companhia devem ser marcados através do método determinado para cada espécie por deliberação da DGAV, publicitado no respetivo sítio na Internet.
 4 - A implantação do transponder referido no n.º 2 deve ser efetuada por médico veterinário, no centro da face lateral esquerda do pescoço, após verificação de que o animal não se encontra já marcado por outro dispositivo de identificação.
 5 - Se não for possível, por motivo justificado, aplicar o transponder no local referido no número anterior, deve o mesmo ser aplicado num local alternativo, devendo o médico veterinário inserir essa informação no documento de identificação do animal e no SIAC.
 6 – Caso a marcação não seja tecnicamente possível ou exista alguma contraindicação que por motivos de saúde temporariamente não permita a sua marcação, o registo deve ser realizado no SIAC pelo médico veterinário, com a emissão de uma declaração, conforme modelo aprovado pela DGAV, publicitado no respetivo sítio na Internet.
 7 – A emissão de declaração prevista no número anterior é igualmente aplicável aos casos em que não exista ainda a deliberação prevista no n.º 3 do presente artigo.
-Artigo 19º- Dispositivos de identificação 
+Artigo 19º- Dispositivos de identificação
 1 - A colocação no mercado nacional de transponders e outros dispositivos de identificação individual invioláveis depende de acreditação prévia para efeitos do seu registo e autorização da sua comercialização, de acordo com os procedimentos estabelecidos pela DGAV.
-2 - Às entidades autorizadas a comercializar transponders e outros dispositivos de identificação individual invioláveis para animais de companhia é atribuído um acesso único ao SIAC, para que estas registem todos os dispositivos que tenham comercializado para cada médico veterinário ou entidade autorizada perante o SIAC a deter meios de identificação, de acordo com procedimento a determinar pela DGAV 
+2 - Às entidades autorizadas a comercializar transponders e outros dispositivos de identificação individual invioláveis para animais de companhia é atribuído um acesso único ao SIAC, para que estas registem todos os dispositivos que tenham comercializado para cada médico veterinário ou entidade autorizada perante o SIAC a deter meios de identificação, de acordo com procedimento a determinar pela DGAV
 3 - Para a marcação só pode ser utilizado um transponder ou outro dispositivo de identificação individual que tenha sido previamente registado no SIAC pela empresa comercializadora, e atribuído ao médico veterinário ou a uma entidade autorizada a identificar animais de companhia.</t>
         </is>
       </c>
@@ -4534,18 +4534,18 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
-The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
-The number of breeding establishments approved per year, as referred to in Article 10.
-The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
+          <t>1. The number of dogs and cats registered per year, as referred to in Article 20 and Article 26(3).
+2. The number of breeding establishments, selling establishments, shelters and foster homes registered per year in accordance with Article 9.
+3. The number of breeding establishments approved per year, as referred to in Article 10.
+4. The number of breeding establishments approval of which has been suspended or withdrawn per year.</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
- O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
-O número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 10.º. 
-O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
+          <t>1. O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
+2.  O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
+3. O número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 10.º.
+4. O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4556,13 +4556,13 @@
       <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Artigo 20.º — Sistema de Informação de Animais de Companhia (SIAC)
-O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
-A DGAV é a entidade responsável pelo SIAC, assegurando seu funcionamento e tratamento seguro de informação.
-A DGAV pode atribuir gestão do SIAC a outras entidades, mediante protocolo e parecer da Comissão Nacional de Proteção de Dados.
-Normas e procedimentos constam de Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.
+1. O SIAC reúne informação relativa à: a) Rastreabilidade de dispositivos de identificação; b) Identificação dos animais de companhia; c) Sua titularidade ou detenção; d) Informação de saúde pública, saúde animal e bem-estar animal.
+2. A DGAV é a entidade responsável pelo SIAC, assegurando seu funcionamento e tratamento seguro de informação.
+3. A DGAV pode atribuir gestão do SIAC a outras entidades, mediante protocolo e parecer da Comissão Nacional de Proteção de Dados.
+4. Normas e procedimentos constam de Manual de Procedimentos SIAC, aprovado pelo diretor-geral de alimentação e veterinária.
 Artigo 46.º — Relatório Nacional Anual
-Para efeitos de monitorização, os centros de bem-estar animal e alojamentos com fins de promoção do bem-estar animal remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com os números de animais de companhia recolhidos, restituídos aos detentores, eutanasiados, cedidos a associações zoófilas, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados no âmbito de programas CED.
-A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo o acompanhamento da política internacional do Estado Português na área do bem-estar dos animais de companhia, a prestação dos apoios públicos, a atividade do SIAC, os resultados dos planos de controlo, os processos contraordenacionais instaurados e coimas e sanções acessórias aplicadas, a atividade dos centros de bem-estar animal e dos alojamentos com fins de promoção de bem-estar animal, bem como os programas e ações de interesse nacional em matéria do bem-estar dos animais de companhia, incluindo ações informativas, formativas, educativas e estudos desenvolvidos, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal previsto na alínea i) do n.º 1 do artigo 3.º do Decreto-Regulamentar n.º 3/2021, de 25 de junho;</t>
+1. Para efeitos de monitorização, os centros de bem-estar animal e alojamentos com fins de promoção do bem-estar animal remetem à DGAV no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com os números de animais de companhia recolhidos, restituídos aos detentores, eutanasiados, cedidos a associações zoófilas, adotados, devolvidos após adoção, vacinados, esterilizados e intervencionados no âmbito de programas CED.
+2. A DGVA consolida a informação a nível nacional sobre bem-estar animal em cada ano, incluindo o acompanhamento da política internacional do Estado Português na área do bem-estar dos animais de companhia, a prestação dos apoios públicos, a atividade do SIAC, os resultados dos planos de controlo, os processos contraordenacionais instaurados e coimas e sanções acessórias aplicadas, a atividade dos centros de bem-estar animal e dos alojamentos com fins de promoção de bem-estar animal, bem como os programas e ações de interesse nacional em matéria do bem-estar dos animais de companhia, incluindo ações informativas, formativas, educativas e estudos desenvolvidos, para efeitos de elaboração do Relatório Anual sobre a situação do Bem-Estar Animal previsto na alínea i) do n.º 1 do artigo 3.º do Decreto-Regulamentar n.º 3/2021, de 25 de junho;</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal. 
+          <t>Decreto-Regulamentar 3/2021 (Art. 3.º) requer Relatório Anual sobre situação do Bem-Estar Animal.
 nº 9 e 10, artigo 3.º da Lei nº 27/2016, de 23 de agosto
 9 - Para efeitos de monitorização, todos os centros de recolha oficial de animais publicitam, no primeiro mês de cada ano civil, os relatórios de gestão do ano anterior, com os números de recolhas, abates ou occisões, eutanásias, adoções, vacinações e esterilizações efetuadas.
 10 - Com base nos relatórios referidos no número anterior, a Direção-Geral de Alimentação e Veterinária elabora e publicita um relatório anual sobre a situação ao nível nacional, até ao fim do primeiro trimestre de cada ano civil.</t>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -680,8 +680,8 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
-2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
+          <t>1. Um estabelecimento de criação em que não sejam produzidas mais de duas ninhadas por ano civil para colocação no mercado apenas está sujeito às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 2, 3 e 4, no artigo 8.º, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º, n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º, no artigo 19.º, n.º 1 e nos pontos 3 e 4.3 do nexo I.
+2. Os abrigos que detenham, no máximo, um total combinado de 15 cães ou gatos, a todo o momento, ou quaisquer casas de acolhimento, apenas estão sujeitos às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 2, 3, 4, e 5, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas a), b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º e no ponto 4.3 do nexo I.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
-(a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
-(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
-(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
-(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
-(e) (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
+          <t>Os operadores ▌devem aplicar os seguintes princípios gerais de bem‑estar no que diz respeito aos cães ou gatos criados ou detidos no seu estabelecimento:
+a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que lhes uma nutrição e hidratação adequadas;
+b) Os cães e os gatos são detidos num ambiente físico que é adequado e limpo com regularidade, que é seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, luz, proteção contra condições climáticas adversas e que é suficientemente grande para prevenir a sobrelotação e para lhes proporcionar facilidade de circulação;
+c) Os cães e os gatos são detidos em segurança, limpos e em boa saúde, devendo as doenças, ▌lesões e dores que decorrem em especial da gestão, das práticas de manuseamento e das práticas de criação, ser prevenidas;
+d) Os cães e os gatos são detidos num ambiente que lhes permite exibir comportamentos específicos da espécie e sociais não nocivos e estabelecer uma relação positiva com os seres humanos;
+e) Os cães e os gatos são detidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo ▌os estímulos negativos em termos de duração e intensidade, bem como maximizando as oportunidades de estímulos positivos em termos de duração e intensidade, de forma que previna o desenvolvimento de comportamentos repetitivos anormais ou de outros comportamentos indicadores de um deficiente bem-estar animal, e que tenha em conta as necessidades de cada animal nos domínios referidos nas alíneas a) a d).</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -831,15 +831,16 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
-2. No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
-O Estado-Membro em que se situa o lar de acolhimento pode autorizar um maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações do lar de acolhimento disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais no lar de acolhimento seja suficiente para garantir o bem-estar dos cães e gatos.
-3. Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
-4. Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
-5. Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
-6. Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
-7. Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
-8. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
+          <t>1. Os operadores ▌ são responsáveis pelo bem‑estar dos cães e gatos detidos em estabelecimentos sob a sua responsabilidade e controlo e pela minimização de quaisquer riscos para o bem‑estar desses animais.
+2. No caso das casas de acolhimento, a responsabilidade incumbe aos operadores em cujo nome os cães ou gatos são detidos. Tais operadores não devem, em nenhum momento, colocar mais do que um total combinado de cinco cães ou gatos, ou mais do que uma ninhada, com ou sem mãe, numa casa de acolhimento, e devem à família de acolhimento as informações adequadas sobre as obrigações em matéria de bem-estar dos animais, assim como sobre as necessidades individuais dos cães ou gatos, devendo ainda assegurar que nessas casas de acolhimento sejam respeitadas as obrigações pertinentes previstas no presente regulamento.
+O Estado-Membro em que se situa a casa de acolhimento pode autorizar que um maior número de cães, gatos ou ninhadas seja colocado na casa de acolhimento, desde que as instalações desta disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais na referida casa seja suficiente para assegurar o bem-estar dos cães ou gatos.
+3. Os operadores não podem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, nomeadamente fazendo-os participar em atividades suscetíveis de resultar em atos de crueldade, abuso ou maus-tratos dos cães ou gatos criados ou detidos pelo operador.
+4. Os operadores não abandona os cães ou gatos por eles criados ou detidos.
+5. Antes de cessarem as suas atividades num estabelecimento, os operadores devem garantir que os cães ou gatos aí detidos sejam realojados, quer assumindo eles próprios a propriedade dos animais de companhia, quer transferindo a responsabilidade pelos cães e gatos, ou a propriedade dos mesmos, para outros operadores ou adquirentes.
+6. Os operadores ▌devem assegurar que os cães e gatos sejam manuseados por um número de cuidadores de animais suficiente para satisfazer as necessidades de bem-estar dos cães ou dos gatos que são detidos nos seus estabelecimentos, e que esses cuidadores possuam as ▌competências exigidas nos termos do artigo 12.º
+7. Os operadores devem assegurar o bem-estar dos cães ou dos gatos pelos quais são responsáveis, fazendo um dos indicadores relativos ao comportamento e aspeto físico baseados nos animais e tomando medidas em função do resultado dess .
+8. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º para complementar o presente regulamento, prevendo indicadores relativos ao comportamento e aspeto físico baseados nos animais, que devem ser usados pelos operadores para efeitos d a realizar em conformidade com o n.º 7 do presente artigo, assim como os métodos a usar pelos operadores para a sua medição.
+.▌</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1037,24 +1038,16 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
-2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
-3. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
-(a) características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
-(b) características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
-4. Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
-5. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-6. São proibidos na gestão da reprodução de cães e gatos:
-(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
-(b) o cruzamento para produção de híbridos.
-@regulamento — Tradução PT-PT · ANEXO I, Ponto 3 do Regulamento 2023/0447
-1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
-2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
-3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
-5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
-6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
-O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de reprodução minimizem o risco de produção de cães ou gatos com genótipos associados a efeitos prejudiciais para a saúde e bem-estar desses animais.
+2. Os operadores de estabelecimentos de criação não devem utilizar, para fins de reprodução, cães ou gatos com características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses cães ou gatos ou da sua descendência. Antes de selecionar um cão ou gato que possa ter uma característica de conformação excessiva para a reprodução, o operador deve consultar um veterinário ou uma pessoa qualificada independente que atue sob a responsabilidade de um veterinário. Tal veterinário ou pessoa qualificada independente deve avaliar se o cão ou gato tem uma característica de conformação excessiva.
+3. A Comissão fica habilitada a adotar atos delegados nos termos do artigo 28.º, que complementem o presente regulamento, definindo:
+a) As características dos genótipos a que se refere o n.º 1 que devem ser excluídas da reprodução, bem como os métodos para a sua avaliação e os requisitos em matéria de manutenção de registos;
+b) As características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídas da reprodução, os métodos para a sua avaliação e os requisitos em matéria de conservação de registos.
+Ao adotar esses atos delegados, a Comissão toma em consideração o parecer científico da Autoridade Europeia para a Segurança dos Alimentos, bem como quaisquer impactos sociais e económicos dos referidos atos delegados.
+Os atos delegados relativos às características de conformação excessivas devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+4. No contexto da gestão da reprodução de cães e gatos, são proibidas as seguintes práticas:
+a) Reprodução entre progenitores e descendência, entre irmãos, entre meios-irmãos ou entre avós e netos, salvo aprovação pela autoridade competente com base numa necessidade específica de preservação de raças locais com património genético limitado;
+b) Reprodução para produção de híbridos.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1192,18 +1185,18 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
-(a) o nome, morada e contactos do operador;
-(b) a localização do estabelecimento;
-(c) o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
-(d) as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
-(e) a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
-(f) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
-2. Os operadores devem notificar a autoridade competente de:
-(a) quaisquer alterações relativas às informações referidas no n.º 1;
-(b) quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
-3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
-4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
+          <t>1. Os operadores ▌devem notificar as autoridades competentes da sua atividade, facultando pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+a) O nome, o endereço e dados de contacto do operador;
+b) A localização do estabelecimento;
+c) O tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou casa de acolhimento;
+d) A espécie e, para os estabelecimentos de criação, as raças dos cães ou gatos detidos no estabelecimento;
+e) A capacidade do estabelecimento, expressa em termos de número máximo de cães e gatos que podem ser detidos no estabelecimento
+f) No caso dos estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+2. Os operadores comunicam à autoridade competente:
+a) Qualquer alteração relativa às informações referidas no n.º 1;
+b) Se for o caso, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data;
+3. Os Estados-Membros devem utilizar as informações facultadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já comunicadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
+4. A autoridade competente deve manter um registo de estabelecimentos. A autoridade competente pode utilizar, para este efeito, o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1465,14 +1458,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
-2. A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
-3. A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
-(a) o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
-(b) a morada do estabelecimento;
-(c) o nome do operador;
-(d) a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
-(e) o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
+          <t>1. Os operadores de estabelecimentos de criação que produzam ou tencionem produzir mais de cinco ninhadas por ano civil, ou que, a qualquer momento, detenham um total combinado de mais de cinco cadelas ou gatas, só podem colocar cães ou gatos no mercado após aprovação do seu estabelecimento pela autoridade competente.
+2. A autoridade competente deve efetuar inspeções no local para verificar se o estabelecimento cumpre os requisitos do presente regulamento. Os Estados-Membros podem autorizar que estas inspeções sejam realizadas à distância, desde que o meio de comunicação à distância utilizado permita recolher provas suficientes para que a autoridade competente realize inspeções fiáveis. A autoridade competente só deve conceder certificados de aprovação a estabelecimentos de criação que cumpram os requisitos do presente regulamento.
+3. A autoridade competente deve manter uma lista acessível ao público que contenha as seguintes informações para cada estabelecimento aprovado:
+a) O nome, os dados de contacto e, sempre que disponível, o URL do sítio Web do estabelecimento;
+b) O endereço do estabelecimento;
+c) O nome do operador;
+d) As espécies e, sendo caso disso, as raças relacionadas com as atividades aprovadas do estabelecimento;
+e) O número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data de aprovação e de cessação das atividades.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1550,11 +1543,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
-2. A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
-(a) o estado de vacinação do cão ou gato;
-(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
-Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
+          <t>1. ▌Os operadores ▌devem facultar ao adquirente de um cão ou de um gato as informações escritas necessárias para permitir ao adquirente assegurar o bem‑estar do animal, incluindo informações sobre a propriedade responsável e sobre as necessidades específicas do animal em termos de alimentação, cuidados, saúde e alojamento, assim como informação a respeito das suas necessidades comportamentais e do seu historial sanitário.
+2. As informações escritas sobre do cão ou gato referidas no primeiro parágrafo devem incluir, pelo menos:
+a) A situação do animal em termos de vacinação;
+b) Quaisquer problemas de saúde ou predisposição para doenças, incluindo alergias, que sejam do conhecimento do operador, e quaisquer resultados de testes de diagnóstico do cão ou gato que se encontrem à disposição do operador.
+Sempre que as informações sobre  do animal constarem de um documento exigido por força do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1646,15 +1639,15 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1. Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
-(a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
-(b) capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e adotar as medidas de atenuação adequadas nesses casos;
-(c) capacidade para aplicar boas práticas de gestão animal, incluindo o condicionamento operante e o reforço positivo, para utilizar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
-(d) conhecimento das obrigações que lhes incumbem por força do presente regulamento.​
-2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
-3. Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
-4. A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
-O ato de execução relativo aos cursos de formação referidos no n.º 3 é adotado até … [3 anos a contar da data de entrada em vigor do presente regulamento].​
+          <t>1. Os cuidadores de animais, os voluntários em abrigos e os estagiários que atuem sob a responsabilidade de um cuidador animal competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+a) Compreensão do comportamento biológico dos animais e das suas necessidades fisiológicas e etológicas;
+b) Capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e tomar as medidas de atenuação adequadas ▌nesses casos;
+c) Capacidade para aplicar boas práticas de gestão animal, nomeadamente o condicionamento operante e o reforço positivo, para usar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
+d) Conhecimento das obrigações que incumbem aos cuidadores por força do presente regulamento.
+2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Para determinar se um cuidador animal tem as competências referidas no n.º 1 apenas serão tidos em conta o ensino, a formação ou a experiência profissional que se encontrem documentados.
+3. Os operadores devem garantir que pelo menos um cuidador de animais do estabelecimento,  voluntários ou estagiários, tenha concluído os cursos de formação referidos no artigo 22.º Os operadores devem garantir que esse cuidador de animais partilhe os seus conhecimentos com os outros cuidadores de animais do estabelecimento.
+4. A Comissão adota atos de execução que estabeleçam requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais tem as competências a que se refere o n.º 1 e para os cursos de formação a que se refere o n.º 3.
+O ato de execução relativo aos cursos de formação a que se refere o n.º 3 é adotado até... [anos a data de entrada em vigor do presente regulamento].
 Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
         </is>
       </c>
@@ -1756,10 +1749,10 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem:
-(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
-(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
-2. Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
+          <t>1. Os operadores ▌devem:
+a) Assegurar que os estabelecimentos sob a sua responsabilidade recebam ▌uma visita de um veterinário, a fim de identificar e avaliar qualquer fator de risco para o bem‑estar dos cães ou gatos, assim como aconselhar o operador ▌sobre as medidas destinadas a dar resposta a esses riscos, inicialmente até ... [três anos após a data de entrada em vigor do presente regulamento] ou um ano a contar da notificação do novo estabelecimento e, posteriormente, se for caso disso, com base numa análise do risco levada a cabo pelas autoridades competentes, ou anualmente, se os Estados-Membros assim o previrem no seu direito nacional;
+b) Conservar um registo das conclusões da visita do veterinário a que se refere a alínea a) e das suas ações de acompanhamento durante ▌pelo menos quatro anos, a contar do dia da visita, e disponibilizar esse registo às autoridades competentes, mediante pedido, assim como aos veterinários que fizerem as visitas de acompanhamento subsequentes.
+2. Até... [24 meses a contar da data de entrada em vigor do presente regulamento], a Comissão adota atos delegados, nos termos do artigo 28.º, que complementem o presente artigo, prevendo os critérios mínimos a avaliar pelo veterinário durante a visita de aconselhamento para assegurar o bem‑estar.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1868,18 +1861,18 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
-2. Os operadores devem assegurar que os cães ou gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
-a) água limpa e fresca, ad libitum;
-b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade e estado reprodutivo dos cães ou gatos, com o objetivo global de alcançar manter um bom estado saúde;
-c) alimento livre de substâncias que possam causar sofrimento;
-d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal em bom funcionamento, em particular durante a fase de desmame.
-3. Os operadores devem assegurar que as instalações de alimentação e abeberamento sejam mantidas limpas e sejam construídas e instaladas de forma a:
-a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
-b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
-c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
-d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
-4.	Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
+          <t>1. Os operadores ▌devem assegurar que os cães e gatos sejam alimentados em conformidade com os requisitos estabelecidos no ponto 1▌.
+2. Além disso, os operadores ▌devem assegurar que os cães e gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
+a) Água limpa e fresca, ad libitum;
+b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas ▌dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade, ▌estado de saúde e reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter a sua boa saúde;
+c) Alimentos para animais isentos de substâncias suscetíveis de causar sofrimento;
+d) Alimentos para animais proporcionados de forma que evite alterações bruscas e assegure o bom funcionamento do sistema gastrointestinal, em especial durante a fase de desmame.
+3. Os operadores ▌devem assegurar que as instalações de alimentação e de abeberamento sejam mantidas limpas e construídas e instaladas de modo a:
+a) Proporcionarem igualdade de acesso a quantidades adequadas de alimentos para animais e água a todos os cães ou gatos e minimizarem a disputa entre eles;
+b) Minimizarem os derrames e evitarem a contaminação dos alimentos para animais e da água com contaminantes físicos, químicos ou biológicos;
+c) Prevenirem que os cães ou gatos sofram lesões, afogamento ou outros danos;
+d) Serem facilmente limpas e desinfetadas para prevenir a propagação de doenças.
+4. Se um veterinário os aconselhar por escrito nesse sentido, os operadores podem ajustar as frequências de alimentação e de abeberamento de um determinado cão ou gato. Os operadores devem manter um registo desses conselhos recebidos por escrito ao longo de toda a duração dos referidos ajustamentos.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1998,24 +1991,24 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
-2. Os operadores devem assegurar que:
-a) os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
-b) todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-c) todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
-d) nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
-e) os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
-f) os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
-g) existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
-Os operadores não devem manter cães ou gatos em contentores.
-3. Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural.
-4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
-5. Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
-6. Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
-7. Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
-8. Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
-Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
-9. Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
+          <t>1. Os operadores de estabelecimentos de criação e de venda devem assegurar que os cães e gatos sejam alojados em conformidade com o ponto 2. Os operadores de abrigos devem assegurar que os cães e gatos sejam alojados em conformidade com o ponto 2.2.
+2. Os operadores ▌devem assegurar que:
+a) Os estabelecimentos onde cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário a todos os cães e gatos e uma inspeção exaustiva dos mesmos;
+b) Todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, ▌e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos de forma adequada, ▌a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
+c) Todos os componentes do edifício do estabelecimento, incluindo o pavimento, e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
+d) ▌Em estabelecimentos de criação e de venda em que os cães ou gatos sejam detidos em espaços interiores, os níveis de poeiras, a temperatura e a humidade relativa do ar e as concentrações de gases ▌não sejam prejudiciais para os cães ou gatos e que a ventilação seja suficiente para evitar o sobreaquecimento ▌;
+e) Os cães os gatos disponham de espaço suficiente para poderem circular livremente e expressar comportamentos específicos da espécie de acordo com as suas necessidades, tendo a possibilidade de se retirarem e de descansarem;
+f) Os cães ou gatos disponham de zonas de descanso limpas, confortáveis e secas, suficientemente grandes e numerosas para garantir que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
+g) Estejam previstas estruturas e medidas adequadas para que cães ou gatos mantidos em espaços exteriores estejam protegidos de condições climáticas adversas, incluindo para prevenir desconforto térmico, queimaduras solares e queimaduras pelo frio.
+3. ▌Os operadores não devem manter os cães ou os gatos em contentores.
+Os contentores podem, no entanto, ser utilizados para  isolamento curta duração de determinados cães ou gatos e para a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com reduzida capacidade de termorregulação ou para cachorros ou gatinhos acompanhados das suas mães, desde que, para os cães ou gatos em causa, o stress seja minimizado e o sofrimento evitado, e que os mesmos possam ficar de pé, virar-se e deitar-se numa posição natural.
+4. Os operadores não podem manter cães com mais de semanas exclusivamente em espaços interiores. Tais cães devem ter acesso diário a uma área ao ar livre, ou serem passeados diariamente, ▌de forma que permita exercício físico, exploração e socialização. A duração combinada mínima desse acesso diário ou passeio deve ser de uma hora no total. O operador só pode ficar isento destas exigências com base num parecer escrito de um veterinário.
+5. Quando os gatos são mantidos em gatis, os operadores devem conceber e construir compartimentos individuais para permitir que os gatos circulem livremente e exibam o seu comportamento natural.
+6. Os operadores de estabelecimentos de criação e venda devem assegurar ▌que nas áreas interiores onde são detidos cães ou gatos, existe uma zona termicamente neutra adequada que tenha em conta o seu tipo de pelagem, a idade, o tamanho, a raça e o estado de saúde.
+7. Os operadores dos estabelecimentos de criação e de venda devem, se necessário, utilizar sistemas de aquecimento ou de arrefecimento nos compartimentos interiores dos seus estabelecimentos, a fim de manter uma boa qualidade do ar e uma temperatura adequada e remover a humidade excessiva.
+8. Os operadores devem assegurar que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos para manterem um ritmo circadiano normal.
+Para efeitos do primeiro parágrafo, entende-se por «luz» a luz natural, complementada, sempre que necessário, devido às condições climáticas e à posição geográfica de um Estado‑Membro, por luz artificial.
+9. O n.º 2, alíneas a), b), c), f) e g), e os n.os 6, 7 e 8 não  nem aos cães de guarda de gado nem aos cães de pastoreio durante os períodos em que esses cães são usados para guardar ou pastorear no contexto da transumância sazonal a pé. O n.º 2, alínea f), não  a cães de guarda de gado durante os períodos em que estes cães são usados para treino.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2157,22 +2150,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que:
-(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
-(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
-(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
-(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
-(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
-A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
-Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
-i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
-ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
+          <t>1. Os operadores ▌devem assegurar que:
+a) Os cães ou gatos pelos quais são responsáveis sejam inspecionados pelos cuidadores de animais pelo menos uma vez por dia e que os cães e gatos vulneráveis, como os recém-nascidos, os cães e gatos doentes ou feridos e as cadelas e gatas em período perinatal, sejam inspecionados com maior frequência;
+b) Os cães ou os gatos cujo ▌bem‑estar esteja comprometido sejam transferidos, se necessário, sem demora injustificada para uma área separada, e, se necessário, recebam tratamento adequado;
+c) Sempre que não seja possível a recuperação de um cão ou de um gato cujo bem-estar esteja comprometido e o cão ou o gato sinta dor ou sofrimento intensos, seja consultado um veterinário sem demora injustificada para decidir se o cão ou o gato deve ser eutanasiado para pôr termo ao seu sofrimento e, se for esse o caso, para proceder à eutanásia com recurso a anestesia e analgesia;
+d) ▌Sejam tomadas medidas para prevenir e controlar parasitas externos e internos e sejam administradas vacinas para prevenir doenças comuns a que os cães ou gatos possam estar expostos;
+e) Os ▌enriquecimentos usados não apresentem, para os cães ou gatos, um risco significativo de lesões ou de contaminação biológica ou química ou qualquer outro risco para a saúde.
+▌	A alínea a) não se aplica a cães de guarda de gado detidos em estabelecimentos de criação enquanto estes cães sejam usados para fins de guarda ou de treino.
+Os Estados-Membros podem conceder isenções ao disposto na alínea c) em casos de urgência nos quais não seja possível contactar um veterinário sem demora injustificada, desde que sejam previstas normas nacionais destinadas a assegurar:
+i) Que qualquer ação imediata que ponha termo à vida do cão ou do gato com um mínimo de dor e sofrimento, com recurso a um método que provoque a morte instantânea, seja levada a cabo por uma pessoa competente formada;
+ii) Que, para efeitos dos controlos oficiais ao abrigo do Regulamento (UE) 2017/625, o operador mantenha um registo da utilização da isenção.
 2. Os operadores de estabelecimentos de criação devem assegurar que:
-(a)  são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
-(b) as cadelas ou gatas só se reproduzem se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
-(c)  As gravidezes das cadelas e gatas que resultem numa ninhada respeitem uma frequência máxima fixada no ponto 3 do Anexo I;
-(d)  as gatas em lactação não sejam acasaladas nem inseminadas;
-(e)  os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
+a) Sejam tomadas medidas para proteger a saúde dos cães ou dos gatos, em conformidade com o ponto 3;
+b) As cadelas ou as gatas só se reproduzam se tiverem atingido uma idade mínima e a maturidade esquelética em conformidade com o ponto 3 ▌, e apenas se não tiverem nenhuma doença diagnosticada, sinais clínicos de doenças ou problemas físicos que possam ter um impacto negativo na gravidez e no seu bem‑estar;
+c) As gravidezes das cadelas ou gatas respeitem uma frequência máxima, em conformidade com o ponto 3;
+d) As gatas em lactação não sejam sujeitas a acasalamento nem inseminação;
+e) ▌Cães e gatos que já não sejam utilizados para reprodução, nomeadamente por força das disposições do presente regulamento, sejam detidos, vendidos, doados ou realojados, e não mortos ou abandonados. ▌</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2308,19 +2301,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
-2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
-a) exames físicos;
-b) identificação individual de cães ou gatos e leitura da informação de identificação;
-c) recolha de amostras e vacinações;
-d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
-e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
-3. O acorrentamento por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
-4. Os Estados-Membros podem conceder isenções ao disposto no n.º 3 para os cães destinados a ser utilizados nos serviços militares, policiais e aduaneiros que sejam mantidos em estabelecimentos de criação ou de venda.
-5.  Os operadores devem assegurar que os cães ou gatos sejam mantidos em condições que lhes permitam exibir comportamentos sociais não prejudiciais e comportamentos específicos da espécie, bem como vivenciar emoções positivas.
-6. Os operadores devem assegurar que os cães ou gatos possam socializar em conformidade com o ponto 4 do anexo I. Os operadores de estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização.
-Em derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães sejam utilizados para fins de guarda ou de treino, nem aos cães de pastoreio durante a transumância sazonal.
-7. Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
+          <t>1. Os operadores ▌devem assegurar que sejam tomadas medidas para satisfazer as necessidades comportamentais dos cães e gatos em conformidade com o ponto 4.
+2. Além disso, os operadores não devem deter cães ou gatos em zonas que restrinjam os seus movimentos naturais, exceto em casos em que o artigo 15.º, n.º 3, segundo parágrafo, é aplicável ou em que os seguintes procedimentos ou tratamentos são realizados:
+a) Exames físicos ▌;
+b) Identificação individual de cães ou gatos, ou leitura das referidas informações de identificação;
+c) Colheita de amostras e vacinação;
+d) Procedimentos de limpeza e tosquia, procedimentos higiénicos, sanitários ou reprodutivos que não o acasalamento;
+e) Tratamento médico, incluindo tratamentos cirúrgicos ou reabilitação receitada.
+3. É proibido o acorrentamento ▌por um período superior a uma hora, exceto durante um tratamento médico ou para participação em espetáculos, exposições e concursos de cães ou gatos.
+4. Os Estados-Membros podem conceder isenções ao disposto no n.º 3 no caso dos cães destinados a serem usados nos serviços militares, policiais e aduaneiros que sejam detidos em estabelecimentos de criação ou venda.
+5. Os operadores ▌devem assegurar que os cães ou gatos sejam detidos em condições que lhes permitm exibir comportamentos sociais não nocivos, comportamentos específicos da espécie, e experienciar emoções positivas.
+6. Os operadores devem assegurar que os cães ou gatos possam socializar de acordo com o previsto no ponto 4. Os operadores dos estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização.
+Em derrogação do primeiro parágrafo, as exigências em matéria de socialização não se aplicam a cães de guarda de gado detidos em estabelecimentos de criação quando esses cães forem usados para fins de guarda ou de treino, ou a cães de pastoreio durante a transumância sazonal.
+7. Os operadores devem garantir que os enriquecimentos sejam oferecidos e estejam acessíveis a todos os cães ou gatos, criando um ambiente estimulante, permitindo que exibam comportamentos específicos da espécie e reduzindo a sua frustração.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2412,19 +2405,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
-2. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
-3. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos errantes quando esterilizados sob um programa de captura-esterilização-libertação.
-4. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
-5. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
-a)	amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
-b)	chutar, bater, arrastar, atirar, apertar cães ou gatos;
-c)	aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
-d)	uso de açaimos, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
-e)	uso de colares de espinhos;
-f)	uso de colares de estrangulamento sem paragem de segurança;
-g)	levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
-Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
+          <t>1. ▌Os operadores devem assegurar que as mutilações, incluindo o corte das orelhas, o corte da cauda, a remoção de garras ou outros tipos de amputação digital parcial ou completa, assim como a ressecção de cordas ou pregas vocais, não sejam efetuadas a menos que se justifiquem por indicação médica, incluindo quando o procedimento é profilático, e com o único objetivo de manter ou melhorar a saúde dos cães ou gatos ou de prevenir que estes se lesionem. Nesse caso, o procedimento só pode ser realizado ▌sob anestesia e analgesia prolongada, e exclusivamente por um veterinário.
+2. As indicações médicas que justificam a mutilação e os pormenores do procedimento realizado devem constar de um documento elaborado por um veterinário. Este documento deve ser conservado pelo operador e deve acompanhar o cão ou o gato quando este for transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve conservar uma cópia do documento durante os primeiros três anos após essa transferência.
+3. A título de derrogação do n.º 1, os Estados-Membros podem autorizar, no contexto da marcação de gatos vadios esterilizados no âmbito de um programa de captura, esterilização e libertação, que se faça um entalhe na orelha dos gatos ou se corte a ponta da mesma.
+4. Os operadores devem assegurar que a esterilização seja efetuada unicamente sob anestesia e analgesia prolongada e apenas por um veterinário. No entanto, os Estados-Membros podem autorizar que a esterilização de gatos machos seja efetuada por um enfermeiro veterinário autorizado.
+5. Os operadores devem assegurar a ausência de práticas de manuseamento que causem dor ou sofrimento, incluindo as seguintes:
+a) Atar partes do corpo, a menos que tal seja exigido por razões médicas e limitado ao período mínimo necessário;
+b) Pontapear, bater, arrastar, lançar ou apertar os cães ou os gatos;
+c) Aplicar corrente elétrica aos cães ou aos gatos, a menos que tal seja efetuado por motivos médicos;
+d) Utilizar ▌açaimes, a menos que tal seja exigido por razões médicas ou por razões de segurança animal ou humana, caso em que a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado;
+e) Utilizar coleiras de garras;
+f) Utilizar coleiras estranguladoras sem travão de segurança;
+g) Levantar os cães ou os gatos pelos membros, cabeça, orelhas, cauda ou pelo, ou levantar os cães ou gatos adultos pela pele.
+Os Estados-Membros podem conceder isenções ao disposto no primeiro parágrafo para os cães destinados a ser utilizados nos serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2517,8 +2510,10 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
-2. Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
+          <t>1. Nos espetáculos de beleza, nas exposições e nos concursos de cães e gatos, os operadores de estabelecimentos de criação e venda não podem utilizar cães ou gatos com características de conformação excessivas, nem cães ou gatos que tenham sido mutilados de uma forma que altere as suas características físicas.
+2. Ao organizarem espetáculos, exposições e concursos de cães e gatos, os organizadores devem excluir os cães e gatos que tenham características de conformação excessivas e os cães e gatos que tenham sido mutilados de uma forma que altere as suas características físicas.
+CAPÍTULO III
+IDENTIFICAÇÃO E REGISTO DE CÃES E GATOS</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2684,21 +2679,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1.	Todos os cães e gatos mantidos em estabelecimentos, colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
-2.	Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda e abrigos, e os operadores que colocam e são responsáveis por cães e gatos em famílias de acolhimento, devem assegurar que os cães e gatos que entrem nos seus estabelecimentos ou fiquem sob a sua responsabilidade sejam identificados individualmente no prazo de 30 dias após a chegada e, em qualquer caso, antes da data da sua colocação no mercado.
-Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que não sejam operadores e que sejam proprietários de cães ou gatos devem assegurar que cada cão ou gato seja identificado individualmente o mais tardar quando o animal atingir a idade de três meses ou, caso o cão ou gato seja colocado no mercado, antes da data dessa colocação no mercado.
-A implantação do transponder deve ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders seja efetuada por pessoas que não sejam médicos veterinários, desde que adotem regras nacionais que estabeleçam as qualificações mínimas que essas pessoas devem ter.
-Caso os cães e gatos tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip em conformidade com o direito da União ou nacional antes de … [data dois anos após a data de entrada em vigor do presente Regulamento], considera-se que cumprem os requisitos do n.º 1 e do primeiro, segundo, terceiro e quarto parágrafos do presente número, desde que o microchip seja ainda legível.
-3.	No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional referida no artigo 23.º. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que os Estados-Membros disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados. No caso de cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento responsável pelo cão ou gato. No caso de cães e gatos detidos por quaisquer outras pessoas singulares ou coletivas, o registo deve ser efetuado em nome dessas pessoas.
-Os Estados-Membros podem conceder derrogações ao primeiro parágrafo do presente número relativamente a cães militares, policiais e aduaneiros.
-4.	Em caso de colocação no mercado ou cedência ocasional por pessoas singulares sem recorrer a publicidade em linha, a pessoa singular ou coletiva que transfere a propriedade ou a responsabilidade pelo cão ou gato deve assegurar que a mudança de propriedade ou de responsabilidade pelo cão ou gato é registada na base de dados referida no artigo 23.º, no prazo de duas semanas a contar da data dessa transferência, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
-5.	Em caso de morte de um cão ou gato, o operador, o dono do animal de companhia ou a pessoa singular ou coletiva proprietária do cão ou gato deve assegurar que a morte é registada na base de dados referida no artigo 23.º, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
-6.	Caso um transponder seja ou fique ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato deve assegurar que um novo transponder é injetado e que o registo na base de dados é atualizado com o número de identificação desse novo transponder.
-7.	Os requisitos de identificação e registo do presente artigo são aplicáveis:
-(a)	aos operadores e às pessoas singulares ou coletivas que colocam cães e gatos no mercado, a partir de … [4 anos após a entrada em vigor do presente Regulamento];
-(b)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem cães no mercado, a partir de … [10 anos após a entrada em vigor do presente Regulamento];
-(c)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem gatos no mercado, a partir de … [15 anos após a entrada em vigor do presente Regulamento].</t>
+          <t>1. ▌Todos os cães e gatos detidos em estabelecimentos, colocados no mercado ou detidos por um proprietário de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente através de um único transpondedor injetável que contenha um circuito integrado legível que cumpra os requisitos estabelecidos no anexo II. ▌
+2. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o seu nascimento e sempre antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda e de abrigos e os operadores que coloquem e tenham a seu cargo cães e gatos em de acolhimento devem assegurar que os cães e gatos que são admitidos nos seus estabelecimentos ou passam a estar sob a sua responsabilidade sejam identificados individualmente no prazo de 30 dias a contar da sua chegada e sempre antes da data da sua colocação no mercado.
+Os proprietários de animais de companhia e quaisquer outras pessoas singulares ou coletivas operadores, que sejam proprietáris de cães ou gatos devem assegurar que cada cão ou gato seja identificado individualmente, o mais tardar quando atinge três meses de idade ou, se o cão ou gato for colocado no mercado, antes da data dessa colocação no mercado.
+A implantação do transpondedor deve ser efetuada por um veterinário. Os Estados-Membros podem autorizar a implantação de transpondedores por outras pessoas que não os veterinários, desde que adotem disposições nacionais que estabeleçam as qualificações mínimas que essas pessoas devem possuir.
+Considera-se que cumprem os requisitos estabelecidos no n.º 1 e no primeiro, segundo, terceiro e quarto parágrafos do presente número os cães e gatos que, em conformidade com o direito da União ou nacional, tenham sido identificados individualmente antes de … [dois anos após a data de entrada em vigor do presente regulamento] através de um transpondedor injetável que contenha um circuito integrado, desde que o circuito integrado permaneça legível.
+3. No prazo de dois dias úteis após a sua identificação, os cães e gatos ▌devem ser registados por um veterinário ▌numa base de dados nacional referida no artigo 23.º. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que os Estados-Membros tenham medidas em vigor para garantir a exatidão das informações que as pessoas em causa inserem na base de dados. No caso dos cães e dos gatos detidos em estabelecimentos ▌, o registo deve ser feito em nome do operador do estabelecimento ▌responsável pelo cão ou gato. No caso dos cães e dos gatos detidos por quaisquer outras pessoas singulares ou coletivas, o registo deve ser feito em nome dessas pessoas. ▌
+Os Estados-Membros podem conceder isenções ao disposto no primeiro parágrafo do presente número no que respeita aos cães destinados aos serviços militares, policiais e aduaneiros.
+4. Quando cães ou gatos forem colocados no mercado ou forem doados ocasionalmente por pessoas singulares sem recurso a publicidade em linha, a pessoa singular ou coletiva que transfere a propriedade ou a responsabilidade pelo cão ou gato deve assegurar que a mudança de propriedade ou de responsabilidade pelo cão ou gato seja registada na base de dados a que se refere o artigo 23.º, no prazo de duas semanas a contar da data dessa transferência, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+5. Em caso de morte de um cão ou de um gato, o operador, o proprietário do animal de companhia ou a pessoa singular ou coletiva que é proprietária do cão ou do gato deve assegurar que a morte seja registada na base de dados a que se refere o artigo 23.º, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+6. Se um transpondedor for ou ficar ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato deve assegurar que um novo transpondedor seja injetado e que o registo na base de dados seja atualizado com o número de identificação desse novo transpondedor.
+.Os requisitos de identificação e registo estabelecidos no presente artigo são aplicáveis do seguinte modo:
+a) Para os operadores e as pessoas singulares ou coletivas que colocam cães e gatos no mercado, a partir de … [anos a contar da data de entrada em vigor do presente regulamento];
+b) Para os proprietários de animais de companhia e outras pessoas singulares ou coletivasoperadores, que não colocam cães no mercado, a partir de … [10 anos a contar da data de entrada em vigor do presente regulamento];
+c)  Para os proprietários de animais de companhia e outras pessoas singulares ou coletivas operadores, que não colocam gatos no mercado, a partir de … [15 anos a contar da data de entrada em vigor do presente regulamento].</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2813,32 +2808,34 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>1.	Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
-"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
-2.	Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no n.º 1 ou uma redação diferente com significado equivalente.
-3.	Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve fornecer ao adquirente:
-(a)	prova da identificação e do registo do cão ou gato em conformidade com o artigo 20.º;
-(b)	as seguintes informações sobre o cão ou gato:
-(i)	a sua espécie;
-(ii)	o seu sexo;
-(iii)	a sua data e país de nascimento; e
-(iv)	quando relevante, a sua raça.
-Caso uma pessoa singular ou coletiva anuncie um cão ou gato online com vista ao seu colocamento no mercado da União, essa pessoa deve utilizar o sistema referido no n.º 5 para gerar um token único de verificação e incluir esse token no anúncio, juntamente com uma ligação web para o sistema referido no n.º 5.
-O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online.
-4.	Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações nos termos dos n.ºs 1 a 3 do presente artigo, e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou gato no sistema de verificação online referido no n.º 5, acessível através de uma ligação web.
-Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações fornecidas através da interface da plataforma online. Nenhuma disposição do presente número pode ser interpretada como impondo uma obrigação geral de monitorização ao fornecedor da plataforma online, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
-5.	A Comissão garante que um sistema de verificação destinado a realizar controlos automatizados da autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está publicamente disponível online, a título gratuito, e gera o token único de verificação referido no segundo parágrafo do n.º 3 do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento deste sistema a uma entidade independente, escolhida para essa missão na sequência de um processo de seleção pública. O sistema deve assegurar:
-(a)	a verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato, utilizando as bases de dados nacionais referidas no artigo 23.º;
-(b)	a conformidade com a proteção de dados, em conformidade com o Regulamento (UE) 2018/1725 e o Regulamento (UE) 2016/679.
-6.	A Comissão adota atos de execução que estabelecem:
-(a)	as informações a fornecer pelas pessoas singulares e coletivas que colocam cães ou gatos no mercado como prova de identificação e registo dos cães e gatos em conformidade com o n.º 3, alínea a);
-(b)	as informações a fornecer pelas pessoas singulares e coletivas que anunciam cães ou gatos ao sistema de verificação referido no n.º 5, para efeitos de demonstração da autenticidade da identificação, do registo e da propriedade do cão ou gato anunciado;
-(c)	as seguintes características do sistema referido no n.º 5:
--	as funções essenciais do sistema;
--	os requisitos técnicos, eletrónicos e criptográficos do sistema;
--	os passos procedimentais a seguir, e as informações a fornecer, pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como os passos e informações exigidos ao adquirente, para que o sistema de verificação online funcione.
-Os atos de execução referidos na alínea a) devem ser adotados até … [dois anos após a data de entrada em vigor do presente Regulamento] e os atos de execução referidos nas alíneas b) e c) devem ser adotados até … [três anos a contar da data de entrada em vigor do presente Regulamento].
-Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>1. Quando recorrem a um anúncio em linha para a colocação no mercado da União de um cão ou de um gato, os operadores devem assegurar que o anúncio inclua a seguinte advertência, em carateres claramente visíveis e a negrito:
+«Um animal não é um brinquedo. Adquirir um animal é uma decisão que muda a sua vida. É seu dever garantir a saúde e o bem-estar do animal e não o abandonar.».
+2. Sempre que anunciem um cão ou um gato em linha com vista à sua colocação no mercado da União, as pessoas singulares ou coletivas operadores devem assegurar que o anúncio inclua uma advertência sobre a propriedade responsável, utilizando a redação constante do n.º 1 ou uma redação diferente com o mesmo significado.
+3. Quando colocam um cão ou um gato no mercado na União, as pessoas singulares ou coletivas que colocam o cão ou o gato no mercado devem ao adquirente:
+a) Prova da identificação e do registo do cão ou do gato em conformidade com o artigo 20.º;
+b) As seguintes informações sobre o cão ou o gato:
+i) a sua espécie,
+ii) o seu sexo,
+iii) a data e país onde nasceu, e
+iv) se for caso disso, a sua raça.
+Sempre que anunciem um cão ou um gato em linha com vista à sua colocação no mercado da União, as pessoas singulares ou coletivas devem utilizar o sistema a que se refere o n.º 5 para gerar um testemunho de verificação único. Essas pessoas devem incluir esse testemunho de verificação no anúncio, juntamente com uma hiperligação para o sistema a que se refere o n.º 5.
+O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade dos cães ou gatos anunciados em linha.
+4. ▌Os fornecedores de plataformas em linha devem assegurar que a sua interface em linha seja concebida e organizada de forma a que os operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado tenham maior facilidade em cumprir as obrigações que lhes incumbem por força dos n.os 1 a 3 do presente artigo e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou do gato no sistema de verificação em linha referido no n.º 5, acedido através de uma hiperligação.
+Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações facultadas através da interface da plataforma em linha. Nenhuma disposição do presente número pode ser interpretada no sentido de impor uma obrigação geral de vigilância ao fornecedor da plataforma em linha, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
+5. ▌A Comissão assegura que um sistema de verificação que efetue controlos automatizados da autenticidade da identificação, do registo e da propriedade dos cães ou gatos anunciados em linha, utilizando a base de dados a que se refere o artigo 23.º, seja disponibilizado em linha ao público, a título gratuito, e gere o testemunho de verificação único referido no n.º 3, segundo parágrafo, do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e a exploração deste sistema a uma entidade independente. Essa entidade independente é escolhida para essa função na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509 do Parlamento Europeu e do Conselho. O sistema deve assegurar o seguinte:
+a) A verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato utilizando as bases de dados nacionais a que se refere o artigo 23.º;
+b) A conformidade com a proteção de dados nos termos do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679.
+6. ▌ A Comissão adota atos de execução que preveem:
+a) As informações que as pessoas singulares e coletivas que colocam cães ou gatos no mercado devem como prova da identificação e do registo de cães e gatos em conformidade com o n.º 3, alínea a);
+b) As informações que as pessoas singulares e coletivas que anunciam cães ou gatos devem ao sistema de verificação referido no n.º 5 para comprovar a autenticidade da identificação, do registo e da propriedade do cão ou do gato anunciado;
+c) As seguintes características do sistema a que se refere o n.º 5:
+–	as funções essenciais do sistema,
+–	os requisitos técnicos, eletrónicos e criptográficos do sistema,
+–	as etapas processuais a seguir e as informações a pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como as etapas e informações exigidas ao adquirente, para que o sistema de verificação em linha funcione.
+Os atos de execução a que se refere a alínea a) são adotados até … [dois anos após a data de entrada em vigor do presente regulamento] e o ato de execução a que se referem as alíneas b) e c) é adotado até … [três anos a contar da data de entrada em vigor do presente regulamento].
+Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.
+CAPÍTULO IV
+AUTORIDADES COMPETENTES</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2982,11 +2979,11 @@
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Para efeitos do artigo 12.º, as autoridades competentes são responsáveis por:
-a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
-b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 12.º, parágrafo 3;
-c) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
-2. As autoridades competentes podem delegar a tarefa referida na alínea (c)
-3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
+a) Assegurar a disponibilidade de cursos de formação para os cuidadores de animais;
+b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), em conformidade com os requisitos mínimos estabelecidos pelos atos de execução a que se refere o artigo 12.º, n.º 4;
+c) Certificar os cuidadores de animais que concluíram com êxito os cursos de formação referidos na alínea a).
+As autoridades competentes podem delegar a tarefa a que se refere a alínea c) em prestadores de cursos de formação.
+2.  centro de referência da União Europeia para o bem-estar animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode elaborar modelos de materiais de formação e recomendações para as autoridades competentes ou outros prestadores de cursos de formação.</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -3115,18 +3112,19 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
-2. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
-3. Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
-4. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
-A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
-(a) o conteúdo mínimo das bases de dados referidas no n.º 1;
-(b) a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
-(c) a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
-(d) o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
-(e) a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
-A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
-Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>1. Os Estados-Membros são responsáveis por criar e manter bases de dados para o registo de cães e gatos identificados em conformidade com o artigo 20.º, n.os 1 e 2, o artigo 26.º, n.º 3, e o artigo 26.º, n.º 4, segundo parágrafo.
+2. Para o efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos adequados entre os Estados-Membros em causa.
+3. ▌Os Estados‑Membros devem assegurar que as suas bases de dados referidas no n.º 1 cumpram os requisitos estabelecidos pelo ato de execução a que se refere o n.º 4, segundo parágrafo, alínea b), a fim de garantir a sua interoperabilidade.
+4. A Comissão cria e mantém uma base de dados indexada que contenha o conjunto mínimo de campos estabelecido nos atos de execução a que se refere o segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento desta base de dados indexada a uma entidade independente, na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509.
+▌A Comissão adota atos de execução que estabelecem disposições pormenorizadas no que diz respeito ao seguinte:
+a) Ao ▌conteúdo mínimo das bases de dados referidas no n.º 1;
+b) À ▌interoperabilidade entre as bases de dados dos Estados‑Membros e a base de dados indexada, incluindo o conjunto mínimo de campos a transmitir à base de dados indexada e os intervalos de transmissão;
+c) À ▌funcionalidade para fornecer prova da identificação e do registo de um cão ou gato, conforme referido no artigo 21.º, n.º 3, alínea a);
+d) Ao registo em que os Estados-Membros declararão as suas bases de dados e os parâmetros necessários para ligar essas bases de dados entre si, em conformidade com as disposições estabelecidas nos termos da alínea b);
+▌	▌
+e) À interligação entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de animais de companhia em viagem referida no artigo 26.º, n.º 4, e o sistema de gestão da informação sobre os controlos oficiais (IMSOC), se for caso disso.
+A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até ... [dois anos após a data de entrada em vigor do presente regulamento]. A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até ... [três anos a contar da data de entrada em vigor do presente regulamento].
+Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -3213,9 +3211,9 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1. As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
-2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
-3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>1. As autoridades competentes devem recolher, analisar e publicar os dados relativos ao bem-estar animal previstos no anexo III.
+2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório, em formato eletrónico, sobre os dados relativos ao bem-estar animal previstos no anexo III, até 31 de agosto de três em três anos. O primeiro desses relatórios deve ser elaborado e transmitido à Comissão até ... [data correspondente a anos a contar da data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
+3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados relativos ao bem-estar animal previstos no anexo III e que estabeleçam um modelo do relatório a que se refere o n.º 2 do presente artigo. Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3287,17 +3285,19 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1. As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
-A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
-É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
-Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
-(a) controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
-(b) o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
-2. Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
-(a) no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
-(b) no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
-(c) no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
-(d) (d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
+          <t>1. As autoridades competentes dos Estados-Membros são responsáveis pelo tratamento na aceção do Regulamento (UE) 2016/679 no que diz respeito ao tratamento de dados pessoais recolhidos ao abrigo dos artigos 9.º e 10.º do presente regulamento, bem como ao abrigo do artigo 23.º, n.º 1, do presente regulamento, quando esses dados sejam utilizados para fins de controlo oficial.
+A Comissão é responsável pelo tratamento na aceção do Regulamento (UE) 2018/1725 no que diz respeito ao tratamento de dados pessoais recolhidos ao abrigo do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do artigo 26.º, n.º 4, terceiro parágrafo, bem como ao abrigo do artigo 23.º, n.º 1, do presente regulamento, quando esses dados sejam utilizados para de cumprimento do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações nos termos do presente regulamento.
+É proibido às pessoas com acesso aos dados pessoais referidos no primeiro e segundo parágrafos divulgar quaisquer dados pessoais de que tenham tido conhecimento no exercício das suas funções ou . Os Estados-Membros e a Comissão tomam todas as medidas adequadas para fazer cumprir esta proibição.
+Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para fins diferentes dos seguintes:
+a) Controlos oficiais, pelas autoridades competentes dos Estados-Membros, do cumprimento dos requisitos relativos ao bem-estar e à rastreabilidade no presente regulamento e do cumprimento do Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
+b) Cumprimento, pela Comissão, das obrigações que lhe incumbem por força do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações que lhe incumbem por força do presente regulamento.
+2. Os dados pessoais a que se refere o n.º 1 do presente artigo são conservados pelos seguintes períodos:
+a) Nos casos previstos nos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
+b) No caso previsto no artigo 21.º, n.º 5, 18 meses após a geração do testemunho de verificação a que se refere o artigo 21.º, n.º 3, segundo parágrafo;
+c) Nos casos previstos no artigo 23.º, n.os 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
+d) No caso previsto no artigo 26.º, n.º 4, terceiro parágrafo, cinco anos após a data da notificação prévia.
+CAPÍTULO V
+ENTRADA DE CÃES E GATOS NA UNIÃO</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3398,25 +3398,27 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1.	Os cães e os gatos podem ser introduzidos na União para efeitos de colocação no mercado da União apenas se estiverem cumpridas as seguintes condições:
-(a)	tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
-(i)	os requisitos do Capítulo II do presente Regulamento;
-(ii)	requisitos reconhecidos pela União, em conformidade com o artigo 129.º do Regulamento (UE) 2017/625, como equivalentes aos estabelecidos no Capítulo II do presente Regulamento; ou
-(iii)	quando aplicável, requisitos constantes de um acordo específico entre a União e o país exportador.
-(b)	provenham de um país terceiro ou território e de um estabelecimento incluído em lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
-2.	O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos introduzidos na União desde países terceiros e territórios para efeitos de colocação no mercado da União deve conter uma atestação certificando a conformidade com o n.º 1 do presente artigo.
-3.	Os cães e gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um médico veterinário por meio de um transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
-O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes são registados por um médico veterinário numa base de dados nacional referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após a sua introdução na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
-4.	O movimento não comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário a uma base de dados online de viajantes da União com animais de estimação, pelo menos cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
-(a)	quando o cão ou gato é introduzido na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) …/… da Comissão; e
-(b)	quando o cão ou gato está registado numa base de dados de um Estado-Membro referida no artigo 23.º, n.º 1, do presente Regulamento.
-Caso o cão ou gato permaneça mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após o termo do sexto mês desde a sua entrada na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
-A Comissão estabelece e mantém a base de dados de viajantes da União com animais de estimação referida no primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados a uma entidade independente, na sequência de um processo de seleção pública. O acesso a essa base de dados fica restrito às autoridades competentes dos Estados-Membros e à Comissão.
-A Comissão assegura que a base de dados aciona notificações iRASFF para os movimentos pré-notificados que apresentem um risco de fraude. O Estado-Membro que recebe a notificação toma as medidas adequadas para dar seguimento à notificação, em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
-A Comissão adota, até … [8 anos após a data de entrada em vigor do presente Regulamento], atos de execução que estabelecem regras pormenorizadas relativas a:
-(i)	as informações a pré-notificar pelos proprietários em conformidade com o n.º 4 do presente artigo na base de dados de viajantes da União com animais de estimação, tendo em conta os requisitos de proteção de dados pessoais do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
-(ii)	o procedimento pelo qual o risco de fraude deve ser determinado, tendo em conta as atividades realizadas pela rede CAA.
-Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
+          <t>1. ▌Os cães e os gatos só podem ser introduzidos na União para efeitos de colocação no mercado da União se estiverem preenchidas as seguintes condições:
+a) Foram criados e detidos em conformidade com qualquer um dos seguintes requisitos:
+i) os requisitos constantes do capítulo II do presente regulamento
+ii) os requisitos reconhecidos pela União, em conformidade com o artigo 129.º do Regulamento (UE) 2017/625, como equivalentes aos estabelecidos no capítulo II do presente regulamento ou
+iii) se for caso disso, os requisitos constantes de um acordo específico entre a União e o país de exportação
+b) ▌São provenientes de um país ou território terceiro e de um estabelecimento constantes de uma lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
+2. ▌O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625, que acompanha os cães e gatos introduzidos na União a partir de países e territórios terceiros com vista à sua colocação no mercado da União, deve conter um atestado que certifique a conformidade com o n.º 1 do presente artigo.
+3. ▌Os cães e os gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um veterinário através de um transpondedor injetável que contenha um circuito integrado legível que cumpra os requisitos estabelecidos no anexo II.
+O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes sejam registados numa base de dados nacional a que se refere o artigo 23.º, n.º 1, por um veterinário, no prazo de cinco dias úteis após a sua na União. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que medidas para garantir a exatidão das informações que as pessoas em causa inserem na base de dados.
+4. A circulação sem caráter comercial de um cão ou gato a partir de um país ou território terceiro para a União deve ser notificada previamente pelo seu proprietário a uma base de dados em linha da União de animais de companhia em viagem, pelo menos, cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
+a) O cão ou o gato é introduzido na União diretamente a partir de países terceiros ou a partir de territórios que preenchem as condições no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) .../... da Comissão, e
+b) O cão ou o gato está registado numa base de dados de um Estado-Membro a que se refere o artigo 23.º, n.º 1, do presente regulamento.
+Se o cão ou o gato permanecer mais de seis meses na União, o proprietário deve assegurar que seja registado na base de dados do Estado-Membro de residência a que se refere o artigo 23.º, n.º 1, por um veterinário, no prazo de cinco dias úteis após o termo do sexto mês desde que entrou na União. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que medidas para garantir a exatidão das informações que as pessoas inserem na base de dados.
+A Comissão deve criar e manter a base de dados da União de animais de companhia em viagem a que se refere o primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento base de dados a uma entidade independente, na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509. O acesso a esta base de dados deve ser limitado às autoridades competentes dos Estados-Membros e à Comissão.
+A Comissão deve assegurar que a base de dados desencadeie notificações iRASFF sobre circulações notificadas previamente que apresentem um risco de fraude. O Estado-Membro que recebe a notificação deve tomar as medidas adequadas para dar seguimento a essa notificação em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
+Até ... [oito anos após a data de entrada em vigor do presente regulamento], a Comissão adota atos de execução que estabelecem disposições pormenorizadas relativas ao seguinte:
+i) As informações a notificar previamente pelos proprietários, em conformidade com o n.º 4 do presente artigo, na base de dados da União de animais de companhia em viagem, tendo em conta os requisitos de proteção de dados pessoais constantes do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
+ii) O procedimento a seguir para determinar o risco de fraude, que deve ter em conta as atividades exercidas pela rede AAC.
+Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.
+CAPÍTULO VI
+DISPOSIÇÕES PROCESSUAIS</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3517,21 +3519,21 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
-(a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
-(b) Requisitos de abastecimento de água e alimentação e processo de desmame;
-(c) Gamas de temperatura;
-(d) Requisitos de iluminação;
-(e) Níveis de amoníaco e monóxido de carbono;
-(f) Conceção de canis e gatis;
-(g) Alojamento em grupo;
-(h) Espaços permitidos para diferentes categorias de cães e gatos;
-(i) Frequência de gestações;
-(j) Idade mínima e máxima de cadelas e gatas para reprodução;
-(k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
-(l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
-(m) Dados a recolher para avaliação e monitorização de políticas.
-Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
+          <t>A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 2.º, que alterem os anexos do presente regulamento para ter em conta o progresso científico e técnico, incluindo, se for caso disso, os pareceres científicos da , no que diz respeito ao seguinte:
+a) Número adequado de cuidadores de animais em estabelecimentos de criação e de venda;
+b) Requisitos de abeberamento e de alimentação e processo de desmame;
+c) Gamas de temperaturas;
+d) Requisitos de iluminação;
+e) Níveis de amoníaco e de monóxido de carbono;
+f) Conceção dos canis e dos gatis;
+g) Alojamento em grupo;
+h) Espaço disponível para as várias categorias de cães e gatos;
+i) Frequência de gravidezes;
+j) Idade mínima e máxima das cadelas e das gatas para a reprodução;
+k) Medidas de socialização, de enriquecimentos e outras para satisfazer as necessidades comportamentais dos cães e gatos;
+l) Requisitos aplicáveis aos transpondedores utilizados para identificar individualmente os cães e gatos;
+m) Dados a recolher para  e a avaliação das políticas.
+Quaisquer aditamentos de requisitos aos anexos devem basear-se em dados científicos ou técnicos atualizados, em especial no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito de aplicação do presente regulamento. Se for caso disso, os atos delegados em causa devem ter em conta os impactos sociais, económicos e ambientais e devem prever períodos de transição suficientes para permitir que os operadores em causa se adaptem aos novos requisitos.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3603,11 +3605,11 @@
       <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1. O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
-2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
-3. A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a contar de ... [data de entrada em vigor do presente regulamento].
+3. A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
 4. Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
 5. Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
-6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
+6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º, n.º 3, do artigo 13.º, n.º 2, e do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação do ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogável por dois meses por iniciativa do Parlamento Europeu ou do Conselho. ▌</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3676,9 +3678,11 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1 — A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité deve ser entendido como comité na aceção do Regulamento (UE) n.º 182/2011.
-2 — Caso se faça referência ao presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
-3 — Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.</t>
+          <t>1. A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité é um comité na aceção do Regulamento (UE) n.º 182/2011.
+2. Caso se remeta para o presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
+Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.
+CAPÍTULO VII
+REGRAS NACIONAIS MAIS E DISPOSIÇÕES FINAIS</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3742,9 +3746,9 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
-2. Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
-3. Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
+          <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham ou adotem regras nacionais mais que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e uma maior rastreabilidade dos cães e gatos, desde que essas regras não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno. ▌
+2. Os Estados-Membros devem informar a Comissão acerca de quaisquer regras nacionais mais . Posteriormente, os Estados-Membros devem informar a Comissão acerca de regras nacionais mais rigorosas antes de as adotarem, a menos que já tenham notificado os projetos de regras nacionais como projetos de regras técnicas nos termos do artigo 5.º da Diretiva (UE) 2015/1535 do Parlamento Europeu e do Conselho. A Comissão transmite essas informações aos outros Estados-Membros.
+3. Os Estados-Membros que disponham de regras nacionais mais a que se refere o n.º 1 não podem proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas regras nacionais mais ▌.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3810,11 +3814,11 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
-2. Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
-a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
-b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
-3. Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
+          <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em quaisquer informações adicionais pertinentes, a Comissão publica, até … [▌anos a contar da data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+2. Até … [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento ▌e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Nessa avaliação e nesse relatório, a Comissão deve examinar, em especial:
+a) Em que medida o presente regulamento contribuiu para assegurar um elevado nível de bem-estar para os cães e gatos, melhorando a sua rastreabilidade e reduzindo o seu comércio ilegal;
+b) O impacto que o presente regulamento teve sobre os operadores de estabelecimentos de criação e venda e de abrigos, bem como sobre os operadores que colocam cães e gatos em de acolhimento, tendo em conta, nomeadamente, os encargos administrativos e os custos de conformidade.
+3. Para efeitos do relatório referido no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração do mesmo.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3881,8 +3885,8 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
-Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
+          <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, inclusive as aplicáveis ao abandono de cães e gatos pelos operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
+Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3954,15 +3958,18 @@
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
-É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
-i. o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
-ii. o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
-iii. o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
-iv. o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
-v. o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
-vi. o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
-vii. o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
-O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
+O presente regulamento é aplicável a partir de … [dois anos a contar da data de entrada em vigor do presente regulamento]. No entanto,
+i) artigo 16.º é aplicável a partir de … [três anos a contar da data de entrada em vigor do presente regulamento]
+ii)  artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos a contar da data de entrada em vigor do presente regulamento]
+iii) artigo 8.º, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º, n.º 2, é aplicável a partir de 1 de julho de 2030
+iv) artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, o artigo 21.º, n.os 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.os 3 e 4, e o artigo 26.º, n.os 1, 2 e 3, são aplicáveis a partir de … [cinco anos a contar da data de entrada em vigor do presente regulamento
+v) artigo 12.º, n.os 2 e 3, é aplicável a partir de … [sete anos a contar da data de entrada em vigor do presente regulamento
+vi) artigo 10.º é aplicável a partir de … [oito anos a contar da data de entrada em vigor do presente regulamentoe
+vii) artigo 26.º, n.º 4, é aplicável a partir de … [10 anos a contar da data de entrada em vigor do presente regulamento].
+O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.
+Feito em …, em …
+Pelo Parlamento Europeu	Pelo Conselho
+A Presidente	O Presidente</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -4035,11 +4042,11 @@
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>1. Alimentação e abeberamento
-1.1 Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
-No entanto, estes requisitos não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que esses cães sejam utilizados para fins de guarda ou de treino.
-2.2 Cada cachorro ou gatinho deve ser alimentado com colostro, pelo menos, durante os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da progenitora ou de uma cadela ou gata lactante. Se tal não for possível, por a progenitora estar doente ou estar de outro modo impossibilitada de alimentar a sua ninhada ou de fornecer leite em quantidade suficiente, o cachorro ou gatinho deve ser alimentado com um sucedâneo de leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as instruções do fabricante ou de um médico veterinário.
-3.3 Todos os cachorros e gatinhos não desmamados devem receber leite, sucedâneo de leite ou uma combinação de ambos em quantidade suficiente para lhes permitir aumentar de peso de forma constante
-4.4 O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
+1.1.	Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
+No entanto, estes requisitos não se aplicam a cães de guarda de gado mantidos em estabelecimentos de criação enquanto estes cães são usados para fins de guarda ou de treino.
+▌1.2.	Cada cachorro ou gatinho ▌deve ser alimentado com colostro durante, pelo menos, os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da respetiva mãe ou de uma cadela ou gata em lactação. Se tal não for possível, em razão de a mãe estar doente ou de, por outro motivo, não poder alimentar a sua cria ou de não poder fornecer leite suficiente, o cachorro ou gatinho deve ser alimentado com um substituto do leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as indicações do fabricante ou de um veterinário.
+1.3.	▌Todos os cachorros e gatinhos não desmamados devem ser alimentados com uma quantidade de leite, de substituto do leite ou de uma combinação destes que seja suficiente para aumentar constantemente o peso corporal.
+1.4.	O desmame deve ser efetuado com a introdução gradual de alimentos sólidos, durante um período não inferior a sete dias, e não deve ser concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4162,30 +4169,18 @@
       <c r="D32" s="4" t="inlineStr">
         <is>
           <t>2. Alojamento
-2.1 Temperatura
-Em estabelecimentos de criação, a temperatura deve ser mantida dentro de uma gama de:
-— 22 a 28°C em áreas de parto de cães durante os primeiros 10 dias de vida dos filhotes;
-— 18 a 27°C em áreas de parto de gatos durante os primeiros 21 dias de vida dos gatinhos.
-2.2 Iluminação
-Cães e gatos devem ser expostos a luz durante pelo menos 7 horas por dia. A luz artificial deve ser de espectro amplo ou espectro completo com uma frequência de pelo menos 80 Hz.
-Cães e gatos devem ter a possibilidade de estar sem luzes artificiais durante pelo menos 8 horas por dia.
-2.3 Espaço adequado
-2.3.1 As áreas de parto devem ser concebidas de modo a permitir que a progenitora se afaste da sua prole.
-2.3.2 No caso dos estabelecimentos de criação e de venda, aplicam-se as seguintes superfícies mínimas para cães e gatos, as quais devem ser calculadas com base na área total permanentemente acessível aos cães ou gatos.
-2.3.3
-Espaço para cães com ou sem crias
-Altura do var (cm):
-&lt; 30 → Área mínima: 4 m², Altura: 200 cm
-30-40 → 5 m², 200 cm
-40-60 → 8 m², 200 cm
-60-70 → 10 m², 200 cm
-&gt;70 → 10 m², 200 cm
-Cada cão adicional: 3/3.5/4/5/6 m² respetivamente.
-Espaço para gatos com ou sem crias
-Um gato: 3 m² solo, 200 cm altura
-Cada adicional: 2 m².
-* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura.
-** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
+2.1.	Temperatura:
+Nos estabelecimentos de criação, a temperatura deve ser mantida numa gama de:
+▌a)	22 °C a 28 °C nas áreas de parto durante os primeiros 10 dias de vida dos cachorros;
+b) 18 °C a 27 °C nas áreas de parto durante os primeiros 21 dias de vida dos gatinhos.
+2.2.	Iluminação
+2.2.1.	Os cães e gatos devem ser expostos à luz durante pelo menos sete horas por dia. ▌
+2.2.2.	A luz artificial deve ser de largo espetro ou de espetro completo e ter uma frequência de pelo menos 80 hertz.
+2.2.3.	Os cães e gatos devem ter a possibilidade de não estar expostos a iluminação artificial durante, pelo menos, oito horas por dia.
+2.3.	Espaço disponível
+2.3.1.	As áreas de parto para as cadelas e gatas devem ser concebidas de modo a permitir que a mãe se afaste das crias.
+2.3.2.	No caso dos estabelecimentos de criação e venda, aplicam-se as seguintes regras aos seguintes espaços disponíveis mínimos para os cães e gatos, com base na área permanentemente acessível total para os cães ou gatos:
+2.3.3.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4255,13 +4250,13 @@
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>3. Saúde
-1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
-2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
-3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
-4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nascimortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
-5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
-6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
-O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
+3.1.	As gatas só podem reproduzir-se se a sua idade for igual ou superior a 10 meses.
+3.2.	As cadelas não podem ser utilizadas para a reprodução antes do seu segundo cio.
+3.3.	Uma cadela ou gata não pode produzir mais de três ninhadas num período de dois anos.
+3.4.	Para as cadelas e gatas que tenham produzido três ninhadas, incluindo nados-mortos, durante um período de dois anos, deve existir um período de recuperação ▌de, pelo menos, um ano.
+3.5.	Qualquer cadela ou gata que tenha sido submetida a duas cesarianas deixará de ser utilizada para a reprodução.
+3.6.	Antes de serem utilizadas para a reprodução, as cadelas com idade igual ou superior a oito anos e as gatas com idade igual ou superior a seis anos devem ser fisicamente examinadas por um veterinário que confirme, por escrito, que, à data desse exame, não existem indicações médicas que obstem à utilização da cadela ou gata em causa para a reprodução.
+O operador deve conservar a confirmação escrita referida no primeiro parágrafo durante um período de, pelo menos, três anos.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4332,16 +4327,16 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Bem-Estar Comportamental
-1.1 Socialização
-A partir das três semanas de idade, cães e gatos devem ser gradualmente fornecidos com oportunidades diárias de contato social com seus congêneres e humanos, e, sempre que possível, com outras espécies animais.
-Cães e gatos que representam uma ameaça um ao outro devido a comportamento agressivo ou causam um ao outro stress excessivo ou desconforto devem ser mantidos separados.
-2.2 Enriquecimento
-Onde gatos são mantidos, deve haver um número suficiente de postes de arranhadura, locais de abrigo e prateleiras para garantir que cada gato pode subir, descansar, observar e retirar-se.
-3.3 Separação
-Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes das 8 semanas de idade.
-Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes das 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes das 12 semanas de idade.
-Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
+          <t>4. Necessidades comportamentais
+4.1.	Socialização
+4.1.1.	A partir das três semanas de idade, os cães e gatos devem dispor gradualmente de oportunidades diárias de contacto social com outros animais da mesma espécie e com seres humanos e, sempre que possível, com animais de outras espécies.
+4.1.2.	Os cães ou gatos que constituam uma ameaça para congéneres devido a comportamentos agressivos ou que causem stress ou desconforto indevidos aos congéneres devem ser mantidos à parte.
+4.2.	Enriquecimentos
+4.2.1.	Os gatos devem dispor de um número suficiente de arranhadores, esconderijos e prateleiras para garantir que cada gato possa subir, descansar, observar e retirar-se.
+4.3.	Separação
+Os cachorros detidos em estabelecimentos não podem ser permanentemente separados das mães antes das oito semanas de idade.
+Os gatinhos detidos em abrigos e casas de acolhimento não podem ser permanentemente separados das mães antes das oito semanas de idade. Os gatinhos detidos em estabelecimentos de criação não podem ser permanentemente separados das mães antes das 12 semanas de idade.
+No entanto, a separação precoce das mães deve ser possível por razões médicas, com base no parecer escrito de um veterinário. O operador deve manter um registo desse parecer até que o último cachorro ou gatinho da ninhada em causa seja colocado no mercado.</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -4458,12 +4453,11 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Identificação e registo de cães e gatos
-Os transponders utilizados para identificar individualmente cães e gatos, tal como exigido nos artigos 20.º e 26.º, devem cumprir os seguintes requisitos:
-(a) O microchip deve conter um número de identificação individual, não repetível e não reprogramável;
-(b) O número de identificação deve começar pelo país de identificação do cão ou gato, identificado em conformidade com a norma ISO 3166;
-(c) A estrutura do código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
-(d) a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
+          <t>Os transpondedores utilizados para identificar individualmente cães e gatos, tal como exigido no artigo 20.º e no artigo 26.º, devem cumprir os seguintes requisitos:
+a) O circuito integrado deve conter um número de identificação individual, não repetível e não reprogramável;
+b) O número de identificação deve começar com o país de identificação do cão ou gato identificado em conformidade com a norma ISO 3166;
+c) A estrutura do código e o conceito técnico da identificação por radiofrequências devem estar em conformidade com as normas ISO 11784 e 11785;
+d) A conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -4542,10 +4536,10 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1. O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
-2.  O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
-3. O número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 10.º.
-4. O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
+          <t>1. Número de cães e gatos registados, por ano, a que se referem o artigo 20.º e o artigo 26.º, n.º 3.
+2. Número de estabelecimentos de criação, estabelecimentos de venda, abrigos e casas de acolhimento registados, por ano, em conformidade com o artigo 9.º.
+3. Número de estabelecimentos de criação aprovados por ano a que se refere o artigo 10.º.
+4. Número de estabelecimentos de criação cuja aprovação foi suspensa ou retirada, por ano.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -680,8 +680,8 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>1. Um estabelecimento de criação em que não sejam produzidas mais de duas ninhadas por ano civil para colocação no mercado apenas está sujeito às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 2, 3 e 4, no artigo 8.º, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º, n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º, no artigo 19.º, n.º 1 e nos pontos 3 e 4.3 do nexo I.
-2. Os abrigos que detenham, no máximo, um total combinado de 15 cães ou gatos, a todo o momento, ou quaisquer casas de acolhimento, apenas estão sujeitos às obrigações previstas no artigo 6.º, no artigo 7.º, n.os 1, 2, 3, 4, e 5, no artigo 9.º, no artigo 11.º, no artigo 14.º, n.os 2, 3 e 4, no artigo 15.º n.os 3, 4 e 8, no artigo 16.º, n.º 1, alíneas a), b), c) e d), no artigo 17.º, n.º 2, 3, 5 e 7, no artigo 18.º e no ponto 4.3 do nexo I.</t>
+          <t>1. Um estabelecimento de criação que produz no máximo duas ninhadas por ano civil para colocação no mercado fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.º 1, alíneas 1b, 1c e 1d), artigo 6a, artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º, artigo 15a (n.º 1) e ponto 3 e 4.3 do Anexo I.
+2. Um abrigo, onde são mantidos no máximo 15 cães ou gatos em qualquer momento, ou qualquer lar de acolhimento fica sujeito apenas às obrigações estabelecidas no artigo 5.º, artigo 6.º (n.ºs 1, 1a, 1b, 1c e 1d), artigo 7.º, artigo 8.º, artigo 11.º (n.ºs 2, 3 e 3a), artigo 12.º (n.ºs 3, 4 e 7), artigo 13.º (n.º 2, alíneas a, b, c e d), artigo 14.º (n.ºs 2, 3, 4 e 5a), artigo 15.º e ponto 4.3 do Anexo I.</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Os operadores ▌devem aplicar os seguintes princípios gerais de bem‑estar no que diz respeito aos cães ou gatos criados ou detidos no seu estabelecimento:
-a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que lhes uma nutrição e hidratação adequadas;
-b) Os cães e os gatos são detidos num ambiente físico que é adequado e limpo com regularidade, que é seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, luz, proteção contra condições climáticas adversas e que é suficientemente grande para prevenir a sobrelotação e para lhes proporcionar facilidade de circulação;
-c) Os cães e os gatos são detidos em segurança, limpos e em boa saúde, devendo as doenças, ▌lesões e dores que decorrem em especial da gestão, das práticas de manuseamento e das práticas de criação, ser prevenidas;
-d) Os cães e os gatos são detidos num ambiente que lhes permite exibir comportamentos específicos da espécie e sociais não nocivos e estabelecer uma relação positiva com os seres humanos;
-e) Os cães e os gatos são detidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo ▌os estímulos negativos em termos de duração e intensidade, bem como maximizando as oportunidades de estímulos positivos em termos de duração e intensidade, de forma que previna o desenvolvimento de comportamentos repetitivos anormais ou de outros comportamentos indicadores de um deficiente bem-estar animal, e que tenha em conta as necessidades de cada animal nos domínios referidos nas alíneas a) a d).</t>
+          <t>Os operadores devem aplicar os seguintes princípios gerais de bem-estar aos cães e gatos criados ou detidos nos seus estabelecimentos:
+(a) Os cães e os gatos recebem água e alimentos de qualidade e numa quantidade que assegura a sua boa e adequada nutrição e hidratação;
+(b) os cães e gatos são mantidos num ambiente físico adequado, regularmente limpo, seguro e confortável, especialmente em termos de espaço, qualidade do ar, temperatura, iluminação, proteção face a condições climáticas adversas e facilidade de movimentação, prevenindo a sobrelotação;
+(c) os cães e gatos são mantidos seguros, limpos e com boa saúde, prevenindo doenças, lesões e dor, nomeadamente através de práticas de maneio, manuseamento e reprodução adequadas;
+(d) os cães e gatos são mantidos num ambiente que lhes permite exibir comportamentos específicos da espécie e comportamentos sociais não nocivos, e estabelecer uma relação positiva com os seres humanos;
+(e) (e) os cães e gatos são mantidos de forma a otimizar o seu estado mental, prevenindo ou reduzindo estímulos negativos em duração e intensidade, maximizando oportunidades de estímulos positivos, prevenindo o desenvolvimento de comportamentos repetitivos anormais, tendo em conta as necessidades individuais do animal nos domínios referidos nas alíneas (a) a (d).</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -831,16 +831,15 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌ são responsáveis pelo bem‑estar dos cães e gatos detidos em estabelecimentos sob a sua responsabilidade e controlo e pela minimização de quaisquer riscos para o bem‑estar desses animais.
-2. No caso das casas de acolhimento, a responsabilidade incumbe aos operadores em cujo nome os cães ou gatos são detidos. Tais operadores não devem, em nenhum momento, colocar mais do que um total combinado de cinco cães ou gatos, ou mais do que uma ninhada, com ou sem mãe, numa casa de acolhimento, e devem à família de acolhimento as informações adequadas sobre as obrigações em matéria de bem-estar dos animais, assim como sobre as necessidades individuais dos cães ou gatos, devendo ainda assegurar que nessas casas de acolhimento sejam respeitadas as obrigações pertinentes previstas no presente regulamento.
-O Estado-Membro em que se situa a casa de acolhimento pode autorizar que um maior número de cães, gatos ou ninhadas seja colocado na casa de acolhimento, desde que as instalações desta disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais na referida casa seja suficiente para assegurar o bem-estar dos cães ou gatos.
-3. Os operadores não podem sujeitar nenhum cão ou gato a crueldade, abuso ou maus-tratos, nomeadamente fazendo-os participar em atividades suscetíveis de resultar em atos de crueldade, abuso ou maus-tratos dos cães ou gatos criados ou detidos pelo operador.
-4. Os operadores não abandona os cães ou gatos por eles criados ou detidos.
-5. Antes de cessarem as suas atividades num estabelecimento, os operadores devem garantir que os cães ou gatos aí detidos sejam realojados, quer assumindo eles próprios a propriedade dos animais de companhia, quer transferindo a responsabilidade pelos cães e gatos, ou a propriedade dos mesmos, para outros operadores ou adquirentes.
-6. Os operadores ▌devem assegurar que os cães e gatos sejam manuseados por um número de cuidadores de animais suficiente para satisfazer as necessidades de bem-estar dos cães ou dos gatos que são detidos nos seus estabelecimentos, e que esses cuidadores possuam as ▌competências exigidas nos termos do artigo 12.º
-7. Os operadores devem assegurar o bem-estar dos cães ou dos gatos pelos quais são responsáveis, fazendo um dos indicadores relativos ao comportamento e aspeto físico baseados nos animais e tomando medidas em função do resultado dess .
-8. A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º para complementar o presente regulamento, prevendo indicadores relativos ao comportamento e aspeto físico baseados nos animais, que devem ser usados pelos operadores para efeitos d a realizar em conformidade com o n.º 7 do presente artigo, assim como os métodos a usar pelos operadores para a sua medição.
-.▌</t>
+          <t>1. Os operadores são responsáveis pelo bem-estar dos cães e gatos detidos nos estabelecimentos sob a sua responsabilidade e controlo, devendo minimizar quaisquer riscos para o bem-estar desses animais.
+2. No caso das famílias de acolhimento, a responsabilidade incumbe ao operador em cujo nome os cães ou gatos são detidos. Tais operadores não colocam mais do que um total combinado de cinco cães ou gatos ou uma ninhada, com ou sem a mãe, num lar de acolhimento em qualquer momento dado e fornecem à família de acolhimento informações adequadas sobre as obrigações em matéria de bem-estar dos animais, bem como sobre as necessidades individuais dos cães ou gatos, e asseguram que as obrigações relevantes previstas no presente regulamento são cumpridas nos lares de acolhimento.
+O Estado-Membro em que se situa o lar de acolhimento pode autorizar um maior número de cães, gatos ou ninhadas na família de acolhimento, desde que as instalações do lar de acolhimento disponham de espaço suficiente, incluindo espaço exterior, e que o número de cuidadores de animais no lar de acolhimento seja suficiente para garantir o bem-estar dos cães e gatos.
+3. Os operadores não sujeitam qualquer cão ou gato a crueldade, abusos ou maus-tratos, incluindo fazendo-os participar em atividades suscetíveis de resultar em crueldade, abusos ou maus-tratos para os cães ou gatos criados ou detidos pelo operador.
+4. Os operadores não abandonam os cães ou gatos criados ou detidos por eles.
+5. Antes de os operadores cessarem as atividades num estabelecimento, asseguram que os cães ou gatos aí detidos são realojados, seja assumindo eles próprios a propriedade de animal de companhia, seja transferindo a responsabilidade pela propriedade dos cães e gatos para outros operadores ou adquirentes.
+6. Os operadores asseguram que os cães e gatos são manuseados por um número suficiente de cuidadores de animais para satisfazer as necessidades de bem-estar dos cães ou gatos detidos nos seus estabelecimentos, e que esses cuidadores possuem as competências exigidas no artigo 12.º.
+7. Os operadores asseguram o bem-estar dos cães ou gatos pelos quais são responsáveis, monitorizando indicadores baseados nos animais relativos ao comportamento e à aparência física, e adotando ações com base nos resultados desse monitoramento.
+8. A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 28.º, que complementem o presente regulamento, estabelecendo os indicadores baseados nos animais relativos ao comportamento e à aparência física que os operadores devem utilizar para efeitos de monitorização nos termos do n.º 7 do presente artigo, bem como os métodos pelos quais os operadores devem medi-los.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1038,16 +1037,24 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de reprodução minimizem o risco de produção de cães ou gatos com genótipos associados a efeitos prejudiciais para a saúde e bem-estar desses animais.
-2. Os operadores de estabelecimentos de criação não devem utilizar, para fins de reprodução, cães ou gatos com características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses cães ou gatos ou da sua descendência. Antes de selecionar um cão ou gato que possa ter uma característica de conformação excessiva para a reprodução, o operador deve consultar um veterinário ou uma pessoa qualificada independente que atue sob a responsabilidade de um veterinário. Tal veterinário ou pessoa qualificada independente deve avaliar se o cão ou gato tem uma característica de conformação excessiva.
-3. A Comissão fica habilitada a adotar atos delegados nos termos do artigo 28.º, que complementem o presente regulamento, definindo:
-a) As características dos genótipos a que se refere o n.º 1 que devem ser excluídas da reprodução, bem como os métodos para a sua avaliação e os requisitos em matéria de manutenção de registos;
-b) As características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídas da reprodução, os métodos para a sua avaliação e os requisitos em matéria de conservação de registos.
-Ao adotar esses atos delegados, a Comissão toma em consideração o parecer científico da Autoridade Europeia para a Segurança dos Alimentos, bem como quaisquer impactos sociais e económicos dos referidos atos delegados.
-Os atos delegados relativos às características de conformação excessivas devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
-4. No contexto da gestão da reprodução de cães e gatos, são proibidas as seguintes práticas:
-a) Reprodução entre progenitores e descendência, entre irmãos, entre meios-irmãos ou entre avós e netos, salvo aprovação pela autoridade competente com base numa necessidade específica de preservação de raças locais com património genético limitado;
-b) Reprodução para produção de híbridos.</t>
+          <t>1. Os operadores de estabelecimentos de criação devem assegurar que as suas estratégias de criação minimizam o risco de produzir cães ou gatos com genótipos associados a efeitos prejudiciais para a sua saúde e bem-estar.
+2. Os operadores de estabelecimentos de criação não devem utilizar para reprodução cães ou gatos que apresentem características de conformação excessivas que acarretem um elevado risco de efeitos prejudiciais para o bem-estar desses animais ou das suas crias. Antes da seleção para reprodução de um animal potencialmente afetado por características de conformação excessivas, o operador deve consultar um médico veterinário ou uma pessoa qualificada independente sob responsabilidade veterinária. O médico veterinário ou a pessoa qualificada independente devem avaliar se o animal tem uma característica de conformação excessiva.
+3. A Comissão tem competência para adotar atos delegados em conformidade com o artigo 28.º que complementem este Regulamento, definindo:
+(a) características dos genótipos a que se refere o n.º 1 que devem ser excluídos da reprodução, e os métodos para a sua avaliação e requisitos de manutenção de registos;
+(b) características de conformação excessivas a que se refere o n.º 2 do presente artigo que devem ser excluídos da reprodução, os métodos para a sua avaliação e requisitos de manutenção de registos.
+4. Ao adotar esses atos delegados, a Comissão tem em conta os pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos (EFSA), bem como os impactos sociais e económicos desses atos delegados.
+5. Os atos delegados relativos aos traços conformacionais excessivos devem ser adotados até 1 de julho de 2030. Os atos delegados relativos aos genótipos devem ser adotados até 1 de julho de 2036.
+6. São proibidos na gestão da reprodução de cães e gatos:
+(a) o cruzamento entre progenitores e descendentes, entre irmãos, entre meios-irmãos ou entre avós e netos, exceto com aprovação da autoridade competente por razão de necessidade específica de preservação de raças locais com reserva genética limitada;
+(b) o cruzamento para produção de híbridos.
+@regulamento — Tradução PT-PT · ANEXO I, Ponto 3 do Regulamento 2023/0447
+1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nado-mortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1185,18 +1192,18 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌devem notificar as autoridades competentes da sua atividade, facultando pelo menos as seguintes informações para cada um dos seus estabelecimentos:
-a) O nome, o endereço e dados de contacto do operador;
-b) A localização do estabelecimento;
-c) O tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou casa de acolhimento;
-d) A espécie e, para os estabelecimentos de criação, as raças dos cães ou gatos detidos no estabelecimento;
-e) A capacidade do estabelecimento, expressa em termos de número máximo de cães e gatos que podem ser detidos no estabelecimento
-f) No caso dos estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
-2. Os operadores comunicam à autoridade competente:
-a) Qualquer alteração relativa às informações referidas no n.º 1;
-b) Se for o caso, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data;
-3. Os Estados-Membros devem utilizar as informações facultadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já comunicadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
-4. A autoridade competente deve manter um registo de estabelecimentos. A autoridade competente pode utilizar, para este efeito, o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
+          <t>1. Os operadores devem notificar as autoridades competentes da sua atividade, fornecendo pelo menos as seguintes informações para cada um dos seus estabelecimentos:
+(a) o nome, morada e contactos do operador;
+(b) a localização do estabelecimento;
+(c) o tipo de estabelecimento: estabelecimento de criação, estabelecimento de venda, abrigo ou família de acolhimento;
+(d) as espécies e, para os estabelecimentos de criação, as raças dos cães ou gatos mantidos no estabelecimento;
+(e) a capacidade do estabelecimento, expressa no número máximo de cães e gatos que podem ser alojados no estabelecimento;
+(f) para os estabelecimentos de criação, o número estimado de ninhadas a colocar no mercado por ano.
+2. Os operadores devem notificar a autoridade competente de:
+(a) quaisquer alterações relativas às informações referidas no n.º 1;
+(b) quando aplicável, a data prevista de cessação das suas atividades, o mais tardar cinco dias úteis antes dessa data.
+3.	Os Estados-Membros devem utilizar as informações fornecidas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429. Os operadores não são obrigados a notificar novamente as informações já apresentadas em conformidade com o artigo 84.º do Regulamento (UE) 2016/429.
+4.	A autoridade competente deve manter um registo dos estabelecimentos. A autoridade competente pode utilizar para esse efeito o registo previsto no artigo 101.º, n.º 1, alínea a), do Regulamento (UE) 2016/429.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1458,14 +1465,14 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação que produzam ou tencionem produzir mais de cinco ninhadas por ano civil, ou que, a qualquer momento, detenham um total combinado de mais de cinco cadelas ou gatas, só podem colocar cães ou gatos no mercado após aprovação do seu estabelecimento pela autoridade competente.
-2. A autoridade competente deve efetuar inspeções no local para verificar se o estabelecimento cumpre os requisitos do presente regulamento. Os Estados-Membros podem autorizar que estas inspeções sejam realizadas à distância, desde que o meio de comunicação à distância utilizado permita recolher provas suficientes para que a autoridade competente realize inspeções fiáveis. A autoridade competente só deve conceder certificados de aprovação a estabelecimentos de criação que cumpram os requisitos do presente regulamento.
-3. A autoridade competente deve manter uma lista acessível ao público que contenha as seguintes informações para cada estabelecimento aprovado:
-a) O nome, os dados de contacto e, sempre que disponível, o URL do sítio Web do estabelecimento;
-b) O endereço do estabelecimento;
-c) O nome do operador;
-d) As espécies e, sendo caso disso, as raças relacionadas com as atividades aprovadas do estabelecimento;
-e) O número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data de aprovação e de cessação das atividades.</t>
+          <t>1. Os operadores de estabelecimentos de criação que produzem ou pretendem produzir mais de cinco ninhadas por ano civil ou que mantêm mais do que um total combinado de cinco cadelas ou gatas em qualquer momento podem colocar cães ou gatos no mercado apenas após a aprovação do seu estabelecimento pela autoridade competente.
+2. A autoridade competente deve realizar inspeções no local para verificar que o estabelecimento atende aos requisitos do presente Regulamento. Os Estados-Membros podem permitir que tais inspeções sejam realizadas remotamente, desde que o meio de comunicação à distância utilizado forneça provas suficientes para a autoridade competente realizar inspeções fiáveis. A autoridade competente deve conceder certificados de aprovação apenas aos estabelecimentos de criação que cumprem os requisitos do presente Regulamento.
+3. A autoridade competente deve manter uma lista disponível ao público incluindo as seguintes informações para cada estabelecimento aprovado:
+(a) o nome, dados de contacto e, se disponível, o URL do site do estabelecimento;
+(b) a morada do estabelecimento;
+(c) o nome do operador;
+(d) a(s) espécie(s) e, se relevante, a(s) raça(s) relacionada(s) com as atividades do estabelecimento aprovadas;
+(e) o número de aprovação único atribuído ao estabelecimento pela autoridade competente e a data da aprovação e cessação de atividades.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1543,11 +1550,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1. ▌Os operadores ▌devem facultar ao adquirente de um cão ou de um gato as informações escritas necessárias para permitir ao adquirente assegurar o bem‑estar do animal, incluindo informações sobre a propriedade responsável e sobre as necessidades específicas do animal em termos de alimentação, cuidados, saúde e alojamento, assim como informação a respeito das suas necessidades comportamentais e do seu historial sanitário.
-2. As informações escritas sobre do cão ou gato referidas no primeiro parágrafo devem incluir, pelo menos:
-a) A situação do animal em termos de vacinação;
-b) Quaisquer problemas de saúde ou predisposição para doenças, incluindo alergias, que sejam do conhecimento do operador, e quaisquer resultados de testes de diagnóstico do cão ou gato que se encontrem à disposição do operador.
-Sempre que as informações sobre  do animal constarem de um documento exigido por força do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
+          <t>1. Os operadores devem fornecer ao adquirente de um cão ou gato informação escrita necessária para lhe permitir assegurar o bem-estar do cão ou gato, incluindo informação sobre detenção responsável e sobre as necessidades específicas do cão ou gato em termos de alimentação, cuidados, saúde e alojamento, bem como informação sobre as suas necessidades comportamentais e historial de saúde.
+2. A informação escrita sobre o historial de saúde do cão ou gato referida no n.º 1 deve incluir pelo menos:
+(a) o estado de vacinação do cão ou gato;
+(b) quaisquer condições médicas ou predisposições a doenças, incluindo alergias, conhecidas pelo operador, e quaisquer resultados de testes de diagnóstico para o cão ou gato que estejam disponíveis para o operador.
+Caso a informação sobre o historial de saúde do cão ou gato esteja prevista num documento exigido nos termos do Regulamento (UE) 2016/429, o operador deve transmitir esse documento ao adquirente.</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1639,15 +1646,15 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1. Os cuidadores de animais, os voluntários em abrigos e os estagiários que atuem sob a responsabilidade de um cuidador animal competente, devem ter as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
-a) Compreensão do comportamento biológico dos animais e das suas necessidades fisiológicas e etológicas;
-b) Capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e tomar as medidas de atenuação adequadas ▌nesses casos;
-c) Capacidade para aplicar boas práticas de gestão animal, nomeadamente o condicionamento operante e o reforço positivo, para usar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
-d) Conhecimento das obrigações que incumbem aos cuidadores por força do presente regulamento.
-2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Para determinar se um cuidador animal tem as competências referidas no n.º 1 apenas serão tidos em conta o ensino, a formação ou a experiência profissional que se encontrem documentados.
-3. Os operadores devem garantir que pelo menos um cuidador de animais do estabelecimento,  voluntários ou estagiários, tenha concluído os cursos de formação referidos no artigo 22.º Os operadores devem garantir que esse cuidador de animais partilhe os seus conhecimentos com os outros cuidadores de animais do estabelecimento.
-4. A Comissão adota atos de execução que estabeleçam requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais tem as competências a que se refere o n.º 1 e para os cursos de formação a que se refere o n.º 3.
-O ato de execução relativo aos cursos de formação a que se refere o n.º 3 é adotado até... [anos a data de entrada em vigor do presente regulamento].
+          <t>1. Os cuidadores de animais, com exceção dos voluntários em abrigos e dos estagiários que atuem sob a responsabilidade de um cuidador de animais competente, devem possuir as seguintes competências no que diz respeito aos cães e gatos que manuseiam:
+(a) compreensão do comportamento biológico dos animais e das respetivas necessidades fisiológicas e etológicas;​
+(b) capacidade para reconhecer as expressões dos animais, incluindo qualquer sinal de sofrimento, e para identificar e adotar as medidas de atenuação adequadas nesses casos;
+(c) capacidade para aplicar boas práticas de gestão animal, incluindo o condicionamento operante e o reforço positivo, para utilizar e manter o equipamento utilizado para os cães ou gatos sob o seu cuidado e para minimizar quaisquer riscos para o bem-estar desses cães ou gatos, prevenindo o seu sofrimento;
+(d) conhecimento das obrigações que lhes incumbem por força do presente regulamento.​
+2. As competências referidas no n.º 1 podem ser adquiridas através de ensino, formação ou experiência profissional. Só o ensino, a formação ou a experiência profissional documentada são tidos em conta para determinar se um cuidador de animais possui as competências referidas no n.º 1.​
+3. Os operadores asseguram que, em cada estabelecimento, pelo menos um cuidador de animais, que não seja voluntário nem estagiário, tenha concluído os cursos de formação a que se refere o artigo 22.º. Os operadores asseguram que esse cuidador de animais transmita os seus conhecimentos aos restantes cuidadores de animais do estabelecimento.
+4. A Comissão adota atos de execução que estabelecem requisitos mínimos relativos ao ensino formal, à formação ou à experiência profissional referidos no n.º 2 do presente artigo, necessários para determinar se um cuidador de animais possui as competências referidas no n.º 1, bem como relativos aos cursos de formação a que se refere o n.º 3.​
+O ato de execução relativo aos cursos de formação referidos no n.º 3 é adotado até … [3 anos a contar da data de entrada em vigor do presente regulamento].​
 Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º</t>
         </is>
       </c>
@@ -1749,10 +1756,10 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌devem:
-a) Assegurar que os estabelecimentos sob a sua responsabilidade recebam ▌uma visita de um veterinário, a fim de identificar e avaliar qualquer fator de risco para o bem‑estar dos cães ou gatos, assim como aconselhar o operador ▌sobre as medidas destinadas a dar resposta a esses riscos, inicialmente até ... [três anos após a data de entrada em vigor do presente regulamento] ou um ano a contar da notificação do novo estabelecimento e, posteriormente, se for caso disso, com base numa análise do risco levada a cabo pelas autoridades competentes, ou anualmente, se os Estados-Membros assim o previrem no seu direito nacional;
-b) Conservar um registo das conclusões da visita do veterinário a que se refere a alínea a) e das suas ações de acompanhamento durante ▌pelo menos quatro anos, a contar do dia da visita, e disponibilizar esse registo às autoridades competentes, mediante pedido, assim como aos veterinários que fizerem as visitas de acompanhamento subsequentes.
-2. Até... [24 meses a contar da data de entrada em vigor do presente regulamento], a Comissão adota atos delegados, nos termos do artigo 28.º, que complementem o presente artigo, prevendo os critérios mínimos a avaliar pelo veterinário durante a visita de aconselhamento para assegurar o bem‑estar.</t>
+          <t>1. Os operadores devem:
+(a) assegurar que os estabelecimentos sob a sua responsabilidade recebem uma visita de um médico veterinário no prazo de um ano a partir da data de aplicação do presente Regulamento ou no prazo de um ano após notificação de novo estabelecimento, com o objetivo de identificar e avaliar quaisquer fatores de risco para o bem-estar dos cães ou gatos e aconselhar o operador sobre medidas para resolver esses riscos; depois, as visitas do médico veterinário devem ocorrer quando apropriado, com base numa análise de risco pelas autoridades competentes; os Estados-Membros podem estabelecer que as visitas de aconselhamento de bem-estar sejam anuais;
+(b) manter registos dos resultados da visita do médico veterinário referida na alínea (a) e das ações de acompanhamento por um período mínimo de 4 anos, a partir da data da visita, e disponibilizá-los às autoridades competentes a pedido e ao médico veterinário que realiza visitas de aconselhamento subsequentes.
+2. Dentro de 24 meses a partir da data de entrada em vigor do presente Regulamento, a Comissão deve adotar atos delegados em conformidade com o artigo 28.º que complementem o presente artigo de forma a estabelecer critérios mínimos a serem avaliados durante a visita de aconselhamento de bem-estar.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1861,18 +1868,18 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌devem assegurar que os cães e gatos sejam alimentados em conformidade com os requisitos estabelecidos no ponto 1▌.
-2. Além disso, os operadores ▌devem assegurar que os cães e gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
-a) Água limpa e fresca, ad libitum;
-b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas ▌dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade, ▌estado de saúde e reprodutivo dos cães ou gatos, com o objetivo geral de atingir e manter a sua boa saúde;
-c) Alimentos para animais isentos de substâncias suscetíveis de causar sofrimento;
-d) Alimentos para animais proporcionados de forma que evite alterações bruscas e assegure o bom funcionamento do sistema gastrointestinal, em especial durante a fase de desmame.
-3. Os operadores ▌devem assegurar que as instalações de alimentação e de abeberamento sejam mantidas limpas e construídas e instaladas de modo a:
-a) Proporcionarem igualdade de acesso a quantidades adequadas de alimentos para animais e água a todos os cães ou gatos e minimizarem a disputa entre eles;
-b) Minimizarem os derrames e evitarem a contaminação dos alimentos para animais e da água com contaminantes físicos, químicos ou biológicos;
-c) Prevenirem que os cães ou gatos sofram lesões, afogamento ou outros danos;
-d) Serem facilmente limpas e desinfetadas para prevenir a propagação de doenças.
-4. Se um veterinário os aconselhar por escrito nesse sentido, os operadores podem ajustar as frequências de alimentação e de abeberamento de um determinado cão ou gato. Os operadores devem manter um registo desses conselhos recebidos por escrito ao longo de toda a duração dos referidos ajustamentos.</t>
+          <t>1. Os operadores devem assegurar que os cães ou gatos são alimentados em conformidade com os requisitos estabelecidos no ponto 1 do Anexo I.
+2. Os operadores devem assegurar que os cães ou gatos sejam alimentados e hidratados de forma adequada, fornecendo-lhes:
+a) água limpa e fresca, ad libitum;
+b) Alimentos para animais em quantidade e qualidade suficientes para satisfazer as necessidades fisiológicas, nutricionais e metabólicas dos cães e gatos, no âmbito de uma dieta adaptada à idade, raça, categoria, nível de atividade e estado reprodutivo dos cães ou gatos, com o objetivo global de alcançar manter um bom estado saúde;
+c) alimento livre de substâncias que possam causar sofrimento;
+d) alimento de forma a evitar mudanças abruptas e assegurar um sistema gastrointestinal em bom funcionamento, em particular durante a fase de desmame.
+3. Os operadores devem assegurar que as instalações de alimentação e abeberamento sejam mantidas limpas e sejam construídas e instaladas de forma a:
+a) proporcionar acesso igualitário a quantidades adequadas de alimento e água para todos os cães ou gatos e minimizar a competição entre eles;
+b) minimizar derramamentos e evitar a contaminação do alimento e da água com contaminantes físicos, químicos ou biológicos prejudiciais;
+c) evitar ferimentos, afogamento ou outro dano aos cães ou gatos;
+d) ser facilmente limpas e desinfetadas para evitar a propagação de doenças.
+4.	Quando aconselhado por escrito por um médico veterinário, os operadores podem ajustar as frequências de alimentação e hidratação para um cão ou gato individual. Os operadores devem manter um registo do conselho durante toda a sua duração, conforme aconselhado pelo médico veterinário.</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1991,24 +1998,24 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores de estabelecimentos de criação e de venda devem assegurar que os cães e gatos sejam alojados em conformidade com o ponto 2. Os operadores de abrigos devem assegurar que os cães e gatos sejam alojados em conformidade com o ponto 2.2.
-2. Os operadores ▌devem assegurar que:
-a) Os estabelecimentos onde cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário a todos os cães e gatos e uma inspeção exaustiva dos mesmos;
-b) Todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, ▌e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos de forma adequada, ▌a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
-c) Todos os componentes do edifício do estabelecimento, incluindo o pavimento, e as divisórias, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos a fim de garantir que não representam qualquer risco para o bem-estar dos cães ou gatos;
-d) ▌Em estabelecimentos de criação e de venda em que os cães ou gatos sejam detidos em espaços interiores, os níveis de poeiras, a temperatura e a humidade relativa do ar e as concentrações de gases ▌não sejam prejudiciais para os cães ou gatos e que a ventilação seja suficiente para evitar o sobreaquecimento ▌;
-e) Os cães os gatos disponham de espaço suficiente para poderem circular livremente e expressar comportamentos específicos da espécie de acordo com as suas necessidades, tendo a possibilidade de se retirarem e de descansarem;
-f) Os cães ou gatos disponham de zonas de descanso limpas, confortáveis e secas, suficientemente grandes e numerosas para garantir que todos podem deitar-se e descansar ao mesmo tempo numa posição natural;
-g) Estejam previstas estruturas e medidas adequadas para que cães ou gatos mantidos em espaços exteriores estejam protegidos de condições climáticas adversas, incluindo para prevenir desconforto térmico, queimaduras solares e queimaduras pelo frio.
-3. ▌Os operadores não devem manter os cães ou os gatos em contentores.
-Os contentores podem, no entanto, ser utilizados para  isolamento curta duração de determinados cães ou gatos e para a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com reduzida capacidade de termorregulação ou para cachorros ou gatinhos acompanhados das suas mães, desde que, para os cães ou gatos em causa, o stress seja minimizado e o sofrimento evitado, e que os mesmos possam ficar de pé, virar-se e deitar-se numa posição natural.
-4. Os operadores não podem manter cães com mais de semanas exclusivamente em espaços interiores. Tais cães devem ter acesso diário a uma área ao ar livre, ou serem passeados diariamente, ▌de forma que permita exercício físico, exploração e socialização. A duração combinada mínima desse acesso diário ou passeio deve ser de uma hora no total. O operador só pode ficar isento destas exigências com base num parecer escrito de um veterinário.
-5. Quando os gatos são mantidos em gatis, os operadores devem conceber e construir compartimentos individuais para permitir que os gatos circulem livremente e exibam o seu comportamento natural.
-6. Os operadores de estabelecimentos de criação e venda devem assegurar ▌que nas áreas interiores onde são detidos cães ou gatos, existe uma zona termicamente neutra adequada que tenha em conta o seu tipo de pelagem, a idade, o tamanho, a raça e o estado de saúde.
-7. Os operadores dos estabelecimentos de criação e de venda devem, se necessário, utilizar sistemas de aquecimento ou de arrefecimento nos compartimentos interiores dos seus estabelecimentos, a fim de manter uma boa qualidade do ar e uma temperatura adequada e remover a humidade excessiva.
-8. Os operadores devem assegurar que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos para manterem um ritmo circadiano normal.
-Para efeitos do primeiro parágrafo, entende-se por «luz» a luz natural, complementada, sempre que necessário, devido às condições climáticas e à posição geográfica de um Estado‑Membro, por luz artificial.
-9. O n.º 2, alíneas a), b), c), f) e g), e os n.os 6, 7 e 8 não  nem aos cães de guarda de gado nem aos cães de pastoreio durante os períodos em que esses cães são usados para guardar ou pastorear no contexto da transumância sazonal a pé. O n.º 2, alínea f), não  a cães de guarda de gado durante os períodos em que estes cães são usados para treino.</t>
+          <t>1. Os operadores de estabelecimentos de criação e venda devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2 do Anexo I. Os operadores de abrigos devem assegurar que os cães ou gatos dispõem de alojamento em conformidade com o ponto 2.2 do Anexo I.
+2. Os operadores devem assegurar que:
+a) os estabelecimentos onde os cães ou gatos são detidos e o equipamento neles utilizado sejam adequados aos tipos e ao número de cães ou gatos, e permitam o acesso necessário e a inspeção exaustiva de todos os cães ou gatos;​
+b) todos os componentes do edifício do estabelecimento, incluindo o pavimento e o telhado, e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam construídos e mantidos adequadamente, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+c) todos os componentes do edifício do estabelecimento, incluindo o pavimento e as divisões de espaço, bem como o equipamento utilizado para cães ou gatos, sejam mantidos limpos, de modo a garantir que não representem quaisquer riscos para o bem-estar dos cães ou gatos;​
+d) nos estabelecimentos de criação e venda onde os cães ou gatos são detidos em espaços interiores, os níveis de poeira, a temperatura, a humidade relativa do ar e as concentrações de gases não sejam prejudiciais para os cães ou gatos e a ventilação seja suficiente para evitar o sobreaquecimento;​
+e) os cães ou gatos disponham de espaço suficiente para circular livremente e exprimir comportamentos específicos da espécie de acordo com as suas necessidades, com a possibilidade de se retirarem e descansarem;​
+f) os cães ou gatos disponham de locais de repouso limpos, confortáveis e secos, suficientemente amplos e numerosos para garantir que todos eles possam deitar-se e descansar em posição natural ao mesmo tempo;​
+g) existam estruturas e medidas adequadas para os cães ou gatos detidos ao ar livre, de modo a protegê-los de condições climáticas adversas, incluindo para prevenir stress térmico, queimaduras solares e queimaduras pelo frio.
+Os operadores não devem manter cães ou gatos em contentores.
+3. Contudo, contentores podem ser utilizados para o transporte, o isolamento de curto prazo de cães ou gatos individuais e durante a participação em espetáculos, exposições e concursos, para cachorros ou gatinhos com capacidade de termorregulação reduzida ou cachorros ou gatinhos acompanhados das respetivas mães, desde que seja minimizado o stress e evitado o sofrimento e os cães e gatos possam estar de pé e deitar-se numa posição natural.
+4. Os operadores não devem manter cães com mais de 8 semanas exclusivamente no interior. Tais cães devem ter acesso diário a uma área ao ar livre, ou ser passeados diariamente, para permitir exercício, exploração e socialização. A duração do acesso diário a uma área ao ar livre ou passeio deve ser mínimo uma hora no total. O operador só pode desviar-se destes requisitos com base no parecer escrito de um veterinário.
+5. Quando gatos são mantidos em gatis, os operadores devem desenhar e construir compartimentos individuais para permitir aos gatos mover-se livremente e expressar o seu comportamento natural.
+6. Os operadores dos estabelecimentos de criação e venda devem garantir que, nas áreas interiores onde os cães e gatos são detidos, seja mantida uma zona termicamente neutra adequada que tenha em conta o tipo de pelagem, a idade, o tamanho, a raça e a saúde deles.
+7. Os operadores dos estabelecimentos de criação e venda devem, quando necessário, utilizar sistemas de aquecimento ou arrefecimento nos recintos interiores dos seus estabelecimentos para manter uma boa qualidade do ar, uma temperatura adequada e eliminar a humidade excessiva.
+8. Os operadores devem garantir que os cães ou gatos sejam expostos à luz e possam permanecer no escuro durante períodos suficientes e ininterruptos, a fim de manter um ritmo circadiano normal.
+Para efeitos do primeiro parágrafo, 'luz' significa luz natural, complementada, quando necessário, devido às condições climáticas e posição geográfica de um Estado-Membro, por luz artificial.
+9. Os n.ºs 2 (a), (b), (c), (f) e (g), 6, 7 e 8 não se aplicam nem aos cães de guarda de gado, nem aos cães de pastoreio, durante os períodos em que tais cães são utilizados para guarda ou pastoreio no contexto da transumância sazonal a pé. A alínea (f) do ponto 2 não se aplica aos cães de guarda de gado durante os períodos em que tais cães são utilizados para fins de formação.</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2150,22 +2157,22 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌devem assegurar que:
-a) Os cães ou gatos pelos quais são responsáveis sejam inspecionados pelos cuidadores de animais pelo menos uma vez por dia e que os cães e gatos vulneráveis, como os recém-nascidos, os cães e gatos doentes ou feridos e as cadelas e gatas em período perinatal, sejam inspecionados com maior frequência;
-b) Os cães ou os gatos cujo ▌bem‑estar esteja comprometido sejam transferidos, se necessário, sem demora injustificada para uma área separada, e, se necessário, recebam tratamento adequado;
-c) Sempre que não seja possível a recuperação de um cão ou de um gato cujo bem-estar esteja comprometido e o cão ou o gato sinta dor ou sofrimento intensos, seja consultado um veterinário sem demora injustificada para decidir se o cão ou o gato deve ser eutanasiado para pôr termo ao seu sofrimento e, se for esse o caso, para proceder à eutanásia com recurso a anestesia e analgesia;
-d) ▌Sejam tomadas medidas para prevenir e controlar parasitas externos e internos e sejam administradas vacinas para prevenir doenças comuns a que os cães ou gatos possam estar expostos;
-e) Os ▌enriquecimentos usados não apresentem, para os cães ou gatos, um risco significativo de lesões ou de contaminação biológica ou química ou qualquer outro risco para a saúde.
-▌	A alínea a) não se aplica a cães de guarda de gado detidos em estabelecimentos de criação enquanto estes cães sejam usados para fins de guarda ou de treino.
-Os Estados-Membros podem conceder isenções ao disposto na alínea c) em casos de urgência nos quais não seja possível contactar um veterinário sem demora injustificada, desde que sejam previstas normas nacionais destinadas a assegurar:
-i) Que qualquer ação imediata que ponha termo à vida do cão ou do gato com um mínimo de dor e sofrimento, com recurso a um método que provoque a morte instantânea, seja levada a cabo por uma pessoa competente formada;
-ii) Que, para efeitos dos controlos oficiais ao abrigo do Regulamento (UE) 2017/625, o operador mantenha um registo da utilização da isenção.
+          <t>1. Os operadores devem assegurar que:
+(a) os cães e gatos sob a sua responsabilidade são inspecionados por cuidadores pelo menos uma vez por dia, e os animais vulneráveis, como recém-nascidos, doentes, lesionados e fêmeas em período peri-parto, são inspecionados com maior frequência;
+(b) os cães e gatos com bem-estar comprometido são, quando necessário, transferidos sem demora injustificada para uma área separada e, se necessário, recebem tratamento adequado;
+(c) quando a recuperação de um cão ou gato com bem-estar comprometido não seja alcançável e o animal experiencie dor ou sofrimento severo, um médico veterinário é consultado sem demora injustificada para decidir se o animal deve ser objeto de eutanásia para pôr termo ao seu sofrimento e, em caso afirmativo, para realizar a eutanásia com recurso a anestesia e analgesia;
+(d) são implementadas medidas de prevenção e controlo de parasitas externos e internos, bem como vacinações para prevenção de doenças comuns às quais os cães ou gatos são suscetíveis de estar expostos;
+(e) os enriquecimentos não apresentam risco significativo de lesões ou de contaminação biológica ou química, nem qualquer outro risco para a saúde.
+A alínea (a) não se aplica aos cães de guarda de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães são utilizados para fins de guarda ou treino.
+Os Estados-Membros podem conceder derrogações relativamente à alínea (c) em casos de emergência, quando não seja possível contactar um médico veterinário sem demora injustificada, desde que sejam estabelecidas regras nacionais que assegurem que:
+i) é tomada imediatamente uma ação que ponha fim à vida do cão ou gato com o mínimo de dor e sofrimento, utilizando um método que induza a morte instantânea, por uma pessoa competente e devidamente habilitada;
+ii) o operador mantém um registo da utilização da derrogação para efeitos de controlo oficial.
 2. Os operadores de estabelecimentos de criação devem assegurar que:
-a) Sejam tomadas medidas para proteger a saúde dos cães ou dos gatos, em conformidade com o ponto 3;
-b) As cadelas ou as gatas só se reproduzam se tiverem atingido uma idade mínima e a maturidade esquelética em conformidade com o ponto 3 ▌, e apenas se não tiverem nenhuma doença diagnosticada, sinais clínicos de doenças ou problemas físicos que possam ter um impacto negativo na gravidez e no seu bem‑estar;
-c) As gravidezes das cadelas ou gatas respeitem uma frequência máxima, em conformidade com o ponto 3;
-d) As gatas em lactação não sejam sujeitas a acasalamento nem inseminação;
-e) ▌Cães e gatos que já não sejam utilizados para reprodução, nomeadamente por força das disposições do presente regulamento, sejam detidos, vendidos, doados ou realojados, e não mortos ou abandonados. ▌</t>
+(a)  são tomadas medidas para salvaguardar a saúde dos cães ou gatos em conformidade com o ponto 3 do Anexo I;
+(b) as cadelas ou gatas só se reproduzem se tiverem atingido a idade mínima e a maturidade esquelética em conformidade com o ponto 3 do Anexo I, e não apresentem doença diagnosticada, sinais clínicos de doença ou condições físicas que possam impactar negativamente a gestação e o seu bem-estar;
+(c)  As gravidezes das cadelas e gatas que resultem numa ninhada respeitem uma frequência máxima fixada no ponto 3 do Anexo I;
+(d)  as gatas em lactação não sejam acasaladas nem inseminadas;
+(e)  os cães e gatos que deixem de ser utilizados para reprodução, nomeadamente em resultado das disposições do presente Regulamento, são mantidos ou vendidos, doados ou realojados, não sendo mortos nem abandonados.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2301,19 +2308,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>1. Os operadores ▌devem assegurar que sejam tomadas medidas para satisfazer as necessidades comportamentais dos cães e gatos em conformidade com o ponto 4.
-2. Além disso, os operadores não devem deter cães ou gatos em zonas que restrinjam os seus movimentos naturais, exceto em casos em que o artigo 15.º, n.º 3, segundo parágrafo, é aplicável ou em que os seguintes procedimentos ou tratamentos são realizados:
-a) Exames físicos ▌;
-b) Identificação individual de cães ou gatos, ou leitura das referidas informações de identificação;
-c) Colheita de amostras e vacinação;
-d) Procedimentos de limpeza e tosquia, procedimentos higiénicos, sanitários ou reprodutivos que não o acasalamento;
-e) Tratamento médico, incluindo tratamentos cirúrgicos ou reabilitação receitada.
-3. É proibido o acorrentamento ▌por um período superior a uma hora, exceto durante um tratamento médico ou para participação em espetáculos, exposições e concursos de cães ou gatos.
-4. Os Estados-Membros podem conceder isenções ao disposto no n.º 3 no caso dos cães destinados a serem usados nos serviços militares, policiais e aduaneiros que sejam detidos em estabelecimentos de criação ou venda.
-5. Os operadores ▌devem assegurar que os cães ou gatos sejam detidos em condições que lhes permitm exibir comportamentos sociais não nocivos, comportamentos específicos da espécie, e experienciar emoções positivas.
-6. Os operadores devem assegurar que os cães ou gatos possam socializar de acordo com o previsto no ponto 4. Os operadores dos estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização.
-Em derrogação do primeiro parágrafo, as exigências em matéria de socialização não se aplicam a cães de guarda de gado detidos em estabelecimentos de criação quando esses cães forem usados para fins de guarda ou de treino, ou a cães de pastoreio durante a transumância sazonal.
-7. Os operadores devem garantir que os enriquecimentos sejam oferecidos e estejam acessíveis a todos os cães ou gatos, criando um ambiente estimulante, permitindo que exibam comportamentos específicos da espécie e reduzindo a sua frustração.</t>
+          <t>1. Os operadores devem assegurar que medidas são tomadas para satisfazer as necessidades comportamentais de cães ou gatos em conformidade com o ponto 4 do Anexo I.
+2. Os operadores não devem manter cães ou gatos em áreas que restringem os seus movimentos naturais, exceto no caso do artigo 15.º (parágrafo 3), segundo parágrafo, ou para realizar os seguintes procedimentos ou tratamentos:
+a) exames físicos;
+b) identificação individual de cães ou gatos e leitura da informação de identificação;
+c) recolha de amostras e vacinações;
+d) procedimentos de higiene, higiénicos, de saúde ou reprodutivos que não sejam acasalamento;
+e) tratamento médico, incluindo tratamento cirúrgico ou reabilitação prescrita.
+3. O acorrentamento por mais de 1 hora é proibido, exceto durante a duração de um tratamento médico ou participação em espetáculos, exposições e competições de cães e gatos.
+4. Os Estados-Membros podem conceder isenções ao disposto no n.º 3 para os cães destinados a ser utilizados nos serviços militares, policiais e aduaneiros que sejam mantidos em estabelecimentos de criação ou de venda.
+5.  Os operadores devem assegurar que os cães ou gatos sejam mantidos em condições que lhes permitam exibir comportamentos sociais não prejudiciais e comportamentos específicos da espécie, bem como vivenciar emoções positivas.
+6. Os operadores devem assegurar que os cães ou gatos possam socializar em conformidade com o ponto 4 do anexo I. Os operadores de estabelecimentos de criação devem dispor de uma estratégia documentada para essa socialização.
+Em derrogação do primeiro parágrafo, os requisitos de socialização não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que tais cães sejam utilizados para fins de guarda ou de treino, nem aos cães de pastoreio durante a transumância sazonal.
+7. Os operadores devem assegurar que o enriquecimento seja facultado e esteja acessível a todos os cães ou gatos, criando-lhes um ambiente estimulante que lhes permita desenvolver e exibir comportamentos específicos da espécie e reduza a sua frustração.</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2405,19 +2412,19 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1. ▌Os operadores devem assegurar que as mutilações, incluindo o corte das orelhas, o corte da cauda, a remoção de garras ou outros tipos de amputação digital parcial ou completa, assim como a ressecção de cordas ou pregas vocais, não sejam efetuadas a menos que se justifiquem por indicação médica, incluindo quando o procedimento é profilático, e com o único objetivo de manter ou melhorar a saúde dos cães ou gatos ou de prevenir que estes se lesionem. Nesse caso, o procedimento só pode ser realizado ▌sob anestesia e analgesia prolongada, e exclusivamente por um veterinário.
-2. As indicações médicas que justificam a mutilação e os pormenores do procedimento realizado devem constar de um documento elaborado por um veterinário. Este documento deve ser conservado pelo operador e deve acompanhar o cão ou o gato quando este for transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve conservar uma cópia do documento durante os primeiros três anos após essa transferência.
-3. A título de derrogação do n.º 1, os Estados-Membros podem autorizar, no contexto da marcação de gatos vadios esterilizados no âmbito de um programa de captura, esterilização e libertação, que se faça um entalhe na orelha dos gatos ou se corte a ponta da mesma.
-4. Os operadores devem assegurar que a esterilização seja efetuada unicamente sob anestesia e analgesia prolongada e apenas por um veterinário. No entanto, os Estados-Membros podem autorizar que a esterilização de gatos machos seja efetuada por um enfermeiro veterinário autorizado.
-5. Os operadores devem assegurar a ausência de práticas de manuseamento que causem dor ou sofrimento, incluindo as seguintes:
-a) Atar partes do corpo, a menos que tal seja exigido por razões médicas e limitado ao período mínimo necessário;
-b) Pontapear, bater, arrastar, lançar ou apertar os cães ou os gatos;
-c) Aplicar corrente elétrica aos cães ou aos gatos, a menos que tal seja efetuado por motivos médicos;
-d) Utilizar ▌açaimes, a menos que tal seja exigido por razões médicas ou por razões de segurança animal ou humana, caso em que a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado;
-e) Utilizar coleiras de garras;
-f) Utilizar coleiras estranguladoras sem travão de segurança;
-g) Levantar os cães ou os gatos pelos membros, cabeça, orelhas, cauda ou pelo, ou levantar os cães ou gatos adultos pela pele.
-Os Estados-Membros podem conceder isenções ao disposto no primeiro parágrafo para os cães destinados a ser utilizados nos serviços militares, policiais ou aduaneiros.</t>
+          <t>1. Os operadores devem assegurar que mutilações, incluindo corte de orelhas, corte de cauda, remoção de garras ou amputação parcial ou completa de dígitos, e ressecção de cordas vocais ou pregas, não são realizadas a menos que por indicação médica, que pode incluir profilática, com o único propósito de preservar, melhorar a saúde de cães ou gatos ou prevenir ferimentos. Nesse caso, o procedimento deve ser realizado apenas sob anestesia e analgesia prolongada e por um médico veterinário.
+2. A indicação médica para a mutilação e os detalhes do procedimento realizado devem ser documentados por um médico veterinário. Este documento deve ser retido pelo operador até que o cão ou gato, juntamente com este documento, seja transferido para outro estabelecimento ou proprietário. O operador do estabelecimento onde a mutilação foi realizada deve reter uma cópia do documento durante três anos após a transferência do cão ou gato.
+3. A título de derrogação do parágrafo 1, os Estados-Membros podem permitir o corte de orelhas por entalhe ou ponta das orelhas de gatos no contexto de marcação de gatos errantes quando esterilizados sob um programa de captura-esterilização-libertação.
+4. Os operadores devem assegurar que a esterilização é realizada apenas sob anestesia e analgesia prolongada e por um médico veterinário. A título de derrogação, os Estados-Membros podem permitir que a esterilização de gatos machos seja realizada por um enfermeiro veterinário licenciado.
+5. Os operadores devem assegurar que práticas de manipulação que causam dor ou sofrimento não são realizadas, incluindo:
+a)	amarrar partes do corpo a menos que por razões médicas em cujo caso a duração deve ser limitada ao período mínimo necessário;
+b)	chutar, bater, arrastar, atirar, apertar cães ou gatos;
+c)	aplicar corrente elétrica a cães ou gatos a menos que realizado por razões médicas;
+d)	uso de açaimos, a menos que necessário por razões médicas, segurança animal ou humana, em cujo caso a duração deve ser limitada ao período mínimo necessário e o cão ou gato deve ser supervisionado.
+e)	uso de colares de espinhos;
+f)	uso de colares de estrangulamento sem paragem de segurança;
+g)	levantar cães ou gatos pelas extremidades, cabeça, orelhas, cauda ou pêlo, ou levantar cães ou gatos adultos pela pele.
+Os Estados-Membros podem conceder derrogações do primeiro parágrafo para cães destinados a uso em serviços militares, policiais ou aduaneiros.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2510,10 +2517,8 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>1. Nos espetáculos de beleza, nas exposições e nos concursos de cães e gatos, os operadores de estabelecimentos de criação e venda não podem utilizar cães ou gatos com características de conformação excessivas, nem cães ou gatos que tenham sido mutilados de uma forma que altere as suas características físicas.
-2. Ao organizarem espetáculos, exposições e concursos de cães e gatos, os organizadores devem excluir os cães e gatos que tenham características de conformação excessivas e os cães e gatos que tenham sido mutilados de uma forma que altere as suas características físicas.
-CAPÍTULO III
-IDENTIFICAÇÃO E REGISTO DE CÃES E GATOS</t>
+          <t>1. Os operadores de estabelecimentos de criação e venda não devem utilizar em espetáculos, exposições e competições estéticas de cães e gatos, cães ou gatos com características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.
+2. Os organizadores de espetáculos, exposições e competições estéticas de cães e gatos devem excluir de tais espetáculos, exposições e competições cães e gatos que tenham características conformacionais excessivas ou cães ou gatos que tenham sido mutilados de tal forma que resulte numa alteração de características físicas.</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2679,21 +2684,21 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1. ▌Todos os cães e gatos detidos em estabelecimentos, colocados no mercado ou detidos por um proprietário de animais de companhia ou por qualquer outra pessoa singular ou coletiva devem ser identificados individualmente através de um único transpondedor injetável que contenha um circuito integrado legível que cumpra os requisitos estabelecidos no anexo II. ▌
-2. Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o seu nascimento e sempre antes da data da sua colocação no mercado.
-Os operadores de estabelecimentos de venda e de abrigos e os operadores que coloquem e tenham a seu cargo cães e gatos em de acolhimento devem assegurar que os cães e gatos que são admitidos nos seus estabelecimentos ou passam a estar sob a sua responsabilidade sejam identificados individualmente no prazo de 30 dias a contar da sua chegada e sempre antes da data da sua colocação no mercado.
-Os proprietários de animais de companhia e quaisquer outras pessoas singulares ou coletivas operadores, que sejam proprietáris de cães ou gatos devem assegurar que cada cão ou gato seja identificado individualmente, o mais tardar quando atinge três meses de idade ou, se o cão ou gato for colocado no mercado, antes da data dessa colocação no mercado.
-A implantação do transpondedor deve ser efetuada por um veterinário. Os Estados-Membros podem autorizar a implantação de transpondedores por outras pessoas que não os veterinários, desde que adotem disposições nacionais que estabeleçam as qualificações mínimas que essas pessoas devem possuir.
-Considera-se que cumprem os requisitos estabelecidos no n.º 1 e no primeiro, segundo, terceiro e quarto parágrafos do presente número os cães e gatos que, em conformidade com o direito da União ou nacional, tenham sido identificados individualmente antes de … [dois anos após a data de entrada em vigor do presente regulamento] através de um transpondedor injetável que contenha um circuito integrado, desde que o circuito integrado permaneça legível.
-3. No prazo de dois dias úteis após a sua identificação, os cães e gatos ▌devem ser registados por um veterinário ▌numa base de dados nacional referida no artigo 23.º. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que os Estados-Membros tenham medidas em vigor para garantir a exatidão das informações que as pessoas em causa inserem na base de dados. No caso dos cães e dos gatos detidos em estabelecimentos ▌, o registo deve ser feito em nome do operador do estabelecimento ▌responsável pelo cão ou gato. No caso dos cães e dos gatos detidos por quaisquer outras pessoas singulares ou coletivas, o registo deve ser feito em nome dessas pessoas. ▌
-Os Estados-Membros podem conceder isenções ao disposto no primeiro parágrafo do presente número no que respeita aos cães destinados aos serviços militares, policiais e aduaneiros.
-4. Quando cães ou gatos forem colocados no mercado ou forem doados ocasionalmente por pessoas singulares sem recurso a publicidade em linha, a pessoa singular ou coletiva que transfere a propriedade ou a responsabilidade pelo cão ou gato deve assegurar que a mudança de propriedade ou de responsabilidade pelo cão ou gato seja registada na base de dados a que se refere o artigo 23.º, no prazo de duas semanas a contar da data dessa transferência, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
-5. Em caso de morte de um cão ou de um gato, o operador, o proprietário do animal de companhia ou a pessoa singular ou coletiva que é proprietária do cão ou do gato deve assegurar que a morte seja registada na base de dados a que se refere o artigo 23.º, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
-6. Se um transpondedor for ou ficar ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato deve assegurar que um novo transpondedor seja injetado e que o registo na base de dados seja atualizado com o número de identificação desse novo transpondedor.
-.Os requisitos de identificação e registo estabelecidos no presente artigo são aplicáveis do seguinte modo:
-a) Para os operadores e as pessoas singulares ou coletivas que colocam cães e gatos no mercado, a partir de … [anos a contar da data de entrada em vigor do presente regulamento];
-b) Para os proprietários de animais de companhia e outras pessoas singulares ou coletivasoperadores, que não colocam cães no mercado, a partir de … [10 anos a contar da data de entrada em vigor do presente regulamento];
-c)  Para os proprietários de animais de companhia e outras pessoas singulares ou coletivas operadores, que não colocam gatos no mercado, a partir de … [15 anos a contar da data de entrada em vigor do presente regulamento].</t>
+          <t>1.	Todos os cães e gatos mantidos em estabelecimentos, colocados no mercado ou detidos por donos de animais de companhia ou por qualquer outra pessoa singular ou coletiva, devem ser identificados individualmente por meio de um único transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
+2.	Os operadores devem assegurar que os cães e gatos nascidos nos seus estabelecimentos sejam identificados individualmente no prazo de três meses após o nascimento e, em qualquer caso, antes da data da sua colocação no mercado.
+Os operadores de estabelecimentos de venda e abrigos, e os operadores que colocam e são responsáveis por cães e gatos em famílias de acolhimento, devem assegurar que os cães e gatos que entrem nos seus estabelecimentos ou fiquem sob a sua responsabilidade sejam identificados individualmente no prazo de 30 dias após a chegada e, em qualquer caso, antes da data da sua colocação no mercado.
+Os donos de animais de companhia e quaisquer outras pessoas singulares ou coletivas que não sejam operadores e que sejam proprietários de cães ou gatos devem assegurar que cada cão ou gato seja identificado individualmente o mais tardar quando o animal atingir a idade de três meses ou, caso o cão ou gato seja colocado no mercado, antes da data dessa colocação no mercado.
+A implantação do transponder deve ser efetuada por um médico veterinário. Os Estados-Membros podem permitir que a implantação de transponders seja efetuada por pessoas que não sejam médicos veterinários, desde que adotem regras nacionais que estabeleçam as qualificações mínimas que essas pessoas devem ter.
+Caso os cães e gatos tenham sido identificados individualmente por meio de um transponder injetável contendo um microchip em conformidade com o direito da União ou nacional antes de … [data dois anos após a data de entrada em vigor do presente Regulamento], considera-se que cumprem os requisitos do n.º 1 e do primeiro, segundo, terceiro e quarto parágrafos do presente número, desde que o microchip seja ainda legível.
+3.	No prazo de dois dias úteis após a sua identificação, os cães e gatos devem ser registados por um médico veterinário numa base de dados nacional referida no artigo 23.º. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que os Estados-Membros disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados. No caso de cães e gatos mantidos em estabelecimentos, o registo deve ser efetuado em nome do operador do estabelecimento responsável pelo cão ou gato. No caso de cães e gatos detidos por quaisquer outras pessoas singulares ou coletivas, o registo deve ser efetuado em nome dessas pessoas.
+Os Estados-Membros podem conceder derrogações ao primeiro parágrafo do presente número relativamente a cães militares, policiais e aduaneiros.
+4.	Em caso de colocação no mercado ou cedência ocasional por pessoas singulares sem recorrer a publicidade em linha, a pessoa singular ou coletiva que transfere a propriedade ou a responsabilidade pelo cão ou gato deve assegurar que a mudança de propriedade ou de responsabilidade pelo cão ou gato é registada na base de dados referida no artigo 23.º, no prazo de duas semanas a contar da data dessa transferência, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+5.	Em caso de morte de um cão ou gato, o operador, o dono do animal de companhia ou a pessoa singular ou coletiva proprietária do cão ou gato deve assegurar que a morte é registada na base de dados referida no artigo 23.º, em conformidade com as condições estabelecidas pelo Estado-Membro responsável por essa base de dados.
+6.	Caso um transponder seja ou fique ilegível, o operador ou a pessoa singular ou coletiva responsável pelo cão ou gato deve assegurar que um novo transponder é injetado e que o registo na base de dados é atualizado com o número de identificação desse novo transponder.
+7.	Os requisitos de identificação e registo do presente artigo são aplicáveis:
+(a)	aos operadores e às pessoas singulares ou coletivas que colocam cães e gatos no mercado, a partir de … [4 anos após a entrada em vigor do presente Regulamento];
+(b)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem cães no mercado, a partir de … [10 anos após a entrada em vigor do presente Regulamento];
+(c)	aos donos de animais de companhia e outras pessoas singulares ou coletivas que não sejam operadores e que não coloquem gatos no mercado, a partir de … [15 anos após a entrada em vigor do presente Regulamento].</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2808,34 +2813,32 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>1. Quando recorrem a um anúncio em linha para a colocação no mercado da União de um cão ou de um gato, os operadores devem assegurar que o anúncio inclua a seguinte advertência, em carateres claramente visíveis e a negrito:
-«Um animal não é um brinquedo. Adquirir um animal é uma decisão que muda a sua vida. É seu dever garantir a saúde e o bem-estar do animal e não o abandonar.».
-2. Sempre que anunciem um cão ou um gato em linha com vista à sua colocação no mercado da União, as pessoas singulares ou coletivas operadores devem assegurar que o anúncio inclua uma advertência sobre a propriedade responsável, utilizando a redação constante do n.º 1 ou uma redação diferente com o mesmo significado.
-3. Quando colocam um cão ou um gato no mercado na União, as pessoas singulares ou coletivas que colocam o cão ou o gato no mercado devem ao adquirente:
-a) Prova da identificação e do registo do cão ou do gato em conformidade com o artigo 20.º;
-b) As seguintes informações sobre o cão ou o gato:
-i) a sua espécie,
-ii) o seu sexo,
-iii) a data e país onde nasceu, e
-iv) se for caso disso, a sua raça.
-Sempre que anunciem um cão ou um gato em linha com vista à sua colocação no mercado da União, as pessoas singulares ou coletivas devem utilizar o sistema a que se refere o n.º 5 para gerar um testemunho de verificação único. Essas pessoas devem incluir esse testemunho de verificação no anúncio, juntamente com uma hiperligação para o sistema a que se refere o n.º 5.
-O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade dos cães ou gatos anunciados em linha.
-4. ▌Os fornecedores de plataformas em linha devem assegurar que a sua interface em linha seja concebida e organizada de forma a que os operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado tenham maior facilidade em cumprir as obrigações que lhes incumbem por força dos n.os 1 a 3 do presente artigo e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou do gato no sistema de verificação em linha referido no n.º 5, acedido através de uma hiperligação.
-Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações facultadas através da interface da plataforma em linha. Nenhuma disposição do presente número pode ser interpretada no sentido de impor uma obrigação geral de vigilância ao fornecedor da plataforma em linha, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
-5. ▌A Comissão assegura que um sistema de verificação que efetue controlos automatizados da autenticidade da identificação, do registo e da propriedade dos cães ou gatos anunciados em linha, utilizando a base de dados a que se refere o artigo 23.º, seja disponibilizado em linha ao público, a título gratuito, e gere o testemunho de verificação único referido no n.º 3, segundo parágrafo, do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e a exploração deste sistema a uma entidade independente. Essa entidade independente é escolhida para essa função na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509 do Parlamento Europeu e do Conselho. O sistema deve assegurar o seguinte:
-a) A verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato utilizando as bases de dados nacionais a que se refere o artigo 23.º;
-b) A conformidade com a proteção de dados nos termos do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679.
-6. ▌ A Comissão adota atos de execução que preveem:
-a) As informações que as pessoas singulares e coletivas que colocam cães ou gatos no mercado devem como prova da identificação e do registo de cães e gatos em conformidade com o n.º 3, alínea a);
-b) As informações que as pessoas singulares e coletivas que anunciam cães ou gatos devem ao sistema de verificação referido no n.º 5 para comprovar a autenticidade da identificação, do registo e da propriedade do cão ou do gato anunciado;
-c) As seguintes características do sistema a que se refere o n.º 5:
-–	as funções essenciais do sistema,
-–	os requisitos técnicos, eletrónicos e criptográficos do sistema,
-–	as etapas processuais a seguir e as informações a pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como as etapas e informações exigidas ao adquirente, para que o sistema de verificação em linha funcione.
-Os atos de execução a que se refere a alínea a) são adotados até … [dois anos após a data de entrada em vigor do presente regulamento] e o ato de execução a que se referem as alíneas b) e c) é adotado até … [três anos a contar da data de entrada em vigor do presente regulamento].
-Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.
-CAPÍTULO IV
-AUTORIDADES COMPETENTES</t>
+          <t>1.	Quando operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação do seguinte aviso no anúncio em caracteres claramente visíveis e em negrito:
+"Um animal não é um brinquedo. Ter um é uma decisão que muda a vida. É seu dever assegurar a sua saúde e bem-estar e não o abandonar."
+2.	Quando pessoas singulares ou coletivas que não sejam operadores anunciem online um cão ou gato com vista ao seu colocamento no mercado da União, devem assegurar a apresentação de um aviso sobre detenção responsável utilizando a redação referida no n.º 1 ou uma redação diferente com significado equivalente.
+3.	Ao colocar um cão ou gato no mercado na União, a pessoa singular ou coletiva que coloca o cão ou gato no mercado deve fornecer ao adquirente:
+(a)	prova da identificação e do registo do cão ou gato em conformidade com o artigo 20.º;
+(b)	as seguintes informações sobre o cão ou gato:
+(i)	a sua espécie;
+(ii)	o seu sexo;
+(iii)	a sua data e país de nascimento; e
+(iv)	quando relevante, a sua raça.
+Caso uma pessoa singular ou coletiva anuncie um cão ou gato online com vista ao seu colocamento no mercado da União, essa pessoa deve utilizar o sistema referido no n.º 5 para gerar um token único de verificação e incluir esse token no anúncio, juntamente com uma ligação web para o sistema referido no n.º 5.
+O sistema referido no n.º 5 deve permitir aos adquirentes verificar a autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online.
+4.	Os fornecedores de plataformas online devem assegurar que a sua interface online é concebida e organizada de forma a facilitar aos operadores ou outras pessoas singulares ou coletivas que colocam cães ou gatos no mercado o cumprimento das suas obrigações nos termos dos n.ºs 1 a 3 do presente artigo, e em conformidade com o artigo 31.º do Regulamento (UE) 2022/2065, e devem informar os adquirentes, de forma visível, da possibilidade de verificar a autenticidade da identificação, do registo e da propriedade do cão ou gato no sistema de verificação online referido no n.º 5, acessível através de uma ligação web.
+Apenas a pessoa singular ou coletiva que coloca cães ou gatos no mercado é responsável pela exatidão das informações fornecidas através da interface da plataforma online. Nenhuma disposição do presente número pode ser interpretada como impondo uma obrigação geral de monitorização ao fornecedor da plataforma online, na aceção do artigo 8.º do Regulamento (UE) 2022/2065.
+5.	A Comissão garante que um sistema de verificação destinado a realizar controlos automatizados da autenticidade da identificação, do registo e da propriedade de cães ou gatos anunciados online, utilizando a base de dados referida no artigo 23.º, está publicamente disponível online, a título gratuito, e gera o token único de verificação referido no segundo parágrafo do n.º 3 do presente artigo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento deste sistema a uma entidade independente, escolhida para essa missão na sequência de um processo de seleção pública. O sistema deve assegurar:
+(a)	a verificação fiável da autenticidade da identificação, do registo e da propriedade do cão ou gato, utilizando as bases de dados nacionais referidas no artigo 23.º;
+(b)	a conformidade com a proteção de dados, em conformidade com o Regulamento (UE) 2018/1725 e o Regulamento (UE) 2016/679.
+6.	A Comissão adota atos de execução que estabelecem:
+(a)	as informações a fornecer pelas pessoas singulares e coletivas que colocam cães ou gatos no mercado como prova de identificação e registo dos cães e gatos em conformidade com o n.º 3, alínea a);
+(b)	as informações a fornecer pelas pessoas singulares e coletivas que anunciam cães ou gatos ao sistema de verificação referido no n.º 5, para efeitos de demonstração da autenticidade da identificação, do registo e da propriedade do cão ou gato anunciado;
+(c)	as seguintes características do sistema referido no n.º 5:
+-	as funções essenciais do sistema;
+-	os requisitos técnicos, eletrónicos e criptográficos do sistema;
+-	os passos procedimentais a seguir, e as informações a fornecer, pela pessoa singular ou coletiva que coloca o cão ou gato no mercado, bem como os passos e informações exigidos ao adquirente, para que o sistema de verificação online funcione.
+Os atos de execução referidos na alínea a) devem ser adotados até … [dois anos após a data de entrada em vigor do presente Regulamento] e os atos de execução referidos nas alíneas b) e c) devem ser adotados até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2979,11 +2982,11 @@
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>1. Para efeitos do artigo 12.º, as autoridades competentes são responsáveis por:
-a) Assegurar a disponibilidade de cursos de formação para os cuidadores de animais;
-b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), em conformidade com os requisitos mínimos estabelecidos pelos atos de execução a que se refere o artigo 12.º, n.º 4;
-c) Certificar os cuidadores de animais que concluíram com êxito os cursos de formação referidos na alínea a).
-As autoridades competentes podem delegar a tarefa a que se refere a alínea c) em prestadores de cursos de formação.
-2.  centro de referência da União Europeia para o bem-estar animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode elaborar modelos de materiais de formação e recomendações para as autoridades competentes ou outros prestadores de cursos de formação.</t>
+a) Assegurar que existem cursos de formação disponíveis para cuidadores de animais;
+b) Aprovar o conteúdo dos cursos de formação referidos na alínea a), tendo em conta os requisitos mínimos estabelecidos pelos atos de execução referidos no artigo 12.º, parágrafo 3;
+c) Certificar os cuidadores de animais que completaram com sucesso os cursos de formação referidos na alínea a).
+2. As autoridades competentes podem delegar a tarefa referida na alínea (c)
+3. O Centro de Referência da União Europeia para o Bem-Estar Animal designado em conformidade com o artigo 95.º do Regulamento (UE) 2017/625 pode desenvolver modelos de materiais de formação e recomendações para os fornecedores dos cursos de formação referidos no parágrafo 1.</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -3112,19 +3115,18 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1. Os Estados-Membros são responsáveis por criar e manter bases de dados para o registo de cães e gatos identificados em conformidade com o artigo 20.º, n.os 1 e 2, o artigo 26.º, n.º 3, e o artigo 26.º, n.º 4, segundo parágrafo.
-2. Para o efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos adequados entre os Estados-Membros em causa.
-3. ▌Os Estados‑Membros devem assegurar que as suas bases de dados referidas no n.º 1 cumpram os requisitos estabelecidos pelo ato de execução a que se refere o n.º 4, segundo parágrafo, alínea b), a fim de garantir a sua interoperabilidade.
-4. A Comissão cria e mantém uma base de dados indexada que contenha o conjunto mínimo de campos estabelecido nos atos de execução a que se refere o segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento desta base de dados indexada a uma entidade independente, na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509.
-▌A Comissão adota atos de execução que estabelecem disposições pormenorizadas no que diz respeito ao seguinte:
-a) Ao ▌conteúdo mínimo das bases de dados referidas no n.º 1;
-b) À ▌interoperabilidade entre as bases de dados dos Estados‑Membros e a base de dados indexada, incluindo o conjunto mínimo de campos a transmitir à base de dados indexada e os intervalos de transmissão;
-c) À ▌funcionalidade para fornecer prova da identificação e do registo de um cão ou gato, conforme referido no artigo 21.º, n.º 3, alínea a);
-d) Ao registo em que os Estados-Membros declararão as suas bases de dados e os parâmetros necessários para ligar essas bases de dados entre si, em conformidade com as disposições estabelecidas nos termos da alínea b);
-▌	▌
-e) À interligação entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de animais de companhia em viagem referida no artigo 26.º, n.º 4, e o sistema de gestão da informação sobre os controlos oficiais (IMSOC), se for caso disso.
-A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até ... [dois anos após a data de entrada em vigor do presente regulamento]. A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até ... [três anos a contar da data de entrada em vigor do presente regulamento].
-Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.</t>
+          <t>1. Os Estados-Membros são responsáveis pela criação e manutenção de bases de dados para o registo de cães e gatos identificados, em conformidade com o artigo 20.º, n.ºs 1 e 2, e com o artigo 26.º, n.ºs 3 e 4, segundo parágrafo.
+2. Para este efeito, os Estados-Membros podem utilizar bases de dados mantidas por outro Estado-Membro, com base em acordos apropriados entre esses Estados-Membros.
+3. Os Estados-Membros asseguram que as suas bases de dados referidas no n.º 1 estão em conformidade com os requisitos estabelecidos pelo ato de execução referido no n.º 4, segundo parágrafo, alínea b), de modo a assegurar a sua interoperabilidade.
+4. A Comissão estabelece e mantém uma base de dados de índice contendo o conjunto mínimo de campos estabelecido nos atos de execução referidos no segundo parágrafo, alínea b). A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados de índice a uma entidade independente, na sequência de um processo de seleção pública.
+A Comissão adota atos de execução que estabelecem regras pormenorizadas relativas a:
+(a) o conteúdo mínimo das bases de dados referidas no n.º 1;
+(b) a interoperabilidade entre as bases de dados dos Estados-Membros e a base de dados de índice, incluindo o conjunto mínimo de campos a transmitir à base de dados de índice e os intervalos da transmissão;
+(c) a funcionalidade para fornecer prova de identificação e registo de um cão ou gato, tal como referido no artigo 21.º, n.º 3, alínea a);
+(d) o registo onde os Estados-Membros declaram as suas bases de dados, e os parâmetros necessários para a conexão dessas bases de dados entre si, em conformidade com as disposições estabelecidas em aplicação da alínea b);
+(e) a interconexão entre as bases de dados dos Estados-Membros referidas no n.º 1, a base de dados de viajantes da União com animais de estimação referida no artigo 26.º, n.º 4, e o Sistema de Gestão da Informação para os Controlos Oficiais (IMSOC), quando relevante.
+A Comissão adota os atos de execução referidos no segundo parágrafo, alíneas a) e c), até … [data dois anos após a data de entrada em vigor do presente Regulamento]. Adota os atos de execução referidos no segundo parágrafo, alíneas b), d) e e), até … [três anos a contar da data de entrada em vigor do presente Regulamento].
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -3211,9 +3213,9 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1. As autoridades competentes devem recolher, analisar e publicar os dados relativos ao bem-estar animal previstos no anexo III.
-2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório, em formato eletrónico, sobre os dados relativos ao bem-estar animal previstos no anexo III, até 31 de agosto de três em três anos. O primeiro desses relatórios deve ser elaborado e transmitido à Comissão até ... [data correspondente a anos a contar da data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
-3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados relativos ao bem-estar animal previstos no anexo III e que estabeleçam um modelo do relatório a que se refere o n.º 2 do presente artigo. Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.</t>
+          <t>1. As autoridades competentes devem recolher, analisar e publicar os dados sobre bem-estar animal estabelecidos no Anexo III.
+2. As autoridades competentes devem elaborar e transmitir à Comissão um relatório em formato eletrónico, sobre os dados relativos ao bem-estar animal estabelecidos no Anexo III, até 31 de agosto, com periodicidade trienal. O primeiro relatório deve ser elaborado e transmitido à Comissão até ... [data 6 anos após a data de entrada em vigor do presente regulamento]. Cada relatório deve conter um resumo dos dados recolhidos durante os três anos anteriores.
+3. A Comissão pode adotar atos de execução que estabeleçam uma metodologia harmonizada para a recolha dos dados sobre bem-estar animal estabelecidos no Anexo III e que definam um modelo para o relatório referido no n.º 2 do presente artigo. Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3285,19 +3287,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1. As autoridades competentes dos Estados-Membros são responsáveis pelo tratamento na aceção do Regulamento (UE) 2016/679 no que diz respeito ao tratamento de dados pessoais recolhidos ao abrigo dos artigos 9.º e 10.º do presente regulamento, bem como ao abrigo do artigo 23.º, n.º 1, do presente regulamento, quando esses dados sejam utilizados para fins de controlo oficial.
-A Comissão é responsável pelo tratamento na aceção do Regulamento (UE) 2018/1725 no que diz respeito ao tratamento de dados pessoais recolhidos ao abrigo do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do artigo 26.º, n.º 4, terceiro parágrafo, bem como ao abrigo do artigo 23.º, n.º 1, do presente regulamento, quando esses dados sejam utilizados para de cumprimento do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações nos termos do presente regulamento.
-É proibido às pessoas com acesso aos dados pessoais referidos no primeiro e segundo parágrafos divulgar quaisquer dados pessoais de que tenham tido conhecimento no exercício das suas funções ou . Os Estados-Membros e a Comissão tomam todas as medidas adequadas para fazer cumprir esta proibição.
-Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para fins diferentes dos seguintes:
-a) Controlos oficiais, pelas autoridades competentes dos Estados-Membros, do cumprimento dos requisitos relativos ao bem-estar e à rastreabilidade no presente regulamento e do cumprimento do Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
-b) Cumprimento, pela Comissão, das obrigações que lhe incumbem por força do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações que lhe incumbem por força do presente regulamento.
-2. Os dados pessoais a que se refere o n.º 1 do presente artigo são conservados pelos seguintes períodos:
-a) Nos casos previstos nos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
-b) No caso previsto no artigo 21.º, n.º 5, 18 meses após a geração do testemunho de verificação a que se refere o artigo 21.º, n.º 3, segundo parágrafo;
-c) Nos casos previstos no artigo 23.º, n.os 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
-d) No caso previsto no artigo 26.º, n.º 4, terceiro parágrafo, cinco anos após a data da notificação prévia.
-CAPÍTULO V
-ENTRADA DE CÃES E GATOS NA UNIÃO</t>
+          <t>1. As autoridades competentes dos Estados-Membros devem ser controladoras na aceção do Regulamento (UE) 2016/679 no que respeita ao tratamento de dados pessoais recolhidos nos termos dos artigos 9.º e 10.º do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando utilizados para efeitos de controlo oficial.
+A Comissão deve ser controladora na aceção do Regulamento (UE) 2018/1725 no que respeita ao tratamento de dados pessoais recolhidos nos termos do artigo 21.º, n.º 5, do artigo 23.º, n.º 4, e do terceiro parágrafo do artigo 26.º, n.º 4, do presente Regulamento, bem como no âmbito do artigo 23.º, n.º 1, do presente Regulamento quando esses dados são utilizados para efeitos de conformidade com o artigo 108.º do Regulamento (UE) 2017/625 e de obrigações de comunicação de informações previstas no presente Regulamento.
+É proibido a qualquer pessoa com acesso aos dados pessoais referidos nos primeiro e segundo parágrafos divulgar quaisquer dados pessoais cujo conhecimento tenha sido adquirido no exercício das suas funções ou a título acessório do exercício dessas funções. Os Estados-Membros e a Comissão devem adotar todas as medidas adequadas para fazer respeitar essa proibição.
+Os dados pessoais recolhidos nos termos do primeiro e segundo parágrafos não podem ser utilizados para outros fins que não:
+(a) controlos oficiais pelas autoridades competentes dos Estados-Membros da conformidade com os requisitos de bem-estar e de rastreabilidade do presente Regulamento e da conformidade com o Regulamento (UE) 2016/429, incluindo a deteção de práticas fraudulentas; e
+(b) o cumprimento pela Comissão das suas obrigações nos termos do artigo 108.º do Regulamento (UE) 2017/625 e das obrigações de comunicação de informações da Comissão previstas no presente Regulamento.
+2. Os dados pessoais referidos no n.º 1 do presente artigo são conservados pelos seguintes períodos:
+(a) no caso dos artigos 9.º e 10.º, 10 anos após a data de cessação da atividade do estabelecimento;
+(b) no caso do artigo 21.º, n.º 5, 18 meses após a geração do token referido no artigo 21.º, n.º 3, segundo parágrafo;
+(c) no caso dos artigos 23.º, n.ºs 1 e 4, 25 anos após o primeiro registo do cão ou gato na base de dados referida nesse artigo ou cinco anos após o registo da morte do cão ou gato nessa base de dados;
+(d) (d)	no caso do artigo 26.º, n.º 4, terceiro parágrafo, 5 anos após a data da pré-notificação.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3398,27 +3398,25 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1. ▌Os cães e os gatos só podem ser introduzidos na União para efeitos de colocação no mercado da União se estiverem preenchidas as seguintes condições:
-a) Foram criados e detidos em conformidade com qualquer um dos seguintes requisitos:
-i) os requisitos constantes do capítulo II do presente regulamento
-ii) os requisitos reconhecidos pela União, em conformidade com o artigo 129.º do Regulamento (UE) 2017/625, como equivalentes aos estabelecidos no capítulo II do presente regulamento ou
-iii) se for caso disso, os requisitos constantes de um acordo específico entre a União e o país de exportação
-b) ▌São provenientes de um país ou território terceiro e de um estabelecimento constantes de uma lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
-2. ▌O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625, que acompanha os cães e gatos introduzidos na União a partir de países e territórios terceiros com vista à sua colocação no mercado da União, deve conter um atestado que certifique a conformidade com o n.º 1 do presente artigo.
-3. ▌Os cães e os gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um veterinário através de um transpondedor injetável que contenha um circuito integrado legível que cumpra os requisitos estabelecidos no anexo II.
-O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes sejam registados numa base de dados nacional a que se refere o artigo 23.º, n.º 1, por um veterinário, no prazo de cinco dias úteis após a sua na União. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que medidas para garantir a exatidão das informações que as pessoas em causa inserem na base de dados.
-4. A circulação sem caráter comercial de um cão ou gato a partir de um país ou território terceiro para a União deve ser notificada previamente pelo seu proprietário a uma base de dados em linha da União de animais de companhia em viagem, pelo menos, cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
-a) O cão ou o gato é introduzido na União diretamente a partir de países terceiros ou a partir de territórios que preenchem as condições no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) .../... da Comissão, e
-b) O cão ou o gato está registado numa base de dados de um Estado-Membro a que se refere o artigo 23.º, n.º 1, do presente regulamento.
-Se o cão ou o gato permanecer mais de seis meses na União, o proprietário deve assegurar que seja registado na base de dados do Estado-Membro de residência a que se refere o artigo 23.º, n.º 1, por um veterinário, no prazo de cinco dias úteis após o termo do sexto mês desde que entrou na União. Os Estados-Membros podem autorizar o registo por outras pessoas que não os veterinários, desde que medidas para garantir a exatidão das informações que as pessoas inserem na base de dados.
-A Comissão deve criar e manter a base de dados da União de animais de companhia em viagem a que se refere o primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento base de dados a uma entidade independente, na sequência de um processo de seleção público, nos termos das disposições pertinentes do título VII do Regulamento (UE, Euratom) 2024/2509. O acesso a esta base de dados deve ser limitado às autoridades competentes dos Estados-Membros e à Comissão.
-A Comissão deve assegurar que a base de dados desencadeie notificações iRASFF sobre circulações notificadas previamente que apresentem um risco de fraude. O Estado-Membro que recebe a notificação deve tomar as medidas adequadas para dar seguimento a essa notificação em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
-Até ... [oito anos após a data de entrada em vigor do presente regulamento], a Comissão adota atos de execução que estabelecem disposições pormenorizadas relativas ao seguinte:
-i) As informações a notificar previamente pelos proprietários, em conformidade com o n.º 4 do presente artigo, na base de dados da União de animais de companhia em viagem, tendo em conta os requisitos de proteção de dados pessoais constantes do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
-ii) O procedimento a seguir para determinar o risco de fraude, que deve ter em conta as atividades exercidas pela rede AAC.
-Os referidos atos de execução são adotados pelo procedimento de exame a que se refere o artigo 29.º.
-CAPÍTULO VI
-DISPOSIÇÕES PROCESSUAIS</t>
+          <t>1.	Os cães e os gatos podem ser introduzidos na União para efeitos de colocação no mercado da União apenas se estiverem cumpridas as seguintes condições:
+(a)	tenham sido criados e mantidos em conformidade com qualquer das seguintes situações:
+(i)	os requisitos do Capítulo II do presente Regulamento;
+(ii)	requisitos reconhecidos pela União, em conformidade com o artigo 129.º do Regulamento (UE) 2017/625, como equivalentes aos estabelecidos no Capítulo II do presente Regulamento; ou
+(iii)	quando aplicável, requisitos constantes de um acordo específico entre a União e o país exportador.
+(b)	provenham de um país terceiro ou território e de um estabelecimento incluído em lista em conformidade com os artigos 126.º e 127.º do Regulamento (UE) 2017/625.
+2.	O certificado oficial referido no artigo 126.º, n.º 2, alínea c), do Regulamento (UE) 2017/625 que acompanha os cães e gatos introduzidos na União desde países terceiros e territórios para efeitos de colocação no mercado da União deve conter uma atestação certificando a conformidade com o n.º 1 do presente artigo.
+3.	Os cães e gatos introduzidos na União para efeitos de colocação no mercado da União devem ser identificados antes da sua entrada na União por um médico veterinário por meio de um transponder injetável contendo um microchip legível em conformidade com os requisitos estabelecidos no Anexo II.
+O operador responsável pela importação dos cães ou gatos para a União deve assegurar que estes são registados por um médico veterinário numa base de dados nacional referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após a sua introdução na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+4.	O movimento não comercial de um cão ou gato desde um país terceiro ou território para a União deve ser pré-notificado pelo seu proprietário a uma base de dados online de viajantes da União com animais de estimação, pelo menos cinco dias úteis antes de o cão ou gato atravessar a fronteira da União, exceto nos seguintes casos:
+(a)	quando o cão ou gato é introduzido na União diretamente desde países terceiros ou territórios que satisfazem as condições estabelecidas no artigo 17.º, n.º 1, alínea a), do Regulamento Delegado (UE) …/… da Comissão; e
+(b)	quando o cão ou gato está registado numa base de dados de um Estado-Membro referida no artigo 23.º, n.º 1, do presente Regulamento.
+Caso o cão ou gato permaneça mais de seis meses na União, o proprietário deve assegurar o seu registo por um médico veterinário na base de dados do Estado-Membro de residência referida no artigo 23.º, n.º 1, no prazo de cinco dias úteis após o termo do sexto mês desde a sua entrada na União. Os Estados-Membros podem permitir o registo por pessoas que não sejam médicos veterinários, desde que disponham de medidas para assegurar a exatidão das informações que essas pessoas introduzem na base de dados.
+A Comissão estabelece e mantém a base de dados de viajantes da União com animais de estimação referida no primeiro parágrafo. A Comissão pode confiar o desenvolvimento, a manutenção e o funcionamento dessa base de dados a uma entidade independente, na sequência de um processo de seleção pública. O acesso a essa base de dados fica restrito às autoridades competentes dos Estados-Membros e à Comissão.
+A Comissão assegura que a base de dados aciona notificações iRASFF para os movimentos pré-notificados que apresentem um risco de fraude. O Estado-Membro que recebe a notificação toma as medidas adequadas para dar seguimento à notificação, em conformidade com o artigo 105.º, n.º 2, do Regulamento (UE) 2017/625.
+A Comissão adota, até … [8 anos após a data de entrada em vigor do presente Regulamento], atos de execução que estabelecem regras pormenorizadas relativas a:
+(i)	as informações a pré-notificar pelos proprietários em conformidade com o n.º 4 do presente artigo na base de dados de viajantes da União com animais de estimação, tendo em conta os requisitos de proteção de dados pessoais do Regulamento (UE) 2018/1725 e do Regulamento (UE) 2016/679;
+(ii)	o procedimento pelo qual o risco de fraude deve ser determinado, tendo em conta as atividades realizadas pela rede CAA.
+Esses atos de execução são adotados em conformidade com o procedimento de exame referido no artigo 29.º.</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3519,21 +3517,21 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>A Comissão fica habilitada a adotar atos delegados, nos termos do artigo 2.º, que alterem os anexos do presente regulamento para ter em conta o progresso científico e técnico, incluindo, se for caso disso, os pareceres científicos da , no que diz respeito ao seguinte:
-a) Número adequado de cuidadores de animais em estabelecimentos de criação e de venda;
-b) Requisitos de abeberamento e de alimentação e processo de desmame;
-c) Gamas de temperaturas;
-d) Requisitos de iluminação;
-e) Níveis de amoníaco e de monóxido de carbono;
-f) Conceção dos canis e dos gatis;
-g) Alojamento em grupo;
-h) Espaço disponível para as várias categorias de cães e gatos;
-i) Frequência de gravidezes;
-j) Idade mínima e máxima das cadelas e das gatas para a reprodução;
-k) Medidas de socialização, de enriquecimentos e outras para satisfazer as necessidades comportamentais dos cães e gatos;
-l) Requisitos aplicáveis aos transpondedores utilizados para identificar individualmente os cães e gatos;
-m) Dados a recolher para  e a avaliação das políticas.
-Quaisquer aditamentos de requisitos aos anexos devem basear-se em dados científicos ou técnicos atualizados, em especial no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito de aplicação do presente regulamento. Se for caso disso, os atos delegados em causa devem ter em conta os impactos sociais, económicos e ambientais e devem prever períodos de transição suficientes para permitir que os operadores em causa se adaptem aos novos requisitos.</t>
+          <t>A Comissão fica habilitada a adotar atos delegados em conformidade com o artigo 28.º que alterem os anexos do presente Regulamento para ter em conta o progresso científico e técnico, incluindo, quando relevante, pareceres científicos da Autoridade Europeia para a Segurança dos Alimentos, nos seguintes aspetos:
+(a) Um número adequado de cuidadores de animais em estabelecimentos de criação e venda;
+(b) Requisitos de abastecimento de água e alimentação e processo de desmame;
+(c) Gamas de temperatura;
+(d) Requisitos de iluminação;
+(e) Níveis de amoníaco e monóxido de carbono;
+(f) Conceção de canis e gatis;
+(g) Alojamento em grupo;
+(h) Espaços permitidos para diferentes categorias de cães e gatos;
+(i) Frequência de gestações;
+(j) Idade mínima e máxima de cadelas e gatas para reprodução;
+(k) Socialização, enriquecimento e outras medidas para satisfazer as necessidades comportamentais de cães e gatos;
+(l) Requisitos para transponders utilizados na identificação individual de cães e gatos;
+(m) Dados a recolher para avaliação e monitorização de políticas.
+Qualquer complemento de requisitos nos Anexos deve ser baseado em evidência científica ou técnica atualizada, em particular no que diz respeito às condições específicas necessárias para assegurar o bem-estar dos cães e gatos abrangidos pelo âmbito do presente Regulamento. Quando relevante, esses atos delegados devem levar em conta impactos sociais, económicos e ambientais e prever períodos de transição suficientes para permitir aos operadores envolvidos a adaptação aos novos requisitos.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3605,11 +3603,11 @@
       <c r="D25" s="4" t="inlineStr">
         <is>
           <t>1. O poder de adotar atos delegados é conferido à Comissão nas condições estabelecidas no presente artigo.
-2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a contar de ... [data de entrada em vigor do presente regulamento].
-3. A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
+2. O poder de adotar atos delegados referido no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º é conferido à Comissão por tempo indeterminado a partir de [data de entrada em vigor do presente regulamento].
+3. A delegação de poderes referida no artigo 7.º, n.º 8, no artigo 8.º-A, n.º 3, no artigo 13.º, n.º 2, e no artigo 27.º pode ser revogada em qualquer momento pelo Parlamento Europeu ou pelo Conselho. A decisão de revogação põe termo à delegação dos poderes nela especificados. A decisão de revogação produz efeitos a partir do dia seguinte ao da sua publicação no Jornal Oficial da União Europeia ou de uma data posterior nela especificada. A decisão de revogação não afeta os atos delegados já em vigor.
 4. Antes de adotar um ato delegado, a Comissão consulta os peritos designados por cada Estado-Membro de acordo com os princípios estabelecidos no Acordo Interinstitucional, de 13 de abril de 2016, sobre legislar melhor.
 5. Assim que adotar um ato delegado, a Comissão notifica-o simultaneamente ao Parlamento Europeu e ao Conselho.
-6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º, n.º 3, do artigo 13.º, n.º 2, e do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação do ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogável por dois meses por iniciativa do Parlamento Europeu ou do Conselho. ▌</t>
+6. Os atos delegados adotados nos termos do artigo 7.º, n.º 8, do artigo 8.º-A, n.º 3, do artigo 13.º, n.º 2, ou do artigo 27.º só entram em vigor se não tiverem sido formuladas objeções pelo Parlamento Europeu ou pelo Conselho no prazo de dois meses a contar da notificação desse ato ao Parlamento Europeu e ao Conselho, ou se, antes do termo desse prazo, o Parlamento Europeu e o Conselho tiverem informado a Comissão de que não têm objeções a formular. O referido prazo é prorrogado por dois meses por iniciativa do Parlamento Europeu ou do Conselho.</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3678,11 +3676,9 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1. A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité é um comité na aceção do Regulamento (UE) n.º 182/2011.
-2. Caso se remeta para o presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
-Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.
-CAPÍTULO VII
-REGRAS NACIONAIS MAIS E DISPOSIÇÕES FINAIS</t>
+          <t>1 — A Comissão é assistida pelo Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal criado pelo artigo 58.º, n.º 1, do Regulamento (CE) n.º 178/2002. Este comité deve ser entendido como comité na aceção do Regulamento (UE) n.º 182/2011.
+2 — Caso se faça referência ao presente número, aplica-se o artigo 5.º do Regulamento (UE) n.º 182/2011.
+3 — Na falta de parecer do comité, a Comissão não adota o projeto de ato de execução, aplicando-se o artigo 5.º, n.º 4, terceiro parágrafo, do Regulamento (UE) n.º 182/2011.</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3746,9 +3742,9 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham ou adotem regras nacionais mais que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e uma maior rastreabilidade dos cães e gatos, desde que essas regras não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno. ▌
-2. Os Estados-Membros devem informar a Comissão acerca de quaisquer regras nacionais mais . Posteriormente, os Estados-Membros devem informar a Comissão acerca de regras nacionais mais rigorosas antes de as adotarem, a menos que já tenham notificado os projetos de regras nacionais como projetos de regras técnicas nos termos do artigo 5.º da Diretiva (UE) 2015/1535 do Parlamento Europeu e do Conselho. A Comissão transmite essas informações aos outros Estados-Membros.
-3. Os Estados-Membros que disponham de regras nacionais mais a que se refere o n.º 1 não podem proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas regras nacionais mais ▌.</t>
+          <t>1. O presente regulamento não obsta a que os Estados-Membros mantenham disposições nacionais mais restritivas que visem uma proteção mais ampla do bem-estar dos cães e gatos detidos em estabelecimentos e a rastreabilidade dos cães e gatos, desde que essas disposições não sejam incompatíveis com o presente regulamento e não interfiram com o bom funcionamento do mercado interno.
+2. Os Estados-Membros devem informar a Comissão acerca de tais disposições nacionais existentes até [data de aplicação do presente regulamento] e devem informar a Comissão acerca de tais disposições nacionais novas antes da sua adoção, salvo se os Estados-Membros tiverem notificado os projetos de disposições nacionais em conformidade com a Diretiva (UE) 2015/1535. A Comissão transmite essas informações aos outros Estados-Membros.
+3. Um Estado-Membro que tenha disposições nacionais mais restritivas referidas no n.º 1 não pode proibir ou impedir a colocação no mercado, no seu território, de cães e gatos detidos noutro Estado-Membro com o fundamento de que os cães e gatos em causa não estiveram detidos em conformidade com as suas disposições nacionais mais rigorosas.</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3814,11 +3810,11 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em quaisquer informações adicionais pertinentes, a Comissão publica, até … [▌anos a contar da data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
-2. Até … [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento ▌e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Nessa avaliação e nesse relatório, a Comissão deve examinar, em especial:
-a) Em que medida o presente regulamento contribuiu para assegurar um elevado nível de bem-estar para os cães e gatos, melhorando a sua rastreabilidade e reduzindo o seu comércio ilegal;
-b) O impacto que o presente regulamento teve sobre os operadores de estabelecimentos de criação e venda e de abrigos, bem como sobre os operadores que colocam cães e gatos em de acolhimento, tendo em conta, nomeadamente, os encargos administrativos e os custos de conformidade.
-3. Para efeitos do relatório referido no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração do mesmo.</t>
+          <t>1. Com base nos relatórios recebidos em conformidade com o artigo 24.º e em informações adicionais pertinentes, a Comissão publica, até [7 anos após a data de entrada em vigor do presente regulamento] e, posteriormente, de três em três anos, um relatório de monitorização sobre o bem-estar dos cães e gatos colocados no mercado da União.
+2. Até [14 anos a contar da data de entrada em vigor do presente regulamento], a Comissão procede a uma avaliação do presente regulamento e apresenta um relatório sobre as principais conclusões ao Parlamento Europeu, ao Conselho, ao Comité Económico e Social Europeu e ao Comité das Regiões. Em particular, a Comissão avalia:
+a) O grau em que o presente regulamento contribuiu para assegurar um elevado nível de bem-estar dos cães e gatos, melhorando a rastreabilidade, reduzindo o comércio ilegal;
+b) O impacto do presente regulamento nos operadores de estabelecimentos de criação e venda e de abrigos, e nos operadores que colocam cães e gatos em lares de acolhimento, incluindo o encargo administrativo e os custos de conformidade.
+3. Para efeitos dos relatórios referidos no n.º 2, os Estados-Membros devem fornecer à Comissão as informações necessárias para a elaboração dos mesmos.</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3885,8 +3881,8 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, inclusive as aplicáveis ao abandono de cães e gatos pelos operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
-Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior.</t>
+          <t>Os Estados-Membros estabelecem as regras relativas às sanções aplicáveis em caso de violação do disposto no presente regulamento, incluindo as resultantes do abandono de cães e gatos por parte de operadores, e tomam todas as medidas necessárias para garantir a sua aplicação. As sanções previstas devem ser efetivas, proporcionadas e dissuasivas.
+Os Estados-Membros notificam a Comissão dessas regras e dessas medidas e também, sem demora, de qualquer alteração ulterior das mesmas.</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3958,18 +3954,15 @@
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>O presente regulamento entra em vigor no vigésimo dia seguinte ao da sua publicação no Jornal Oficial da União Europeia.
-O presente regulamento é aplicável a partir de … [dois anos a contar da data de entrada em vigor do presente regulamento]. No entanto,
-i) artigo 16.º é aplicável a partir de … [três anos a contar da data de entrada em vigor do presente regulamento]
-ii)  artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos a contar da data de entrada em vigor do presente regulamento]
-iii) artigo 8.º, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º, n.º 2, é aplicável a partir de 1 de julho de 2030
-iv) artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, o artigo 21.º, n.os 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.os 3 e 4, e o artigo 26.º, n.os 1, 2 e 3, são aplicáveis a partir de … [cinco anos a contar da data de entrada em vigor do presente regulamento
-v) artigo 12.º, n.os 2 e 3, é aplicável a partir de … [sete anos a contar da data de entrada em vigor do presente regulamento
-vi) artigo 10.º é aplicável a partir de … [oito anos a contar da data de entrada em vigor do presente regulamentoe
-vii) artigo 26.º, n.º 4, é aplicável a partir de … [10 anos a contar da data de entrada em vigor do presente regulamento].
-O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.
-Feito em …, em …
-Pelo Parlamento Europeu	Pelo Conselho
-A Presidente	O Presidente</t>
+É aplicável a partir de … [dois anos após a data de entrada em vigor do presente Regulamento]. Todavia:
+i. o artigo 16.º é aplicável a partir de … [três anos após a data de entrada em vigor do presente Regulamento];
+ii. o artigo 21.º, n.º 3, e o artigo 23.º, n.º 1, são aplicáveis a partir de … [quatro anos após a entrada em vigor do presente Regulamento];
+iii. o artigo 8.º-A, n.º 1, é aplicável a partir de 1 de julho de 2036 e o artigo 8.º-A, n.º 2, é aplicável a partir de 1 de julho de 2030;
+iv. o artigo 15.º, o artigo 21.º, n.º 3, segundo parágrafo, n.ºs 4 e 5, o artigo 22.º, n.º 1, alíneas a), b) e c), o artigo 23.º, n.ºs 3 e 4, e o artigo 26.º, n.ºs 1, 2 e 3, são aplicáveis a partir de … [cinco anos após a data de entrada em vigor do presente Regulamento];
+v. o artigo 12.º, n.ºs 2 e 3, é aplicável a partir de … [sete anos após a data de entrada em vigor do presente Regulamento];
+vi. o artigo 10.º é aplicável a partir de … [oito anos após a data de entrada em vigor do presente Regulamento]; e
+vii. o artigo 26.º, n.º 4, é aplicável a partir de … [10 anos após a entrada em vigor do presente Regulamento].
+O presente regulamento é obrigatório em todos os seus elementos e diretamente aplicável em todos os Estados-Membros.</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -4042,11 +4035,11 @@
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>1. Alimentação e abeberamento
-1.1.	Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
-No entanto, estes requisitos não se aplicam a cães de guarda de gado mantidos em estabelecimentos de criação enquanto estes cães são usados para fins de guarda ou de treino.
-▌1.2.	Cada cachorro ou gatinho ▌deve ser alimentado com colostro durante, pelo menos, os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da respetiva mãe ou de uma cadela ou gata em lactação. Se tal não for possível, em razão de a mãe estar doente ou de, por outro motivo, não poder alimentar a sua cria ou de não poder fornecer leite suficiente, o cachorro ou gatinho deve ser alimentado com um substituto do leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as indicações do fabricante ou de um veterinário.
-1.3.	▌Todos os cachorros e gatinhos não desmamados devem ser alimentados com uma quantidade de leite, de substituto do leite ou de uma combinação destes que seja suficiente para aumentar constantemente o peso corporal.
-1.4.	O desmame deve ser efetuado com a introdução gradual de alimentos sólidos, durante um período não inferior a sete dias, e não deve ser concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
+1.1 Os cães e gatos devem ser alimentados, pelo menos, duas vezes por dia. Os cachorros e gatinhos devem ser alimentados com maior frequência.
+No entanto, estes requisitos não se aplicam aos cães de proteção de gado mantidos em estabelecimentos de criação durante os períodos em que esses cães sejam utilizados para fins de guarda ou de treino.
+2.2 Cada cachorro ou gatinho deve ser alimentado com colostro, pelo menos, durante os dois primeiros dias de vida. Posteriormente, deve ser alimentado com leite da progenitora ou de uma cadela ou gata lactante. Se tal não for possível, por a progenitora estar doente ou estar de outro modo impossibilitada de alimentar a sua ninhada ou de fornecer leite em quantidade suficiente, o cachorro ou gatinho deve ser alimentado com um sucedâneo de leite concebido para cachorros e gatinhos. A frequência dessa alimentação deve respeitar as instruções do fabricante ou de um médico veterinário.
+3.3 Todos os cachorros e gatinhos não desmamados devem receber leite, sucedâneo de leite ou uma combinação de ambos em quantidade suficiente para lhes permitir aumentar de peso de forma constante
+4.4 O desmame deve ser efetuado através da introdução gradual de alimentos sólidos durante um período não inferior a sete dias e não deve estar concluído antes das seis semanas de idade, tanto para os cachorros como para os gatinhos.</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4169,18 +4162,30 @@
       <c r="D32" s="4" t="inlineStr">
         <is>
           <t>2. Alojamento
-2.1.	Temperatura:
-Nos estabelecimentos de criação, a temperatura deve ser mantida numa gama de:
-▌a)	22 °C a 28 °C nas áreas de parto durante os primeiros 10 dias de vida dos cachorros;
-b) 18 °C a 27 °C nas áreas de parto durante os primeiros 21 dias de vida dos gatinhos.
-2.2.	Iluminação
-2.2.1.	Os cães e gatos devem ser expostos à luz durante pelo menos sete horas por dia. ▌
-2.2.2.	A luz artificial deve ser de largo espetro ou de espetro completo e ter uma frequência de pelo menos 80 hertz.
-2.2.3.	Os cães e gatos devem ter a possibilidade de não estar expostos a iluminação artificial durante, pelo menos, oito horas por dia.
-2.3.	Espaço disponível
-2.3.1.	As áreas de parto para as cadelas e gatas devem ser concebidas de modo a permitir que a mãe se afaste das crias.
-2.3.2.	No caso dos estabelecimentos de criação e venda, aplicam-se as seguintes regras aos seguintes espaços disponíveis mínimos para os cães e gatos, com base na área permanentemente acessível total para os cães ou gatos:
-2.3.3.</t>
+2.1 Temperatura
+Em estabelecimentos de criação, a temperatura deve ser mantida dentro de uma gama de:
+— 22 a 28°C em áreas de parto de cães durante os primeiros 10 dias de vida dos filhotes;
+— 18 a 27°C em áreas de parto de gatos durante os primeiros 21 dias de vida dos gatinhos.
+2.2 Iluminação
+Cães e gatos devem ser expostos a luz durante pelo menos 7 horas por dia. A luz artificial deve ser de espectro amplo ou espectro completo com uma frequência de pelo menos 80 Hz.
+Cães e gatos devem ter a possibilidade de estar sem luzes artificiais durante pelo menos 8 horas por dia.
+2.3 Espaço adequado
+2.3.1 As áreas de parto devem ser concebidas de modo a permitir que a progenitora se afaste da sua prole.
+2.3.2 No caso dos estabelecimentos de criação e de venda, aplicam-se as seguintes superfícies mínimas para cães e gatos, as quais devem ser calculadas com base na área total permanentemente acessível aos cães ou gatos.
+2.3.3
+Espaço para cães com ou sem crias
+Altura do var (cm):
+&lt; 30 → Área mínima: 4 m², Altura: 200 cm
+30-40 → 5 m², 200 cm
+40-60 → 8 m², 200 cm
+60-70 → 10 m², 200 cm
+&gt;70 → 10 m², 200 cm
+Cada cão adicional: 3/3.5/4/5/6 m² respetivamente.
+Espaço para gatos com ou sem crias
+Um gato: 3 m² solo, 200 cm altura
+Cada adicional: 2 m².
+* No caso de cães de raça pura, as alturas do var podem ser calculadas com base no cercado individual; mantêm-se apenas as colunas para área de superfície mínima para a altura.
+** A superfície com enriquecimento para gatos não é incluída na área mínima do solo.</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4250,13 +4255,13 @@
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>3. Saúde
-3.1.	As gatas só podem reproduzir-se se a sua idade for igual ou superior a 10 meses.
-3.2.	As cadelas não podem ser utilizadas para a reprodução antes do seu segundo cio.
-3.3.	Uma cadela ou gata não pode produzir mais de três ninhadas num período de dois anos.
-3.4.	Para as cadelas e gatas que tenham produzido três ninhadas, incluindo nados-mortos, durante um período de dois anos, deve existir um período de recuperação ▌de, pelo menos, um ano.
-3.5.	Qualquer cadela ou gata que tenha sido submetida a duas cesarianas deixará de ser utilizada para a reprodução.
-3.6.	Antes de serem utilizadas para a reprodução, as cadelas com idade igual ou superior a oito anos e as gatas com idade igual ou superior a seis anos devem ser fisicamente examinadas por um veterinário que confirme, por escrito, que, à data desse exame, não existem indicações médicas que obstem à utilização da cadela ou gata em causa para a reprodução.
-O operador deve conservar a confirmação escrita referida no primeiro parágrafo durante um período de, pelo menos, três anos.</t>
+1.1 As gatas só devem ser utilizadas para reprodução se tiverem, pelo menos, 10 meses de idade.
+2.2 As cadelas só devem ser utilizadas para reprodução a partir do seu segundo estro.
+3.3 Uma cadela ou gata não deve ter mais de 3 ninhadas num período de 2 anos.
+4.4 No caso de cadelas e gatas que tenham tido 3 ninhadas num período de 2 anos, incluindo nascimortos, deve ser respeitado um período de recuperação de, pelo menos, 1 ano.
+5.5 Qualquer cadela ou gata que tenha sido submetida a duas cesarianas não pode ser utilizada para reprodução.
+6.6 Antes de qualquer cadela com 8 ou mais anos de idade e de qualquer gata com 6 ou mais anos de idade serem utilizadas para reprodução, devem ser submetidas a um exame físico por um médico veterinário que confirme, por escrito, que, à data do exame, não existem contraindicações para a gestação.
+O operador deve conservar a confirmação escrita referida no ponto 3.4.b por um período de, pelo menos, 3 anos.</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -4327,16 +4332,16 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>4. Necessidades comportamentais
-4.1.	Socialização
-4.1.1.	A partir das três semanas de idade, os cães e gatos devem dispor gradualmente de oportunidades diárias de contacto social com outros animais da mesma espécie e com seres humanos e, sempre que possível, com animais de outras espécies.
-4.1.2.	Os cães ou gatos que constituam uma ameaça para congéneres devido a comportamentos agressivos ou que causem stress ou desconforto indevidos aos congéneres devem ser mantidos à parte.
-4.2.	Enriquecimentos
-4.2.1.	Os gatos devem dispor de um número suficiente de arranhadores, esconderijos e prateleiras para garantir que cada gato possa subir, descansar, observar e retirar-se.
-4.3.	Separação
-Os cachorros detidos em estabelecimentos não podem ser permanentemente separados das mães antes das oito semanas de idade.
-Os gatinhos detidos em abrigos e casas de acolhimento não podem ser permanentemente separados das mães antes das oito semanas de idade. Os gatinhos detidos em estabelecimentos de criação não podem ser permanentemente separados das mães antes das 12 semanas de idade.
-No entanto, a separação precoce das mães deve ser possível por razões médicas, com base no parecer escrito de um veterinário. O operador deve manter um registo desse parecer até que o último cachorro ou gatinho da ninhada em causa seja colocado no mercado.</t>
+          <t>Bem-Estar Comportamental
+1.1 Socialização
+A partir das três semanas de idade, cães e gatos devem ser gradualmente fornecidos com oportunidades diárias de contato social com seus congêneres e humanos, e, sempre que possível, com outras espécies animais.
+Cães e gatos que representam uma ameaça um ao outro devido a comportamento agressivo ou causam um ao outro stress excessivo ou desconforto devem ser mantidos separados.
+2.2 Enriquecimento
+Onde gatos são mantidos, deve haver um número suficiente de postes de arranhadura, locais de abrigo e prateleiras para garantir que cada gato pode subir, descansar, observar e retirar-se.
+3.3 Separação
+Cachorros mantidos em estabelecimentos não devem ser permanentemente separados das suas mães antes das 8 semanas de idade.
+Gatinhos mantidos em abrigos e casas de acolhimento não devem ser permanentemente separados das suas mães antes das 8 semanas de idade. Gatinhos mantidos em estabelecimentos de criação não devem ser permanentemente separados das suas mães antes das 12 semanas de idade.
+Por derrogação, separação anterior é possível por razões médicas com base em parecer escrito de um veterinário. O operador deve conservar o parecer até o último cachorro ou gatinho da ninhada em questão ser colocado no mercado.</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -4453,11 +4458,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Os transpondedores utilizados para identificar individualmente cães e gatos, tal como exigido no artigo 20.º e no artigo 26.º, devem cumprir os seguintes requisitos:
-a) O circuito integrado deve conter um número de identificação individual, não repetível e não reprogramável;
-b) O número de identificação deve começar com o país de identificação do cão ou gato identificado em conformidade com a norma ISO 3166;
-c) A estrutura do código e o conceito técnico da identificação por radiofrequências devem estar em conformidade com as normas ISO 11784 e 11785;
-d) A conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1.</t>
+          <t>Identificação e registo de cães e gatos
+Os transponders utilizados para identificar individualmente cães e gatos, tal como exigido nos artigos 20.º e 26.º, devem cumprir os seguintes requisitos:
+(a) O microchip deve conter um número de identificação individual, não repetível e não reprogramável;
+(b) O número de identificação deve começar pelo país de identificação do cão ou gato, identificado em conformidade com a norma ISO 3166;
+(c) A estrutura do código e o conceito técnico da identificação por radiofrequência devem estar em conformidade com as normas ISO 11784 e 11785;
+(d) a conformidade com as normas ISO 11784 e 11785 deve ser avaliada de acordo com a norma ISO 24631-1</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -4536,10 +4542,10 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1. Número de cães e gatos registados, por ano, a que se referem o artigo 20.º e o artigo 26.º, n.º 3.
-2. Número de estabelecimentos de criação, estabelecimentos de venda, abrigos e casas de acolhimento registados, por ano, em conformidade com o artigo 9.º.
-3. Número de estabelecimentos de criação aprovados por ano a que se refere o artigo 10.º.
-4. Número de estabelecimentos de criação cuja aprovação foi suspensa ou retirada, por ano.</t>
+          <t>1. O número de cães e gatos registados por ano, conforme referido no artigo 20.º e no artigo 26.º, n.º 3.
+2.  O número de estabelecimentos de criação, estabelecimentos de venda, abrigos e famílias de acolhimento registados por ano em conformidade com o artigo 9.º.
+3. O número de estabelecimentos de criação aprovados por ano, conforme referido no artigo 10.º.
+4. O número de estabelecimentos de criação cuja aprovação tenha sido suspensa ou retirada por ano.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -704,27 +704,27 @@
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica — a legislação nacional não utiliza o modelo de limiares de isenção adoptado pelo Regulamento (≤2 ninhadas/ano; ≤15 animais em abrigo). A Portaria n.º 148/2016 regula o registo de cães que integrem matilhas de caça maior junto do ICNF, I. P., mas não fixa limiares de isenção de obrigações de bem-estar.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>O n.º 1 do Art.º 5.º define um limiar de 2 ninhadas por ano civil que libera os pequenos criadores das obrigações de bem-estar mais exigentes do Capítulo II. Este limiar pode capturar proprietários de matilhas de caça em Portugal (especialmente caça maior) sem actividade comercial, que regularmente produzem ninhadas de cães de trabalho. No debate legislativo europeu (EP A10-0104/2025), as federações de caçadores (FACE, Federación Española de Caza) argumentaram que o limiar de 2 ninhadas deveria isentar a criação não comercial de cães de caça, enquanto as ONG de bem-estar animal (AnimaNaturalis, Eurogroup for Animals) exigiram a aplicação universal do Regulamento sem excepções. O texto final não criou uma derrogação explícita para cães de caça. A aplicação prática deste limiar a proprietários de matilhas portuguesas (que podem deter 20–120 cães) terá de ser avaliada pela autoridade competente.</t>
+          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não — artigo de isenções de aplicação directa; o limiar é fixado pelo Regulamento e não carece de transposição. Pode carecer de orientação administrativa para aplicação a matilhas de caça.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -2363,29 +2363,21 @@
 2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.º 8.º) prevê genericamente que os animais devem 'dispor de um espaço adequado às suas necessidades fisiológicas e etológicas' e de 'esconderijos', mas sem requisitos de socialização, enriquecimento documentado ou estratégia formal. A Portaria n.º 148/2016 regula o registo de cães em matilhas de caça maior (junto do ICNF, I. P.) mas não fixa normas de bem-estar comportamental para esses cães. O @rgbeac (art.º 10.º, n.º 3) isenta expressamente os cães utilizados na caça durante os atos venatórios da obrigação de trela — o que representa uma derrogação análoga (embora com âmbito e fundamento distintos) à derrogação do n.º 4 do Art.º 17.º do Regulamento para cães militares/policiais/aduaneiros. Não existe, no entanto, na legislação nacional, qualquer equivalente à isenção de socialização para cães de proteção de gado ou de pastoreio em transumância.</t>
-        </is>
-      </c>
+      <c r="K14" s="8" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (DL 214/2013) não contém especificações sobre socialização, enriquecimento ambiental ou estratégia documentada de socialização por parte dos criadores. O art.º 13.º prevê genericamente 'espaço para exercício físico e expressão de comportamentos naturais', mas sem os requisitos quantitativos ou processuais do Regulamento. Não inclui as derrogações para cães funcionais.</t>
+          <t>Sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac cobre parcialmente: prevê 'exercício físico e estímulo mental' (art.º 10.º, n.º 1, al. a), i)), 'métodos de reforço positivo' como obrigação (art.º 10.º, n.º 1, al. c)) e proíbe 'métodos aversivos, punitivos ou violentos' (art.º 12.º, al. v)). Prevê ainda obrigação de 'plano de socialização e enriquecimento ambiental' (art.º 52.º, n.º 7) para alojamentos. No entanto, o @rgbeac não contempla as derrogações específicas do Regulamento: (1) isenção dos cães de proteção de gado («livestock guardian dogs») dos requisitos de socialização durante períodos de guarda ou treino; (2) isenção dos cães de pastoreio durante a transumância sazonal; (3) isenção de cães militares, policiais e aduaneiros da proibição de acorrentamento superior a 1 hora. Também não inclui a obrigação de 'estratégia documentada de socialização' para criadores.</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>O Regulamento introduz obrigações novas sem equivalente nacional: (1) proibição de acorrentamento superior a 1 hora (com isenção para cães militares, policiais e aduaneiros); (2) obrigação de estratégia documentada de socialização por parte dos criadores; (3) isenção explícita de socialização para cães de proteção de gado ("livestock guardian dogs") durante guarda/treino e para cães de pastoreio em transumância sazonal. Em Portugal, a realidade dos cães de caça (matilhas) é relevante: a Portaria n.º 148/2016 exige registo mas não impõe normas de bem-estar comportamental. O Regulamento não inclui derrogação explícita para cães de caça — estes estão abrangidos pelas obrigações gerais do Art.º 17.º enquanto permanecerem em estabelecimentos de criação ou venda.</t>
-        </is>
-      </c>
+          <t>Cobertura mais significtiva</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Sim — necessidade de: (1) criar regime de proibição de acorrentamento superior a 1 hora com as isenções previstas; (2) impor estratégia documentada de socialização aos criadores; (3) clarificar o estatuto dos cães de caça e matilhas face às obrigações comportamentais.</t>
+          <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -2486,29 +2478,22 @@
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (arts. 17.º e 18.º) exige que as intervenções cirúrgicas (incluindo corte de caudas) sejam realizadas por médico veterinário e que as amputações estejam documentadas por atestado. Não existe proibição expressa de corte de cauda anterior a 2013. O @rgbeac e o @codigo já proíbem o corte de cauda desde 2015 (art.º 52.º, n.º 3 do @codigo), o que excede o regime do Regulamento no que respeita a cães de caça (o Regulamento admite a excepção profilática que poderia ser invocada para justificar o corte de cauda em cães de caça). A derrogação do n.º 5 do Art.º 18.º para cães militares, policiais e aduaneiros não tem equivalente na legislação nacional. A proibição de coleiras de espinhos e de estrangulamento sem paragem de segurança não consta expressamente da legislação nacional vigente (embora o uso de 'aguilhões' e instrumentos perfurantes na condução de animais seja proibido pela Lei n.º 92/95).</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (DL 214/2013) proíbe mutilações com fins não curativos (art.º 52.º, n.º 1), incluindo corte de orelhas, cordas vocais, garras ou unhas, dentes ou presas. O art.º 52.º, n.º 3 proíbe o corte de cauda para todos os cães nascidos a partir de 1 de Janeiro de 2015 — regime mais restritivo que o Regulamento, que admite corte de cauda por razões profiláticas (incluindo potencialmente para cães de caça). O @codigo exige atestado veterinário (n.º 4) alinhado com o n.º 2 do Art.º 18.º. Não cobre explicitamente a proibição de coleiras de espinhos (prong collars) nem de coleiras de estrangulamento sem paragem de segurança prevista no n.º 5, als. (e) e (f) do Regulamento.</t>
-        </is>
-      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 12.º, al. i)) proíbe intervenções cirúrgicas com objectivo de modificar a aparência, incluindo 'corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais'. O art.º 34.º do @rgbeac exige atestado veterinário para qualquer intervenção curativa que modifique a aparência, alinhando com o n.º 2 do Art.º 18.º do Regulamento. O @rgbeac também proíbe coleiras elétricas, de choques, estranguladores e açaimos fechados (art.º 12.º, al. aa)), convergindo com o n.º 5 do Art.º 18.º. A derrogação do Art.º 18.º, n.º 3, sobre corte de orelha de gatos em programas TNR está coberta pela ressalva do @rgbeac ('fins de identificação de animais esterilizados conforme boas práticas internacionais').</t>
+          <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>Portugal está em grande medida alinhado com o Regulamento no que respeita à proibição de mutilações: o corte de cauda já é proibido desde 2015 (mais restritivo do que o Regulamento, que admite excepção profilática para cães de caça). Os principais gaps são: (1) ausência de proibição expressa de coleiras de espinhos (prong collars) e de estrangulamento sem paragem de segurança; (2) ausência de derrogação específica para cães militares, policiais e aduaneiros; (3) necessidade de clarificar que a excepção profilática do Art.º 18.º, n.º 1 não se aplica ao corte de cauda de cães de caça em Portugal (o @codigo e @rgbeac são mais restritivos). Exige anestesia e analgesia prolongada como condição obrigatória para qualquer procedimento justificado — requisito que a legislação nacional não especifica explicitamente.</t>
+          <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
+Rever proibições na análise do art.7.º</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Sim — necessidade de: (1) proibir expressamente coleiras de espinhos e de estrangulamento sem paragem de segurança; (2) clarificar o âmbito da excepção profilática face ao regime mais restritivo nacional; (3) confirmar conformidade do regime de atestado veterinário com os requisitos documentais do Art.º 18.º, n.º 2.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -704,27 +704,27 @@
       <c r="J2" s="7" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica — a legislação nacional não utiliza o modelo de limiares de isenção adoptado pelo Regulamento (≤2 ninhadas/ano; ≤15 animais em abrigo). A Portaria n.º 148/2016 regula o registo de cães que integrem matilhas de caça maior junto do ICNF, I. P., mas não fixa limiares de isenção de obrigações de bem-estar.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo processual de isenções sem correspondência nas propostas nacionais.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="N2" s="11" t="inlineStr">
         <is>
-          <t>O n.º 1 do Art.º 5.º define um limiar de 2 ninhadas por ano civil que libera os pequenos criadores das obrigações de bem-estar mais exigentes do Capítulo II. Este limiar pode capturar proprietários de matilhas de caça em Portugal (especialmente caça maior) sem actividade comercial, que regularmente produzem ninhadas de cães de trabalho. No debate legislativo europeu (EP A10-0104/2025), as federações de caçadores (FACE, Federación Española de Caza) argumentaram que o limiar de 2 ninhadas deveria isentar a criação não comercial de cães de caça, enquanto as ONG de bem-estar animal (AnimaNaturalis, Eurogroup for Animals) exigiram a aplicação universal do Regulamento sem excepções. O texto final não criou uma derrogação explícita para cães de caça. A aplicação prática deste limiar a proprietários de matilhas portuguesas (que podem deter 20–120 cães) terá de ser avaliada pela autoridade competente.</t>
+          <t>Artigo de isenções do Regulamento europeu — não tem correspondência directa em legislação portuguesa.</t>
         </is>
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>Não — artigo de isenções de aplicação directa; o limiar é fixado pelo Regulamento e não carece de transposição. Pode carecer de orientação administrativa para aplicação a matilhas de caça.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -762,77 +762,45 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Art.º 7.º do RGBEAC (proposta, jun. 2025)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>1 – Todos têm o dever de garantir condições de bem-estar aos animais de companhia, em especial que:
-a) não passem fome ou sede, nem sejam sujeitos a malnutrição;
-b) não sejam expostos a situações de desconforto físico ou térmico;
-c) não sofram dor, lesão física ou doença;
-d) possam expressar padrões normais de comportamento; e
-e) não sejam colocados em situações que lhes provoquem stresse, medo ou ansiedade injustificados.
-2 - As condições de detenção e de alojamento dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-3 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no presente decreto-lei ou se não se adaptar ao cativeiro.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Arts. 4.º e 5.º do Código do Animal (DL n.º 214/2013)</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Artigo 4.º — Detenção responsável
-Cabe aos detentores de animais de companhia assegurar as necessidades básicas de bem-estar dos mesmos, garantir o controlo da sua reprodução, salvaguardar a sua saúde e prevenir os riscos inerentes à transmissão de doenças a pessoas e a outros animais e, ainda, a segurança das populações, garantindo a salubridade dos locais e a tranquilidade das pessoas.
-Artigo 5.º — Princípios básicos para o bem-estar dos animais
-1 - As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal.
-2 - Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 - É proibida a violência contra animais, considerando-se como tal todos os atos que, sem necessidade, infligem a morte, o sofrimento, abuso ou lesões a um animal, designadamente os seguintes:
-a) Agredir animais, nomeadamente com o uso de chicotes, estimulantes elétricos ou objetos contundentes ou perfurantes, ou com murros, bofetadas ou pontapés;
-b) Restringir a liberdade de movimentos dos animais de tal forma que lhes seja impedido levantar-se, deitar-se ou virar-se sobre si próprios;
-c) Usar equipamentos de maneio, contenção ou treino, que causem sofrimento desnecessário ou lesões aos animais;
-d) Incitar, realizar ou promover lutas entre animais de companhia, quando destas possa resultar sofrimento, lesões ou morte dos animais.
-4 - É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, sempre que daí resultem para aqueles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>n.ºs 1, 2, 3 e 4 do art.º 7.º do DL n.º 276/2001, de 17 de outubro</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>1 — As condições de detenção e de alojamento para reprodução, criação, manutenção e acomodação dos animais de companhia devem salvaguardar os seus parâmetros de bem-estar animal, nomeadamente nos termos dos artigos seguintes.
-2 — Nenhum animal deve ser detido como animal de companhia se não estiverem asseguradas as condições referidas no número anterior ou se não se adaptar ao cativeiro.
-3 — São proibidas todas as violências contra animais, considerando-se como tais os atos consistentes em, sem necessidade, se infligir a morte, o sofrimento ou lesões a um animal.
-4 — É proibido utilizar animais para fins didáticos e lúdicos, de treino, filmagens, exibições, publicidade ou atividades semelhantes, na medida em que daí resultem para eles dor ou sofrimentos consideráveis, salvo experiência científica de comprovada necessidade e justificada nos termos da lei.</t>
-        </is>
-      </c>
+          <t>Análise no Art.º 7</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>O DL 276/2001 (Art.º 7.º) enuncia princípios gerais de bem-estar sem estrutura de cinco domínios. Os princípios (d) e (e) do Regulamento não têm correspondência. As obrigações específicas estão desenvolvidas nos arts. 8.º a 16.º do DL 276/2001.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Arts. 4.º e 5.º) estabelece princípios gerais equivalentes mas sem a estrutura de cinco domínios explícitos do Regulamento. Os princípios (d) — relação positiva com os seres humanos — e (e) — otimização do estado mental e prevenção de comportamentos repetitivos anormais — não têm correspondência no @codigo. As obrigações específicas estão desenvolvidas nos arts. 13.º a 16.º e 46.º a 48.º do @codigo.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 7.º, n.º 1) enuncia cinco domínios de bem-estar em alíneas a) a e) análogas às do Regulamento — correspondência estrutural directa. Divergência: o Regulamento dirige-se exclusivamente aos operadores de estabelecimentos; o @rgbeac dirige-se a todos os cidadãos. O princípio (e) do Regulamento — otimização do estado mental e prevenção de comportamentos repetitivos anormais — não tem correspondência literal no @rgbeac: a alínea e) do @rgbeac refere apenas a proibição de stresse/medo/ansiedade. O domínio (d) do Regulamento — 'relação positiva com os seres humanos' — não consta do @rgbeac. As obrigações específicas para operadores são desenvolvidas nos arts. 9.º a 12.º e 47.º a 55.º do @rgbeac.</t>
+          <t>Análise no Art.º 7</t>
         </is>
       </c>
       <c r="N3" s="11" t="inlineStr">
         <is>
-          <t>O Art.º 6.º do Regulamento codifica os 'Five Domains' de bem-estar animal como obrigação jurídica para operadores. Os diplomas nacionais reconhecem os primeiros três domínios (nutrição, ambiente físico, saúde) mas não desenvolvem explicitamente os domínios comportamental e mental tal como formulados no Regulamento. As obrigações específicas de cada princípio são desenvolvidas nos Arts. 14.º a 17.º do Regulamento, com correspondências nacionais detalhadas em cada artigo.</t>
+          <t>Regulamento especifica novos conceitos: estabelecer uma relação positiva com os seres humanos; otimizar o seu estado mental; prevenindo o desenvolvimento de comportamentos repetitivos anormais;</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr"/>
@@ -1173,19 +1141,15 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 não contém disposições específicas sobre estratégia de reprodução, limites etários para criadores, restrições de consanguinidade ou proibição de traços conformacionais excessivos. As normas de reprodução estão essencialmente remetidas para os artigos de alojamento (arts. 21.º a 26.º). Sem equivalência material ao Art.º 8.º do Regulamento.</t>
+          <t>Breve referência. Sem equivalência</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade próxima (pais/filhos, irmãos, avós/netos). Não proíbe a produção de híbridos. Não exige avaliação veterinária prévia ao acasalamento nem limita o número de descendentes por macho reprodutor.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (Art.º 70.º) prevê limites de idade para reprodução (cadelas 18 meses a 6 anos; gatas 12 meses a 6 anos; machos 12 meses a 7 anos), máximo de 4 ninhadas com intervalo mínimo de 12 meses, testes genéticos e de saúde e proibição de reprodução após 2 cesarianas — vários destes requisitos são mais detalhados que o Regulamento. O Art.º 70.º, n.º 7 remete para portaria a definição de coeficiente de consanguinidade e limite de descendentes por macho, sem proibição expressa de cruzamentos entre pais/filhos, irmãos ou avós/netos como o Regulamento. O conceito de 'características conformacionais excessivas' não está explicitado no @rgbeac, embora o n.º 8 proíba genericamente a reprodução quando se espere efeito prejudicial na saúde com base no fenótipo. A proibição de híbridos (espécies distintas) não consta do @rgbeac.</t>
-        </is>
-      </c>
+          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
       <c r="N5" s="11" t="inlineStr">
         <is>
           <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados.
@@ -1546,19 +1510,11 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Conceito de ‘aprovação’ específica de estabelecimentos de criação com limiar numérico (&gt;5 ninhadas/ano ou &gt;5 fêmeas) é novo no Regulamento, sem equivalente na legislação vigente. O DL n.º 276/2001 exige licença/autorização para alojamentos de hospedagem mas sem distinguir criadores por volume de atividade.</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (Art.º 37.º) publicita a lista de alojamentos de hospedagem, mas não prevê aprovação específica de estabelecimentos de criação com limiar numérico, nem revisão da aprovação por alteração das condições. O @codigo trata o licenciamento de criadores como parte do regime geral de alojamentos, sem o limiar específico do Regulamento.</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>O @rgbeac (Art.º 62.º) divulga a lista de alojamentos autorizados através do balcão único eletrónico e do sítio da DGAV, mas não distingue ‘aprovação de estabelecimento de criação’ como procedimento específico com limiar numérico (&gt;5 ninhadas/ano ou &gt;5 fêmeas reprodutoras). O @rgbeac não exige revisão da aprovação por alteração das condições, nem prevê o mecanismo de consulta de aprovação por autoridades de outros Estados-Membros.</t>
-        </is>
-      </c>
+          <t>Conceito novo de ‘aprovação’ com limiar (&gt;5 ninhadas/ano ou &gt;5 cadelas/gatas)</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="10" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Artigo novo no Regulamento, introduz aprovação formal de criadores com limiar numérico para ninhadas ou fêmeas no local.
@@ -1976,14 +1932,11 @@
 6 — Os animais devem dispor de água potável e sem qualquer restrição, salvo por razões médico-veterinárias.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (Art.º 12.º) tem disposições de nutrição substancialmente equivalentes às do @codigo (Art.º 46.º) e ao @rgbeac (Art.º 51.º): programa de alimentação bem definido, valor nutritivo adequado, refeições variadas, comedouros/bebedouros adequados, água potável ad libitum, higiene e refrigeração. Divergências face ao Regulamento: (1) não especifica dieta adaptada a raça, nível de atividade ou categoria do animal; (2) não exige transições alimentares graduais nem cuidados específicos de desmame; (3) não prevê obrigação de instalações de alimentação que previnam ferimentos, afogamento ou outros danos físicos; (4) não regula ajuste de frequência alimentar por conselho veterinário escrito.</t>
-        </is>
-      </c>
+      <c r="K11" s="8" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Art.º 46.º) restringe a aplicação das obrigações de nutrição aos estabelecimentos de criação, manutenção, venda, centros de recolha e instalações de hospedagem — não se aplica à detenção doméstica individual. O Regulamento dirige-se aos operadores em geral. O n.º 7 do Art.º 46.º do @codigo proíbe alimentar com restos de comida, pastelaria e desperdícios da indústria alimentar — requisito mais restritivo que o Regulamento, que apenas proíbe substâncias causadoras de sofrimento. O @codigo não prevê dieta adaptada a nível de atividade, categoria ou transições alimentares graduais (desmame), nem registro de ajuste de frequência por conselho veterinário escrito.</t>
+          <t>Parece restringir as obrigações aos estabelecimentos.
+Apenas @código proíbe restos, pastelaria e desperdícios.</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -1995,7 +1948,8 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>Regulamento introduz mais «categorias» de adaptação da dieta — raça, categoria, nível de atividade e estado reprodutivo — que os diplomas nacionais não contemplam. Nenhum dos diplomas nacionais aborda transições alimentares graduais, cuidados específicos com desmame, prevenção de ferimentos por instalações de alimentação, ou registo de ajuste de frequência por conselho veterinário. O @codigo é mais restritivo que o Regulamento na proibição de restos de comida e desperdícios.</t>
+          <t>Regulamento introduz mais «categorias» - raça, categoria, nível de atividade e estado reprodutivo.
+Nenhum aborda transições alimentares graduais, cuidados específicos com desmame, segurança estrutural das instalações.</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -2148,27 +2102,19 @@
 Artigo 15.º — Os alojamentos devem assegurar que as espécies animais neles mantidas não possam causar quaisquer riscos para a saúde e para a segurança de pessoas, outros animais e bens.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (Arts. 8.º e 9.º) prevê espaço adequado às necessidades fisiológicas e etológicas, esconderijos, enriquecimento ambiental e fatores ambientais (temperatura, ventilação, luz). Não proíbe a manutenção permanente em contentores, não impõe acesso mínimo ao exterior nem contém o mecanismo de desvio por parecer veterinário escrito do Regulamento n.4. As dimensões mínimas das instalações para cada espécie e categoria constam de legislação complementar (portarias).</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (Arts. 13.º e 14.º) estabelece que os animais devem dispor de 'espaço adequado às necessidades fisiológicas e etológicas', possibilidade de exercício físico, esconderijos e enriquecimento ambiental. Não proíbe expressamente a manutenção permanente em contentores (Regulamento n.2) nem impõe acesso mínimo ao exterior (Regulamento n.4). Não regula dimensões mínimas das instalações nem a proibição de manutenção exclusiva no interior por mais de 8 semanas. O Art.º 14.º do @codigo prevê exigências de temperatura, ventilação, luz e obscuridade mas sem parâmetros quantitativos específicos.</t>
-        </is>
-      </c>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 47.º, n.º 6) prevê acesso diário a área de exercício exterior, pelo menos 2 vezes por dia, durante 30 minutos — mais específico que o Regulamento (mínimo 1h total). O @rgbeac não contém a proibição explícita de manutenção de cães &gt;8 semanas exclusivamente no interior (Regulamento n.4, primeira parte), nem o mecanismo de desvio desta proibição por parecer veterinário escrito. O @rgbeac não proíbe expressamente a manutenção permanente em contentores (Regulamento n.2), embora a exigência de espaço adequado às necessidades etológicas (Art.º 47.º, n.º 1) produza efeito equivalente.</t>
+          <t>@rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total),</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>N.º 2 — Proibição expressa de manter cães ou gatos em contentores: não coberta por nenhum dos três diplomas de forma explícita.
-N.º 3 — Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe): não coberta.
-N.º 4 — Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito: parcialmente coberto pelo @rgbeac (art.º 47.º, n.º 6) mas ausente no @codigo e @legislacao.
-Necessidade de portaria complementar com especificações técnicas de alojamento por espécie/categoria.</t>
+          <t>N.º 2, Proibição expressa de manter cães ou gatos em contentores : não coberto, nenhum dos três diplomas contém esta proibição explícita.
+N.º 3 – Exceções ao uso de contentores (transporte, isolamento curto prazo, espetáculos, neonatos com termorregulação reduzida ou acompanhados da mãe) Não coberto
+N.º 4 – Proibição de manter cães &gt;8 semanas exclusivamente no interior; acesso diário ao exterior mínimo 1h total (ou passeio); desvio apenas por parecer veterinário escrito - Parcialmente coberto no n.º 6, art.º 47.º @rgbeac prevê acesso diário a área de exercício exterior 2x/dia durante 30 minutos (= 1h total), mas não contém a proibição explícita de manutenção exclusiva no interior nem o mecanismo de desvio por parecer veterinário escrito. Ausente no @codigo e @legislacao.
+Prever exceções para cães de guarda de rebanho</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
@@ -2379,81 +2325,59 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Arts. 47.º e 52.º (n.º 7) do RGBEAC (proposta, jun. 2025)</t>
+          <t>RGBEAC (proposta, jun. 2025) - Artigos 7 a 12 e 52º</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Artigo 47.º — Condições dos alojamentos
-1 - Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
-a) A prática de exercício físico adequado;
-b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 - Os animais devem dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
-4 - As instalações devem providenciar um enriquecimento ambiental complexo e estimulante de acordo com as necessidades específicas dos animais que albergam, incluindo materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente materiais para substrato, cama ou ninhos, ramos, buracos, locais para banhos, brinquedos e outros adequados ao fim em vista.
-5 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar ameaça ao bem-estar dos animais, designadamente não podem conter objetos ou equipamentos perigosos para os animais.[/dim]
-6 – Os cães devem ter acesso diário a uma área de exercício fora do seu alojamento habitual, pelo menos duas vezes por dia, durante 30 minutos.
-7 – As áreas de exercício referidas no número anterior devem incluir equipamento de enriquecimento ambiental e agilidade, incluindo piscinas, plataformas elevadas e outros adequados ao fim em vista.
-Artigo 52.º — Maneio (excerto)
-7 – Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.</t>
+          <t>Analisado no Art.º 8.º do Reg.
+Especificação clara: 'exercício físico e estímulo mental', 'Contato social adequado'. (Art.º 10.º).
+Métodos de 'reforço positivo' (OBRIGATÓRIO).
+Proibição explícita de 'métodos aversivos, punitivos ou violentos'.
+n.º 7, do art.º 52.º
+Todos os alojamentos para hospedagem de cães e gatos, à exceção dos alojamentos com fins higiénicos, devem dispor de um plano de socialização e enriquecimento ambiental.
+(Documentação obrigatória de estratégia de socialização - criadores).
+Fatores de socialização também previstos no treino dos perigosos e PP.</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Art.º 13.º do Código do Animal (DL 214/2013)</t>
+          <t>Arts. 5.º e 13.º do Código do Animal (DL 214/2013)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Artigo 13.º — Condições dos alojamentos
-1 - Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
-a) A prática de exercício físico adequado;
-b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 - Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 - [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
-4 - [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação, não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
-5 - As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão dos comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
+          <t>Artigo 5.º - Princípios que proíbem violência e maus-tratos, garantem bem-estar.
+Artigo 13.º - Espaço para exercício físico e expressão de comportamentos naturais.
+Analisado no art.º 8.º do Reg.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>art.º 8.º do DL n.º 276/2001, de 17 de outubro</t>
+          <t>Decreto-Lei n.º 276/2001 - Artigo 8.º</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>1 — Os animais devem dispor do espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir:
-a) A prática de exercício físico adequado;
-b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
-2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.
-3 — [dim]As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.[/dim]
-4 — [dim]As estruturas físicas das instalações, todo o equipamento nelas introduzido e a vegetação não podem representar nenhum tipo de ameaça ao bem-estar dos animais, designadamente não podem possuir objetos ou equipamentos perigosos para os animais.[/dim]
-5 — As instalações devem ser equipadas de acordo com as necessidades específicas dos animais que albergam, com materiais e equipamento que estimulem a expressão do repertório de comportamentos naturais, nomeadamente material para substrato, cama ou ninhos, ramos, buracos, locais para banhos e outros quaisquer adequados ao fim em vista.</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (art.º 8.º) prevê genericamente que os animais devem 'dispor de um espaço adequado às suas necessidades fisiológicas e etológicas' e de 'esconderijos', mas sem requisitos de socialização, enriquecimento documentado ou estratégia formal. A Portaria n.º 148/2016 regula o registo de cães em matilhas de caça maior (junto do ICNF, I. P.) mas não fixa normas de bem-estar comportamental para esses cães. O @rgbeac (art.º 10.º, n.º 3) isenta expressamente os cães utilizados na caça durante os atos venatórios da obrigação de trela — o que representa uma derrogação análoga (embora com âmbito e fundamento distintos) à derrogação do n.º 4 do Art.º 17.º do Regulamento para cães militares/policiais/aduaneiros. Não existe, no entanto, na legislação nacional, qualquer equivalente à isenção de socialização para cães de proteção de gado ou de pastoreio em transumância.</t>
-        </is>
-      </c>
+          <t>1 — Os animais devem dispor de um espaço adequado às suas necessidades fisiológicas e etológicas, devendo o mesmo permitir: a) A prática de exercício físico adequado; b) A fuga e refúgio de animais sujeitos a agressão por parte de outros.
+2 — Os animais devem poder dispor de esconderijos para salvaguarda das suas necessidades de proteção, sempre que o desejarem.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (DL 214/2013) não contém especificações sobre socialização, enriquecimento ambiental ou estratégia documentada de socialização por parte dos criadores. O art.º 13.º prevê genericamente 'espaço para exercício físico e expressão de comportamentos naturais', mas sem os requisitos quantitativos ou processuais do Regulamento. Não inclui as derrogações para cães funcionais.</t>
+          <t>Sem especificações sobre socialização e enriquecimento</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 47.º, n.º 4) prevê 'enriquecimento ambiental complexo e estimulante' e o Art.º 47.º, n.º 6 impõe acesso diário a área de exercício, pelo menos 2 vezes por dia durante 30 minutos — obrigação mais específica que o Regulamento. O n.º 7 do Art.º 52.º do @rgbeac impõe 'plano de socialização e enriquecimento ambiental' a todos os alojamentos de hospedagem, mas não especifica 'estratégia documentada de socialização' exclusiva para criadores. Derrogações não contempladas: (1) isenção dos cães de proteção de gado («livestock guardian dogs») dos requisitos de socialização durante períodos de guarda/treino; (2) isenção dos cães de pastoreio durante transumância sazonal; (3) isenção de cães militares/policiais/aduaneiros da proibição de acorrentamento superior a 1 hora.</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>O Regulamento introduz obrigações novas sem equivalente nacional: (1) proibição de acorrentamento superior a 1 hora (com isenção para cães militares, policiais e aduaneiros); (2) obrigação de estratégia documentada de socialização por parte dos criadores; (3) isenção explícita de socialização para cães de proteção de gado ("livestock guardian dogs") durante guarda/treino e para cães de pastoreio em transumância sazonal. Em Portugal, a realidade dos cães de caça (matilhas) é relevante: a Portaria n.º 148/2016 exige registo mas não impõe normas de bem-estar comportamental. O Regulamento não inclui derrogação explícita para cães de caça — estes estão abrangidos pelas obrigações gerais do Art.º 17.º enquanto permanecerem em estabelecimentos de criação ou venda.</t>
-        </is>
-      </c>
+          <t>Cobertura mais significtiva</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Sim — necessidade de: (1) criar regime de proibição de acorrentamento superior a 1 hora com as isenções previstas; (2) impor estratégia documentada de socialização aos criadores; (3) clarificar o estatuto dos cães de caça e matilhas face às obrigações comportamentais.</t>
+          <t>Em análise. RGBEAC alinha melhor; implementação de reforço positivo obrigatório recomendada</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -2554,29 +2478,22 @@
 2 — O documento referido no número anterior deve ter a forma de um atestado, do qual constem a identificação do médico veterinário, o número da cédula profissional e a sua assinatura.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (arts. 17.º e 18.º) exige que as intervenções cirúrgicas (incluindo corte de caudas) sejam realizadas por médico veterinário e que as amputações estejam documentadas por atestado. Não existe proibição expressa de corte de cauda anterior a 2013. O @rgbeac e o @codigo já proíbem o corte de cauda desde 2015 (art.º 52.º, n.º 3 do @codigo), o que excede o regime do Regulamento no que respeita a cães de caça (o Regulamento admite a excepção profilática que poderia ser invocada para justificar o corte de cauda em cães de caça). A derrogação do n.º 5 do Art.º 18.º para cães militares, policiais e aduaneiros não tem equivalente na legislação nacional. A proibição de coleiras de espinhos e de estrangulamento sem paragem de segurança não consta expressamente da legislação nacional vigente (embora o uso de 'aguilhões' e instrumentos perfurantes na condução de animais seja proibido pela Lei n.º 92/95).</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>O @codigo (DL 214/2013) proíbe mutilações com fins não curativos (art.º 52.º, n.º 1), incluindo corte de orelhas, cordas vocais, garras ou unhas, dentes ou presas. O art.º 52.º, n.º 3 proíbe o corte de cauda para todos os cães nascidos a partir de 1 de Janeiro de 2015 — regime mais restritivo que o Regulamento, que admite corte de cauda por razões profiláticas (incluindo potencialmente para cães de caça). O @codigo exige atestado veterinário (n.º 4) alinhado com o n.º 2 do Art.º 18.º. Não cobre explicitamente a proibição de coleiras de espinhos (prong collars) nem de coleiras de estrangulamento sem paragem de segurança prevista no n.º 5, als. (e) e (f) do Regulamento.</t>
-        </is>
-      </c>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (art.º 12.º, al. i)) proíbe intervenções cirúrgicas com objectivo de modificar a aparência, incluindo 'corte da cauda, secção das cordas vocais, remoção de unhas ou dentes, e corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais'. O art.º 34.º do @rgbeac exige atestado veterinário para qualquer intervenção curativa que modifique a aparência, alinhando com o n.º 2 do Art.º 18.º do Regulamento. O @rgbeac também proíbe coleiras elétricas, de choques, estranguladores e açaimos fechados (art.º 12.º, al. aa)), convergindo com o n.º 5 do Art.º 18.º. A derrogação do Art.º 18.º, n.º 3, sobre corte de orelha de gatos em programas TNR está coberta pela ressalva do @rgbeac ('fins de identificação de animais esterilizados conforme boas práticas internacionais').</t>
+          <t>@rgbeac ressalva expressamente o corte das orelhas que não seja realizada para fins de identificação de animais esterilizados conforme boas práticas internacionais", o que cobre o essencial desta derrogação.</t>
         </is>
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>Portugal está em grande medida alinhado com o Regulamento no que respeita à proibição de mutilações: o corte de cauda já é proibido desde 2015 (mais restritivo do que o Regulamento, que admite excepção profilática para cães de caça). Os principais gaps são: (1) ausência de proibição expressa de coleiras de espinhos (prong collars) e de estrangulamento sem paragem de segurança; (2) ausência de derrogação específica para cães militares, policiais e aduaneiros; (3) necessidade de clarificar que a excepção profilática do Art.º 18.º, n.º 1 não se aplica ao corte de cauda de cães de caça em Portugal (o @codigo e @rgbeac são mais restritivos). Exige anestesia e analgesia prolongada como condição obrigatória para qualquer procedimento justificado — requisito que a legislação nacional não especifica explicitamente.</t>
+          <t>exige expressamente anestesia e analgesia prolongada como condição do procedimento.
+Rever proibições na análise do art.7.º</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Sim — necessidade de: (1) proibir expressamente coleiras de espinhos e de estrangulamento sem paragem de segurança; (2) clarificar o âmbito da excepção profilática face ao regime mais restritivo nacional; (3) confirmar conformidade do regime de atestado veterinário com os requisitos documentais do Art.º 18.º, n.º 2.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>
@@ -3018,19 +2935,15 @@
 4 - No caso de anúncios de animais de raça indeterminada é proibida qualquer referência a raças no texto do anúncio.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 276/2001 (Art.º 57.º) permite publicitar animais de companhia na Internet mas proíbe a venda em linha — apenas em local de criação ou estabelecimentos licenciados. O DL n.º 82/2019 (Art.º 53.º) estabelece requisitos para anúncios de transmissão (identificação, raça, informação sanitária) mas sem a especificidade dos requisitos do Regulamento para plataformas digitais.</t>
-        </is>
-      </c>
+      <c r="K18" s="8" t="inlineStr"/>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Art.º 80.º) proíbe a venda pela Internet e exige documentação adequada. Cobre a identificação obrigatória e informações sobre o animal antes da venda. Não inclui os requisitos de informação específica exigidos pelo Regulamento para anúncios em linha (número de registo do operador, informação sobre saúde, socialização e comportamento).</t>
+          <t>Apenas proíbe a venda de animais de companhia sem documentação adequada e restringe a comercialização de animais com comportamentos perigosos. As disposições cobrem identificação obrigatória e informações sobre o animal antes da venda.</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 91.º) proíbe a venda de cães, gatos e furões através da Internet e exige que a transmissão decorra presencialmente em alojamentos autorizados, convergindo com o Regulamento na proibição da venda em linha. No entanto, os requisitos específicos do Regulamento sobre informação obrigatória em anúncios (número de registo, informação de bem-estar, rastreabilidade) vão além do que o @rgbeac prevê explicitamente.</t>
+          <t>SIM - Proibição clara de publicidade e venda online, com requisitos de local licenciado</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
@@ -3257,19 +3170,15 @@
           <t>DL 82/2019 estabelece o SIAC com extensas disposições cobrindo: criação da base de dados, procedimentos de registo e controlos de acesso, gestão por DGAV, identificação eletrónica via transponder, segurança de dados e autorização de acesso, integração de registos de identificação de animais, gestão da distribuição de dispositivos de identificação, procedimentos de registo e atualização. O sistema é operacional desde 2019.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 82/2019 operacionalizou o SIAC como sistema nacional de identificação e registo de animais de companhia (cães, gatos e furões), com registo centralizado sob responsabilidade da DGAV, identificação por microchip e dados sanitários. O SIAC cobre os requisitos fundamentais do Art.º 23.º do Regulamento. Lacuna: ausência de disposição sobre interoperabilidade com bases de dados de outros Estados-Membros da UE.</t>
-        </is>
-      </c>
+      <c r="K20" s="8" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Art.º 53.º) estabelece estrutura completa de identificação e registo com classificações (normal/perigoso/potencialmente perigoso), integra dados de saúde. Alinhado com os requisitos de base de dados do Regulamento. Sem disposições sobre interoperabilidade entre Estados-Membros.</t>
+          <t>Código do Animal estabelece estrutura completa com classificações</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 20.º) reafirma e fortalece o sistema SIAC, alargando o âmbito de dados registados (comportamento, bem-estar, histórico sanitário). Alinhado com os requisitos de base de dados do Regulamento. O @rgbeac não especifica mecanismos de interoperabilidade com bases de dados de outros Estados-Membros, que o Regulamento exige.</t>
+          <t>Reafirma e fortalece o sistema SIAC</t>
         </is>
       </c>
       <c r="N20" s="11" t="inlineStr">
@@ -3327,24 +3236,20 @@
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 82/2019 prevê recolha de dados no SIAC (identificação, saúde, registos) mas não estabelece obrigação de reporte periódico à Comissão Europeia sobre indicadores de bem-estar animal. A legislação vigente não prevê o mecanismo trienal de relatório ao nível nacional nem a consolidação de dados por categorias de operadores.</t>
-        </is>
-      </c>
+      <c r="K21" s="8" t="inlineStr"/>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>O @codigo não prevê mecanismo de recolha de dados sobre bem-estar animal para fins de reporte à Comissão Europeia. Os dados de identificação e registo são recolhidos pelo SIAC mas não consolidados para os indicadores do Regulamento.</t>
+          <t>Análise no Anexo III</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 46.º) prevê relatório anual de gestão dos centros de bem-estar animal, mas não tem equivalente ao mecanismo de recolha de dados e relatório trienal à Comissão Europeia exigido pelo Regulamento. Não há disposição sobre indicadores de bem-estar animal baseados em animais para reporte à UE.</t>
+          <t>Análise no Anexo III</t>
         </is>
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>Necessário: alinhamento da periodicidade de relatórios (atualmente anual para centros de recolha; Regulamento requer trienal à Comissão) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
+          <t>necessário: alinhamento da periodicidade de relatórios (atualmente anual; Regulamento requer trienal) e inclusão dos dados específicos de Annex III da EU (quando publicado).</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -3434,19 +3339,15 @@
 1 - Os animais de companhia abrangidos pela obrigação de identificação devem ser registados pelo médico veterinário no SIAC, imediatamente após a sua marcação com o transponder, em nome do respetivo titular.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>O DL n.º 82/2019 (Art.º 20.º) estabelece que o SIAC é operado em conformidade com a legislação de proteção de dados (Regulamento (UE) 2016/679 — RGPD). A legislação vigente implementa os requisitos do Art.º 25.º do Regulamento. Sem lacunas identificadas.</t>
-        </is>
-      </c>
+      <c r="K22" s="8" t="inlineStr"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Art.º 55.º) prevê cobertura expressa de proteção de dados em conformidade com legislação aplicável. Alinhado com os requisitos do Regulamento.</t>
+          <t>Cobertura expressa em Art. 55.º</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>O @rgbeac (Art.º 20.º, n.º 8) prevê que o tratamento de dados pessoais no âmbito do SIAC observa o regime geral de proteção de dados — implementação completa dos requisitos do Regulamento.</t>
+          <t>Implementação completa em Arts. 20.º</t>
         </is>
       </c>
       <c r="N22" s="11" t="inlineStr">
@@ -3653,27 +3554,23 @@
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em legislação nacional.</t>
+          <t>Sem equivalência.</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em proposta nacional.</t>
+          <t>Sem equivalência.</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Sem equivalência — artigo de habilitação delegada da Comissão Europeia, sem correspondência em proposta nacional.</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr">
-        <is>
-          <t>Artigo de habilitação delegada — confere poderes à Comissão para actualizar os Anexos com base em evidência científica. Implica que os requisitos técnicos dos Anexos (espaço por animal, temperatura, iluminação, etc.) poderão ser actualizados sem necessidade de co-decisão do Parlamento/Conselho. Para Portugal, implica monitorização contínua das actualizações dos Anexos e adaptação da legislação complementar (portarias) sempre que os Anexos forem alterados.</t>
-        </is>
-      </c>
+          <t>Sem equivalência.</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>Sem necessidade de alteração directa — obrigação de acompanhamento e transposição das actualizações dos Anexos.</t>
+          <t>sem equivalência</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
@@ -3804,27 +3701,23 @@
       <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Não se aplica — artigo de procedimento institucional europeu.</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr">
-        <is>
-          <t>Artigo processual sobre procedimento de comité — designa o Comité Permanente dos Vegetais, Animais e dos Alimentos para Consumo Humano e Animal como comité assistente da Comissão para atos de execução do Regulamento. Sem impacto directo na legislação nacional.</t>
-        </is>
-      </c>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr"/>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>Não — artigo processual sobre procedimento de comité europeu.</t>
+          <t>Não - Artigo processual sobre procedimento de comité — assistência à Comissão Europeia.</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr"/>
@@ -3874,27 +3767,23 @@
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Relevante: o DL n.º 276/2001 (Art.º 57.º) permite publicitar animais na Internet mas proíbe a venda online — medida mais restritiva que o Regulamento. Portugal deverá notificar a Comissão desta disposição nacional mais restritiva ao abrigo do n.º 2 do Art.º 30.º do Regulamento.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Relevante: o @codigo (Art.º 80.º) proíbe a venda de animais de companhia pela Internet — medida mais restritiva que o Regulamento. Portugal poderá manter esta proibição ao abrigo do n.º 1.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>Relevante: o @rgbeac (Art.º 12.º, als. m) a r)) proíbe a venda online de cães, gatos e furões — medida mais restritiva que o Regulamento, que apenas exige requisitos de informação para venda em linha. Portugal poderá manter esta proibição ao abrigo do n.º 1.</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr">
-        <is>
-          <t>Portugal detém várias disposições nacionais mais restritivas que o Regulamento — nomeadamente a proibição de venda online de cães, gatos e furões (DL 276/2001, Art.º 57.º; @codigo Art.º 80.º; @rgbeac Art.º 12.º). Estas disposições são compatíveis com o Regulamento ao abrigo do n.º 1. Obrigação de notificação à Comissão Europeia nos termos do n.º 2: Portugal deve comunicar as medidas mais restritivas que pretenda manter no prazo de dois anos após a entrada em vigor do Regulamento.</t>
-        </is>
-      </c>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>Não — mas obrigação de notificação das medidas nacionais mais restritivas à Comissão nos termos do n.º 2.</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr"/>
@@ -4016,27 +3905,23 @@
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>O DL n.º 276/2001 (Arts. 66.º a 72.º) estabelece o regime de contraordenações e coimas para infracções. Portugal já dispõe de regime sancionatório aplicável — necessidade de verificar se as sanções existentes são suficientemente efetivas, proporcionadas e dissuasivas para as infracções ao Regulamento, e de notificar a Comissão.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (Arts. 88.º a 97.º) estabelece o regime de contraordenações e sanções para infracções à legislação de bem-estar animal. O Regulamento não fixa os montantes — remete para os Estados-Membros.</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Artigo de habilitação nacional — o @rgbeac (Arts. 138.º a 160.º) contém o regime sancionatório nacional. O Regulamento não fixa sanções — remete para os Estados-Membros a obrigação de estabelecerem sanções efetivas, proporcionadas e dissuasivas.</t>
-        </is>
-      </c>
-      <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Artigo de habilitação nacional para sanções. Portugal dispõe de regime sancionatório no DL 276/2001 (Arts. 66.º-72.º), @codigo (Arts. 88.º-97.º) e @rgbeac (Arts. 138.º-160.º). Obrigação de: (1) verificar se as sanções existentes cobrem todas as infracções ao Regulamento, em particular o abandono por operadores; (2) garantir proporcionalidade e carácter dissuasivo; (3) notificar a Comissão das regras de sanções e de qualquer alteração ulterior.</t>
-        </is>
-      </c>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr"/>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>Verificar cobertura completa e notificar a Comissão das sanções nacionais aplicáveis.</t>
+          <t>Responsabilidade dos Estados-Membros em estabelecer sanções e notificar a Comissão destas, e de qualquer alteração ulterior das mesmas.</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr"/>

--- a/comparativo_reuniao_exemplo.xlsx
+++ b/comparativo_reuniao_exemplo.xlsx
@@ -1200,14 +1200,88 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>O @codigo (art.º 8.º, n.º 2) exclui da reprodução animais com defeitos genéticos e malformações (monorquidia, displasia, rim poliquístico e alterações comportamentais) e proíbe cios sucessivos, mas não prevê o conceito de traços conformacionais excessivos nem a proibição de consanguinidade.</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
+          <t>Exclui da reprodução animais com defeitos genéticos e malformações, mas especifica monorquidia, displasia, rim poliquístico e alterações comportamentais. 
+Proíbe cios sucessivos
+Não prevê o conceito de conformações extremas nem a proibição de consanguinidade.</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Prevê limites de idade para reprodução (cadelas 18 meses a 6 anos; gatas 12 meses a 6 anos; machos 12 meses a 7 anos), máximo de 4 ninhadas com intervalo mínimo de 12 meses, testes genéticos e de saúde e proibição de reprodução após 2 cesarianas — vários destes requisitos são mais detalhados que o Regulamento. 
+O Art.º 70.º, n.º 7 remete para portaria a definição de coeficiente de consanguinidade e limite de descendentes por macho, sem proibição expressa de cruzamentos entre pais/filhos, irmãos ou avós/netos como o Regulamento.
+O conceito de 'características conformacionais excessivas' não está explícito, embora o n.º 8 proíba genericamente a reprodução quando se espere efeito prejudicial na saúde com base no fenótipo. 
+A proibição de híbridos não consta.</t>
+        </is>
+      </c>
       <c r="N5" s="11" t="inlineStr">
         <is>
-          <t>Introduzir conceito de características conformacionais excessivas (a regular por ato delegado europeu até 2030); (2) proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos); (3) proibir a produção de híbridos; (4) impor consulta veterinária prévia ao acasalamento de animais potencialmente afetados. 
-ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva. Recomenda-se: (i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); (ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); (iii) exigir período de recuperação 1 ano após atingir limite; (iv) proibir uso após 2 cesarianas; (v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.</t>
+          <t>1. Idades mínimas de reprodução
+2. Idades máximas de reprodução
+3. Limites de ninhadas e intervalos
+4. Cesarianas
+5. Consanguinidade e híbridos
+6. Conformação e genótipo
+7. Reprodução assistida
+8. Temperamento e comportamento
+9. Registo e obrigações administrativas
+10. Separação das crias da progenitora
+11. Desmame (processo e critérios)
+12. Socialização das crias
+Regulamento obriga a:
+Introduzir conceito de características conformacionais excessivas/conformações extremas (a regular por ato delegado europeu até 2030); 
+Proibir consanguinidade próxima (pais/filhos, irmãos, avós/netos);
+Proibir a produção de híbridos; 
+Impõe consulta veterinária prévia ao acasalamento de animais potencialmente afetados.
+ANNEX I, Ponto 3 estabelece requisitos técnicos obrigatórios de saúde reprodutiva.
+Recomenda-se: 
+(i) incorporar idade mínima 10 meses (gatas) e 2º estro (cadelas); 
+(ii) estabelecer máximo imperativo de 3 ninhadas em 2 anos (sem exceções veterinárias); 
+(iii) exigir período de recuperação 1 ano após atingir limite;
+(iv) proibir uso após 2 cesarianas; 
+(v) exigir avaliação veterinária escrita para cadelas ≥8 anos e gatas ≥6 anos.
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Cadelas (fêmeas canídeos) | A partir do 2.º estro(Anexo I, n.º 2.2) | Raças pequeno/médio porte: 3.º cioRaças grande porte: 2 anos(Art.º 8.º, n.º 2, al. a) + Anexo I) | 18 meses(Art.º 70.º, n.º 2) | Regulamento impõe-se
+Gatas (fêmeas felídeos) | A partir dos 10 meses(Anexo I, n.º 1.1) | 1 ano(Anexo I) | 12 meses(Art.º 70.º, n.º 3) | 1 ano
+Cães (machos canídeos) | Não fixado(Art.º 8.º não estabelece limite mínimo para machos) | Raças pequeno/médio porte: 1,5 anosRaças grande porte: 2 anos(Anexo I) | 12 meses(Art.º 70.º, n.º 4) | Raças pequeno/médio porte: 1,5 anosRaças grande porte: 2 anosv
+Gatos (machos felídeos) | Não fixado | 1 ano(Anexo I) | 12 meses(Art.º 70.º, n.º 4) | 1 ano
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Cadelas | Exame veterinário escrito obrigatório a partir dos 8 anos (não proibição)(Anexo I, n.º 3.6) | 8 anos; ou 5 anos se for a 1.ª gestação(Anexo I) | 6 anos(Art.º 70.º, n.º 2) | Código, eventualmente com adenda do Regulamentohttps://food.ec.europa.eu/system/files/2020-11/aw_platform_plat-conc_guide_dog-breeding.pdf
+Gatas | Exame veterinário escrito obrigatório a partir dos 6 anos (não proibição)(Anexo I, n.º 3.6) | 12 anos(Anexo I) | 6 anos(Art.º 70.º, n.º 3) | RGBEAC, eventualmente com adenda do Regulamentohttps://food.ec.europa.eu/system/files/2020-11/aw_platform_plat-conc_guide_cat-breeding.pdf
+Cães machos | Não fixado | 12 anos, ou mais se o estatuto sanitário o permitir(Anexo I) | 7 anos(Art.º 70.º, n.º 4) | Debatível. Talvez mais bem definido em Portaria que facilite adaptações.Maior risco de patologias e transmissão de defeitos com o avançar da idade, com queda mais marcada em cães acima de 7–9 anos. Mas esperança média de vida tem aumentado, o risco de patologia reprodutiva aumenta e o risco de abandono potencialmente pode aumentar com propostas mais restritivas
+Gatos machos | Não fixado | 12 anos(Anexo I) | 7 anos(Art.º 70.º, n.º 4) | Ver supra
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+N.º máximo de ninhadas por período | Máx. 3 ninhadas em 2 anos (cadelas e gatas)(Anexo I, n.º 3.3) | Cadelas: 1 ninhada/ano; máx. 4–6 na vidaGatas: 1 ninhada/ano (máx. 3 em 2 anos, com aprovação MV); máx. 8–10 na vida(Anexo I) | Máx. 4 ninhadas na vida reprodutiva(Art.º 70.º, n.ºs 2 e 3) | Definir um número entre 4 e 6. Os documentos supra indicam limites de 4 ninhadas na vida para ambas.
+Intervalo mínimo entre ninhadas | Período de recuperação de, pelo menos, 1 ano após atingir o limite de 3 ninhadas em 2 anos(Anexo I, n.º 4.4) | Cadelas: 1 ciclo reprodutivoGatas: 3–6 meses(Anexo I) | Mínimo de 12 meses entre cada ninhada (cadelas e gatas)(Art.º 70.º, n.ºs 2 e 3) | Rgbeac
+Cios sucessivos (fêmeas) | Não regulado explicitamente | Proibido acasalamento em cios sucessivos(Art.º 8.º, n.º 2, al. a)) | Não regulado explicitamente (intervalo de 12 meses implica proibição) | “É proibido o acasalamento em cios sucessivos, devendo ser assegurando um intervalo mínimo de X meses entre as ninhadas…”
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Após 1.ª cesariana | Não regulado | Não regulado | Exige atestado do MV assistente confirmando ausência de risco(Art.º 70.º, n.º 10) | ?
+Após 2 cesarianas | Proibição de usar para reprodução(Anexo I, Pt. 3, n.º 5.5) | Não regulado explicitamente | Proibição de usar para reprodução(Art.º 70.º, n.º 12) | Proibição conforme Rregulamento
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Cruzamentos consanguíneos (pai/filho, irmãos, avós/netos) | Proibidos, salvo autorização da autoridade competente para preservação de raças locais com reserva genética limitada(Art.º 8.º, n.º 6, al. a)) | Não regulado explicitamente;  Exclui animais com defeitos genéticos e malformações específicas(Art.º 8.º, n.º 2, al. c)) | Sujeitos a portaria (coeficiente de consanguinidade e limites definidos por portaria)(Art.º 70.º, n.º 7) | Regulamento
+Produção de híbridos (cruzamento interespecífico/inter-racial para fins comerciais) | Proibida(Art.º 8.º, n.º 6, al. b)) | Proibida, exceto cruzamentos autorizados para melhoramento de raça ou investigação, ou cruzamentos acidentais sem fins comerciais Acresce exceção para cruzamentos de raças, em particular caninas, que tenham ocorrido acidentalmente e não tenham fins comerciais(Art.º 8.º, n.º 3) | Não regulado explicitamente | Regulamento + ponderar excluir cruzamentos acidentais
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Traços conformacionais excessivos/Conformações extremas | Proibida a reprodução;  Exige consulta prévia a MV; Atos delegados até julho de 2030 definirão critérios(Art.º 8.º, n.ºs 2 e 3, al. b)) | Excluídos da reprodução animais com defeitos genéticos e malformações específicas (ex: displasia da anca, rim poliquístico)(Art.º 8.º, n.º 2, al. c)) | Reprodução condicionada a parecer do MV que ateste ausência de efeito prejudicial com base em genótipo/fenótipo;  Restrição de reprodução de raças específicas por portaria(Art.º 70.º, n.ºs 8 e 9) | Regulamento, com a disposição do rgbeac até haver derrogação?
+Testes genéticos e rastreios de saúde | Atos delegados da Comissão definirão critérios (até julho de 2036 para genótipos)(Art.º 8.º, n.ºs 1 e 3, al. a)) | Excluídos animais com defeitos genéticos específicos (rim poliquístico, displasia, etc.)(Art.º 8.º, n.º 2, al. c)) | Obrigatórios; critérios definidos por portaria específicos para cada raça(Art.º 70.º, n.º 7) | 
+Porte semelhante dos progenitores (prevenção de distócia) | Não regulado explicitamente | Obrigatório(Art.º 8.º, n.º 2, al. b)) | Não regulado explicitamente | Código
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Inseminação artificial (IA) | Não regulado | Não regulado | Restrita a situações excecionais, previstas em portaria(Art.º 70.º, n.º 11) | rgbeac
+Electroejaculação | Não regulado | Não regulado | Proibida(Art.º 70.º, n.º 12) | rgbeac
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Critérios comportamentais para seleção de reprodutores | Não regulado | Excluídos animais com alterações comportamentais(Art.º 8.º, n.º 2, al. c)) | Obrigatório temperamento amistoso e confiante; proibida reprodução de animais perigosos ou com comportamento agressivo ou excessivamente tímido(Art.º 70.º, n.º 6) | Combinaria código e rgbeac
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Registo de reprodutores | Não regulado | Não regulado  | Inscrição obrigatória no SIAC como animal reprodutor(Art.º 70.º, n.º 6) | Rgbeac
+Obrigação de esterilização após fim da vida reprodutiva | Não regulado | Não regulado | Obrigação do detentor de esterilizar o animal e garantir o seu bem-estar até ao final da vida(Art.º 70.º, n.º 13) | Dúvida sobre a aplicabilidade da obrigação, mas a favor do rgbeac
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Cachorros — idade mínima de separação | 8 semanas (estabelecimentos de criação, abrigos e famílias de acolhimento)Derrogação por razões médicas com parecer escrito do MV(Anexo I, n.º 3.3) | Não regulado especificamente. Proibição de exposição em locais de venda até à 8ª semana (n.º 2, art. 23.º; e n.º 2, art. 82.º) | 10.ª semana de idade(com período de desmame gradual)(Art.º 70.º, n.º 5) | RGBEAC Mais restritivo
+Gatinhos — idade mínima de separação | Abrigos e famílias de acolhimento: 8 semanasEstabelecimentos de criação: 12 semanasDerrogação por razões médicas com parecer escrito do MV. O operador conserva o registo até ao último cachorro/gatinho da ninhada ser colocado no mercado(Anexo I, n.º 4.3) | Não regulado especificamente. Proibição de exposição em locais de venda até à 8ª semana (n.º 2, art. 23.º; e n.º 2, art. 82.º) | 12.ª semana de idade(com período de desmame gradual)(Art.º 70.º, n.º 5) | Regulamento = rgbeac
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Processo de desmame — duração e método | Introdução gradual de alimentos sólidos ao longo de um período não inferior a 7 dias(Anexo I, n.º 4.4) | Não regulado especificamente.Prevê programa de alimentação adequado à fase fisiológica — Art.º 8.º, n.º 2, al. a) por referência ao Anexo I) | «Período de desmame gradual» salvaguardado antes da separação(Art.º 70.º, n.º 5 — não especifica duração) | Regulamento + rgbeac
+Idade mínima para conclusão do desmame | Não antes das 6 semanas de idade (tanto para cachorros como para gatinhos)(Anexo I, n.º 4.4) | Não regulado explicitamente | Não regulado explicitamente | Regulamento
+Alimentação de cachorros/gatinhos não desmamados | Colostro nos primeiros 2 dias; depois leite da progenitora ou de cadela/gata lactante; se impossível, sucedâneo de leite específico para cachorros/gatinhos(Anexo I, n.º 2.2) | Não regulado especificamente. Descrito nas condições de alimentação e abeberamento: alimentação deve estar de acordo com fase de evolução fisiológica – idade, sexo, fêmeas prenhes ou em fase de lactação. (Art. 46º, n.º 1) | Não regulado especificamente. | Regulamento
+Monitorização do crescimento de não desmamados | Todos os cachorros/gatinhos não desmamados devem receber leite, sucedâneo ou combinação em quantidade suficiente para ganho de peso constante(Anexo I, n.º 3.3) | Não regulado | Não regulado | Regulamento
+Critério | Regulamento (UE) 2023/0447 | @codigo(proposta DL 214/2013) | @rgbeac(proposta jun. 2025) | Proposta
+Idade de início e tipo de socialização | A partir das 3 semanas de idade: oportunidades diárias e progressivas de contacto social com congéneres, seres humanos e, sempre que possível, outras espécies(Anexo I, n.º 1.1) | Não regulado especificamente na secção de reprodução(o @codigo exige enriquecimento ambiental — Art.º 13.º, n.º 5) | Todos os alojamentos de criação de cães e gatos devem dispor de um plano de socialização e enriquecimento ambiental(Art.º 52.º, n.º 7 do @rgbeac) | Regulamento + rgbeac
+Separação comportamento agressivo | Animais que representem ameaça ou causem stress excessivo devem ser mantidos separados(Anexo I, n.º 1.1) | Não regulado especificamente. As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar.(Art. 13.º, n.º 3) Artigo 83.º - As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda.   | Não regulado especificamente. 3 - As fêmeas em período de incubação, de gestação ou com crias devem ser alojadas de forma a assegurarem a sua função reprodutiva natural em situação de bem-estar (Art.º 47.º, n.º 3) Artigo 76.º- As fêmeas prenhes, bem como as ninhadas em período de aleitamento, não podem ser mantidas nos locais de venda. | Regulamento + qq um</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
